--- a/editais.xlsx
+++ b/editais.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/editais.xlsx
+++ b/editais.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G198"/>
+  <dimension ref="A1:G199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,27 +456,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CNPq</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Chamada Pública CNPq/ERC Nº 21/2026</t>
+          <t>5ª Chamada Pública Conjunta - Finep e Conselho Norueguês de Pesquisa (RCN)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>16/12/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-21-2026/chamada-publica-cnpq-N-21-2026</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/1019381</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -492,22 +492,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Chamada CNPq/CT-Biotec/FNDCT/MCTI Nº 24/2026 - Apoio à Pesquisa, Desenvolvimento e Inovação em Biotecnologia</t>
+          <t>Chamada Pública CNPq/ERC Nº 21/2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-24-2026/chamada-publica-cnpq-N-24-2026</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-21-2026/chamada-publica-cnpq-N-21-2026</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -518,27 +518,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FAPESB</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DIRETRIZES ESPECÍFICAS DA FAPESB – 1ª CHAMADA DA PARCERIA DE MATÉRIAS- PRIMAS PARA A TRANSIÇÃO VERDE E DIGITAL (RAMP) 2026-2027</t>
+          <t>Chamada CNPq/CT-Biotec/FNDCT/MCTI Nº 24/2026 - Apoio à Pesquisa, Desenvolvimento e Inovação em Biotecnologia</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>15/02/2027</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/diretrizes-especificas-da-fapesb-1a-chamada-da-parceria-de-materias-primas-para-a-transicao-verde-e-digital-ramp-2026-2027/</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-24-2026/chamada-publica-cnpq-N-24-2026</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -554,22 +554,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CHAMADA CDTI ESPANHA (2026-2027) – DIRETRIZES ESPECÍFICAS DA FAPESB</t>
+          <t>DIRETRIZES ESPECÍFICAS DA FAPESB – 1ª CHAMADA DA PARCERIA DE MATÉRIAS- PRIMAS PARA A TRANSIÇÃO VERDE E DIGITAL (RAMP) 2026-2027</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>15/02/2027</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/chamada-cdti-espanha-2026-2027-diretrizes-especificas-da-fapesb/</t>
+          <t>https://www.fapesb.ba.gov.br/diretrizes-especificas-da-fapesb-1a-chamada-da-parceria-de-materias-primas-para-a-transicao-verde-e-digital-ramp-2026-2027/</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -585,22 +585,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CHAMADA 2026- PROGRAMA DE AUXILIO PARA DOUTORANDOS COM BOLSA NACIONAL – DAAD</t>
+          <t>CHAMADA CDTI ESPANHA (2026-2027) – DIRETRIZES ESPECÍFICAS DA FAPESB</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/chamada-2026-programa-de-auxilio-para-doutorandos-com-bolsa-nacional-daad/</t>
+          <t>https://www.fapesb.ba.gov.br/chamada-cdti-espanha-2026-2027-diretrizes-especificas-da-fapesb/</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -616,7 +616,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CHAMADA GCUB – MOB Nº 2026/2027 – PROGRAMA DE MOBILIDADE INTERNACIONAL DO GCUB (GCUB-MOB)</t>
+          <t>CHAMADA 2026- PROGRAMA DE AUXILIO PARA DOUTORANDOS COM BOLSA NACIONAL – DAAD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -624,10 +624,14 @@
           <t>13/07/2026</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/chamada-gcub-mob-no-20262027-programa-de-mobilidade-internacional-do-gcub-gcub-mob/</t>
+          <t>https://www.fapesb.ba.gov.br/chamada-2026-programa-de-auxilio-para-doutorandos-com-bolsa-nacional-daad/</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -638,23 +642,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CNPq</t>
+          <t>FAPESB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Chamada CNPq/MCTI nº 25/2026 - Endometriose e Saúde Menstrual</t>
+          <t>CHAMADA GCUB – MOB Nº 2026/2027 – PROGRAMA DE MOBILIDADE INTERNACIONAL DO GCUB (GCUB-MOB)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-25-2026/chamada-publica-cnpq-N-25-2026</t>
+          <t>https://www.fapesb.ba.gov.br/chamada-gcub-mob-no-20262027-programa-de-mobilidade-internacional-do-gcub-gcub-mob/</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -665,23 +669,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FAPESB</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EDITAL DE SELEÇÃO PÚBLICA Nº 017/ 2026 Subvenção Econômica à Pesquisa,Desenvolvimento e Inovação (P,D&amp;I) Soluções de Sistemas Inteligentes para a Administração Estadual – Rodada 2</t>
+          <t>Chamada CNPq/MCTI nº 25/2026 - Endometriose e Saúde Menstrual</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/edital-de-selecao-publica-no-017-2026-subvencao-economica-a-pesquisadesenvolvimento-e-inovacao-pdi-solucoes-de-sistemas-inteligentes-para-a-administracao-estadual-rodada-2/</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-25-2026/chamada-publica-cnpq-N-25-2026</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -697,7 +701,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EDITAL FAPESB No 018/2026 – APOIO À PUBLICAÇÃO CIENTÍFICA, TECNOLÓGICA OU DE POPULARIZAÇÃO DAS CIÊNCIAS</t>
+          <t>EDITAL DE SELEÇÃO PÚBLICA Nº 017/ 2026 Subvenção Econômica à Pesquisa,Desenvolvimento e Inovação (P,D&amp;I) Soluções de Sistemas Inteligentes para a Administração Estadual – Rodada 2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -708,7 +712,7 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/edital-fapesb-no-0182026-apoio-a-publicacao-cientifica-tecnologica-ou-de-popularizacao-das-ciencias/</t>
+          <t>https://www.fapesb.ba.gov.br/edital-de-selecao-publica-no-017-2026-subvencao-economica-a-pesquisadesenvolvimento-e-inovacao-pdi-solucoes-de-sistemas-inteligentes-para-a-administracao-estadual-rodada-2/</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -724,7 +728,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EDITAL FAPESB/SECTI – Nº 010/2026 – UNIVERSAL</t>
+          <t>EDITAL FAPESB No 018/2026 – APOIO À PUBLICAÇÃO CIENTÍFICA, TECNOLÓGICA OU DE POPULARIZAÇÃO DAS CIÊNCIAS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -732,14 +736,10 @@
           <t>03/07/2026</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>03/09/2026</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/edital-fapesbsecti-no-0102026-universal/</t>
+          <t>https://www.fapesb.ba.gov.br/edital-fapesb-no-0182026-apoio-a-publicacao-cientifica-tecnologica-ou-de-popularizacao-das-ciencias/</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -755,7 +755,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EDITAL FAPESB/SECTI/CNPq/CAPES – No 11/2026 – PROFIX-CB</t>
+          <t>EDITAL FAPESB/SECTI – Nº 010/2026 – UNIVERSAL</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/edital-fapesbsecticnpqcapes-no-112026-profix-cb/</t>
+          <t>https://www.fapesb.ba.gov.br/edital-fapesbsecti-no-0102026-universal/</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -786,7 +786,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EDITAL Nº 019/2026 – CIÊNCIA NA MESA 5: BASE DE DADOS E SISTEMAS DE INFORMAÇÕES PARA TOMADA DE DECISÃO EM SOBERANIA ALIMENTAR E NUTRICIONAL</t>
+          <t>EDITAL FAPESB/SECTI/CNPq/CAPES – No 11/2026 – PROFIX-CB</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -794,10 +794,14 @@
           <t>03/07/2026</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/edital-no-0192026-ciencia-na-mesa-5-base-de-dados-e-sistemas-de-informacoes-para-tomada-de-decisao-em-soberania-alimentar-e-nutricional/</t>
+          <t>https://www.fapesb.ba.gov.br/edital-fapesbsecticnpqcapes-no-112026-profix-cb/</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -808,23 +812,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CNPq</t>
+          <t>FAPESB</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Chamamento Público CNPq/FNDCT/MCTI Nº 01/2026 Para Participação no Programa de Apoio à Popularização da Ciência nas Unidades da Federação</t>
+          <t>EDITAL Nº 019/2026 – CIÊNCIA NA MESA 5: BASE DE DADOS E SISTEMAS DE INFORMAÇÕES PARA TOMADA DE DECISÃO EM SOBERANIA ALIMENTAR E NUTRICIONAL</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamamento-no-01-2026/chamamento-publico-01-2026</t>
+          <t>https://www.fapesb.ba.gov.br/edital-no-0192026-ciencia-na-mesa-5-base-de-dados-e-sistemas-de-informacoes-para-tomada-de-decisao-em-soberania-alimentar-e-nutricional/</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -840,22 +844,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Chamada Pública CNPq/MMULHERES Nº 19/2026 - Programa Asas para o Futuro</t>
+          <t>Chamamento Público CNPq/FNDCT/MCTI Nº 01/2026 Para Participação no Programa de Apoio à Popularização da Ciência nas Unidades da Federação</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-19-2026/chamada-publica-cnpq-N-19-2026</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamamento-no-01-2026/chamamento-publico-01-2026</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Chamada Pública MCTI/CNPq/MIR/MMulheres/MPI Nº 20/2026 Atlânticas - Programa Beatriz Nascimento de Mulheres na Ciência</t>
+          <t>Chamada Pública CNPq/MMULHERES Nº 19/2026 - Programa Asas para o Futuro</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -879,10 +879,14 @@
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-20-2026/chamada-publica-cnpq-N-20-2026</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-19-2026/chamada-publica-cnpq-N-19-2026</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -893,12 +897,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BRICs - CHAMADA PÚBLICA Cooperação Multilateral em Inovação</t>
+          <t>Chamada Pública MCTI/CNPq/MIR/MMulheres/MPI Nº 20/2026 Atlânticas - Programa Beatriz Nascimento de Mulheres na Ciência</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -906,14 +910,10 @@
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>14/08/2026</t>
-        </is>
-      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/991625</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-20-2026/chamada-publica-cnpq-N-20-2026</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -924,27 +924,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CNPq</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Chamada Pública CNPq/CAPES/MRE N° 16/2026 - Programa de Estudantes-Convênio de Pós-Graduação (PEC-PG)</t>
+          <t>BRICs - CHAMADA PÚBLICA Cooperação Multilateral em Inovação</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-16-2026/chamada-publica-cnpq-N-16-2026</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/991625</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -955,27 +955,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FIP Conexões Startups – 2026</t>
+          <t>Chamada Pública CNPq/CAPES/MRE N° 16/2026 - Programa de Estudantes-Convênio de Pós-Graduação (PEC-PG)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/986129</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-16-2026/chamada-publica-cnpq-N-16-2026</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -986,27 +986,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CNPq</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Chamada CNPq/MinC nº 17/2026 - Apoio ao funcionamento de incubadoras voltadas à Economia Criativa</t>
+          <t>FIP Conexões Startups – 2026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-17-2026/chamada-publica-cnpq-N-17-2026</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/986129</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1017,27 +1017,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Subvenção Descentralizada Seleção de Parceiros em Fluxo Contínuo - Pró Amazônia Empreende</t>
+          <t>Chamada CNPq/MinC nº 17/2026 - Apoio ao funcionamento de incubadoras voltadas à Economia Criativa</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/972778</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-17-2026/chamada-publica-cnpq-N-17-2026</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1048,27 +1048,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CNPq</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Chamada CNPq/FNDCT nº 06/2026 – UNIVERSAL</t>
+          <t>Subvenção Descentralizada Seleção de Parceiros em Fluxo Contínuo - Pró Amazônia Empreende</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-06-2026/chamada-publica-cnpq-N-06-2026</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/972778</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1079,27 +1079,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DESAFIO TECNOLÓGICO ELETROLISADOR NACIONAL</t>
+          <t>Chamada CNPq/FNDCT nº 06/2026 – UNIVERSAL</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/968467</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-06-2026/chamada-publica-cnpq-N-06-2026</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1115,22 +1115,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CARTA CONVITE MCTI/FINEP - PROGRAMA TECNOVA 2026/2027</t>
+          <t>DESAFIO TECNOLÓGICO ELETROLISADOR NACIONAL</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/958302</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/968467</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1141,23 +1141,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FAPESB</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DIRETRIZES ESPECÍFICAS DA FAPESB – CHAMADA MOBILITY CONFAP ITALY 2026</t>
+          <t>CARTA CONVITE MCTI/FINEP - PROGRAMA TECNOVA 2026/2027</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/diretrizes-especificas-da-fapesb-chamada-mobility-confap-italy-2026/</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/958302</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1173,18 +1177,18 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Edital 009/2026 – Apoio a Organização de Eventos</t>
+          <t>DIRETRIZES ESPECÍFICAS DA FAPESB – CHAMADA MOBILITY CONFAP ITALY 2026</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/edital-0092026-apoio-a-organizacao-de-eventos/</t>
+          <t>https://www.fapesb.ba.gov.br/diretrizes-especificas-da-fapesb-chamada-mobility-confap-italy-2026/</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1195,27 +1199,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>FAPESB</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO UNIDADES DE PESQUISA MCTI – PROINFRA 2026</t>
+          <t>Edital 009/2026 – Apoio a Organização de Eventos</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>07/07/2026</t>
-        </is>
-      </c>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/945796</t>
+          <t>https://www.fapesb.ba.gov.br/edital-0092026-apoio-a-organizacao-de-eventos/</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1226,27 +1226,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CNPq</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Chamada Pública CNPq N° 07/2026 - Programa Institucional de Bolsas de Pós-Graduação (PIBPG)</t>
+          <t>MANUTENÇÃO UNIDADES DE PESQUISA MCTI – PROINFRA 2026</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-07-2026/chamada-publica-cnpq-N-07-2026</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/945796</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1257,27 +1257,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CARTA CONVITE MCTI/FINEP/FNDCT - PROMOÇÃO DA AUTONOMIA TECNOLÓGICA NA ÁREA DA DEFESA</t>
+          <t>Chamada Pública CNPq N° 07/2026 - Programa Institucional de Bolsas de Pós-Graduação (PIBPG)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/943682</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-07-2026/chamada-publica-cnpq-N-07-2026</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1288,33 +1288,33 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Edital nº 10/2026 - Programas CAPES/MATH/STIC/CLIMAT-AMSUD, formato - pdf, 283kb</t>
+          <t>CARTA CONVITE MCTI/FINEP/FNDCT - PROMOÇÃO DA AUTONOMIA TECNOLÓGICA NA ÁREA DA DEFESA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/copy2_of_15042026_Edital_2803264_SEI_2802205_Edital_10_2026.pdf</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/943682</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Alteração Edital nº 10/2026 - Programas CAPES/MATH/STIC/CLIMAT-AMSUD, formato - pdf, 53,1kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/25052026_Edital_2826286_SEI_2825187_Edital_10_2026___alteracao.pdf ; Alteração do Edital  nº 10/2026 - Programas CAPES/MATH/STIC/CLIMAT-AMSUD, formato - pdf, 53,1kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/25052026_Edital_2826286_SEI_2825187_Edital_10_2026___alteracao.pdf</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1324,18 +1324,18 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Edital nº 12/2026 - Programa CAPES/MES-CUBA - Projetos , formato, pdf, 222kb</t>
+          <t>Edital nº 10/2026 - Programas CAPES/MATH/STIC/CLIMAT-AMSUD, formato - pdf, 283kb</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23042026_Edital_2806973_SEI_2806062_Edital_12_2026.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/copy2_of_15042026_Edital_2803264_SEI_2802205_Edital_10_2026.pdf</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lista de inscritos do Edital nº 12/2026 - Programa CAPES/MES-CUBA - Projetos, formato, pdf, 148kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/lista_listagem_2857109_lista_de_inscritos_projetos.pdf/@@display-file/file ; Alteração Edital nº 12/2026 - Programa CAPES/MES-CUBA - Projetos , formato, pdf, 53,1kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/25052026_Edital_2826296_SEI_2825183_Edital_12_2026___ALTERACAO.pdf</t>
+          <t>Alteração Edital nº 10/2026 - Programas CAPES/MATH/STIC/CLIMAT-AMSUD, formato - pdf, 53,1kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/25052026_Edital_2826286_SEI_2825187_Edital_10_2026___alteracao.pdf ; Alteração do Edital  nº 10/2026 - Programas CAPES/MATH/STIC/CLIMAT-AMSUD, formato - pdf, 53,1kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/25052026_Edital_2826286_SEI_2825187_Edital_10_2026___alteracao.pdf</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Edital nº 13/2026 - Programa CAPES/MES-CUBA - Docentes , formato, pdf, 123kb</t>
+          <t>Edital nº 12/2026 - Programa CAPES/MES-CUBA - Projetos , formato, pdf, 222kb</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1366,7 +1366,7 @@
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23042026_Edital_2806981_SEI_2806195_Edital_13_2026.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23042026_Edital_2806973_SEI_2806062_Edital_12_2026.pdf</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1374,71 +1374,71 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Edital nº 13/2026 - Lista de Inscritos, formarto, pdf, 130kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/lista_listagem_2854147_lista_de_inscritos_docentes.pdf/@@display-file/file ; Alteração Edital nº 13/2026 - Programa CAPES/MES-CUBA - Docentes , formato, pdf, 123kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/25052026_Edital_2826299_SEI_2825184_Edital_13_2026___ALTERACAO.pdf</t>
+          <t>Lista de inscritos do Edital nº 12/2026 - Programa CAPES/MES-CUBA - Projetos, formato, pdf, 148kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/lista_listagem_2857109_lista_de_inscritos_projetos.pdf/@@display-file/file ; Alteração Edital nº 12/2026 - Programa CAPES/MES-CUBA - Projetos , formato, pdf, 53,1kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/25052026_Edital_2826296_SEI_2825183_Edital_12_2026___ALTERACAO.pdf</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CNPq</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Chamada Pública CNPq/MCTI nº 15/2026 - Programa de Cooperação Afro-Brasileira em Ciência e Tecnologia - PROAFRICA</t>
+          <t>Edital nº 13/2026 - Programa CAPES/MES-CUBA - Docentes , formato, pdf, 123kb</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-15-2026/chamada-publica-cnpq-N-15-2026</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23042026_Edital_2806981_SEI_2806195_Edital_13_2026.pdf</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Edital nº 13/2026 - Lista de Inscritos, formarto, pdf, 130kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/lista_listagem_2854147_lista_de_inscritos_docentes.pdf/@@display-file/file ; Alteração Edital nº 13/2026 - Programa CAPES/MES-CUBA - Docentes , formato, pdf, 123kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/25052026_Edital_2826299_SEI_2825184_Edital_13_2026___ALTERACAO.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Edital Conjunto nº 4/2026, formato, pdf, 310kb</t>
+          <t>Chamada Pública CNPq/MCTI nº 15/2026 - Programa de Cooperação Afro-Brasileira em Ciência e Tecnologia - PROAFRICA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19052026_Edital_2823166_EDITAL_CONJUNTO_4_2026___CAPES_CFN.pdf</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-15-2026/chamada-publica-cnpq-N-15-2026</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Prorrogação - Edital Conjunto nº 4/2026, formato, pdf, 52,5kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/documentos/edital_2863852_sei_2863595_edital_conjunto_n__4_2026___prorrogacao.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1448,26 +1448,26 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Edital CAPES Nº 18/2026 - Programa Cátedra Maison Du Brésil - pdf, 122kb</t>
+          <t>Edital Conjunto nº 4/2026, formato, pdf, 310kb</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15052026_Edital_2821031_SEI_2819915_Edital_18_2026.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19052026_Edital_2823166_EDITAL_CONJUNTO_4_2026___CAPES_CFN.pdf</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alteração Edital CAPES Nº 18/2026 - Programa Cátedra Maison Du Brésil - pdf, 56,1kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2837190_SEI_2835880_Edital_18__2026___Alteracao.pdf ; Lista de inscritos Edital CAPES Nº 18/2026 - Programa Cátedra Maison Du Brésil - pdf, 116kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/lista_listagem_2853883_lista_de_inscritos.pdf/@@display-file/file</t>
+          <t>Prorrogação - Edital Conjunto nº 4/2026, formato, pdf, 52,5kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/documentos/edital_2863852_sei_2863595_edital_conjunto_n__4_2026___prorrogacao.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -1479,18 +1479,18 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Edital nº 17/2026 - seleção de projetos conjuntos de pesquisa por chamada no âmbito do Programa CAPES - AUGM</t>
+          <t>Edital CAPES Nº 18/2026 - Programa Cátedra Maison Du Brésil - pdf, 122kb</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/copy_of_13052026_Edital_2819298_SEI_2819065_Edital_17_2026.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15052026_Edital_2821031_SEI_2819915_Edital_18_2026.pdf</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Edital nº 17/2026 - Relação das Inscrições Recebidas, formato, pdf, 178kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2865911_lista_de_inscritos.pdf/@@display-file/file ; Edital nº 17/2026 - Prorrogação, formato, pdf, 52,5kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2850525_sei_2848632_edital_n__17_2026.pdf/@@display-file/file</t>
+          <t>Alteração Edital CAPES Nº 18/2026 - Programa Cátedra Maison Du Brésil - pdf, 56,1kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2837190_SEI_2835880_Edital_18__2026___Alteracao.pdf ; Lista de inscritos Edital CAPES Nº 18/2026 - Programa Cátedra Maison Du Brésil - pdf, 116kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/lista_listagem_2853883_lista_de_inscritos.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -1510,80 +1510,84 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Edital nº 26/2025 - Política de Novação para Bolsistas e Ex-Bolsistas no Exterior, formato - pdf, 96kb</t>
+          <t>Edital nº 17/2026 - seleção de projetos conjuntos de pesquisa por chamada no âmbito do Programa CAPES - AUGM</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>22/12/2025</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/22122025_Edital_2740775.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/copy_of_13052026_Edital_2819298_SEI_2819065_Edital_17_2026.pdf</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alteração do edital nº 26/2025 - Política de Novação para Bolsistas e Ex-Bolsistas no Exterior, formato - pdf, 60,5kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11052026_Edital_2817202_SEI_2816655_Edital_n__26_2025___Alteracao.pdf</t>
+          <t>Edital nº 17/2026 - Relação das Inscrições Recebidas, formato, pdf, 178kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2865911_lista_de_inscritos.pdf/@@display-file/file ; Edital nº 17/2026 - Prorrogação, formato, pdf, 52,5kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2850525_sei_2848632_edital_n__17_2026.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FAPESB</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CHAMADA CONFAP/ERC 2026 – CALL RESEARCH OPPORTUNITIES IN EUROPE FOR ACTIVE PHD RESEARCHERS FROM BRAZIL</t>
+          <t>Edital nº 26/2025 - Política de Novação para Bolsistas e Ex-Bolsistas no Exterior, formato - pdf, 96kb</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>10/07/2026</t>
-        </is>
-      </c>
+          <t>22/12/2025</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/chamada-confaperc-2026-call-research-opportunities-in-europe-for-active-phd-researchers-from-brazil/</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/22122025_Edital_2740775.pdf</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alteração do edital nº 26/2025 - Política de Novação para Bolsistas e Ex-Bolsistas no Exterior, formato - pdf, 60,5kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11052026_Edital_2817202_SEI_2816655_Edital_n__26_2025___Alteracao.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>FAPESB</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Edital nº 15/2026 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 134kb</t>
+          <t>CHAMADA CONFAP/ERC 2026 – CALL RESEARCH OPPORTUNITIES IN EUROPE FOR ACTIVE PHD RESEARCHERS FROM BRAZIL</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/30042026_Edital_2811434_SEI_2811079_Edital_15_2026.pdf</t>
+          <t>https://www.fapesb.ba.gov.br/chamada-confaperc-2026-call-research-opportunities-in-europe-for-active-phd-researchers-from-brazil/</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1599,38 +1603,34 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Edital conjunto ProEB e Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edição Moçambique nº 3/2026 - formato, pdf, 128kb</t>
+          <t>Edital nº 15/2026 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 134kb</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/28042026_Edital_2809885_SEI_2804920_Edital_Conjunto_3_2026.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/30042026_Edital_2811434_SEI_2811079_Edital_15_2026.pdf</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>4</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Alteração - Edital Conjunto nº 3/2026 - ProEB e Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul - Edição Moçambique | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2827276_SEI_2826404_Edital_Conjunto_n__3_2026.pdf ; Retificação - Edital Conjunto nº 3/2026 - ProEB e Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul - Edição Moçambique | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2824561_Edital_Conjunto_n__03.2026.pdf ; Alteração - Edital conjunto ProEB e Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edição Moçambique nº 3/2026 - formato, pdf, 64,1kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2858440_sei_2857414_edital_conjunto_n__3_2026___alteracao.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CNPq</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Chamada CNPq/SETEC/MCTI N° 13/2026 - Apoio a Eventos de Promoção do Empreendedorismo e da Inovação no Brasil</t>
+          <t>Edital conjunto ProEB e Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edição Moçambique nº 3/2026 - formato, pdf, 128kb</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1641,34 +1641,38 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-13-2026/chamada-publica-cnpq-N-13-2026</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/28042026_Edital_2809885_SEI_2804920_Edital_Conjunto_3_2026.pdf</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alteração - Edital Conjunto nº 3/2026 - ProEB e Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul - Edição Moçambique | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2827276_SEI_2826404_Edital_Conjunto_n__3_2026.pdf ; Retificação - Edital Conjunto nº 3/2026 - ProEB e Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul - Edição Moçambique | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2824561_Edital_Conjunto_n__03.2026.pdf ; Alteração - Edital conjunto ProEB e Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edição Moçambique nº 3/2026 - formato, pdf, 64,1kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2858440_sei_2857414_edital_conjunto_n__3_2026___alteracao.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Edital nº 11/2026 - Programa Cátedra Jorge Amado, formato, pdf, 196kb</t>
+          <t>Chamada CNPq/SETEC/MCTI N° 13/2026 - Apoio a Eventos de Promoção do Empreendedorismo e da Inovação no Brasil</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23042026_Edital_2806958_SEI_2806040_Edital_11_2026.pdf</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-13-2026/chamada-publica-cnpq-N-13-2026</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1684,28 +1688,24 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Edital nº 5/2026 - Programa CAPES - PURDUE deProjetos conjuntos de pesquisa, formato, pdf, 257kb</t>
+          <t>Edital nº 11/2026 - Programa Cátedra Jorge Amado, formato, pdf, 196kb</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09032026_Edital_2780596_SEI_2779319_Edital_5__de_2026.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23042026_Edital_2806958_SEI_2806040_Edital_11_2026.pdf</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>5</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Lista de inscritos do Edital nº 5/2026 - Programa CAPES - PURDUE de Projetos conjuntos de pesquisa, formato, pdf, 144kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Lista_Listagem_2841625_Lista_de_inscritos.pdf/@@display-file/file ; Alteração do Edital nº 5/2026 - Programa CAPES - PURDUE de Projetos conjuntos de pesquisa, formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15042026_Edital_2803256_SEI_2801466_Edital_5__de_2026.pdf/@@display-file/file ; Edital nº 5/2026 - Programa CAPES - PURDUE de Projetos conjuntos de pesquisa, formato, pdf, 257kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09032026_Edital_2780596_SEI_2779319_Edital_5__de_2026.pdf/@@display-file/file ; Alteração do Edital nº 5/2026 - Programa CAPES - PURDUE deProjetos conjuntos de pesquisa,formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15042026_Edital_2803256_SEI_2801466_Edital_5__de_2026.pdf</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1715,86 +1715,90 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Edital CAPES/DAAD Probral nº 08/2026, formato - pdf, 214kb</t>
+          <t>Edital nº 5/2026 - Programa CAPES - PURDUE deProjetos conjuntos de pesquisa, formato, pdf, 257kb</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/01042026_Edital_2795382_SEI_2794361_Edital_8__de_2026.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09032026_Edital_2780596_SEI_2779319_Edital_5__de_2026.pdf</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lista de Inscritos - Edital nº 08/2026, formato - pdf, 199 kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/lista_listagem_2841542_lista_de_inscritos.pdf/@@display-file/file ; Alteração do Edital CAPES/DAAD Probral nº 08/2026, formato - pdf, 48kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/13042026_Edital_2801456_SEI_2800616_Edital_8_2026.pdf</t>
+          <t>Lista de inscritos do Edital nº 5/2026 - Programa CAPES - PURDUE de Projetos conjuntos de pesquisa, formato, pdf, 144kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Lista_Listagem_2841625_Lista_de_inscritos.pdf/@@display-file/file ; Alteração do Edital nº 5/2026 - Programa CAPES - PURDUE de Projetos conjuntos de pesquisa, formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15042026_Edital_2803256_SEI_2801466_Edital_5__de_2026.pdf/@@display-file/file ; Edital nº 5/2026 - Programa CAPES - PURDUE de Projetos conjuntos de pesquisa, formato, pdf, 257kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09032026_Edital_2780596_SEI_2779319_Edital_5__de_2026.pdf/@@display-file/file ; Alteração do Edital nº 5/2026 - Programa CAPES - PURDUE deProjetos conjuntos de pesquisa,formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15042026_Edital_2803256_SEI_2801466_Edital_5__de_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FIP Startup Inteligência Artificial</t>
+          <t>Edital CAPES/DAAD Probral nº 08/2026, formato - pdf, 214kb</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/756012</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/01042026_Edital_2795382_SEI_2794361_Edital_8__de_2026.pdf</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lista de Inscritos - Edital nº 08/2026, formato - pdf, 199 kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/lista_listagem_2841542_lista_de_inscritos.pdf/@@display-file/file ; Alteração do Edital CAPES/DAAD Probral nº 08/2026, formato - pdf, 48kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/13042026_Edital_2801456_SEI_2800616_Edital_8_2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Edital n° 14/2022 - formato, pdf, 380kb</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
+          <t>FIP Startup Inteligência Artificial</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/08062022_Lista_Listagem_1727316_Humboldt.pdf/@@display-file/file</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/756012</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>11</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Lista de Inscritos no Edital nº 14/2022 do Programa de Bolsas para Pesquisa CAPES/Humboldt - 26° chamada | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Lista_de_inscritos_26_chamada.pdf/@@display-file/file ; Lista de inscritos - Chamada nª 23 do Edital n° 14/2022 - formato, pdf, 396kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/18122024_SEI_CAPES___2508050___Edital_Minuta_ok.pdf/@@display-file/file ; Lista de inscritos - Chamada nº 22 do Edital n° 14/2022 - formato, pdf, 99kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/17062024_Lista_Listagem_2395643_Lista_de_inscritos.pdf/@@display-file/file ; Lista de inscritos - Chamada nº 21 do Edital n° 14/2022 - formato, pdf, 151kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/22122023_Lista_Listagem_2297511_Lista_de_inscritos_21_.pdf/@@display-file/file ; Lista de inscritos - Chamada nª 20 do Edital 14/2022, formato , pdf, 391kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/Lista_Listagem_2001777_Lista_de_inscritos_final_2.pdf/@@display-file/file ; Relação final das inscrições recebidas - Chamada nº 19 do Edital n° 14/2022 - formato, pdf, 380kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/13122022_Lista_Listagem_1874367_Lista_Inscritos_Humboldt__1_.pdf/@@display-file/file ; Relação das inscrições recebidas do Editaln°14/2022 - formato, pdf, 372kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/20092022_Lista_Listagem_1805835_Lista_Final_Humboldt_pdf_para_word_edital_14_22.pdf/@@display-file/file ; Lista de Inscritos - Chamada nº 24 do Edital nº 14/2022 - formato, pdf, 150kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/17062025_Lista_Listagem_2616980_Lista_de_inscritos_24_chamada.pdf ; Lista de Inscritos - Chamada nº 25 do Edital nº 14/2022 - formato, pdf, 241kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/17122025_Lista_Listagem_2735806_SEI___23038.004870_2021_69_25__chamada.pdf ; Alteração do Edital n° 14/2022 - formato, pdf, 49kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/06042026_Edital_2797322_SEI_2796265_Edital_14__de_2022.pdf</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1804,26 +1808,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesPanamá, Angola e México, formato pdf, 151kb</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>09/01/2026</t>
-        </is>
-      </c>
+          <t>Edital n° 14/2022 - formato, pdf, 380kb</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09012026_Edital_2748950_SEI_2748603_Edital_Conjunto_n__1_2026.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/08062022_Lista_Listagem_1727316_Humboldt.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Prorrogação Edital Conjunto nº 1/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México, formato pdf, 65,6kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2855428_sei_2855023_edital_conjunto_n__1_2026___prorrogacao.pdf/@@display-file/file ; Lista de inscritos Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Angola e México, formato pdf, 435kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/01042026_Lista_Listagem_2788855_Lista_de_inscritos_Angola_e_Mexico.pdf/@@display-file/file ; Lista de inscritos Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México, formato pdf, 421kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/12032026_Lista_Listagem_2780399_Lista_de_Inscritos_Panama.pdf/@@display-file/file ; Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México - Retificação do Cumprimento de decisão judicial, formato pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/13022026_Edital_2768872_SEI_2768349_Edital_Conjunto_n__1_2026____Retificacao_de_Decisao_Judicial.pdf/@@display-file/file ; Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México - Cumprimento de decisão judicial, formato pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11022026_Edital_2766993_SEI_2766572_Edital_Conjunto_1_2026_.pdf/@@display-file/file ; Alteração do edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México, formato pdf, 81kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/03022026_Edital_2762271_SEI_2757276_Edital_Conjunto_n__1_2026_CAPES_MIR_____1_.pdf/@@display-file/file ; Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México, formato pdf, 151kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09012026_Edital_2748950_SEI_2748603_Edital_Conjunto_n__1_2026.pdf/@@display-file/file ; Alteração do edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesPanamá, Angola e México, formato pdf, 81kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/03022026_Edital_2762271_SEI_2757276_Edital_Conjunto_n__1_2026_CAPES_MIR_____1_.pdf ; Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesPanamá, Angola e México - Cumprimento de decisão judicial, formato pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11022026_Edital_2766993_SEI_2766572_Edital_Conjunto_1_2026_.pdf ; Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesPanamá, Angola e México - Retificação do Cumprimento de decisão judicial, formato pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/13022026_Edital_2768872_SEI_2768349_Edital_Conjunto_n__1_2026____Retificacao_de_Decisao_Judicial.pdf ; Lista de inscritos Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesPanamá, Angola e México, formato pdf, 421kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/12032026_Lista_Listagem_2780399_Lista_de_Inscritos_Panama.pdf ; Lista de inscritos Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesAngola e México, formato pdf, 435kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/01042026_Lista_Listagem_2788855_Lista_de_inscritos_Angola_e_Mexico.pdf</t>
+          <t>Lista de Inscritos no Edital nº 14/2022 do Programa de Bolsas para Pesquisa CAPES/Humboldt - 26° chamada | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Lista_de_inscritos_26_chamada.pdf/@@display-file/file ; Lista de inscritos - Chamada nª 23 do Edital n° 14/2022 - formato, pdf, 396kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/18122024_SEI_CAPES___2508050___Edital_Minuta_ok.pdf/@@display-file/file ; Lista de inscritos - Chamada nº 22 do Edital n° 14/2022 - formato, pdf, 99kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/17062024_Lista_Listagem_2395643_Lista_de_inscritos.pdf/@@display-file/file ; Lista de inscritos - Chamada nº 21 do Edital n° 14/2022 - formato, pdf, 151kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/22122023_Lista_Listagem_2297511_Lista_de_inscritos_21_.pdf/@@display-file/file ; Lista de inscritos - Chamada nª 20 do Edital 14/2022, formato , pdf, 391kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/Lista_Listagem_2001777_Lista_de_inscritos_final_2.pdf/@@display-file/file ; Relação final das inscrições recebidas - Chamada nº 19 do Edital n° 14/2022 - formato, pdf, 380kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/13122022_Lista_Listagem_1874367_Lista_Inscritos_Humboldt__1_.pdf/@@display-file/file ; Relação das inscrições recebidas do Editaln°14/2022 - formato, pdf, 372kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/20092022_Lista_Listagem_1805835_Lista_Final_Humboldt_pdf_para_word_edital_14_22.pdf/@@display-file/file ; Lista de Inscritos - Chamada nº 24 do Edital nº 14/2022 - formato, pdf, 150kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/17062025_Lista_Listagem_2616980_Lista_de_inscritos_24_chamada.pdf ; Lista de Inscritos - Chamada nº 25 do Edital nº 14/2022 - formato, pdf, 241kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/17122025_Lista_Listagem_2735806_SEI___23038.004870_2021_69_25__chamada.pdf ; Alteração do Edital n° 14/2022 - formato, pdf, 49kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/06042026_Edital_2797322_SEI_2796265_Edital_14__de_2022.pdf</t>
         </is>
       </c>
     </row>
@@ -1835,69 +1835,69 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Edital nº 07/2026 - CAPES/Cofecub, formato, pdf, 545kb</t>
+          <t>Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesPanamá, Angola e México, formato pdf, 151kb</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/30032026_EDITAL72026CAPESCOFECUB.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09012026_Edital_2748950_SEI_2748603_Edital_Conjunto_n__1_2026.pdf</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alteração do Edital nº 07/2026 - CAPES/Cofecub, formato, pdf, 143kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2832325_EDITAL_7_2026___ALTERACAO.pdf ; Lista de inscritos  no Edital n° 7/2026 - Programa CAPES/COFECUB, formato, pdf, 116kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Lista_Listagem_2841501_Lista_de_inscritos.pdf/@@display-file/file</t>
+          <t>Prorrogação Edital Conjunto nº 1/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México, formato pdf, 65,6kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2855428_sei_2855023_edital_conjunto_n__1_2026___prorrogacao.pdf/@@display-file/file ; Lista de inscritos Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Angola e México, formato pdf, 435kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/01042026_Lista_Listagem_2788855_Lista_de_inscritos_Angola_e_Mexico.pdf/@@display-file/file ; Lista de inscritos Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México, formato pdf, 421kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/12032026_Lista_Listagem_2780399_Lista_de_Inscritos_Panama.pdf/@@display-file/file ; Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México - Retificação do Cumprimento de decisão judicial, formato pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/13022026_Edital_2768872_SEI_2768349_Edital_Conjunto_n__1_2026____Retificacao_de_Decisao_Judicial.pdf/@@display-file/file ; Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México - Cumprimento de decisão judicial, formato pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11022026_Edital_2766993_SEI_2766572_Edital_Conjunto_1_2026_.pdf/@@display-file/file ; Alteração do edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México, formato pdf, 81kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/03022026_Edital_2762271_SEI_2757276_Edital_Conjunto_n__1_2026_CAPES_MIR_____1_.pdf/@@display-file/file ; Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México, formato pdf, 151kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09012026_Edital_2748950_SEI_2748603_Edital_Conjunto_n__1_2026.pdf/@@display-file/file ; Alteração do edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesPanamá, Angola e México, formato pdf, 81kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/03022026_Edital_2762271_SEI_2757276_Edital_Conjunto_n__1_2026_CAPES_MIR_____1_.pdf ; Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesPanamá, Angola e México - Cumprimento de decisão judicial, formato pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11022026_Edital_2766993_SEI_2766572_Edital_Conjunto_1_2026_.pdf ; Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesPanamá, Angola e México - Retificação do Cumprimento de decisão judicial, formato pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/13022026_Edital_2768872_SEI_2768349_Edital_Conjunto_n__1_2026____Retificacao_de_Decisao_Judicial.pdf ; Lista de inscritos Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesPanamá, Angola e México, formato pdf, 421kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/12032026_Lista_Listagem_2780399_Lista_de_Inscritos_Panama.pdf ; Lista de inscritos Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesAngola e México, formato pdf, 435kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/01042026_Lista_Listagem_2788855_Lista_de_inscritos_Angola_e_Mexico.pdf</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FAPESB</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DIRETRIZES ESPECÍFICAS DA FAPESB – CHAMADA 2026 CONFAP – BRASILLINOIS</t>
+          <t>Edital nº 07/2026 - CAPES/Cofecub, formato, pdf, 545kb</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/diretrizes-especificas-da-fapesb-chamada-2026-confap-brasillinois/</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/30032026_EDITAL72026CAPESCOFECUB.pdf</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alteração do Edital nº 07/2026 - CAPES/Cofecub, formato, pdf, 143kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2832325_EDITAL_7_2026___ALTERACAO.pdf ; Lista de inscritos  no Edital n° 7/2026 - Programa CAPES/COFECUB, formato, pdf, 116kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Lista_Listagem_2841501_Lista_de_inscritos.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>FAPESB</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Agricultura familiar para ICTs 2026</t>
+          <t>DIRETRIZES ESPECÍFICAS DA FAPESB – CHAMADA 2026 CONFAP – BRASILLINOIS</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/755892</t>
+          <t>https://www.fapesb.ba.gov.br/diretrizes-especificas-da-fapesb-chamada-2026-confap-brasillinois/</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ecossistema Tecnológico de Biorrefino</t>
+          <t>Agricultura familiar para ICTs 2026</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/755795</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/755892</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -1954,23 +1954,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Edital nº 06/2026 Programa Rede de Pesquisa e Desenvolvimento da Amazônia Legal - formato, pdf, 168kb</t>
+          <t>Ecossistema Tecnológico de Biorrefino</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
+          <t>25/03/2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20032026_Edital_2787827_SEI_2787352_Edital_6_2026.pdf</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/755795</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -1981,27 +1985,23 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Prêmio Mulheres Inovadoras – 7ª edição – 2026</t>
+          <t>Edital nº 06/2026 Programa Rede de Pesquisa e Desenvolvimento da Amazônia Legal - formato, pdf, 168kb</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/755727</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20032026_Edital_2787827_SEI_2787352_Edital_6_2026.pdf</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2017,22 +2017,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Finep Mais Inovação Brasil - Rodada 2 – Tecnologias Digitais</t>
+          <t>Prêmio Mulheres Inovadoras – 7ª edição – 2026</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/755485</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/755727</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Finep Mais Inovação Brasil – Rodada 2 – Semicondutores</t>
+          <t>Finep Mais Inovação Brasil - Rodada 2 – Tecnologias Digitais</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/755605</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/755485</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2074,23 +2074,27 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FAPESB</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EDITAL FAPESB N° 05/2026 MOVE 2026 – PARTICIPAÇÃO DE PESQUISADORES EM EVENTOS NO EXTERIOR</t>
+          <t>Finep Mais Inovação Brasil – Rodada 2 – Semicondutores</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>12/03/2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/edital-fapesb-n-052026-move-2026-participacao-de-pesquisadores-em-eventos-no-exterior/</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/755605</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2101,27 +2105,23 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>FAPESB</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Finep Mais Inovação Brasil – Rodada 2 – Mobilidade Sustentável</t>
+          <t>EDITAL FAPESB N° 05/2026 MOVE 2026 – PARTICIPAÇÃO DE PESQUISADORES EM EVENTOS NO EXTERIOR</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/755376</t>
+          <t>https://www.fapesb.ba.gov.br/edital-fapesb-n-052026-move-2026-participacao-de-pesquisadores-em-eventos-no-exterior/</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2132,23 +2132,27 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FAPESB</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Chamada Fundação de Amparo à Pesquisa da Bahia/SECTI/SEMA/FGB nº 01/2026</t>
+          <t>Finep Mais Inovação Brasil – Rodada 2 – Mobilidade Sustentável</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/chamada-fundacao-de-amparo-a-pesquisa-da-bahiasectisemafgb-no-012026/</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/755376</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2164,7 +2168,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EDITAL FAPESB/SECTI/IEL nº 004/2026 – Chamada Estratégica FAPESB/SECTI/IEL</t>
+          <t>Chamada Fundação de Amparo à Pesquisa da Bahia/SECTI/SEMA/FGB nº 01/2026</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2175,7 +2179,7 @@
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/edital-fapesbsectiiel-no-0042026-chamada-estrategica-fapesbsectiiel/</t>
+          <t>https://www.fapesb.ba.gov.br/chamada-fundacao-de-amparo-a-pesquisa-da-bahiasectisemafgb-no-012026/</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2186,64 +2190,60 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>FAPESB</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Edital nº 2/2026 - Pé-de-Meia Licenciaturas - formato, pdf, 81kb</t>
+          <t>EDITAL FAPESB/SECTI/IEL nº 004/2026 – Chamada Estratégica FAPESB/SECTI/IEL</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>16/01/2026</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/16012026_Edital_2753123_SEI_2753038_Edital_2_2026.pdf</t>
+          <t>https://www.fapesb.ba.gov.br/edital-fapesbsectiiel-no-0042026-chamada-estrategica-fapesbsectiiel/</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2</v>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Alteração do edital nº 2/2026 - Pé-de-Meia Licenciaturas - formato, pdf, 55kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19022026_Edital_2769828_SEI_2769557_Edital__2_2026.pdf</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Finep Mais Inovação Brasil – Rodada 2 – Economia Circular e Cidades Sustentáveis</t>
+          <t>Edital nº 2/2026 - Pé-de-Meia Licenciaturas - formato, pdf, 81kb</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>13/02/2026</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
+          <t>16/01/2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/755213</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/16012026_Edital_2753123_SEI_2753038_Edital_2_2026.pdf</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Alteração do edital nº 2/2026 - Pé-de-Meia Licenciaturas - formato, pdf, 55kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19022026_Edital_2769828_SEI_2769557_Edital__2_2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Finep Mais Inovação Brasil - Rodada 2 - Saúde / Empresas</t>
+          <t>Finep Mais Inovação Brasil – Rodada 2 – Economia Circular e Cidades Sustentáveis</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>13/02/2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/754704</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/755213</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Finep Mais Inovação Brasil - Rodada 2 - Subvenção Econômica Regional</t>
+          <t>Finep Mais Inovação Brasil - Rodada 2 - Saúde / Empresas</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/755080</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/754704</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Finep Mais Inovação Brasil – Rodada 2 - Base Industrial de Defesa</t>
+          <t>Finep Mais Inovação Brasil - Rodada 2 - Subvenção Econômica Regional</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/754961</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/755080</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Finep Mais Inovação Brasil – Rodada 2 – Cadeias Agroindustriais Sustentáveis</t>
+          <t>Finep Mais Inovação Brasil – Rodada 2 - Base Industrial de Defesa</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/754839</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/754961</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Finep Mais Inovação Brasil – Rodada 2 – Transformação Mineral</t>
+          <t>Finep Mais Inovação Brasil – Rodada 2 – Cadeias Agroindustriais Sustentáveis</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2387,12 +2387,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/754473</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/754839</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Finep Mais Inovação Brasil – Rodada 2 – Transição Energética</t>
+          <t>Finep Mais Inovação Brasil – Rodada 2 – Transformação Mineral</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/754567</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/754473</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -2434,23 +2434,27 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FAPESB</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DIRETRIZES ESPECÍFICAS DA FAPESB – Chamada para submissão de propostas do programa de Intercâmbio de Pessoal (MSCA SE) em coordenação com o Horizonte Europa</t>
+          <t>Finep Mais Inovação Brasil – Rodada 2 – Transição Energética</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/diretrizes-especificas-da-fapesb-chamada-para-submissao-de-propostas-do-programa-de-intercambio-de-pessoal-msca-se-em-coordenacao-com-o-horizonte-europa-2/</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/754567</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -2466,18 +2470,18 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>EDITAL FAPESB/SECTI nº 003/2026 – Apoio a Pesquisas e Inovações para a Defesa Nacional e a Segurança Pública</t>
+          <t>DIRETRIZES ESPECÍFICAS DA FAPESB – Chamada para submissão de propostas do programa de Intercâmbio de Pessoal (MSCA SE) em coordenação com o Horizonte Europa</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>20/01/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/edital-fapesbsecti-no-0032026-apoio-a-pesquisas-e-inovacoes-para-a-defesa-nacional-e-a-seguranca-publica/</t>
+          <t>https://www.fapesb.ba.gov.br/diretrizes-especificas-da-fapesb-chamada-para-submissao-de-propostas-do-programa-de-intercambio-de-pessoal-msca-se-em-coordenacao-com-o-horizonte-europa-2/</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -2488,23 +2492,23 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>FAPESB</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SELEÇÃO PÚBLICA MCTI/FINEP/FNDCT - Subvenção Econômica à Inovação - DESAFIOS TECNOLÓGICOS PARA AGRICULTURA FAMILIAR</t>
+          <t>EDITAL FAPESB/SECTI nº 003/2026 – Apoio a Pesquisas e Inovações para a Defesa Nacional e a Segurança Pública</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>23/12/2025</t>
+          <t>20/01/2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/754098</t>
+          <t>https://www.fapesb.ba.gov.br/edital-fapesbsecti-no-0032026-apoio-a-pesquisas-e-inovacoes-para-a-defesa-nacional-e-a-seguranca-publica/</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2520,22 +2524,18 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Pesquisa Aplicada Em Centros Temáticos 2025</t>
+          <t>SELEÇÃO PÚBLICA MCTI/FINEP/FNDCT - Subvenção Econômica à Inovação - DESAFIOS TECNOLÓGICOS PARA AGRICULTURA FAMILIAR</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>19/12/2025</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
+          <t>23/12/2025</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/753688</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/754098</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -2551,18 +2551,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PROCESSO DE SELEÇÃO Nº 01/2025 PARA CELEBRAÇÃO DE CONVÊNIO COM ENTIDADE FECHADA DE PREVIDÊNCIA COMPLEMENTAR - EFPC</t>
+          <t>Pesquisa Aplicada Em Centros Temáticos 2025</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/753680</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/753688</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2573,23 +2577,23 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FAPESB</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>EDITAL FAPESB Nº 030/2025 APOIO À PESQUISA CIENTÍFICA, TECNOLÓGICA E/OU DE INOVAÇÃO EM DOENÇAS E AGRAVOS PREVALENTES NA POPULAÇÃO NEGRA, COM ÊNFASE EM DOENÇA FALCIFORME E OS IMPACTOS DO RACISMO ESTRUTURAL NA SAÚDE – EDIÇÃO ANTÔNIA GARCIA</t>
+          <t>PROCESSO DE SELEÇÃO Nº 01/2025 PARA CELEBRAÇÃO DE CONVÊNIO COM ENTIDADE FECHADA DE PREVIDÊNCIA COMPLEMENTAR - EFPC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/edital-fapesb-no-0302025-apoio-a-pesquisa-cientifica-tecnologica-eou-de-inovacao-em-doencas-e-agravos-prevalentes-na-populacao-negra-com-enfase-em-doenca-falciforme-e-os-impactos-do-racismo-estrut/</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/753680</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -2600,23 +2604,23 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>FAPESB</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>FIP Bioeconomia e Sustentabilidade</t>
+          <t>EDITAL FAPESB Nº 030/2025 APOIO À PESQUISA CIENTÍFICA, TECNOLÓGICA E/OU DE INOVAÇÃO EM DOENÇAS E AGRAVOS PREVALENTES NA POPULAÇÃO NEGRA, COM ÊNFASE EM DOENÇA FALCIFORME E OS IMPACTOS DO RACISMO ESTRUTURAL NA SAÚDE – EDIÇÃO ANTÔNIA GARCIA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/752980</t>
+          <t>https://www.fapesb.ba.gov.br/edital-fapesb-no-0302025-apoio-a-pesquisa-cientifica-tecnologica-eou-de-inovacao-em-doencas-e-agravos-prevalentes-na-populacao-negra-com-enfase-em-doenca-falciforme-e-os-impactos-do-racismo-estrut/</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2627,23 +2631,23 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FAPESB</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Edital Nº 024/2025 Programa Nacional de Apoio à Geração de Empreendimentos Inovadores Programa Centelha 3 Bahia</t>
+          <t>FIP Bioeconomia e Sustentabilidade</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>06/11/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/edital-no-0242025-programa-nacional-de-apoio-a-geracao-de-empreendimentos-inovadores-programa-centelha-3-bahia/</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/752980</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -2654,29 +2658,29 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>FAPESB</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Edital Conjunto nº 04/2024 - Programa CAMINHOS AMEFRICANOS: PROGRAMA DE INTERCÂMBIOS SUL-SUL - EDIÇÃO PERU, EDIÇÃO ANGOLA e EDIÇÃO REPÚBLICA DOMINICANA, formato pdf, 146kb</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr"/>
+          <t>Edital Nº 024/2025 Programa Nacional de Apoio à Geração de Empreendimentos Inovadores Programa Centelha 3 Bahia</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>06/11/2025</t>
+        </is>
+      </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23122024_Edital_2517683_SEI_2515663_Edital_Conjunto_4_2024.pdf/@@display-file/file</t>
+          <t>https://www.fapesb.ba.gov.br/edital-no-0242025-programa-nacional-de-apoio-a-geracao-de-empreendimentos-inovadores-programa-centelha-3-bahia/</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>6</v>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>EDITAL CONJUNTO N° 4/2024 - ALTERAÇÃO - CAMINHOS AMEFRICANOS: PROGRAMA DE INTERCÂMBIOS SUL-SUL - EDIÇÕES PERU, ANGOLA E REPÚBLICA DOMINICANA, formato, pdf, 63kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2620581_SEI_2617290_Edital_Conjunto_4_2024.pdf/@@display-file/file ; Retificação do Edital Conjunto nº 04/2024 - Programa CAMINHOS AMEFRICANOS: PROGRAMA DE INTERCÂMBIOS SUL-SUL - EDIÇÃO PERU, EDIÇÃO ANGOLA e EDIÇÃO REPÚBLICA DOMINICANA, formato pdf, 71kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/16012025_Edital_2528145_SEI_2526246_Edital_Conjunto_N__4_2024___RETIFICACAO.pdf ; Lista de Inscritos do Edital Conjunto nº 04/2024 - Peru - Programa Programa CAMINHOS AMEFRICANOS: PROGRAMA DE INTERCÂMBIOS SUL-SUL - EDIÇÃO PERU, EDIÇÃO ANGOLA e EDIÇÃO REPÚBLICA DOMINICANA, formato pdf, 443kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/06032025_Lista_Listagem_2550258_MIR_lista_de_inscritos___alterado.pdf ; Lista de Inscritos do Edital Conjunto nº 04/2024 - Angola, República Dominicana - Programa Programa CAMINHOS AMEFRICANOS: PROGRAMA DE INTERCÂMBIOS SUL-SUL - EDIÇÃO PERU, EDIÇÃO ANGOLA e EDIÇÃO REPÚBLICA DOMINICANA, formato pdf, 264kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/17032025_Lista_Listagem_2557320_Lista_de_Inscritos_Angola_e_Rep_Dominicana.pdf ; Alteração do Edital Conjunto nº 04/2024 - Programa CAMINHOS AMEFRICANOS: PROGRAMA DE INTERCÂMBIOS SUL-SUL - EDIÇÃO PERU, EDIÇÃO ANGOLA e EDIÇÃO REPÚBLICA DOMINICANA, formato pdf, 63kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/14082025_EditalConjunto42024_Alterao.pdf</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2686,26 +2690,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Edital Nº 07/2025 - CAPES/Brafitec, formato, pdf, 207kb</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>03/04/2025</t>
-        </is>
-      </c>
+          <t>Edital Conjunto nº 04/2024 - Programa CAMINHOS AMEFRICANOS: PROGRAMA DE INTERCÂMBIOS SUL-SUL - EDIÇÃO PERU, EDIÇÃO ANGOLA e EDIÇÃO REPÚBLICA DOMINICANA, formato pdf, 146kb</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/03042025_Edital_2574246_SEI_2572796_Edital_n__7_2025.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23122024_Edital_2517683_SEI_2515663_Edital_Conjunto_4_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alteração do Edital Nº 07/2025 - CAPES/Brafitec, formato, pdf, 65kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/25062025_Edital_2623304_SEI_2622327_Edital_n__7_2025___Alteracao.pdf ; Lista de Inscrições Recebidas no Programa CAPES-BRAFITEC - Edital nº 07/2025, formato, pdf, 173kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/23072025_Lista_Listagem_2636522_lista_de_inscritos___Brafitec.pdf ; Retificação da lista de Inscrições Recebidas no Programa CAPES-BRAFITEC - Edital nº 07/2025, formato, pdf, 201kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/04082025_Listagem_2643912_Lista_de_Inscritos.pdf</t>
+          <t>EDITAL CONJUNTO N° 4/2024 - ALTERAÇÃO - CAMINHOS AMEFRICANOS: PROGRAMA DE INTERCÂMBIOS SUL-SUL - EDIÇÕES PERU, ANGOLA E REPÚBLICA DOMINICANA, formato, pdf, 63kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2620581_SEI_2617290_Edital_Conjunto_4_2024.pdf/@@display-file/file ; Retificação do Edital Conjunto nº 04/2024 - Programa CAMINHOS AMEFRICANOS: PROGRAMA DE INTERCÂMBIOS SUL-SUL - EDIÇÃO PERU, EDIÇÃO ANGOLA e EDIÇÃO REPÚBLICA DOMINICANA, formato pdf, 71kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/16012025_Edital_2528145_SEI_2526246_Edital_Conjunto_N__4_2024___RETIFICACAO.pdf ; Lista de Inscritos do Edital Conjunto nº 04/2024 - Peru - Programa Programa CAMINHOS AMEFRICANOS: PROGRAMA DE INTERCÂMBIOS SUL-SUL - EDIÇÃO PERU, EDIÇÃO ANGOLA e EDIÇÃO REPÚBLICA DOMINICANA, formato pdf, 443kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/06032025_Lista_Listagem_2550258_MIR_lista_de_inscritos___alterado.pdf ; Lista de Inscritos do Edital Conjunto nº 04/2024 - Angola, República Dominicana - Programa Programa CAMINHOS AMEFRICANOS: PROGRAMA DE INTERCÂMBIOS SUL-SUL - EDIÇÃO PERU, EDIÇÃO ANGOLA e EDIÇÃO REPÚBLICA DOMINICANA, formato pdf, 264kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/17032025_Lista_Listagem_2557320_Lista_de_Inscritos_Angola_e_Rep_Dominicana.pdf ; Alteração do Edital Conjunto nº 04/2024 - Programa CAMINHOS AMEFRICANOS: PROGRAMA DE INTERCÂMBIOS SUL-SUL - EDIÇÃO PERU, EDIÇÃO ANGOLA e EDIÇÃO REPÚBLICA DOMINICANA, formato pdf, 63kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/14082025_EditalConjunto42024_Alterao.pdf</t>
         </is>
       </c>
     </row>
@@ -2717,26 +2717,26 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Edital nº 09/2025 - CAPES/Cofecub, formato, pdf, 207kb</t>
+          <t>Edital Nº 07/2025 - CAPES/Brafitec, formato, pdf, 207kb</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>09/04/2025</t>
+          <t>03/04/2025</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09042025_Edital_2578055_SEI_2577896_Edital_n__9_2025.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/03042025_Edital_2574246_SEI_2572796_Edital_n__7_2025.pdf</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Relação das inscrições Recebidas do edital nº 09/2025, formato, pdf, 304kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/25062025_Lista_Listagem_2617939_Lista_de_inscritos_25.pdf</t>
+          <t>Alteração do Edital Nº 07/2025 - CAPES/Brafitec, formato, pdf, 65kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/25062025_Edital_2623304_SEI_2622327_Edital_n__7_2025___Alteracao.pdf ; Lista de Inscrições Recebidas no Programa CAPES-BRAFITEC - Edital nº 07/2025, formato, pdf, 173kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/23072025_Lista_Listagem_2636522_lista_de_inscritos___Brafitec.pdf ; Retificação da lista de Inscrições Recebidas no Programa CAPES-BRAFITEC - Edital nº 07/2025, formato, pdf, 201kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/04082025_Listagem_2643912_Lista_de_Inscritos.pdf</t>
         </is>
       </c>
     </row>
@@ -2748,82 +2748,82 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Edital nº 15/2024 - Política de Novação para Bolsistas e Ex-Bolsistas no Exterior, formato - pdf, 133kb</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr"/>
+          <t>Edital nº 09/2025 - CAPES/Cofecub, formato, pdf, 207kb</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>09/04/2025</t>
+        </is>
+      </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/28062024_Edital_2407822_SEI_2407228_Edital_15_2024.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09042025_Edital_2578055_SEI_2577896_Edital_n__9_2025.pdf</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Prorrogação do Edital nº 15/2024 - Política de Novação para Bolsistas e Ex-Bolsistas no Exterior, formato - pdf, 60kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29102024_Edital_2486324_SEI_2485381_Edital_15_2024.pdf/@@display-file/file ; Alteração do Edital nº 15/2024 - Política de Novação para Bolsistas e Ex-Bolsistas no Exterior, formato - pdf, 61kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/06062025_Publicacao_no_DOU_2612769_SEI_2611767_Edital_15_2024.pdf</t>
+          <t>Relação das inscrições Recebidas do edital nº 09/2025, formato, pdf, 304kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/25062025_Lista_Listagem_2617939_Lista_de_inscritos_25.pdf</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>FIP Transição Energética e Descarbonização</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>04/06/2025</t>
-        </is>
-      </c>
+          <t>Edital nº 15/2024 - Política de Novação para Bolsistas e Ex-Bolsistas no Exterior, formato - pdf, 133kb</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/752871</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/28062024_Edital_2407822_SEI_2407228_Edital_15_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1</v>
-      </c>
-      <c r="G80" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Prorrogação do Edital nº 15/2024 - Política de Novação para Bolsistas e Ex-Bolsistas no Exterior, formato - pdf, 60kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29102024_Edital_2486324_SEI_2485381_Edital_15_2024.pdf/@@display-file/file ; Alteração do Edital nº 15/2024 - Política de Novação para Bolsistas e Ex-Bolsistas no Exterior, formato - pdf, 61kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/06062025_Publicacao_no_DOU_2612769_SEI_2611767_Edital_15_2024.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Edital nº 05/2025 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 21kb</t>
+          <t>FIP Transição Energética e Descarbonização</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/14032025_Edital_2561854_SEI_2560981_Edital_5.pdf</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/752871</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>5</v>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Edital nº 05/2025 - ProgramaCAPES/CLIMAT-AMSUD, formato - pdf, 21kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/14032025_Edital_2561854_SEI_2560981_Edital_5.pdf ; Edital nº 05/2025 - Programa CAPES/STIC-AMSUD, formato - pdf, 21kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/14032025_Edital_2561854_SEI_2560981_Edital_5.pdf ; Lista de inscritos do Edital nº 05/2025 - Programa CAPES/MATH-AMSUD, formato - pdf, 62kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/02062025_Lista_Listagem_2602780_amsud_2025.pdf ; Lista de inscritos do Edital nº 05/2025 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 62kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/02062025_Lista_Listagem_2602780_amsud_2025.pdf</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2833,45 +2833,49 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Edital nº 10/2025 - Política de Novação para Bolsistas e Ex-Bolsistas no Exterior, formato - pdf, 102kb</t>
+          <t>Edital nº 05/2025 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 21kb</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>30/04/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/30042025_Edital_2589477_SEI_2588226_Edital_n__10_2025.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/14032025_Edital_2561854_SEI_2560981_Edital_5.pdf</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1</v>
-      </c>
-      <c r="G82" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Edital nº 05/2025 - ProgramaCAPES/CLIMAT-AMSUD, formato - pdf, 21kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/14032025_Edital_2561854_SEI_2560981_Edital_5.pdf ; Edital nº 05/2025 - Programa CAPES/STIC-AMSUD, formato - pdf, 21kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/14032025_Edital_2561854_SEI_2560981_Edital_5.pdf ; Lista de inscritos do Edital nº 05/2025 - Programa CAPES/MATH-AMSUD, formato - pdf, 62kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/02062025_Lista_Listagem_2602780_amsud_2025.pdf ; Lista de inscritos do Edital nº 05/2025 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 62kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/02062025_Lista_Listagem_2602780_amsud_2025.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Seleção de Gestor para o FIP Complexo da Saúde</t>
+          <t>Edital nº 10/2025 - Política de Novação para Bolsistas e Ex-Bolsistas no Exterior, formato - pdf, 102kb</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>07/04/2025</t>
+          <t>30/04/2025</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/752474</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/30042025_Edital_2589477_SEI_2588226_Edital_n__10_2025.pdf</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -2882,33 +2886,29 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Edital nº 1/2025 - Pé-de-Meia Licenciaturas - formato, pdf, 76kb</t>
+          <t>Seleção de Gestor para o FIP Complexo da Saúde</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>17/01/2025</t>
+          <t>07/04/2025</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/17012025_Edital_2529011_SEI_2528468_Edital_n__1_2025.pdf</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/752474</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>4</v>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Alteração do edital nº 1/2025 - Pé-de-Meia Licenciaturas - formato, pdf, 76kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07022025_Edital_2541491_SEI_2540577_Edital_1_2025.pdf ; Tornar sem efeito a alteração do edital nº 1/2025 - Pé-de-Meia Licenciaturas - formato, pdf, 142kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/17022025_Publicacao_no_DOU_2546770_EDITAL_1_2025__TORNAR_SEM_EFEITO_ALTERACAO.pdf ; Alteração do edital nº 1/2025 - Pé-de-Meia Licenciaturas - Segunda chamada - formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/04042025_Edital_2574981_SEI_2574897_Edital_1_2025.pdf</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2918,22 +2918,26 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Edital Nº 10/2023 - CAPES/Brafitec, formato, pdf, 429kb</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr"/>
+          <t>Edital nº 1/2025 - Pé-de-Meia Licenciaturas - formato, pdf, 76kb</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>17/01/2025</t>
+        </is>
+      </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/13042023_Edital_1953404_Edital_10.2023.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/17012025_Edital_2529011_SEI_2528468_Edital_n__1_2025.pdf</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lista de inscritosEdital Nº 10/2023 - CAPES/Brafitec, formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/18092023_Lista_Listagem_2234997_Lista_de_inscritos_2023.pdf/@@display-file/file ; Alteração do Edital n° 10/2023 - Brafitec, formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/27032025_Edital_2570257_SEI_2569933_Edital_N__10_2023___ALTERACAO.pdf</t>
+          <t>Alteração do edital nº 1/2025 - Pé-de-Meia Licenciaturas - formato, pdf, 76kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07022025_Edital_2541491_SEI_2540577_Edital_1_2025.pdf ; Tornar sem efeito a alteração do edital nº 1/2025 - Pé-de-Meia Licenciaturas - formato, pdf, 142kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/17022025_Publicacao_no_DOU_2546770_EDITAL_1_2025__TORNAR_SEM_EFEITO_ALTERACAO.pdf ; Alteração do edital nº 1/2025 - Pé-de-Meia Licenciaturas - Segunda chamada - formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/04042025_Edital_2574981_SEI_2574897_Edital_1_2025.pdf</t>
         </is>
       </c>
     </row>
@@ -2945,14 +2949,14 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Edital nº 11/2024 - CAPES/Brafitec, formato, pdf, 583kb</t>
+          <t>Edital Nº 10/2023 - CAPES/Brafitec, formato, pdf, 429kb</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15042024_EDITAL112024PROGRAMABRAFITEC.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/13042023_Edital_1953404_Edital_10.2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -2960,7 +2964,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lista de Inscrições Recebidas no Programa CAPES-BRAFITEC - Edital nº 11/2024, formato, pdf, 44kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/24092024_Lista_Listagem_2459366_Lista_de_Inscritos.pdf/@@display-file/file ; Alteração do Edital nº 11/2024 - CAPES/Brafitec, formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/27032025_Edital_2570314_SEI_2569939_Edital__N__11_2024___ALTERACAO.pdf</t>
+          <t>Lista de inscritosEdital Nº 10/2023 - CAPES/Brafitec, formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/18092023_Lista_Listagem_2234997_Lista_de_inscritos_2023.pdf/@@display-file/file ; Alteração do Edital n° 10/2023 - Brafitec, formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/27032025_Edital_2570257_SEI_2569933_Edital_N__10_2023___ALTERACAO.pdf</t>
         </is>
       </c>
     </row>
@@ -2972,14 +2976,14 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Edital nº 16/2024 - Programa CAPES/AUGM, formato - pdf, 235kb</t>
+          <t>Edital nº 11/2024 - CAPES/Brafitec, formato, pdf, 583kb</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/08072024_Edital_2413631_SEI_2413500_Edital_16_2024.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15042024_EDITAL112024PROGRAMABRAFITEC.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -2987,36 +2991,36 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lista de inscritos do Edital nº 16/2024, formato, pdf, 174kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/30092024_Lista_Listagem_2456928_Lista_de_inscritos.pdf/@@display-file/file ; Alteração do Edital nº 16/2024 - Programa CAPES/AUGM, formato - pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/24032025_Edital_2567485_SEI_2566349_Edital_n__16_2024___Alteracao_IV.pdf</t>
+          <t>Lista de Inscrições Recebidas no Programa CAPES-BRAFITEC - Edital nº 11/2024, formato, pdf, 44kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/24092024_Lista_Listagem_2459366_Lista_de_Inscritos.pdf/@@display-file/file ; Alteração do Edital nº 11/2024 - CAPES/Brafitec, formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/27032025_Edital_2570314_SEI_2569939_Edital__N__11_2024___ALTERACAO.pdf</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Conhecimento Brasil</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>07/08/2024</t>
-        </is>
-      </c>
+          <t>Edital nº 16/2024 - Programa CAPES/AUGM, formato - pdf, 235kb</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/749717</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/08072024_Edital_2413631_SEI_2413500_Edital_16_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>1</v>
-      </c>
-      <c r="G88" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Lista de inscritos do Edital nº 16/2024, formato, pdf, 174kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/30092024_Lista_Listagem_2456928_Lista_de_inscritos.pdf/@@display-file/file ; Alteração do Edital nº 16/2024 - Programa CAPES/AUGM, formato - pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/24032025_Edital_2567485_SEI_2566349_Edital_n__16_2024___Alteracao_IV.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3026,18 +3030,18 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Edital FIP Nordeste Capital Semente</t>
+          <t>Conhecimento Brasil</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>10/07/2024</t>
+          <t>07/08/2024</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/749273</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/749717</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -3053,18 +3057,18 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SOLUÇÕES TECNOLÓGICAS PARA AUMENTO DA PRODUTIVIDADE NA AGRICULTURA FAMILIAR, AQUICULTURA E PESCA ARTESANAL</t>
+          <t>Edital FIP Nordeste Capital Semente</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>08/07/2024</t>
+          <t>10/07/2024</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/748141</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/749273</t>
         </is>
       </c>
       <c r="F90" t="n">
@@ -3080,18 +3084,18 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Chamada pública conjunta Finep e Rede Eureka 2024</t>
+          <t>SOLUÇÕES TECNOLÓGICAS PARA AUMENTO DA PRODUTIVIDADE NA AGRICULTURA FAMILIAR, AQUICULTURA E PESCA ARTESANAL</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>31/01/2024</t>
+          <t>08/07/2024</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/747009</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/748141</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -3107,18 +3111,18 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Programa de Investimento em Startups Inovadoras 2ª Rodada</t>
+          <t>Chamada pública conjunta Finep e Rede Eureka 2024</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>21/11/2017</t>
+          <t>31/01/2024</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/721708</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/747009</t>
         </is>
       </c>
       <c r="F92" t="n">
@@ -3134,18 +3138,18 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>COOPERAÇÃO ICT-EMPRESA – 01/2017</t>
+          <t>Programa de Investimento em Startups Inovadoras 2ª Rodada</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>08/05/2017</t>
+          <t>21/11/2017</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/721088</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/721708</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -3161,18 +3165,18 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Finep / CDTI - COOPERAÇÃO ICT-EMPRESA – 01/2017</t>
+          <t>COOPERAÇÃO ICT-EMPRESA – 01/2017</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>07/05/2017</t>
+          <t>08/05/2017</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/721094</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/721088</t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -3188,18 +3192,18 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Chamada Pública Bilateral Finep-CDTI</t>
+          <t>Finep / CDTI - COOPERAÇÃO ICT-EMPRESA – 01/2017</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>13/10/2015</t>
+          <t>07/05/2017</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/719676</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/721094</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -3210,19 +3214,23 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Alteração do Edital CAPES/DAAD Probral nº 14/2019 - pdf, 60kb</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr"/>
+          <t>Chamada Pública Bilateral Finep-CDTI</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>13/10/2015</t>
+        </is>
+      </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/24052024_Edital_2384178_SEI_2382892_Edital_14_2019___Alteracao_II.pdf/@@display-file/file</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/719676</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -3238,14 +3246,14 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Alteração do Edital Nº 12/2019 - CAPES/COFECUB - formato, pdf, 68kb</t>
+          <t>Alteração do Edital CAPES/DAAD Probral nº 14/2019 - pdf, 60kb</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400250_SEI_2399447_Edital_12_2019___ALTERACAO_III.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/24052024_Edital_2384178_SEI_2382892_Edital_14_2019___Alteracao_II.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -3261,14 +3269,14 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Alteração do edital nº 19/2022 -ProgramaCAPES/MATH-AMSUD, formato - pdf, 60kb</t>
+          <t>Alteração do Edital Nº 12/2019 - CAPES/COFECUB - formato, pdf, 68kb</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400204_SEI_2399434_Edital_19_2022___ALTERACAO_II.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400250_SEI_2399447_Edital_12_2019___ALTERACAO_III.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -3284,14 +3292,14 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Alteração do Edital nº 36/2017 - formato, pdf, 246kb</t>
+          <t>Alteração do edital nº 19/2022 -ProgramaCAPES/MATH-AMSUD, formato - pdf, 60kb</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/EDITAL362017_HUMBOLDT_Alterao.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400204_SEI_2399434_Edital_19_2022___ALTERACAO_II.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -3307,14 +3315,14 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Alteração Edital nº 11 - Programa Cátedra Jorge Amado, formato, pdf, 53,3kb</t>
+          <t>Alteração do Edital nº 36/2017 - formato, pdf, 246kb</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2845089_sei_2843522_edital_n__11_2026.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/EDITAL362017_HUMBOLDT_Alterao.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -3330,14 +3338,14 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Alteração Edital nº 16/2026 - Programa AURORA, formato, pdf, 982kb</t>
+          <t>Alteração Edital nº 11 - Programa Cátedra Jorge Amado, formato, pdf, 53,3kb</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2853575_edital.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2845089_sei_2843522_edital_n__11_2026.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -3353,14 +3361,14 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Chamada Pública para Envio de Proposta de Curso Novo - Edital nº 20/2026</t>
+          <t>Alteração Edital nº 16/2026 - Programa AURORA, formato, pdf, 982kb</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2844920.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2853575_edital.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -3376,24 +3384,20 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Edital CAPES/DAAD Probral nº 06/2021, formato, pdf, 254kb</t>
+          <t>Chamada Pública para Envio de Proposta de Curso Novo - Edital nº 20/2026</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/EDITAL6PROBRAL.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2844920.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>Alteração do Edital CAPES/DAAD Probral nº 06/2021, formato, pdf, 67kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400395_SEI_2398543_Edital_6_2021__1_.pdf/@@display-file/file ; Lista de inscritos do Edital CAPES/DAAD Probral nº 06/2021, formato, pdf, 47kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/18062021_Edital_6_2021_PROBRAL.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3403,22 +3407,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Edital CAPES/DAAD Probral nº 09/2023, formato - pdf, 472kb</t>
+          <t>Edital CAPES/DAAD Probral nº 06/2021, formato, pdf, 254kb</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/10042023_Edital_1950397_SEI_CAPES___1950165___Edital_9_2023.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/EDITAL6PROBRAL.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alteração do Edital CAPES/DAAD Probral nº 09/2023, formato - pdf, 60kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400189_SEI_2398591_Edital_21_2022.pdf/@@display-file/file ; Relação das inscrições do Edital CAPES/DAAD Probral nº 09/2023, formato, pdf, 412kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/19072023_Lista_Listagem_2018436_Probral_23.pdf/@@display-file/file ; Alteração do EditalCAPES/DAAD Probalnº9/2023, formato, pdf, 113kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/20062023_Edital_2001190_EDITAL_9_2023_SITE.pdf/@@display-file/file</t>
+          <t>Alteração do Edital CAPES/DAAD Probral nº 06/2021, formato, pdf, 67kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400395_SEI_2398543_Edital_6_2021__1_.pdf/@@display-file/file ; Lista de inscritos do Edital CAPES/DAAD Probral nº 06/2021, formato, pdf, 47kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/18062021_Edital_6_2021_PROBRAL.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3430,22 +3434,22 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Edital CAPES/DAAD Probral nº 09/2024, formato - pdf, 630kb</t>
+          <t>Edital CAPES/DAAD Probral nº 09/2023, formato - pdf, 472kb</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/04042024_EDITAL9CAPESDAADPROBRAL.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/10042023_Edital_1950397_SEI_CAPES___1950165___Edital_9_2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lista de inscritos do Edital CAPES/DAAD Probral nº 09/2024, formato - pdf, 334kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/21062024_Lista_Listagem_2398276_probral.pdf/@@display-file/file ; Alteração do Edital CAPES/DAAD Probral nº 09/2024, formato - pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/03062024_Edital_2388049_SEI_2386684_Edital_9_2024.pdf/@@display-file/file</t>
+          <t>Alteração do Edital CAPES/DAAD Probral nº 09/2023, formato - pdf, 60kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400189_SEI_2398591_Edital_21_2022.pdf/@@display-file/file ; Relação das inscrições do Edital CAPES/DAAD Probral nº 09/2023, formato, pdf, 412kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/19072023_Lista_Listagem_2018436_Probral_23.pdf/@@display-file/file ; Alteração do EditalCAPES/DAAD Probalnº9/2023, formato, pdf, 113kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/20062023_Edital_2001190_EDITAL_9_2023_SITE.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3457,14 +3461,14 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Edital CAPES/DAAD Probral nº 21/2022, formato, pdf, 376kb</t>
+          <t>Edital CAPES/DAAD Probral nº 09/2024, formato - pdf, 630kb</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/18042022_Edital_1681234_Edital_21.22.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/04042024_EDITAL9CAPESDAADPROBRAL.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -3472,7 +3476,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alteração do Edital CAPES/DAAD Probral nº 21/2022, formato, pdf, 101kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400189_SEI_2398591_Edital_21_2022.pdf/@@display-file/file ; Relação das inscrições do Edital CAPES/DAAD Probral nº21/2022, formato, pdf, 78kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/13072022_Lista_Listagem_1748985_Probral.pdf/@@display-file/file</t>
+          <t>Lista de inscritos do Edital CAPES/DAAD Probral nº 09/2024, formato - pdf, 334kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/21062024_Lista_Listagem_2398276_probral.pdf/@@display-file/file ; Alteração do Edital CAPES/DAAD Probral nº 09/2024, formato - pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/03062024_Edital_2388049_SEI_2386684_Edital_9_2024.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3484,20 +3488,24 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Edital Conjunto nº 5/2026 - Programa OBEDUC-EI - Observatório da Educação Especial Inclusiva</t>
+          <t>Edital CAPES/DAAD Probral nº 21/2022, formato, pdf, 376kb</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital-no-5.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/18042022_Edital_1681234_Edital_21.22.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1</v>
-      </c>
-      <c r="G107" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Alteração do Edital CAPES/DAAD Probral nº 21/2022, formato, pdf, 101kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400189_SEI_2398591_Edital_21_2022.pdf/@@display-file/file ; Relação das inscrições do Edital CAPES/DAAD Probral nº21/2022, formato, pdf, 78kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/13072022_Lista_Listagem_1748985_Probral.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3507,14 +3515,14 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Edital nº 039/2013 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 400kb</t>
+          <t>Edital Conjunto nº 5/2026 - Programa OBEDUC-EI - Observatório da Educação Especial Inclusiva</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_039_2013_PDPI.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital-no-5.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F108" t="n">
@@ -3530,24 +3538,20 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Edital nº 05/2023 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 473kb</t>
+          <t>Edital nº 039/2013 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 400kb</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15032023_Edital_1933938_Edital_5_2023.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_039_2013_PDPI.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>Alteração do Edital nº 05/2023 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 60kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400239_SEI_2399449_Edital_05_2023___ALTERACAO_II.pdf/@@display-file/file ; Relação das inscrições do Edital nº 05/2023 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 571kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/30052023_Lista_Listagem_1984677_Lista_de_inscritos_Math_Amsud_Edital_5.2023.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3557,22 +3561,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Edital nº 05/2024 - ProgramaCAPES/CLIMAT-AMSUD, formato - pdf, 239kb</t>
+          <t>Edital nº 05/2023 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 473kb</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20032024_Edital_2343766_SEI_2342530_Edital_05_2024.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15032023_Edital_1933938_Edital_5_2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Edital nº 05/2024 - ProgramaCAPES/STIC-AMSUD, formato - pdf, 239kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20032024_Edital_2343766_SEI_2342530_Edital_05_2024.pdf/@@display-file/file ; Alteração do Edital nº 05/2024 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 57kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07052024_Edital_2373417_SEI_2372656_Edital_05_2024.pdf/@@display-file/file ; Edital nº 05/2024 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 239kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20032024_Edital_2343766_SEI_2342530_Edital_05_2024.pdf/@@display-file/file</t>
+          <t>Alteração do Edital nº 05/2023 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 60kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400239_SEI_2399449_Edital_05_2023___ALTERACAO_II.pdf/@@display-file/file ; Relação das inscrições do Edital nº 05/2023 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 571kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/30052023_Lista_Listagem_1984677_Lista_de_inscritos_Math_Amsud_Edital_5.2023.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3584,22 +3588,22 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Edital nº 06/2023 - ProgramaCAPES/STIC-AMSUD, formato - pdf, 473kb</t>
+          <t>Edital nº 05/2024 - ProgramaCAPES/CLIMAT-AMSUD, formato - pdf, 239kb</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15032023_Edital_1933950_Edital_6_2023.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20032024_Edital_2343766_SEI_2342530_Edital_05_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alteração do Edital nº 06/2023 - Programa CAPES/STIC-AMSUD, formato - pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400119_SEI_2399429_Edital_6_2023___Alteracao_II.pdf/@@display-file/file ; Relação das inscrições do Edital nº 06/2023 - Programa CAPES/STIC-AMSUD, formato - pdf, 571kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/30052023_Lista_Listagem_1984493_Lista_de_inscritos_Stic_Amsud_Edital_6.2023.pdf/@@display-file/file</t>
+          <t>Edital nº 05/2024 - ProgramaCAPES/STIC-AMSUD, formato - pdf, 239kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20032024_Edital_2343766_SEI_2342530_Edital_05_2024.pdf/@@display-file/file ; Alteração do Edital nº 05/2024 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 57kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07052024_Edital_2373417_SEI_2372656_Edital_05_2024.pdf/@@display-file/file ; Edital nº 05/2024 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 239kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20032024_Edital_2343766_SEI_2342530_Edital_05_2024.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3611,22 +3615,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Edital nº 06/2024 - PDSE - formato, pdf, 133kb</t>
+          <t>Edital nº 06/2023 - ProgramaCAPES/STIC-AMSUD, formato - pdf, 473kb</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/21032024_Edital_2344636_SEI_2343579_Edital_6_2024.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15032023_Edital_1933950_Edital_6_2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Prorrogação do Edital nº 06/2024 - PDSE - formato, pdf, 55kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/10052024_Edital_2376323_SEI_2375557_Edital_6_2024.pdf/@@display-file/file</t>
+          <t>Alteração do Edital nº 06/2023 - Programa CAPES/STIC-AMSUD, formato - pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400119_SEI_2399429_Edital_6_2023___Alteracao_II.pdf/@@display-file/file ; Relação das inscrições do Edital nº 06/2023 - Programa CAPES/STIC-AMSUD, formato - pdf, 571kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/30052023_Lista_Listagem_1984493_Lista_de_inscritos_Stic_Amsud_Edital_6.2023.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3638,22 +3642,22 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Edital nº 07/2023 - ProgramaCAPES/CLIMAT-AMSUD, formato - pdf, 466kb</t>
+          <t>Edital nº 06/2024 - PDSE - formato, pdf, 133kb</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15032023_Edital_1933965_Edital_7_2023_.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/21032024_Edital_2344636_SEI_2343579_Edital_6_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alteração doEdital nº 07/2023 - ProgramaCAPES/CLIMAT-AMSUD, formato - pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400133_SEI_2399445_Edital_07_2023___ALTERACAO_II.pdf/@@display-file/file ; Relação das inscrições do Edital nº 07/2023 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 570kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/30052023_Lista_Listagem_1984693_Lista_de_inscritos_Climat_Amsud_Edital_7.2023.pdf/@@display-file/file</t>
+          <t>Prorrogação do Edital nº 06/2024 - PDSE - formato, pdf, 55kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/10052024_Edital_2376323_SEI_2375557_Edital_6_2024.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3665,22 +3669,22 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Edital nº 08/2023 - CAPES/Cofecub, formato, pdf, 495kb</t>
+          <t>Edital nº 07/2023 - ProgramaCAPES/CLIMAT-AMSUD, formato - pdf, 466kb</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/03042023_Edital_1946708_Edital_8_2022.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15032023_Edital_1933965_Edital_7_2023_.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alteração doEdital nº 08/2023 - CAPES/Cofecub, formato, pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20062024_Edital_2401059_SEI_2399441_Edital_08_2023___ALTERACAO_II.pdf/@@display-file/file</t>
+          <t>Alteração doEdital nº 07/2023 - ProgramaCAPES/CLIMAT-AMSUD, formato - pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400133_SEI_2399445_Edital_07_2023___ALTERACAO_II.pdf/@@display-file/file ; Relação das inscrições do Edital nº 07/2023 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 570kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/30052023_Lista_Listagem_1984693_Lista_de_inscritos_Climat_Amsud_Edital_7.2023.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3692,22 +3696,22 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Edital nº 08/2024 - CAPES/Cofecub, formato, pdf, 213kb</t>
+          <t>Edital nº 08/2023 - CAPES/Cofecub, formato, pdf, 495kb</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/22032024_Edital_2345736_SEI_2343959_Edital_8.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/03042023_Edital_1946708_Edital_8_2022.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alteração do Edital nº 08/2024 - Programa CAPES/Cofecub, formato, pdf, 54kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23122024_Edital_2517712_SEI_2516934_Edital_8_2024.pdf/@@display-file/file ; Prorrogação do Edital nº 08/2024 - CAPES/Cofecub, formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/02072024_Edital_2409554_SEI_2409272_Edital_08_2024___Prorrogacao.pdf/@@display-file/file ; Alteração do Edital nº 08/2024 - CAPES/Cofecub, formato, pdf, 57kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07052024_Edital_2373782_SEI_2372654_Edital_08_2024.pdf/@@display-file/file</t>
+          <t>Alteração doEdital nº 08/2023 - CAPES/Cofecub, formato, pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20062024_Edital_2401059_SEI_2399441_Edital_08_2023___ALTERACAO_II.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3719,20 +3723,24 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Edital nº 10/2022 - PDSE - formato, pdf, 337kb</t>
+          <t>Edital nº 08/2024 - CAPES/Cofecub, formato, pdf, 213kb</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/16022022_Edital10.22PDSE.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/22032024_Edital_2345736_SEI_2343959_Edital_8.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1</v>
-      </c>
-      <c r="G116" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Alteração do Edital nº 08/2024 - Programa CAPES/Cofecub, formato, pdf, 54kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23122024_Edital_2517712_SEI_2516934_Edital_8_2024.pdf/@@display-file/file ; Prorrogação do Edital nº 08/2024 - CAPES/Cofecub, formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/02072024_Edital_2409554_SEI_2409272_Edital_08_2024___Prorrogacao.pdf/@@display-file/file ; Alteração do Edital nº 08/2024 - CAPES/Cofecub, formato, pdf, 57kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07052024_Edital_2373782_SEI_2372654_Edital_08_2024.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3742,24 +3750,20 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Edital nº 16/2025 - formato, pdf, 360kb</t>
+          <t>Edital nº 10/2022 - PDSE - formato, pdf, 337kb</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11082025_Edital_2654124.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/16022022_Edital10.22PDSE.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>2</v>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>Lista de inscritos no edital nº 16/2025 - formato, pdf, 207kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/29102025_Lista_Listagem_2693783_SEI___23038.003238_2025_21_buffalo.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3769,20 +3773,24 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Edital nº 16/2026 - Programa AURORA — Continuidade da Trajetória de Mães Cientistas</t>
+          <t>Edital nº 16/2025 - formato, pdf, 360kb</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2818271_SEI_2817084_Edital_16_2026__1_.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11082025_Edital_2654124.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>1</v>
-      </c>
-      <c r="G118" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Lista de inscritos no edital nº 16/2025 - formato, pdf, 207kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/29102025_Lista_Listagem_2693783_SEI___23038.003238_2025_21_buffalo.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3792,14 +3800,14 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Edital nº 19/2017 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 315kb</t>
+          <t>Edital nº 16/2026 - Programa AURORA — Continuidade da Trajetória de Mães Cientistas</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/31052017Edital192017PDPI.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2818271_SEI_2817084_Edital_16_2026__1_.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -3815,14 +3823,14 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Edital nº 19/2026 - Programa Capes/Universidade em Buffalo (Capes/UB) - Professor Visitante - formato, pdf, 139kb</t>
+          <t>Edital nº 19/2017 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 315kb</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2843097_SEI_2842333_Edital_n__19_2026.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/31052017Edital192017PDPI.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F120" t="n">
@@ -3838,24 +3846,20 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Edital nº 20/2022 -Programa CAPES/STIC-AMSUD, formato, pdf - 286kb</t>
+          <t>Edital nº 19/2026 - Programa Capes/Universidade em Buffalo (Capes/UB) - Professor Visitante - formato, pdf, 139kb</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07042022_Edital_1673688_EDITAL_20_2022_STIC_AMSUD.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2843097_SEI_2842333_Edital_n__19_2026.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>3</v>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>Alteração do Edital nº 20/2022 -Programa CAPES/STIC-AMSUD, formato, pdf - 67kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400177_SEI_2399435_Edital_20_2022___ALTERACAO_I.pdf/@@display-file/file ; Relação das inscrições do Edital nº 20/2022 - Programa CAPES/STIC-AMSUD, formato - pdf, 358kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/06062022_Lista_Listagem_1727082_STIC.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3865,20 +3869,24 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Edital nº 21/2026 - Programa de Desenvolvimento da Pós-Graduação (PDPG) – Parcerias Estratégicas nos Estados VI – Rede de Pesquisa e Desenvolvimento da Região Nordeste, formato, pdf, 177kb</t>
+          <t>Edital nº 20/2022 -Programa CAPES/STIC-AMSUD, formato, pdf - 286kb</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2848691_sei_2847430_edital_n__21_2026.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07042022_Edital_1673688_EDITAL_20_2022_STIC_AMSUD.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>1</v>
-      </c>
-      <c r="G122" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Alteração do Edital nº 20/2022 -Programa CAPES/STIC-AMSUD, formato, pdf - 67kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400177_SEI_2399435_Edital_20_2022___ALTERACAO_I.pdf/@@display-file/file ; Relação das inscrições do Edital nº 20/2022 - Programa CAPES/STIC-AMSUD, formato - pdf, 358kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/06062022_Lista_Listagem_1727082_STIC.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3888,24 +3896,20 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Edital nº 22/2026 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 150kb</t>
+          <t>Edital nº 21/2026 - Programa de Desenvolvimento da Pós-Graduação (PDPG) – Parcerias Estratégicas nos Estados VI – Rede de Pesquisa e Desenvolvimento da Região Nordeste, formato, pdf, 177kb</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/sei_2849220_edital_n__22_2026.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2848691_sei_2847430_edital_n__21_2026.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>2</v>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>Alteração Edital nº 22/2026 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 47,4kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2858430_sei_2857160_edital_22_2026___alteracao.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3915,20 +3919,24 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Edital nº 23/2026 - Programa de Desenvolvimento Acadêmico Indígena (PDAI), formato, pdf, 168kb</t>
+          <t>Edital nº 22/2026 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 150kb</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2851776_sei_2851450_edital_n__23_2026.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/sei_2849220_edital_n__22_2026.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>1</v>
-      </c>
-      <c r="G124" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Alteração Edital nº 22/2026 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 47,4kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2858430_sei_2857160_edital_22_2026___alteracao.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3938,20 +3946,24 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Edital nº 23/2026 - Programa Nacional de Formação de Professores da Educação Básica (PARFOR), formato, pdf, 168kb</t>
+          <t>Edital nº 23/2026 - Programa de Desenvolvimento Acadêmico Indígena (PDAI), formato, pdf, 168kb</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2855421_sei_2854365_edital_n__23_2026.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2851776_sei_2851450_edital_n__23_2026.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>1</v>
-      </c>
-      <c r="G125" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Alteração Edital nº 23/2026 - Programa de Desenvolvimento Acadêmico Indígena (PDAI), formato, pdf, 102kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2872644_edital_conjunto_23_2026___alteracao.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3961,24 +3973,20 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Edital nº 25/2022 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 353kb</t>
+          <t>Edital nº 23/2026 - Programa Nacional de Formação de Professores da Educação Básica (PARFOR), formato, pdf, 168kb</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/04052022_Edital_1698011_SEI_CAPES___1696119___Edital_25.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2855421_sei_2854365_edital_n__23_2026.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>3</v>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>Alteração do edital nº 25/2022 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 67kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400217_SEI_2399433_Edital_25_2022___ALTERACAO_I.pdf/@@display-file/file ; Relação das inscrições do Edital nº 25/2022 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 353kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/06062022_Lista_Listagem_1727108_Climat.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3988,14 +3996,14 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Edital nº 26/2024 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE) - Retificação - formato, pdf, 48kb</t>
+          <t>Edital nº 25/2022 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 353kb</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/14102024_Edital_2477735_SEI_2477608_Edital_N__26_2024.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/04052022_Edital_1698011_SEI_CAPES___1696119___Edital_25.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F127" t="n">
@@ -4003,7 +4011,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alteração do Edital nº 26/2024 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE), formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/13032025_Edital_2560841_SEI_2559847_Edital_26_2024___ALTERACAO.pdf/@@display-file/file ; Edital nº 26/2024 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 135kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/08102024_Edital_2474014_SEI_2472849_Edital_26_2024.pdf/@@display-file/file</t>
+          <t>Alteração do edital nº 25/2022 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 67kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400217_SEI_2399433_Edital_25_2022___ALTERACAO_I.pdf/@@display-file/file ; Relação das inscrições do Edital nº 25/2022 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 353kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/06062022_Lista_Listagem_1727108_Climat.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4015,22 +4023,22 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Edital nº 27/2024 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 157kb</t>
+          <t>Edital nº 26/2024 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE) - Retificação - formato, pdf, 48kb</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/05112024_Edital_2490387_SEI_2489251_Edital_27_2024.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/14102024_Edital_2477735_SEI_2477608_Edital_N__26_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alteração do Edital 27/2024 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa no EUA - PDPI - formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/02122024_Edital_2505290_SEI_2504109_Edital_27_2024__.pdf/@@display-file/file</t>
+          <t>Alteração do Edital nº 26/2024 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE), formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/13032025_Edital_2560841_SEI_2559847_Edital_26_2024___ALTERACAO.pdf/@@display-file/file ; Edital nº 26/2024 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 135kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/08102024_Edital_2474014_SEI_2472849_Edital_26_2024.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4042,22 +4050,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Edital nº 30/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 110kb</t>
+          <t>Edital nº 27/2024 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 157kb</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/14022020_Edital_1145537_Edital_SITE.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/05112024_Edital_2490387_SEI_2489251_Edital_27_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Reabertura e alteração do Edital nº 30/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 222kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/28042022_Edital_1691552_SEI_CAPES___1685746___Edital_30_2019.pdf/@@display-file/file ; Suspensão do Edital nº 30/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 111kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_1326070_Edital_Suspensao_site.pdf/@@display-file/file</t>
+          <t>Alteração do Edital 27/2024 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa no EUA - PDPI - formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/02122024_Edital_2505290_SEI_2504109_Edital_27_2024__.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4069,14 +4077,14 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Edital nº 30/2023 - PDSE - formato, pdf, 125kb</t>
+          <t>Edital nº 30/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 110kb</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/06112023_Edital_2263037_SEI_2261948_Edital_30_2023.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/14022020_Edital_1145537_Edital_SITE.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -4084,7 +4092,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Prorrogação do Edital nº 30/2023 - PDSE - formato, pdf, 136kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11012024_Edital_2306448_SEI_CAPES___2305414___Edital_30_2023___Prorrogacao.pdf/@@display-file/file ; Alteração do Edital nº 30/2023 - PDSE - formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/18122023_Edital_2293491_SEI_2293429_Edital_30_2023_Alteracao.pdf/@@display-file/file</t>
+          <t>Reabertura e alteração do Edital nº 30/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 222kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/28042022_Edital_1691552_SEI_CAPES___1685746___Edital_30_2019.pdf/@@display-file/file ; Suspensão do Edital nº 30/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 111kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_1326070_Edital_Suspensao_site.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4096,14 +4104,14 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Edital Nº 32/2022 - CAPES/Cofecub, formato, pdf, 225kb</t>
+          <t>Edital nº 30/2023 - PDSE - formato, pdf, 125kb</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29062022_EDITAL32_2022_COFECUB.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/06112023_Edital_2263037_SEI_2261948_Edital_30_2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -4111,7 +4119,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alteração do Edital Nº 32/2022 - CAPES/Cofecub, formato, pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400143_SEI_2399437_Edital_32_2022___ALTERACAO_III.pdf/@@display-file/file ; Relação de inscritos do Edital Nº 32/2022 - CAPES/Cofecub, formato, pdf, 65kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/25082022_Lista_Listagem_1783309_EDITAL_32_2022___CAPES_COFECUB_Relacao_de_Inscricoes.pdf/@@display-file/file</t>
+          <t>Prorrogação do Edital nº 30/2023 - PDSE - formato, pdf, 136kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11012024_Edital_2306448_SEI_CAPES___2305414___Edital_30_2023___Prorrogacao.pdf/@@display-file/file ; Alteração do Edital nº 30/2023 - PDSE - formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/18122023_Edital_2293491_SEI_2293429_Edital_30_2023_Alteracao.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4123,22 +4131,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Edital nº 32/2023 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 139kb</t>
+          <t>Edital Nº 32/2022 - CAPES/Cofecub, formato, pdf, 225kb</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/16112023_Edital_2271416_SEI_2268914_Edital_32_2023.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29062022_EDITAL32_2022_COFECUB.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alteração do Edital nº 32/2023 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 57kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09022024_SEI_2321458_Edital_N__32_2023___ALTERACAOPDPI.pdf/@@display-file/file</t>
+          <t>Alteração do Edital Nº 32/2022 - CAPES/Cofecub, formato, pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400143_SEI_2399437_Edital_32_2022___ALTERACAO_III.pdf/@@display-file/file ; Relação de inscritos do Edital Nº 32/2022 - CAPES/Cofecub, formato, pdf, 65kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/25082022_Lista_Listagem_1783309_EDITAL_32_2022___CAPES_COFECUB_Relacao_de_Inscricoes.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4150,20 +4158,24 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Edital nº 35/2011 - Certificação em Língua Inglesa - pdf, 615kb</t>
+          <t>Edital nº 32/2023 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 139kb</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_035_CertificacaoEUAprofLingIngl_Fulbright.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/16112023_Edital_2271416_SEI_2268914_Edital_32_2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>1</v>
-      </c>
-      <c r="G133" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Alteração do Edital nº 32/2023 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 57kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09022024_SEI_2321458_Edital_N__32_2023___ALTERACAOPDPI.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4173,14 +4185,14 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Edital nº 4/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 270kb</t>
+          <t>Edital nº 35/2011 - Certificação em Língua Inglesa - pdf, 615kb</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/08022019Edital4.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_035_CertificacaoEUAprofLingIngl_Fulbright.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -4196,24 +4208,20 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Edital nº 44/2012 - Programa de Aperfeiçoamento para Professores de Língua Inglesa nos Eua, pdf, 272kb</t>
+          <t>Edital nº 4/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 270kb</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_0442012_ProfLingIngl_EUA.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/08022019Edital4.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>3</v>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>Edital nº 44/2012 - Retificado - pdf, 528kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_0442012_ProfLIngRetif.pdf/@@display-file/file ; Retificação do Edital nº 44/2012 - pdf, 46kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/RetificacaoEdital442012_ProfLingInglEUA_01out12.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4223,22 +4231,22 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Edital nº 44/2022 - PDSE - formato, pdf, 337kb</t>
+          <t>Edital nº 44/2012 - Programa de Aperfeiçoamento para Professores de Língua Inglesa nos Eua, pdf, 272kb</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/22122022_Edital_1882688_Edital_44_2022.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_0442012_ProfLingIngl_EUA.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alteração do Edital nº 44/2022 - PDSE - formato, pdf, 146kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23052023_Edital_1981709_Edital_44_2023.pdf/@@display-file/file</t>
+          <t>Edital nº 44/2012 - Retificado - pdf, 528kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_0442012_ProfLIngRetif.pdf/@@display-file/file ; Retificação do Edital nº 44/2012 - pdf, 46kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/RetificacaoEdital442012_ProfLingInglEUA_01out12.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4250,20 +4258,24 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Edital nº 52/2010 - Certificação em Língua Inglesa, pdf, 60kbDF</t>
+          <t>Edital nº 44/2022 - PDSE - formato, pdf, 337kb</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_52_Certificacao_LinguaInglesa2010.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/22122022_Edital_1882688_Edital_44_2022.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>1</v>
-      </c>
-      <c r="G137" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Alteração do Edital nº 44/2022 - PDSE - formato, pdf, 146kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23052023_Edital_1981709_Edital_44_2023.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4273,24 +4285,20 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Edital Nº09/2026 - Programa CAPES/BRAFITEC, formato, pdf, 209kb</t>
+          <t>Edital nº 52/2010 - Certificação em Língua Inglesa, pdf, 60kbDF</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2800035_SEI_2799041_Edital_9__de_2026.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_52_Certificacao_LinguaInglesa2010.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>2</v>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>Edital n° 9/2026 - Lista de Inscritos, formato, pdf, 398kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/lista_listagem_2864548_sei_2863010_edital_minuta__.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4300,14 +4308,14 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Lista de inscritos do Edital Conjunto nº 01/2024 - Programa Caminhos Amefricanos, formato, pdf, 407kb</t>
+          <t>Edital Nº09/2026 - Programa CAPES/BRAFITEC, formato, pdf, 209kb</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15052024_Lista_Listagem_2374115_Inscritos_MIR.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2800035_SEI_2799041_Edital_9__de_2026.pdf</t>
         </is>
       </c>
       <c r="F139" t="n">
@@ -4315,7 +4323,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alteração do Edital Conjunto nº 01/2024 - Programa Caminhos Amefricanos, formato, pdf, 63kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29042024_Edital_2368101_SEI_2365347_Edital_Conjunto_n__1_CAPES_MIR.pdf/@@display-file/file</t>
+          <t>Edital n° 9/2026 - Lista de Inscritos, formato, pdf, 398kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/lista_listagem_2864548_sei_2863010_edital_minuta__.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4327,20 +4335,24 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Lista de inscritos do Edital nº 05/2024 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 46kb</t>
+          <t>Lista de inscritos do Edital Conjunto nº 01/2024 - Programa Caminhos Amefricanos, formato, pdf, 407kb</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/10062024_Lista_Listagem_2390159_Lista_de_Inscritos_3.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15052024_Lista_Listagem_2374115_Inscritos_MIR.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>1</v>
-      </c>
-      <c r="G140" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Alteração do Edital Conjunto nº 01/2024 - Programa Caminhos Amefricanos, formato, pdf, 63kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29042024_Edital_2368101_SEI_2365347_Edital_Conjunto_n__1_CAPES_MIR.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4350,14 +4362,14 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Lista de inscritos doEdital nº 8/202 - CAPES/COFECUB, formato, pdf, 581kb</t>
+          <t>Lista de inscritos do Edital nº 05/2024 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 46kb</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/14062023_Lista_Listagem_1990268_Inscricoes_cofecub_2023.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/10062024_Lista_Listagem_2390159_Lista_de_Inscritos_3.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F141" t="n">
@@ -4373,24 +4385,20 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Lista de inscrições - Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 393kb</t>
+          <t>Lista de inscritos doEdital nº 8/202 - CAPES/COFECUB, formato, pdf, 581kb</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Lista_de_Inscricoes_Homologadas_PDSE___2020_REVISADA.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/14062023_Lista_Listagem_1990268_Inscricoes_cofecub_2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>4</v>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>Lista de candidaturas - Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 417kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/documentos/diretoria-de-relacoes-internacionais/pdse/Lista_Listagem_1439062_Lista_de_Inscricoes_Homologadas_PDSE___2020.pdf/@@display-file/file ; Retificação do Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 244kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/EDITAL192020_PDSERETIFICAO.pdf/@@display-file/file ; Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE)- formato, pdf, 236kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09102020_edital-19-pdse.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4400,14 +4408,14 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Lista de inscrições do Edital nº 17/2025 - Primeira chamada Programa Institucional de Doutorado Sanduíche no Exterior (PDSE) - formato, pdf, 8,8mb</t>
+          <t>Lista de inscrições - Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 393kb</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/29102025_Lista_Listagem_2708089_PDSE.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Lista_de_Inscricoes_Homologadas_PDSE___2020_REVISADA.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F143" t="n">
@@ -4415,7 +4423,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lista de inscrições do Edital nº 17/2025 - Segunda chamada Programa Institucional de Doutorado Sanduíche no Exterior (PDSE) - formato, pdf, 1,4mb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/27042026_Lista_Listagem_2808119_Lista_de_inscricoes_homologadas_do_Edital_172025___PDSE___segunda_chamada___formato_pdf__2_.pdf/@@display-file/file ; Alteração do Edital nº 17/2025 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE), formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/08102025_Edital_2696973_SEI_2695934_Edital_17_2025__.pdf/@@display-file/file ; Edital nº 17/2025 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 142kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/21082025_Edital_2662823_SEI_2661209_Edital_n__17_2025.pdf/@@display-file/file</t>
+          <t>Lista de candidaturas - Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 417kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/documentos/diretoria-de-relacoes-internacionais/pdse/Lista_Listagem_1439062_Lista_de_Inscricoes_Homologadas_PDSE___2020.pdf/@@display-file/file ; Retificação do Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 244kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/EDITAL192020_PDSERETIFICAO.pdf/@@display-file/file ; Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE)- formato, pdf, 236kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09102020_edital-19-pdse.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4427,14 +4435,14 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Lista de instituições e cursos pré-aprovados para a 3ª fase do Edital nº 08/2022 - Parfor - formato, pdf, 715kb</t>
+          <t>Lista de inscrições do Edital nº 17/2025 - Primeira chamada Programa Institucional de Doutorado Sanduíche no Exterior (PDSE) - formato, pdf, 8,8mb</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/06052022_Relacao_1700579_LISTA_DE_IES_E_CURSOS_APROVADOS_PARA_A_3__ETAPA_DO_EDITAL_CAPES_N__08.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/29102025_Lista_Listagem_2708089_PDSE.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F144" t="n">
@@ -4442,7 +4450,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alteraçãodo Edital nº 08/2022 - Parfor - formato, xls, 119kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20122022_Edital_1880841_Edital_8_2022___PARFOR.pdf/@@display-file/file ; Alteração do Edital nº 08/2022 - Parfor - formato, pdf, 128kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09062022_Edital_1729649_EDITAL___8_2022.pdf/@@display-file/file ; Edital nº 08/2022 - Parfor - formato, pdf, 203kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07022022_Edital_1629612_SEI_CAPES___1628279___Edital_8.pdf/@@display-file/file</t>
+          <t>Lista de inscrições do Edital nº 17/2025 - Segunda chamada Programa Institucional de Doutorado Sanduíche no Exterior (PDSE) - formato, pdf, 1,4mb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/27042026_Lista_Listagem_2808119_Lista_de_inscricoes_homologadas_do_Edital_172025___PDSE___segunda_chamada___formato_pdf__2_.pdf/@@display-file/file ; Alteração do Edital nº 17/2025 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE), formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/08102025_Edital_2696973_SEI_2695934_Edital_17_2025__.pdf/@@display-file/file ; Edital nº 17/2025 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 142kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/21082025_Edital_2662823_SEI_2661209_Edital_n__17_2025.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4454,14 +4462,14 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Lista e inscritos do Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 520kb</t>
+          <t>Lista de instituições e cursos pré-aprovados para a 3ª fase do Edital nº 08/2022 - Parfor - formato, pdf, 715kb</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/20022024_Lista_Listagem_2324280_SEI_2323841_Inscritos_MIR.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/06052022_Relacao_1700579_LISTA_DE_IES_E_CURSOS_APROVADOS_PARA_A_3__ETAPA_DO_EDITAL_CAPES_N__08.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F145" t="n">
@@ -4469,7 +4477,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alteração do Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 54kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/12062024_Edital_2395239_SEI_2389783_Edital_34_2023.pdf/@@display-file/file ; Prorrogação do Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 54kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/28122023_Edital_2301024_SEI_2300438_Edital_Conjunto_n__34_2023_Prorrogacao.pdf/@@display-file/file ; Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 129kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/04122024_Edital_2282364_SEI_2279471_Edital_Conjunto_n__34_2023.pdf/@@display-file/file</t>
+          <t>Alteraçãodo Edital nº 08/2022 - Parfor - formato, xls, 119kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20122022_Edital_1880841_Edital_8_2022___PARFOR.pdf/@@display-file/file ; Alteração do Edital nº 08/2022 - Parfor - formato, pdf, 128kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09062022_Edital_1729649_EDITAL___8_2022.pdf/@@display-file/file ; Edital nº 08/2022 - Parfor - formato, pdf, 203kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07022022_Edital_1629612_SEI_CAPES___1628279___Edital_8.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4481,22 +4489,22 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Lista final de inscritos no Edital n° 33/2022 - Brafitec, formato, pdf, 372kb</t>
+          <t>Lista e inscritos do Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 520kb</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/22092022_Lista_Listagem_1808291_Lista_inscritos_Brafitec_Edital_33_22.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/20022024_Lista_Listagem_2324280_SEI_2323841_Inscritos_MIR.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alteração do Edital n° 33/2022 - Brafitec, formato, pdf, 193kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23022023_Edital_1920292_Edital_33_22.pdf/@@display-file/file ; Edital n° 33/2022 - Brafitec, formato, pdf, 428kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29062022_EDITAL33_2022_BRAFITEC.pdf/@@display-file/file</t>
+          <t>Alteração do Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 54kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/12062024_Edital_2395239_SEI_2389783_Edital_34_2023.pdf/@@display-file/file ; Prorrogação do Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 54kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/28122023_Edital_2301024_SEI_2300438_Edital_Conjunto_n__34_2023_Prorrogacao.pdf/@@display-file/file ; Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 129kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/04122024_Edital_2282364_SEI_2279471_Edital_Conjunto_n__34_2023.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4508,37 +4516,41 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Prorrogação do Edital nº 01/2024 - Programa Caminhos Amefricanos, formato, pdf, 69kb</t>
+          <t>Lista final de inscritos no Edital n° 33/2022 - Brafitec, formato, pdf, 372kb</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/30082024_Edital_2450719_SEI_2446271_Edital_Conjunto_1_2024.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/22092022_Lista_Listagem_1808291_Lista_inscritos_Brafitec_Edital_33_22.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1</v>
-      </c>
-      <c r="G147" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Alteração do Edital n° 33/2022 - Brafitec, formato, pdf, 193kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23022023_Edital_1920292_Edital_33_22.pdf/@@display-file/file ; Edital n° 33/2022 - Brafitec, formato, pdf, 428kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29062022_EDITAL33_2022_BRAFITEC.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>SETEC</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Chamada (documento Nº 6991254) para seleção de unidades da Rede Federal de Educação Profissional e Tecnológica e das redes públicas estaduais de Educação Profissional e Tecnológica, interessadas em receber apoio técnico para a implementação de programas de aprendizagem profissional articulados a cursos técnicos ou de qualificação profissional com componentes curriculares relacionados à sustentabilidade</t>
+          <t>Prorrogação do Edital nº 01/2024 - Programa Caminhos Amefricanos, formato, pdf, 69kb</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2026/SEI_6991254_chamada.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/30082024_Edital_2450719_SEI_2446271_Edital_Conjunto_1_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4554,14 +4566,14 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Chamada Pública com o objetivo de identificar, avaliar, cadastrar e disponibilizar metodologias, ferramentas e estudos sobre o mapeamento de demandas por Educação Profissional Técnica de Nível Médio, visando aprimorar a definição de ofertas de Educação Profissional Técnica de Nível Médio, no âmbito do Programa Juros por Educação.</t>
+          <t>Chamada (documento Nº 6991254) para seleção de unidades da Rede Federal de Educação Profissional e Tecnológica e das redes públicas estaduais de Educação Profissional e Tecnológica, interessadas em receber apoio técnico para a implementação de programas de aprendizagem profissional articulados a cursos técnicos ou de qualificação profissional com componentes curriculares relacionados à sustentabilidade</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/SEI_6268868_Resultado_de_Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2026/SEI_6991254_chamada.pdf</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -4577,14 +4589,14 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Chamada Pública de Adesão das Instituições da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT), com objetivo de capacitação técnica para submissão de propostas em futuros editais de unidades Embrapii.</t>
+          <t>Chamada Pública com o objetivo de identificar, avaliar, cadastrar e disponibilizar metodologias, ferramentas e estudos sobre o mapeamento de demandas por Educação Profissional Técnica de Nível Médio, visando aprimorar a definição de ofertas de Educação Profissional Técnica de Nível Médio, no âmbito do Programa Juros por Educação.</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/edital-2025/SEI_MEC5650163ResultadodeEdital_.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/SEI_6268868_Resultado_de_Edital.pdf</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4600,14 +4612,14 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Chamada Pública de Adesão à linha de fomento Qualifica Mais EnergIFE</t>
+          <t>Chamada Pública de Adesão das Instituições da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT), com objetivo de capacitação técnica para submissão de propostas em futuros editais de unidades Embrapii.</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/chamadapublica.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/edital-2025/SEI_MEC5650163ResultadodeEdital_.pdf</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -4623,14 +4635,14 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 01/2017 - Trata-se de chamada pública para seleção de servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) para capacitação em Gestão da Inovação.</t>
+          <t>Chamada Pública de Adesão à linha de fomento Qualifica Mais EnergIFE</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/extrato_chamada_dou_cp_01_2017.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/chamadapublica.pdf</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4646,14 +4658,14 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 01/2018 - Trata-se da chamada pública para seleção de propostas e servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) em efetivo exercício, para participarem da capacitação em Gestão da Inovação (GI - CSIRO).</t>
+          <t>Chamada Pública nº 01/2017 - Trata-se de chamada pública para seleção de servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) para capacitação em Gestão da Inovação.</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/20181030Edital012018ChamadaPblicaGICSIRO.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/extrato_chamada_dou_cp_01_2017.pdf</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -4669,14 +4681,14 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 02/2017 - Trata-se de chamada pública para concurso sobre educação profissional da Secretaria de Educação Profissional e Tecnológica (Setec/MEC) em parceria com a Comunidade dos Países de Língua Portuguesa (CPLP).</t>
+          <t>Chamada Pública nº 01/2018 - Trata-se da chamada pública para seleção de propostas e servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) em efetivo exercício, para participarem da capacitação em Gestão da Inovação (GI - CSIRO).</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/edital_concurso_cplp_2017.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/20181030Edital012018ChamadaPblicaGICSIRO.pdf</t>
         </is>
       </c>
       <c r="F154" t="n">
@@ -4692,14 +4704,14 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 02/2018 - Trata-se da chamada pública para seleção de servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) para a capacitação Brasileiros Formando Formadores (BraFF).</t>
+          <t>Chamada Pública nº 02/2017 - Trata-se de chamada pública para concurso sobre educação profissional da Secretaria de Educação Profissional e Tecnológica (Setec/MEC) em parceria com a Comunidade dos Países de Língua Portuguesa (CPLP).</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/Edital_02_2018_BRAFF.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/edital_concurso_cplp_2017.pdf</t>
         </is>
       </c>
       <c r="F155" t="n">
@@ -4715,14 +4727,14 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 38/2018 - Trata do processo de seleção de propostas para credenciamento de instituições da Rede Federal, Faculdades de Tecnologia do Estado de São Paulo (Fatecs) e do Instituto Tecnológico de Aeronáutica (ITA) para atuação como Núcleo de Línguas (NucLi-IsF) no âmbito do Programa Idiomas sem Fronteiras (IsF).</t>
+          <t>Chamada Pública nº 02/2018 - Trata-se da chamada pública para seleção de servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) para a capacitação Brasileiros Formando Formadores (BraFF).</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/Editaln382018ChamadaPblicaparacredenciamentodeinstituiesdaRFEPCTdasFatecsedoITA.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/Edital_02_2018_BRAFF.pdf</t>
         </is>
       </c>
       <c r="F156" t="n">
@@ -4738,14 +4750,14 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 79/2016 - Trata-se de chamada pública para apresentação de propostas por instituição de educação profissional e tecnológica para a oferta de cursos de formação inicial e continuada ou de qualificação profissional e cursos técnicos de nível médio, presenciais ou à distância, sem transferência de recursos, no âmbito do PRONATEC, denominada “PROPOSTAS VOLUNTÁRIAS - PRONATEC”</t>
+          <t>Chamada Pública nº 38/2018 - Trata do processo de seleção de propostas para credenciamento de instituições da Rede Federal, Faculdades de Tecnologia do Estado de São Paulo (Fatecs) e do Instituto Tecnológico de Aeronáutica (ITA) para atuação como Núcleo de Línguas (NucLi-IsF) no âmbito do Programa Idiomas sem Fronteiras (IsF).</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/extrato_edital_79_2016_setec.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/Editaln382018ChamadaPblicaparacredenciamentodeinstituiesdaRFEPCTdasFatecsedoITA.pdf</t>
         </is>
       </c>
       <c r="F157" t="n">
@@ -4761,14 +4773,14 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Chamada Pública que estabelece os procedimentos para a autorização de oferta de cursos técnicos de nível médio por Instituições Privadas de Ensino Superior (IPES) para fins de habilitação ao Programa Juros por Educação, no âmbito do Programa de Pleno Pagamento de Dívidas dos Estados (Propag).</t>
+          <t>Chamada Pública nº 79/2016 - Trata-se de chamada pública para apresentação de propostas por instituição de educação profissional e tecnológica para a oferta de cursos de formação inicial e continuada ou de qualificação profissional e cursos técnicos de nível médio, presenciais ou à distância, sem transferência de recursos, no âmbito do PRONATEC, denominada “PROPOSTAS VOLUNTÁRIAS - PRONATEC”</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/FAQEdital6.2025.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/extrato_edital_79_2016_setec.pdf</t>
         </is>
       </c>
       <c r="F158" t="n">
@@ -4784,14 +4796,14 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Chamamento Público para credenciamento de profissionais no Banco de Especialistas para atuar no Projeto Assistec Inova, junto ao Ministério da Educação, no âmbito da Secretaria de Educação Profissional e Tecnológica.</t>
+          <t>Chamada Pública que estabelece os procedimentos para a autorização de oferta de cursos técnicos de nível médio por Instituições Privadas de Ensino Superior (IPES) para fins de habilitação ao Programa Juros por Educação, no âmbito do Programa de Pleno Pagamento de Dívidas dos Estados (Propag).</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/SEI_23000.035944_2024_89.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/FAQEdital6.2025.pdf</t>
         </is>
       </c>
       <c r="F159" t="n">
@@ -4807,14 +4819,14 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Edital 1/2026 - Chamada Pública de Adesão dos Institutos Federais de Educação, Ciência e Tecnologia, do Centro Federal de Educação Tecnológica Celso Suckow da Fonseca, do Centro Federal de Educação Tecnológica de Minas Gerais e do Colégio Pedro II, com objetivo de capacitação técnica para submissão de propostas em futuros editais de Unidades Embrapii.</t>
+          <t>Chamamento Público para credenciamento de profissionais no Banco de Especialistas para atuar no Projeto Assistec Inova, junto ao Ministério da Educação, no âmbito da Secretaria de Educação Profissional e Tecnológica.</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/edital12026.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/SEI_23000.035944_2024_89.pdf</t>
         </is>
       </c>
       <c r="F160" t="n">
@@ -4830,14 +4842,14 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Edital 84/2021 - Seleção de Projetos para desenvolvimento dos Ambientes de Promotores de Inovação na Rede Federal</t>
+          <t>Edital 1/2026 - Chamada Pública de Adesão dos Institutos Federais de Educação, Ciência e Tecnologia, do Centro Federal de Educação Tecnológica Celso Suckow da Fonseca, do Centro Federal de Educação Tecnológica de Minas Gerais e do Colégio Pedro II, com objetivo de capacitação técnica para submissão de propostas em futuros editais de Unidades Embrapii.</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/editais/2022/ResultadoetapaI.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/edital12026.pdf</t>
         </is>
       </c>
       <c r="F161" t="n">
@@ -4853,14 +4865,14 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Edital nº 01/2017 - APRESENTAÇÃO DE PROPOSTAS PARA A OFERTA DE VAGAS GRATUITAS EM CURSOS TÉCNICOS NA FORMA CONCOMITANTE, NO ÂMBITO DO PRONATEC/MEDIOTEC – 2º/2017 - A Secretária de Educação Profissional e Tecnológica do Ministério da Educação, no uso da atribuição que lhe confere o art. 13, Anexo I, do Decreto n° 7.690, de 02 de março de 2012, e considerando o disposto na Lei nº 12.513, de 26 de outubro de 2011, a Portaria nº 817, de 13 de agosto de 2015, a Portaria nº160, de 05 de março de 2013, alterada pela Portaria nº 701, de 13 de agosto de 2014, TORNA PÚBLICO os procedimentos e o cronograma para a apresentação de propostas visando a oferta de vagas gratuitas em cursos técnicos na forma concomitante e na modalidade presencial, no âmbito do Programa Nacional de Acesso ao Ensino Técnico e Emprego - PRONATEC, por meio da ação MEDIOTEC, para ingresso no segundo semestre de 2017.</t>
+          <t>Edital 84/2021 - Seleção de Projetos para desenvolvimento dos Ambientes de Promotores de Inovação na Rede Federal</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/edital_01_mediotec_2017.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/editais/2022/ResultadoetapaI.pdf</t>
         </is>
       </c>
       <c r="F162" t="n">
@@ -4876,14 +4888,14 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Edital nº 08/2024 - Chamamento Público visando à seleção de autores(as) para elaboração de capítulos de obra a ser publicada cuja temática central é a gestão de Núcleos de Inovação Tecnológica (NITs) e/ou de Agências de Inovação da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) Divulgação das Inscrições Homologadas</t>
+          <t>Edital nº 01/2017 - APRESENTAÇÃO DE PROPOSTAS PARA A OFERTA DE VAGAS GRATUITAS EM CURSOS TÉCNICOS NA FORMA CONCOMITANTE, NO ÂMBITO DO PRONATEC/MEDIOTEC – 2º/2017 - A Secretária de Educação Profissional e Tecnológica do Ministério da Educação, no uso da atribuição que lhe confere o art. 13, Anexo I, do Decreto n° 7.690, de 02 de março de 2012, e considerando o disposto na Lei nº 12.513, de 26 de outubro de 2011, a Portaria nº 817, de 13 de agosto de 2015, a Portaria nº160, de 05 de março de 2013, alterada pela Portaria nº 701, de 13 de agosto de 2014, TORNA PÚBLICO os procedimentos e o cronograma para a apresentação de propostas visando a oferta de vagas gratuitas em cursos técnicos na forma concomitante e na modalidade presencial, no âmbito do Programa Nacional de Acesso ao Ensino Técnico e Emprego - PRONATEC, por meio da ação MEDIOTEC, para ingresso no segundo semestre de 2017.</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/436.SEI_MEC5030251Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/edital_01_mediotec_2017.pdf</t>
         </is>
       </c>
       <c r="F163" t="n">
@@ -4899,14 +4911,14 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Edital nº 1/2023 - Seleção de proposta de selo comemorativo, em alusão aos 15 anos dos Institutos Federais.</t>
+          <t>Edital nº 08/2024 - Chamamento Público visando à seleção de autores(as) para elaboração de capítulos de obra a ser publicada cuja temática central é a gestão de Núcleos de Inovação Tecnológica (NITs) e/ou de Agências de Inovação da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) Divulgação das Inscrições Homologadas</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC4094376Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/436.SEI_MEC5030251Edital.pdf</t>
         </is>
       </c>
       <c r="F164" t="n">
@@ -4922,14 +4934,14 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Edital nº 100/2022 - Chamamento Público para a seleção de propostas para o Desafio Soutec</t>
+          <t>Edital nº 1/2023 - Seleção de proposta de selo comemorativo, em alusão aos 15 anos dos Institutos Federais.</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/secretarias/secretaria-de-educacao-profissional/editais-2022/SEI_MEC3570188Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC4094376Edital.pdf</t>
         </is>
       </c>
       <c r="F165" t="n">
@@ -4945,14 +4957,14 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Edital nº 109/2022 - Chamamento Público - Seleção de projetos voltados à promoção do empreendedorismo inovador, com foco na Economia 4.0, associados ao ensino, à pesquisa e à extensão, destinado às instituições integrantes da Rede Federal de Educação Profissional, Científica e Tecnológica</t>
+          <t>Edital nº 100/2022 - Chamamento Público para a seleção de propostas para o Desafio Soutec</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital109.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/secretarias/secretaria-de-educacao-profissional/editais-2022/SEI_MEC3570188Edital.pdf</t>
         </is>
       </c>
       <c r="F166" t="n">
@@ -4968,14 +4980,14 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Edital nº 11/2024 - Chamamento Público para a seleção de projetos aptos a integrarem a 4ª Semana Nacional de Educação Profissional e Tecnológica Retificação do</t>
+          <t>Edital nº 109/2022 - Chamamento Público - Seleção de projetos voltados à promoção do empreendedorismo inovador, com foco na Economia 4.0, associados ao ensino, à pesquisa e à extensão, destinado às instituições integrantes da Rede Federal de Educação Profissional, Científica e Tecnológica</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-2024-1/Edital_11.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital109.pdf</t>
         </is>
       </c>
       <c r="F167" t="n">
@@ -4991,14 +5003,14 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Edital nº 15/2023 - Chamada Pública para o Workshop para elaboração de Itinerários Formativos em economia circular na Educação Profissional e Tecnológica</t>
+          <t>Edital nº 11/2024 - Chamamento Público para a seleção de projetos aptos a integrarem a 4ª Semana Nacional de Educação Profissional e Tecnológica Retificação do</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/SEI_MEC3884064Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-2024-1/Edital_11.pdf</t>
         </is>
       </c>
       <c r="F168" t="n">
@@ -5014,14 +5026,14 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Edital nº 2/2020 - IFES, de chamada pública para a seleção de projetos voltados à implementação das Oficinas 4.0, aberto às autarquias da Rede Federal.</t>
+          <t>Edital nº 15/2023 - Chamada Pública para o Workshop para elaboração de Itinerários Formativos em economia circular na Educação Profissional e Tecnológica</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://www.ifes.edu.br/chamadas-publicas/19329-chamada-publica-2-2020-apoio-a-implementacao-de-oficinas-4-0</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/SEI_MEC3884064Edital.pdf</t>
         </is>
       </c>
       <c r="F169" t="n">
@@ -5037,14 +5049,14 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Edital nº 20/2021 – Seleção de servidores para atuação em Projetos de Colaboração Técnica junto ao Ministério da Educação.</t>
+          <t>Edital nº 2/2020 - IFES, de chamada pública para a seleção de projetos voltados à implementação das Oficinas 4.0, aberto às autarquias da Rede Federal.</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/SEI_MEC2573324Edital.pdf</t>
+          <t>https://www.ifes.edu.br/chamadas-publicas/19329-chamada-publica-2-2020-apoio-a-implementacao-de-oficinas-4-0</t>
         </is>
       </c>
       <c r="F170" t="n">
@@ -5060,14 +5072,14 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Edital nº 25/2023 - Chamada Pública destinada a selecionar equipes da Rede Federal de Educação Profissional, Científica e Tecnológica (EPCT) para participação no projeto de formação em criatividade, inovação e prototipagem do mercosul (Hackathon Mercosul). Retificação do Edital</t>
+          <t>Edital nº 20/2021 – Seleção de servidores para atuação em Projetos de Colaboração Técnica junto ao Ministério da Educação.</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/SEI_MEC3913111Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/SEI_MEC2573324Edital.pdf</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -5083,14 +5095,14 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Edital nº 26 versão consolidada</t>
+          <t>Edital nº 25/2023 - Chamada Pública destinada a selecionar equipes da Rede Federal de Educação Profissional, Científica e Tecnológica (EPCT) para participação no projeto de formação em criatividade, inovação e prototipagem do mercosul (Hackathon Mercosul). Retificação do Edital</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC3980995Documento.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/SEI_MEC3913111Edital.pdf</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -5106,14 +5118,14 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Edital nº 3/2021 – Chamada Pública para seleção de projetos de iniciação tecnológica com foco na Economia 4.0. Acesse o edital .</t>
+          <t>Edital nº 26 versão consolidada</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://www.ifes.edu.br/chamadas-publicas/19351-chamada-publica-3-2020-projetos-iniciacao-tecnologica-economia-4-0</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC3980995Documento.pdf</t>
         </is>
       </c>
       <c r="F173" t="n">
@@ -5129,24 +5141,20 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Edital nº 35/2020 - Chamada Pública - que tem como objetivo selecionar projetos voltados à criação de Laboratórios IFMaker junto aos Institutos Federais de Educação, Ciência e Tecnologia; Centros Federais de Educação Tecnológica Celso Suckow da Fonseca – Cefet-RJ e de Minas Gerais – Cefet-MG e o Colégio Pedro II, conforme especificado no Despacho SEI nº 2064854</t>
+          <t>Edital nº 3/2021 – Chamada Pública para seleção de projetos de iniciação tecnológica com foco na Economia 4.0. Acesse o edital .</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2020/SEI_MEC_2064339_Edital_Chamada_Publica.pdf</t>
+          <t>https://www.ifes.edu.br/chamadas-publicas/19351-chamada-publica-3-2020-projetos-iniciacao-tecnologica-economia-4-0</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>2</v>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>Retificação Edital nº 35/2020 - Chamada Pública - Seleção de projetos voltados à criação de Laboratórios Maker junto à Rede Federal de Educação Profissional, Científica e Tecnológica Retificação de Cronograma ​do | https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/AlteraodecronogramaRedeMakeredital35.pdf</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -5156,20 +5164,24 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Edital nº 46, de 20 de julho de 2020, que torna público edital para adesão de estados e Distrito Federal à oferta de Curso de Especialização Lato Sensu em Docência para a Educação Profissional e Tecnológica (DocentEPT) aos professores da rede pública estadual e distrital que atuam na oferta de cursos de Educação Profissional e Tecnológica</t>
+          <t>Edital nº 35/2020 - Chamada Pública - que tem como objetivo selecionar projetos voltados à criação de Laboratórios IFMaker junto aos Institutos Federais de Educação, Ciência e Tecnologia; Centros Federais de Educação Tecnológica Celso Suckow da Fonseca – Cefet-RJ e de Minas Gerais – Cefet-MG e o Colégio Pedro II, conforme especificado no Despacho SEI nº 2064854</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2020/Editaldeadeso_DOU.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2020/SEI_MEC_2064339_Edital_Chamada_Publica.pdf</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>1</v>
-      </c>
-      <c r="G175" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Retificação Edital nº 35/2020 - Chamada Pública - Seleção de projetos voltados à criação de Laboratórios Maker junto à Rede Federal de Educação Profissional, Científica e Tecnológica Retificação de Cronograma ​do | https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/AlteraodecronogramaRedeMakeredital35.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -5179,14 +5191,14 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Edital nº 47/2022 - Chamada Pública para oferta de cursos da Plataforma Aprenda Mais</t>
+          <t>Edital nº 46, de 20 de julho de 2020, que torna público edital para adesão de estados e Distrito Federal à oferta de Curso de Especialização Lato Sensu em Docência para a Educação Profissional e Tecnológica (DocentEPT) aos professores da rede pública estadual e distrital que atuam na oferta de cursos de Educação Profissional e Tecnológica</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/editais/2022/Editaln47.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2020/Editaldeadeso_DOU.pdf</t>
         </is>
       </c>
       <c r="F176" t="n">
@@ -5202,14 +5214,14 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Edital nº 48/2022 - Procedimentos para autorização da oferta de cursos técnicos de nível médio por Instituições Privadas de Ensino Superior – Anexos do</t>
+          <t>Edital nº 47/2022 - Chamada Pública para oferta de cursos da Plataforma Aprenda Mais</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/editais/2022/Editaln48.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/editais/2022/Editaln47.pdf</t>
         </is>
       </c>
       <c r="F177" t="n">
@@ -5225,14 +5237,14 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Edital nº 5 /2026 - Seleção de propostas de projetos de extensão voltados ao Acesso, à Permanência e ao Êxito no âmbito da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT).</t>
+          <t>Edital nº 48/2022 - Procedimentos para autorização da oferta de cursos técnicos de nível médio por Instituições Privadas de Ensino Superior – Anexos do</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2026/sei_7012727_edital_5.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/editais/2022/Editaln48.pdf</t>
         </is>
       </c>
       <c r="F178" t="n">
@@ -5248,14 +5260,14 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Edital nº 5/2020 – Chamada para seleção de projetos de apoio ao empreendedorismo inovador com foco na Economia 4.0. Acesse o edital .</t>
+          <t>Edital nº 5 /2026 - Seleção de propostas de projetos de extensão voltados ao Acesso, à Permanência e ao Êxito no âmbito da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT).</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://www.ifes.edu.br/chamadas-publicas/19384-chamada-publica-05-2020-selecao-de-projetos-de-apoio-ao-empreendedorismo-inovador-com-foco-na-economia-4-0</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2026/sei_7012727_edital_5.pdf</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -5271,14 +5283,14 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Edital nº 5/2021 – IF Mais Empreendedor Nacional : Adesão ao Programa IF Mais Empreendedor Nacional</t>
+          <t>Edital nº 5/2020 – Chamada para seleção de projetos de apoio ao empreendedorismo inovador com foco na Economia 4.0. Acesse o edital .</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/editais/2021/Edital05.2021IFEMPREENDEDORNACIONAL.pdf</t>
+          <t>https://www.ifes.edu.br/chamadas-publicas/19384-chamada-publica-05-2020-selecao-de-projetos-de-apoio-ao-empreendedorismo-inovador-com-foco-na-economia-4-0</t>
         </is>
       </c>
       <c r="F180" t="n">
@@ -5294,14 +5306,14 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Edital nº 5/2024 - Seleção de propostas de novos Cursos Abertos, On-line e Massivos (MOOCs), desenvolvidos pela Rede Federa de Educação Profissional, Científica e Tecnológica, a serem disponibilizados na Plataforma APRENDA MAIS.</t>
+          <t>Edital nº 5/2021 – IF Mais Empreendedor Nacional : Adesão ao Programa IF Mais Empreendedor Nacional</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC4659481Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/editais/2021/Edital05.2021IFEMPREENDEDORNACIONAL.pdf</t>
         </is>
       </c>
       <c r="F181" t="n">
@@ -5317,14 +5329,14 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Edital nº 52/2016 – que torna público, para conhecimento dos interessados, que será realizado na modalidade concurso, o PROJETO DESAFIO DA EDUCAÇÃO PROFISSIONAL E TECNOLÓGICA, na forma do REGULAMENTO anexo a este edital, com o objetivo de promover uma campanha nacional para aprimorar a Educação Profissional e Tecnológica estimulando a sociedade a enviar propostas de ações inovadoras e compartilhar experiências exitosas de implementação de ações.</t>
+          <t>Edital nº 5/2024 - Seleção de propostas de novos Cursos Abertos, On-line e Massivos (MOOCs), desenvolvidos pela Rede Federa de Educação Profissional, Científica e Tecnológica, a serem disponibilizados na Plataforma APRENDA MAIS.</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/edital_n_52_2016.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC4659481Edital.pdf</t>
         </is>
       </c>
       <c r="F182" t="n">
@@ -5340,14 +5352,14 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Edital nº 55/2016 , que torna público concurso PROJETO DESAFIO EDUCAÇÃO ZIKAZERO, na forma do REGULAMENTO anexo a este edital, com o objetivo de promover uma campanha nacional de mobilização para o enfrentamento ao Aedes aegyp e à microcefalia estimulando a sociedade a enviar propostas de ações inovadoras e compartilhar experiências exitosas de implementação de ações em prol do combate ao mosquito.</t>
+          <t>Edital nº 52/2016 – que torna público, para conhecimento dos interessados, que será realizado na modalidade concurso, o PROJETO DESAFIO DA EDUCAÇÃO PROFISSIONAL E TECNOLÓGICA, na forma do REGULAMENTO anexo a este edital, com o objetivo de promover uma campanha nacional para aprimorar a Educação Profissional e Tecnológica estimulando a sociedade a enviar propostas de ações inovadoras e compartilhar experiências exitosas de implementação de ações.</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/Edital_55_2016_SEI_MEC_0227936.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/edital_n_52_2016.pdf</t>
         </is>
       </c>
       <c r="F183" t="n">
@@ -5363,14 +5375,14 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Edital nº 6/2021 - Edital de Adesão das instituições ao Sistema Re-Saber</t>
+          <t>Edital nº 55/2016 , que torna público concurso PROJETO DESAFIO EDUCAÇÃO ZIKAZERO, na forma do REGULAMENTO anexo a este edital, com o objetivo de promover uma campanha nacional de mobilização para o enfrentamento ao Aedes aegyp e à microcefalia estimulando a sociedade a enviar propostas de ações inovadoras e compartilhar experiências exitosas de implementação de ações em prol do combate ao mosquito.</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/Edital_06_2021.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/Edital_55_2016_SEI_MEC_0227936.pdf</t>
         </is>
       </c>
       <c r="F184" t="n">
@@ -5386,14 +5398,14 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Edital nº 6/2024 - Edital visa selecionar a proposta de selo/logomarca que será utilizado em confecções comemorativas no contexto dos 115 anos da Rede Federal de Educação Profissional, Científica e Tecnológica, que poderá ser personalizado como selo postal, via Correios. *</t>
+          <t>Edital nº 6/2021 - Edital de Adesão das instituições ao Sistema Re-Saber</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-2024/325.SEI_MEC4985249Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/Edital_06_2021.pdf</t>
         </is>
       </c>
       <c r="F185" t="n">
@@ -5409,14 +5421,14 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Edital nº 61/2019 – Regulamento do Cadastro de Especialistas para compor o Banco de Avaliadores da Secretaria de Educação Profissional e Tecnológica.</t>
+          <t>Edital nº 6/2024 - Edital visa selecionar a proposta de selo/logomarca que será utilizado em confecções comemorativas no contexto dos 115 anos da Rede Federal de Educação Profissional, Científica e Tecnológica, que poderá ser personalizado como selo postal, via Correios. *</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2019/EDITALN612019.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-2024/325.SEI_MEC4985249Edital.pdf</t>
         </is>
       </c>
       <c r="F186" t="n">
@@ -5432,14 +5444,14 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Edital nº 63/2021- Seleção de Projetos de Promoção às Indicações Geográficas</t>
+          <t>Edital nº 61/2019 – Regulamento do Cadastro de Especialistas para compor o Banco de Avaliadores da Secretaria de Educação Profissional e Tecnológica.</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/editais/2021/Edital63.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2019/EDITALN612019.pdf</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -5455,14 +5467,14 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Edital nº 67/2021 - Chamada Pública de Projetos para apoio à implementação das Oficinas 4.0</t>
+          <t>Edital nº 63/2021- Seleção de Projetos de Promoção às Indicações Geográficas</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/SEI_MEC2898796Edital67.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/editais/2021/Edital63.pdf</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -5478,14 +5490,14 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Edital nº 68/2019 – Seleção de servidores para atuação em Projetos Educacionais de Colaboração Técnica junto ao Ministério da Educação.</t>
+          <t>Edital nº 67/2021 - Chamada Pública de Projetos para apoio à implementação das Oficinas 4.0</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2019/EDITALN682019.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/SEI_MEC2898796Edital67.pdf</t>
         </is>
       </c>
       <c r="F189" t="n">
@@ -5501,14 +5513,14 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Edital nº 83/2022 – Seleção de propostas de instituições da Rede Federal para a implementação de programa de capacitação de estudantes denominado Oficinas 4.0</t>
+          <t>Edital nº 68/2019 – Seleção de servidores para atuação em Projetos Educacionais de Colaboração Técnica junto ao Ministério da Educação.</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital83.2022.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2019/EDITALN682019.pdf</t>
         </is>
       </c>
       <c r="F190" t="n">
@@ -5524,14 +5536,14 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Edital nº 88/2022 – Seleção de projetos de iniciação tecnológica de instituições da RFEPCT para o desenvolvimento de ações de formação em programação e/ou robótica e/ou cultura maker para estudantes dos anos finais do ensino fundamental (6º ao 9º ano) das redes públicas de ensino. Retificação ​do</t>
+          <t>Edital nº 83/2022 – Seleção de propostas de instituições da Rede Federal para a implementação de programa de capacitação de estudantes denominado Oficinas 4.0</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital88.2022.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital83.2022.pdf</t>
         </is>
       </c>
       <c r="F191" t="n">
@@ -5547,14 +5559,14 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Edital nº 94/2022 – Chamada Pública para a capacitação de multiplicadores em bioeconomia para a Amazônia Legal. Chamada Pública para a Adesão de parceiros ofertantes da Rede Federal de Educação Profissional, Científica e Tecnológica – RFEPCT à linha de fomento Qualifica Mais EnergIFE, voltada à promoção da oferta de cursos na área das Energias Renováveis. Retificação do</t>
+          <t>Edital nº 88/2022 – Seleção de projetos de iniciação tecnológica de instituições da RFEPCT para o desenvolvimento de ações de formação em programação e/ou robótica e/ou cultura maker para estudantes dos anos finais do ensino fundamental (6º ao 9º ano) das redes públicas de ensino. Retificação ​do</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Editaln94.2022.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital88.2022.pdf</t>
         </is>
       </c>
       <c r="F192" t="n">
@@ -5570,14 +5582,14 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Edital nº 99/2022 - Chamamento Público para a seleção de projetos de inovação e trabalhos acadêmicos aptos a integrarem a Semana Nacional da Educação Profissional e Tecnológica Retificação do</t>
+          <t>Edital nº 94/2022 – Chamada Pública para a capacitação de multiplicadores em bioeconomia para a Amazônia Legal. Chamada Pública para a Adesão de parceiros ofertantes da Rede Federal de Educação Profissional, Científica e Tecnológica – RFEPCT à linha de fomento Qualifica Mais EnergIFE, voltada à promoção da oferta de cursos na área das Energias Renováveis. Retificação do</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/secretarias/secretaria-de-educacao-profissional/SEI_MEC3566713Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Editaln94.2022.pdf</t>
         </is>
       </c>
       <c r="F193" t="n">
@@ -5593,14 +5605,14 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Programa Setec-Capes/NOVA de capacitação para Professores da Rede Federal de Educação Profissional, Científica e Tecnológica . A Secretaria de Educação Profissional e Tecnológica (Setec) do Ministério da Educação, com apoio da Coordenação de Aperfeiçoamento de Pessoal de Nível Superior (Capes), lançam chamada pública de capacitação para professores de inglês em efetivo exercício na Rede Federal de Educação Profissional - Institutos Federais, Cefets, Escolas Técnicas vinculas às Universidades Federais e Colégio Pedro II. (Retificação publicada no Diário Oficial da União em 02 de junho de 2016)</t>
+          <t>Edital nº 99/2022 - Chamamento Público para a seleção de projetos de inovação e trabalhos acadêmicos aptos a integrarem a Semana Nacional da Educação Profissional e Tecnológica Retificação do</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2015/chamada_setec_capes_nova_extrato_dou.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/secretarias/secretaria-de-educacao-profissional/SEI_MEC3566713Edital.pdf</t>
         </is>
       </c>
       <c r="F194" t="n">
@@ -5616,24 +5628,20 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Republicação do Edital nº 76/2022 - Chamamento Público para seleção de projetos voltados ao fortalecimento de Núcleos de Inovação Tecnológica e/ou Agências de Inovação.</t>
+          <t>Programa Setec-Capes/NOVA de capacitação para Professores da Rede Federal de Educação Profissional, Científica e Tecnológica . A Secretaria de Educação Profissional e Tecnológica (Setec) do Ministério da Educação, com apoio da Coordenação de Aperfeiçoamento de Pessoal de Nível Superior (Capes), lançam chamada pública de capacitação para professores de inglês em efetivo exercício na Rede Federal de Educação Profissional - Institutos Federais, Cefets, Escolas Técnicas vinculas às Universidades Federais e Colégio Pedro II. (Retificação publicada no Diário Oficial da União em 02 de junho de 2016)</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Republicaodoedital76.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2015/chamada_setec_capes_nova_extrato_dou.pdf</t>
         </is>
       </c>
       <c r="F195" t="n">
-        <v>2</v>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>Retificação do Edital nº 76/2022 – novo cronograma | https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/SEI_23000.006585_2022_91.pdf</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -5643,20 +5651,24 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições da Rede Federal de Educação Profissional, Científica e Tecnológica).</t>
+          <t>Republicação do Edital nº 76/2022 - Chamamento Público para seleção de projetos voltados ao fortalecimento de Núcleos de Inovação Tecnológica e/ou Agências de Inovação.</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/ResultadoEdital10.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Republicaodoedital76.pdf</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>1</v>
-      </c>
-      <c r="G196" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Retificação do Edital nº 76/2022 – novo cronograma | https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/SEI_23000.006585_2022_91.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -5666,14 +5678,14 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições Privadas de Ensino Superior que ofertam cursos técnicos e Escolas Técnicas Privadas).</t>
+          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições da Rede Federal de Educação Profissional, Científica e Tecnológica).</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/ResultadoEdital09.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/ResultadoEdital10.pdf</t>
         </is>
       </c>
       <c r="F197" t="n">
@@ -5689,20 +5701,43 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições Públicas Estaduais e Distrital de Educação Profissional e Tecnológica).</t>
+          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições Privadas de Ensino Superior que ofertam cursos técnicos e Escolas Técnicas Privadas).</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/ResultadoEdital09.pdf</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>1</v>
+      </c>
+      <c r="G198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>SETEC</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições Públicas Estaduais e Distrital de Educação Profissional e Tecnológica).</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr"/>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
           <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/2147-resultado-preliminar.pdf</t>
         </is>
       </c>
-      <c r="F198" t="n">
-        <v>1</v>
-      </c>
-      <c r="G198" t="inlineStr"/>
+      <c r="F199" t="n">
+        <v>1</v>
+      </c>
+      <c r="G199" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/editais.xlsx
+++ b/editais.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G199"/>
+  <dimension ref="A1:G200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3538,14 +3538,14 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Edital nº 039/2013 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 400kb</t>
+          <t>Edital Conjunto nº 6/2026 - CAPES/CNJ - Apoio a Pesquisas Judiciárias, formato, pdf, 257kb</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_039_2013_PDPI.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2873621_sei___23038-001405_2026_81.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -3561,24 +3561,20 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Edital nº 05/2023 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 473kb</t>
+          <t>Edital nº 039/2013 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 400kb</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15032023_Edital_1933938_Edital_5_2023.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_039_2013_PDPI.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>3</v>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>Alteração do Edital nº 05/2023 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 60kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400239_SEI_2399449_Edital_05_2023___ALTERACAO_II.pdf/@@display-file/file ; Relação das inscrições do Edital nº 05/2023 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 571kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/30052023_Lista_Listagem_1984677_Lista_de_inscritos_Math_Amsud_Edital_5.2023.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3588,22 +3584,22 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Edital nº 05/2024 - ProgramaCAPES/CLIMAT-AMSUD, formato - pdf, 239kb</t>
+          <t>Edital nº 05/2023 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 473kb</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20032024_Edital_2343766_SEI_2342530_Edital_05_2024.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15032023_Edital_1933938_Edital_5_2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Edital nº 05/2024 - ProgramaCAPES/STIC-AMSUD, formato - pdf, 239kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20032024_Edital_2343766_SEI_2342530_Edital_05_2024.pdf/@@display-file/file ; Alteração do Edital nº 05/2024 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 57kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07052024_Edital_2373417_SEI_2372656_Edital_05_2024.pdf/@@display-file/file ; Edital nº 05/2024 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 239kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20032024_Edital_2343766_SEI_2342530_Edital_05_2024.pdf/@@display-file/file</t>
+          <t>Alteração do Edital nº 05/2023 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 60kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400239_SEI_2399449_Edital_05_2023___ALTERACAO_II.pdf/@@display-file/file ; Relação das inscrições do Edital nº 05/2023 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 571kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/30052023_Lista_Listagem_1984677_Lista_de_inscritos_Math_Amsud_Edital_5.2023.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3615,22 +3611,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Edital nº 06/2023 - ProgramaCAPES/STIC-AMSUD, formato - pdf, 473kb</t>
+          <t>Edital nº 05/2024 - ProgramaCAPES/CLIMAT-AMSUD, formato - pdf, 239kb</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15032023_Edital_1933950_Edital_6_2023.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20032024_Edital_2343766_SEI_2342530_Edital_05_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alteração do Edital nº 06/2023 - Programa CAPES/STIC-AMSUD, formato - pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400119_SEI_2399429_Edital_6_2023___Alteracao_II.pdf/@@display-file/file ; Relação das inscrições do Edital nº 06/2023 - Programa CAPES/STIC-AMSUD, formato - pdf, 571kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/30052023_Lista_Listagem_1984493_Lista_de_inscritos_Stic_Amsud_Edital_6.2023.pdf/@@display-file/file</t>
+          <t>Edital nº 05/2024 - ProgramaCAPES/STIC-AMSUD, formato - pdf, 239kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20032024_Edital_2343766_SEI_2342530_Edital_05_2024.pdf/@@display-file/file ; Alteração do Edital nº 05/2024 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 57kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07052024_Edital_2373417_SEI_2372656_Edital_05_2024.pdf/@@display-file/file ; Edital nº 05/2024 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 239kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20032024_Edital_2343766_SEI_2342530_Edital_05_2024.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3642,22 +3638,22 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Edital nº 06/2024 - PDSE - formato, pdf, 133kb</t>
+          <t>Edital nº 06/2023 - ProgramaCAPES/STIC-AMSUD, formato - pdf, 473kb</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/21032024_Edital_2344636_SEI_2343579_Edital_6_2024.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15032023_Edital_1933950_Edital_6_2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Prorrogação do Edital nº 06/2024 - PDSE - formato, pdf, 55kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/10052024_Edital_2376323_SEI_2375557_Edital_6_2024.pdf/@@display-file/file</t>
+          <t>Alteração do Edital nº 06/2023 - Programa CAPES/STIC-AMSUD, formato - pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400119_SEI_2399429_Edital_6_2023___Alteracao_II.pdf/@@display-file/file ; Relação das inscrições do Edital nº 06/2023 - Programa CAPES/STIC-AMSUD, formato - pdf, 571kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/30052023_Lista_Listagem_1984493_Lista_de_inscritos_Stic_Amsud_Edital_6.2023.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3669,22 +3665,22 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Edital nº 07/2023 - ProgramaCAPES/CLIMAT-AMSUD, formato - pdf, 466kb</t>
+          <t>Edital nº 06/2024 - PDSE - formato, pdf, 133kb</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15032023_Edital_1933965_Edital_7_2023_.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/21032024_Edital_2344636_SEI_2343579_Edital_6_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alteração doEdital nº 07/2023 - ProgramaCAPES/CLIMAT-AMSUD, formato - pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400133_SEI_2399445_Edital_07_2023___ALTERACAO_II.pdf/@@display-file/file ; Relação das inscrições do Edital nº 07/2023 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 570kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/30052023_Lista_Listagem_1984693_Lista_de_inscritos_Climat_Amsud_Edital_7.2023.pdf/@@display-file/file</t>
+          <t>Prorrogação do Edital nº 06/2024 - PDSE - formato, pdf, 55kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/10052024_Edital_2376323_SEI_2375557_Edital_6_2024.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3696,22 +3692,22 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Edital nº 08/2023 - CAPES/Cofecub, formato, pdf, 495kb</t>
+          <t>Edital nº 07/2023 - ProgramaCAPES/CLIMAT-AMSUD, formato - pdf, 466kb</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/03042023_Edital_1946708_Edital_8_2022.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15032023_Edital_1933965_Edital_7_2023_.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alteração doEdital nº 08/2023 - CAPES/Cofecub, formato, pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20062024_Edital_2401059_SEI_2399441_Edital_08_2023___ALTERACAO_II.pdf/@@display-file/file</t>
+          <t>Alteração doEdital nº 07/2023 - ProgramaCAPES/CLIMAT-AMSUD, formato - pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400133_SEI_2399445_Edital_07_2023___ALTERACAO_II.pdf/@@display-file/file ; Relação das inscrições do Edital nº 07/2023 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 570kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/30052023_Lista_Listagem_1984693_Lista_de_inscritos_Climat_Amsud_Edital_7.2023.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3723,22 +3719,22 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Edital nº 08/2024 - CAPES/Cofecub, formato, pdf, 213kb</t>
+          <t>Edital nº 08/2023 - CAPES/Cofecub, formato, pdf, 495kb</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/22032024_Edital_2345736_SEI_2343959_Edital_8.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/03042023_Edital_1946708_Edital_8_2022.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alteração do Edital nº 08/2024 - Programa CAPES/Cofecub, formato, pdf, 54kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23122024_Edital_2517712_SEI_2516934_Edital_8_2024.pdf/@@display-file/file ; Prorrogação do Edital nº 08/2024 - CAPES/Cofecub, formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/02072024_Edital_2409554_SEI_2409272_Edital_08_2024___Prorrogacao.pdf/@@display-file/file ; Alteração do Edital nº 08/2024 - CAPES/Cofecub, formato, pdf, 57kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07052024_Edital_2373782_SEI_2372654_Edital_08_2024.pdf/@@display-file/file</t>
+          <t>Alteração doEdital nº 08/2023 - CAPES/Cofecub, formato, pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20062024_Edital_2401059_SEI_2399441_Edital_08_2023___ALTERACAO_II.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3750,20 +3746,24 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Edital nº 10/2022 - PDSE - formato, pdf, 337kb</t>
+          <t>Edital nº 08/2024 - CAPES/Cofecub, formato, pdf, 213kb</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/16022022_Edital10.22PDSE.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/22032024_Edital_2345736_SEI_2343959_Edital_8.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>1</v>
-      </c>
-      <c r="G117" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Alteração do Edital nº 08/2024 - Programa CAPES/Cofecub, formato, pdf, 54kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23122024_Edital_2517712_SEI_2516934_Edital_8_2024.pdf/@@display-file/file ; Prorrogação do Edital nº 08/2024 - CAPES/Cofecub, formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/02072024_Edital_2409554_SEI_2409272_Edital_08_2024___Prorrogacao.pdf/@@display-file/file ; Alteração do Edital nº 08/2024 - CAPES/Cofecub, formato, pdf, 57kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07052024_Edital_2373782_SEI_2372654_Edital_08_2024.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3773,24 +3773,20 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Edital nº 16/2025 - formato, pdf, 360kb</t>
+          <t>Edital nº 10/2022 - PDSE - formato, pdf, 337kb</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11082025_Edital_2654124.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/16022022_Edital10.22PDSE.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>2</v>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>Lista de inscritos no edital nº 16/2025 - formato, pdf, 207kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/29102025_Lista_Listagem_2693783_SEI___23038.003238_2025_21_buffalo.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3800,20 +3796,24 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Edital nº 16/2026 - Programa AURORA — Continuidade da Trajetória de Mães Cientistas</t>
+          <t>Edital nº 16/2025 - formato, pdf, 360kb</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2818271_SEI_2817084_Edital_16_2026__1_.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11082025_Edital_2654124.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>1</v>
-      </c>
-      <c r="G119" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Lista de inscritos no edital nº 16/2025 - formato, pdf, 207kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/29102025_Lista_Listagem_2693783_SEI___23038.003238_2025_21_buffalo.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3823,14 +3823,14 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Edital nº 19/2017 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 315kb</t>
+          <t>Edital nº 16/2026 - Programa AURORA — Continuidade da Trajetória de Mães Cientistas</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/31052017Edital192017PDPI.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2818271_SEI_2817084_Edital_16_2026__1_.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F120" t="n">
@@ -3846,14 +3846,14 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Edital nº 19/2026 - Programa Capes/Universidade em Buffalo (Capes/UB) - Professor Visitante - formato, pdf, 139kb</t>
+          <t>Edital nº 19/2017 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 315kb</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2843097_SEI_2842333_Edital_n__19_2026.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/31052017Edital192017PDPI.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F121" t="n">
@@ -3869,24 +3869,20 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Edital nº 20/2022 -Programa CAPES/STIC-AMSUD, formato, pdf - 286kb</t>
+          <t>Edital nº 19/2026 - Programa Capes/Universidade em Buffalo (Capes/UB) - Professor Visitante - formato, pdf, 139kb</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07042022_Edital_1673688_EDITAL_20_2022_STIC_AMSUD.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2843097_SEI_2842333_Edital_n__19_2026.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>3</v>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>Alteração do Edital nº 20/2022 -Programa CAPES/STIC-AMSUD, formato, pdf - 67kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400177_SEI_2399435_Edital_20_2022___ALTERACAO_I.pdf/@@display-file/file ; Relação das inscrições do Edital nº 20/2022 - Programa CAPES/STIC-AMSUD, formato - pdf, 358kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/06062022_Lista_Listagem_1727082_STIC.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3896,20 +3892,24 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Edital nº 21/2026 - Programa de Desenvolvimento da Pós-Graduação (PDPG) – Parcerias Estratégicas nos Estados VI – Rede de Pesquisa e Desenvolvimento da Região Nordeste, formato, pdf, 177kb</t>
+          <t>Edital nº 20/2022 -Programa CAPES/STIC-AMSUD, formato, pdf - 286kb</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2848691_sei_2847430_edital_n__21_2026.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07042022_Edital_1673688_EDITAL_20_2022_STIC_AMSUD.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>1</v>
-      </c>
-      <c r="G123" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Alteração do Edital nº 20/2022 -Programa CAPES/STIC-AMSUD, formato, pdf - 67kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400177_SEI_2399435_Edital_20_2022___ALTERACAO_I.pdf/@@display-file/file ; Relação das inscrições do Edital nº 20/2022 - Programa CAPES/STIC-AMSUD, formato - pdf, 358kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/06062022_Lista_Listagem_1727082_STIC.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3919,24 +3919,20 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Edital nº 22/2026 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 150kb</t>
+          <t>Edital nº 21/2026 - Programa de Desenvolvimento da Pós-Graduação (PDPG) – Parcerias Estratégicas nos Estados VI – Rede de Pesquisa e Desenvolvimento da Região Nordeste, formato, pdf, 177kb</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/sei_2849220_edital_n__22_2026.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2848691_sei_2847430_edital_n__21_2026.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>2</v>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>Alteração Edital nº 22/2026 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 47,4kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2858430_sei_2857160_edital_22_2026___alteracao.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3946,14 +3942,14 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Edital nº 23/2026 - Programa de Desenvolvimento Acadêmico Indígena (PDAI), formato, pdf, 168kb</t>
+          <t>Edital nº 22/2026 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 150kb</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2851776_sei_2851450_edital_n__23_2026.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/sei_2849220_edital_n__22_2026.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -3961,7 +3957,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alteração Edital nº 23/2026 - Programa de Desenvolvimento Acadêmico Indígena (PDAI), formato, pdf, 102kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2872644_edital_conjunto_23_2026___alteracao.pdf/@@display-file/file</t>
+          <t>Alteração Edital nº 22/2026 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 47,4kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2858430_sei_2857160_edital_22_2026___alteracao.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3973,20 +3969,24 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Edital nº 23/2026 - Programa Nacional de Formação de Professores da Educação Básica (PARFOR), formato, pdf, 168kb</t>
+          <t>Edital nº 23/2026 - Programa de Desenvolvimento Acadêmico Indígena (PDAI), formato, pdf, 168kb</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2855421_sei_2854365_edital_n__23_2026.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2851776_sei_2851450_edital_n__23_2026.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>1</v>
-      </c>
-      <c r="G126" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Alteração Edital nº 23/2026 - Programa de Desenvolvimento Acadêmico Indígena (PDAI), formato, pdf, 102kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2872644_edital_conjunto_23_2026___alteracao.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3996,24 +3996,20 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Edital nº 25/2022 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 353kb</t>
+          <t>Edital nº 23/2026 - Programa Nacional de Formação de Professores da Educação Básica (PARFOR), formato, pdf, 168kb</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/04052022_Edital_1698011_SEI_CAPES___1696119___Edital_25.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2855421_sei_2854365_edital_n__23_2026.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>3</v>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>Alteração do edital nº 25/2022 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 67kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400217_SEI_2399433_Edital_25_2022___ALTERACAO_I.pdf/@@display-file/file ; Relação das inscrições do Edital nº 25/2022 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 353kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/06062022_Lista_Listagem_1727108_Climat.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4023,14 +4019,14 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Edital nº 26/2024 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE) - Retificação - formato, pdf, 48kb</t>
+          <t>Edital nº 25/2022 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 353kb</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/14102024_Edital_2477735_SEI_2477608_Edital_N__26_2024.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/04052022_Edital_1698011_SEI_CAPES___1696119___Edital_25.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -4038,7 +4034,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alteração do Edital nº 26/2024 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE), formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/13032025_Edital_2560841_SEI_2559847_Edital_26_2024___ALTERACAO.pdf/@@display-file/file ; Edital nº 26/2024 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 135kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/08102024_Edital_2474014_SEI_2472849_Edital_26_2024.pdf/@@display-file/file</t>
+          <t>Alteração do edital nº 25/2022 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 67kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400217_SEI_2399433_Edital_25_2022___ALTERACAO_I.pdf/@@display-file/file ; Relação das inscrições do Edital nº 25/2022 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 353kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/06062022_Lista_Listagem_1727108_Climat.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4050,22 +4046,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Edital nº 27/2024 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 157kb</t>
+          <t>Edital nº 26/2024 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE) - Retificação - formato, pdf, 48kb</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/05112024_Edital_2490387_SEI_2489251_Edital_27_2024.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/14102024_Edital_2477735_SEI_2477608_Edital_N__26_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alteração do Edital 27/2024 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa no EUA - PDPI - formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/02122024_Edital_2505290_SEI_2504109_Edital_27_2024__.pdf/@@display-file/file</t>
+          <t>Alteração do Edital nº 26/2024 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE), formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/13032025_Edital_2560841_SEI_2559847_Edital_26_2024___ALTERACAO.pdf/@@display-file/file ; Edital nº 26/2024 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 135kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/08102024_Edital_2474014_SEI_2472849_Edital_26_2024.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4077,22 +4073,22 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Edital nº 30/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 110kb</t>
+          <t>Edital nº 27/2024 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 157kb</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/14022020_Edital_1145537_Edital_SITE.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/05112024_Edital_2490387_SEI_2489251_Edital_27_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Reabertura e alteração do Edital nº 30/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 222kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/28042022_Edital_1691552_SEI_CAPES___1685746___Edital_30_2019.pdf/@@display-file/file ; Suspensão do Edital nº 30/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 111kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_1326070_Edital_Suspensao_site.pdf/@@display-file/file</t>
+          <t>Alteração do Edital 27/2024 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa no EUA - PDPI - formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/02122024_Edital_2505290_SEI_2504109_Edital_27_2024__.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4104,14 +4100,14 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Edital nº 30/2023 - PDSE - formato, pdf, 125kb</t>
+          <t>Edital nº 30/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 110kb</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/06112023_Edital_2263037_SEI_2261948_Edital_30_2023.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/14022020_Edital_1145537_Edital_SITE.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -4119,7 +4115,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Prorrogação do Edital nº 30/2023 - PDSE - formato, pdf, 136kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11012024_Edital_2306448_SEI_CAPES___2305414___Edital_30_2023___Prorrogacao.pdf/@@display-file/file ; Alteração do Edital nº 30/2023 - PDSE - formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/18122023_Edital_2293491_SEI_2293429_Edital_30_2023_Alteracao.pdf/@@display-file/file</t>
+          <t>Reabertura e alteração do Edital nº 30/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 222kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/28042022_Edital_1691552_SEI_CAPES___1685746___Edital_30_2019.pdf/@@display-file/file ; Suspensão do Edital nº 30/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 111kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_1326070_Edital_Suspensao_site.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4131,14 +4127,14 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Edital Nº 32/2022 - CAPES/Cofecub, formato, pdf, 225kb</t>
+          <t>Edital nº 30/2023 - PDSE - formato, pdf, 125kb</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29062022_EDITAL32_2022_COFECUB.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/06112023_Edital_2263037_SEI_2261948_Edital_30_2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -4146,7 +4142,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alteração do Edital Nº 32/2022 - CAPES/Cofecub, formato, pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400143_SEI_2399437_Edital_32_2022___ALTERACAO_III.pdf/@@display-file/file ; Relação de inscritos do Edital Nº 32/2022 - CAPES/Cofecub, formato, pdf, 65kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/25082022_Lista_Listagem_1783309_EDITAL_32_2022___CAPES_COFECUB_Relacao_de_Inscricoes.pdf/@@display-file/file</t>
+          <t>Prorrogação do Edital nº 30/2023 - PDSE - formato, pdf, 136kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11012024_Edital_2306448_SEI_CAPES___2305414___Edital_30_2023___Prorrogacao.pdf/@@display-file/file ; Alteração do Edital nº 30/2023 - PDSE - formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/18122023_Edital_2293491_SEI_2293429_Edital_30_2023_Alteracao.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4158,22 +4154,22 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Edital nº 32/2023 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 139kb</t>
+          <t>Edital Nº 32/2022 - CAPES/Cofecub, formato, pdf, 225kb</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/16112023_Edital_2271416_SEI_2268914_Edital_32_2023.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29062022_EDITAL32_2022_COFECUB.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alteração do Edital nº 32/2023 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 57kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09022024_SEI_2321458_Edital_N__32_2023___ALTERACAOPDPI.pdf/@@display-file/file</t>
+          <t>Alteração do Edital Nº 32/2022 - CAPES/Cofecub, formato, pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400143_SEI_2399437_Edital_32_2022___ALTERACAO_III.pdf/@@display-file/file ; Relação de inscritos do Edital Nº 32/2022 - CAPES/Cofecub, formato, pdf, 65kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/25082022_Lista_Listagem_1783309_EDITAL_32_2022___CAPES_COFECUB_Relacao_de_Inscricoes.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4185,20 +4181,24 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Edital nº 35/2011 - Certificação em Língua Inglesa - pdf, 615kb</t>
+          <t>Edital nº 32/2023 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 139kb</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_035_CertificacaoEUAprofLingIngl_Fulbright.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/16112023_Edital_2271416_SEI_2268914_Edital_32_2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>1</v>
-      </c>
-      <c r="G134" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Alteração do Edital nº 32/2023 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 57kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09022024_SEI_2321458_Edital_N__32_2023___ALTERACAOPDPI.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4208,14 +4208,14 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Edital nº 4/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 270kb</t>
+          <t>Edital nº 35/2011 - Certificação em Língua Inglesa - pdf, 615kb</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/08022019Edital4.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_035_CertificacaoEUAprofLingIngl_Fulbright.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -4231,24 +4231,20 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Edital nº 44/2012 - Programa de Aperfeiçoamento para Professores de Língua Inglesa nos Eua, pdf, 272kb</t>
+          <t>Edital nº 4/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 270kb</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_0442012_ProfLingIngl_EUA.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/08022019Edital4.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>3</v>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>Edital nº 44/2012 - Retificado - pdf, 528kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_0442012_ProfLIngRetif.pdf/@@display-file/file ; Retificação do Edital nº 44/2012 - pdf, 46kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/RetificacaoEdital442012_ProfLingInglEUA_01out12.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4258,22 +4254,22 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Edital nº 44/2022 - PDSE - formato, pdf, 337kb</t>
+          <t>Edital nº 44/2012 - Programa de Aperfeiçoamento para Professores de Língua Inglesa nos Eua, pdf, 272kb</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/22122022_Edital_1882688_Edital_44_2022.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_0442012_ProfLingIngl_EUA.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alteração do Edital nº 44/2022 - PDSE - formato, pdf, 146kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23052023_Edital_1981709_Edital_44_2023.pdf/@@display-file/file</t>
+          <t>Edital nº 44/2012 - Retificado - pdf, 528kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_0442012_ProfLIngRetif.pdf/@@display-file/file ; Retificação do Edital nº 44/2012 - pdf, 46kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/RetificacaoEdital442012_ProfLingInglEUA_01out12.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4285,20 +4281,24 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Edital nº 52/2010 - Certificação em Língua Inglesa, pdf, 60kbDF</t>
+          <t>Edital nº 44/2022 - PDSE - formato, pdf, 337kb</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_52_Certificacao_LinguaInglesa2010.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/22122022_Edital_1882688_Edital_44_2022.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>1</v>
-      </c>
-      <c r="G138" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Alteração do Edital nº 44/2022 - PDSE - formato, pdf, 146kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23052023_Edital_1981709_Edital_44_2023.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4308,24 +4308,20 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Edital Nº09/2026 - Programa CAPES/BRAFITEC, formato, pdf, 209kb</t>
+          <t>Edital nº 52/2010 - Certificação em Língua Inglesa, pdf, 60kbDF</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2800035_SEI_2799041_Edital_9__de_2026.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_52_Certificacao_LinguaInglesa2010.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>2</v>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>Edital n° 9/2026 - Lista de Inscritos, formato, pdf, 398kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/lista_listagem_2864548_sei_2863010_edital_minuta__.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4335,14 +4331,14 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Lista de inscritos do Edital Conjunto nº 01/2024 - Programa Caminhos Amefricanos, formato, pdf, 407kb</t>
+          <t>Edital Nº09/2026 - Programa CAPES/BRAFITEC, formato, pdf, 209kb</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15052024_Lista_Listagem_2374115_Inscritos_MIR.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2800035_SEI_2799041_Edital_9__de_2026.pdf</t>
         </is>
       </c>
       <c r="F140" t="n">
@@ -4350,7 +4346,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alteração do Edital Conjunto nº 01/2024 - Programa Caminhos Amefricanos, formato, pdf, 63kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29042024_Edital_2368101_SEI_2365347_Edital_Conjunto_n__1_CAPES_MIR.pdf/@@display-file/file</t>
+          <t>Edital n° 9/2026 - Lista de Inscritos, formato, pdf, 398kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/lista_listagem_2864548_sei_2863010_edital_minuta__.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4362,20 +4358,24 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Lista de inscritos do Edital nº 05/2024 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 46kb</t>
+          <t>Lista de inscritos do Edital Conjunto nº 01/2024 - Programa Caminhos Amefricanos, formato, pdf, 407kb</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/10062024_Lista_Listagem_2390159_Lista_de_Inscritos_3.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15052024_Lista_Listagem_2374115_Inscritos_MIR.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>1</v>
-      </c>
-      <c r="G141" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Alteração do Edital Conjunto nº 01/2024 - Programa Caminhos Amefricanos, formato, pdf, 63kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29042024_Edital_2368101_SEI_2365347_Edital_Conjunto_n__1_CAPES_MIR.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4385,14 +4385,14 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Lista de inscritos doEdital nº 8/202 - CAPES/COFECUB, formato, pdf, 581kb</t>
+          <t>Lista de inscritos do Edital nº 05/2024 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 46kb</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/14062023_Lista_Listagem_1990268_Inscricoes_cofecub_2023.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/10062024_Lista_Listagem_2390159_Lista_de_Inscritos_3.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F142" t="n">
@@ -4408,24 +4408,20 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Lista de inscrições - Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 393kb</t>
+          <t>Lista de inscritos doEdital nº 8/202 - CAPES/COFECUB, formato, pdf, 581kb</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Lista_de_Inscricoes_Homologadas_PDSE___2020_REVISADA.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/14062023_Lista_Listagem_1990268_Inscricoes_cofecub_2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>4</v>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>Lista de candidaturas - Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 417kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/documentos/diretoria-de-relacoes-internacionais/pdse/Lista_Listagem_1439062_Lista_de_Inscricoes_Homologadas_PDSE___2020.pdf/@@display-file/file ; Retificação do Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 244kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/EDITAL192020_PDSERETIFICAO.pdf/@@display-file/file ; Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE)- formato, pdf, 236kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09102020_edital-19-pdse.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4435,14 +4431,14 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Lista de inscrições do Edital nº 17/2025 - Primeira chamada Programa Institucional de Doutorado Sanduíche no Exterior (PDSE) - formato, pdf, 8,8mb</t>
+          <t>Lista de inscrições - Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 393kb</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/29102025_Lista_Listagem_2708089_PDSE.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Lista_de_Inscricoes_Homologadas_PDSE___2020_REVISADA.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F144" t="n">
@@ -4450,7 +4446,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lista de inscrições do Edital nº 17/2025 - Segunda chamada Programa Institucional de Doutorado Sanduíche no Exterior (PDSE) - formato, pdf, 1,4mb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/27042026_Lista_Listagem_2808119_Lista_de_inscricoes_homologadas_do_Edital_172025___PDSE___segunda_chamada___formato_pdf__2_.pdf/@@display-file/file ; Alteração do Edital nº 17/2025 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE), formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/08102025_Edital_2696973_SEI_2695934_Edital_17_2025__.pdf/@@display-file/file ; Edital nº 17/2025 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 142kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/21082025_Edital_2662823_SEI_2661209_Edital_n__17_2025.pdf/@@display-file/file</t>
+          <t>Lista de candidaturas - Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 417kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/documentos/diretoria-de-relacoes-internacionais/pdse/Lista_Listagem_1439062_Lista_de_Inscricoes_Homologadas_PDSE___2020.pdf/@@display-file/file ; Retificação do Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 244kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/EDITAL192020_PDSERETIFICAO.pdf/@@display-file/file ; Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE)- formato, pdf, 236kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09102020_edital-19-pdse.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4462,14 +4458,14 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Lista de instituições e cursos pré-aprovados para a 3ª fase do Edital nº 08/2022 - Parfor - formato, pdf, 715kb</t>
+          <t>Lista de inscrições do Edital nº 17/2025 - Primeira chamada Programa Institucional de Doutorado Sanduíche no Exterior (PDSE) - formato, pdf, 8,8mb</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/06052022_Relacao_1700579_LISTA_DE_IES_E_CURSOS_APROVADOS_PARA_A_3__ETAPA_DO_EDITAL_CAPES_N__08.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/29102025_Lista_Listagem_2708089_PDSE.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F145" t="n">
@@ -4477,7 +4473,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alteraçãodo Edital nº 08/2022 - Parfor - formato, xls, 119kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20122022_Edital_1880841_Edital_8_2022___PARFOR.pdf/@@display-file/file ; Alteração do Edital nº 08/2022 - Parfor - formato, pdf, 128kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09062022_Edital_1729649_EDITAL___8_2022.pdf/@@display-file/file ; Edital nº 08/2022 - Parfor - formato, pdf, 203kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07022022_Edital_1629612_SEI_CAPES___1628279___Edital_8.pdf/@@display-file/file</t>
+          <t>Lista de inscrições do Edital nº 17/2025 - Segunda chamada Programa Institucional de Doutorado Sanduíche no Exterior (PDSE) - formato, pdf, 1,4mb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/27042026_Lista_Listagem_2808119_Lista_de_inscricoes_homologadas_do_Edital_172025___PDSE___segunda_chamada___formato_pdf__2_.pdf/@@display-file/file ; Alteração do Edital nº 17/2025 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE), formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/08102025_Edital_2696973_SEI_2695934_Edital_17_2025__.pdf/@@display-file/file ; Edital nº 17/2025 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 142kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/21082025_Edital_2662823_SEI_2661209_Edital_n__17_2025.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4489,14 +4485,14 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Lista e inscritos do Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 520kb</t>
+          <t>Lista de instituições e cursos pré-aprovados para a 3ª fase do Edital nº 08/2022 - Parfor - formato, pdf, 715kb</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/20022024_Lista_Listagem_2324280_SEI_2323841_Inscritos_MIR.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/06052022_Relacao_1700579_LISTA_DE_IES_E_CURSOS_APROVADOS_PARA_A_3__ETAPA_DO_EDITAL_CAPES_N__08.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F146" t="n">
@@ -4504,7 +4500,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alteração do Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 54kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/12062024_Edital_2395239_SEI_2389783_Edital_34_2023.pdf/@@display-file/file ; Prorrogação do Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 54kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/28122023_Edital_2301024_SEI_2300438_Edital_Conjunto_n__34_2023_Prorrogacao.pdf/@@display-file/file ; Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 129kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/04122024_Edital_2282364_SEI_2279471_Edital_Conjunto_n__34_2023.pdf/@@display-file/file</t>
+          <t>Alteraçãodo Edital nº 08/2022 - Parfor - formato, xls, 119kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20122022_Edital_1880841_Edital_8_2022___PARFOR.pdf/@@display-file/file ; Alteração do Edital nº 08/2022 - Parfor - formato, pdf, 128kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09062022_Edital_1729649_EDITAL___8_2022.pdf/@@display-file/file ; Edital nº 08/2022 - Parfor - formato, pdf, 203kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07022022_Edital_1629612_SEI_CAPES___1628279___Edital_8.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4516,22 +4512,22 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Lista final de inscritos no Edital n° 33/2022 - Brafitec, formato, pdf, 372kb</t>
+          <t>Lista e inscritos do Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 520kb</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/22092022_Lista_Listagem_1808291_Lista_inscritos_Brafitec_Edital_33_22.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/20022024_Lista_Listagem_2324280_SEI_2323841_Inscritos_MIR.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alteração do Edital n° 33/2022 - Brafitec, formato, pdf, 193kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23022023_Edital_1920292_Edital_33_22.pdf/@@display-file/file ; Edital n° 33/2022 - Brafitec, formato, pdf, 428kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29062022_EDITAL33_2022_BRAFITEC.pdf/@@display-file/file</t>
+          <t>Alteração do Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 54kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/12062024_Edital_2395239_SEI_2389783_Edital_34_2023.pdf/@@display-file/file ; Prorrogação do Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 54kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/28122023_Edital_2301024_SEI_2300438_Edital_Conjunto_n__34_2023_Prorrogacao.pdf/@@display-file/file ; Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 129kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/04122024_Edital_2282364_SEI_2279471_Edital_Conjunto_n__34_2023.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4543,37 +4539,41 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Prorrogação do Edital nº 01/2024 - Programa Caminhos Amefricanos, formato, pdf, 69kb</t>
+          <t>Lista final de inscritos no Edital n° 33/2022 - Brafitec, formato, pdf, 372kb</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/30082024_Edital_2450719_SEI_2446271_Edital_Conjunto_1_2024.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/22092022_Lista_Listagem_1808291_Lista_inscritos_Brafitec_Edital_33_22.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1</v>
-      </c>
-      <c r="G148" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Alteração do Edital n° 33/2022 - Brafitec, formato, pdf, 193kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23022023_Edital_1920292_Edital_33_22.pdf/@@display-file/file ; Edital n° 33/2022 - Brafitec, formato, pdf, 428kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29062022_EDITAL33_2022_BRAFITEC.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>SETEC</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Chamada (documento Nº 6991254) para seleção de unidades da Rede Federal de Educação Profissional e Tecnológica e das redes públicas estaduais de Educação Profissional e Tecnológica, interessadas em receber apoio técnico para a implementação de programas de aprendizagem profissional articulados a cursos técnicos ou de qualificação profissional com componentes curriculares relacionados à sustentabilidade</t>
+          <t>Prorrogação do Edital nº 01/2024 - Programa Caminhos Amefricanos, formato, pdf, 69kb</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2026/SEI_6991254_chamada.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/30082024_Edital_2450719_SEI_2446271_Edital_Conjunto_1_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -4589,14 +4589,14 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Chamada Pública com o objetivo de identificar, avaliar, cadastrar e disponibilizar metodologias, ferramentas e estudos sobre o mapeamento de demandas por Educação Profissional Técnica de Nível Médio, visando aprimorar a definição de ofertas de Educação Profissional Técnica de Nível Médio, no âmbito do Programa Juros por Educação.</t>
+          <t>Chamada (documento Nº 6991254) para seleção de unidades da Rede Federal de Educação Profissional e Tecnológica e das redes públicas estaduais de Educação Profissional e Tecnológica, interessadas em receber apoio técnico para a implementação de programas de aprendizagem profissional articulados a cursos técnicos ou de qualificação profissional com componentes curriculares relacionados à sustentabilidade</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/SEI_6268868_Resultado_de_Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2026/SEI_6991254_chamada.pdf</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4612,14 +4612,14 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Chamada Pública de Adesão das Instituições da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT), com objetivo de capacitação técnica para submissão de propostas em futuros editais de unidades Embrapii.</t>
+          <t>Chamada Pública com o objetivo de identificar, avaliar, cadastrar e disponibilizar metodologias, ferramentas e estudos sobre o mapeamento de demandas por Educação Profissional Técnica de Nível Médio, visando aprimorar a definição de ofertas de Educação Profissional Técnica de Nível Médio, no âmbito do Programa Juros por Educação.</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/edital-2025/SEI_MEC5650163ResultadodeEdital_.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/SEI_6268868_Resultado_de_Edital.pdf</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -4635,14 +4635,14 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Chamada Pública de Adesão à linha de fomento Qualifica Mais EnergIFE</t>
+          <t>Chamada Pública de Adesão das Instituições da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT), com objetivo de capacitação técnica para submissão de propostas em futuros editais de unidades Embrapii.</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/chamadapublica.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/edital-2025/SEI_MEC5650163ResultadodeEdital_.pdf</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4658,14 +4658,14 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 01/2017 - Trata-se de chamada pública para seleção de servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) para capacitação em Gestão da Inovação.</t>
+          <t>Chamada Pública de Adesão à linha de fomento Qualifica Mais EnergIFE</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/extrato_chamada_dou_cp_01_2017.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/chamadapublica.pdf</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -4681,14 +4681,14 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 01/2018 - Trata-se da chamada pública para seleção de propostas e servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) em efetivo exercício, para participarem da capacitação em Gestão da Inovação (GI - CSIRO).</t>
+          <t>Chamada Pública nº 01/2017 - Trata-se de chamada pública para seleção de servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) para capacitação em Gestão da Inovação.</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/20181030Edital012018ChamadaPblicaGICSIRO.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/extrato_chamada_dou_cp_01_2017.pdf</t>
         </is>
       </c>
       <c r="F154" t="n">
@@ -4704,14 +4704,14 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 02/2017 - Trata-se de chamada pública para concurso sobre educação profissional da Secretaria de Educação Profissional e Tecnológica (Setec/MEC) em parceria com a Comunidade dos Países de Língua Portuguesa (CPLP).</t>
+          <t>Chamada Pública nº 01/2018 - Trata-se da chamada pública para seleção de propostas e servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) em efetivo exercício, para participarem da capacitação em Gestão da Inovação (GI - CSIRO).</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/edital_concurso_cplp_2017.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/20181030Edital012018ChamadaPblicaGICSIRO.pdf</t>
         </is>
       </c>
       <c r="F155" t="n">
@@ -4727,14 +4727,14 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 02/2018 - Trata-se da chamada pública para seleção de servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) para a capacitação Brasileiros Formando Formadores (BraFF).</t>
+          <t>Chamada Pública nº 02/2017 - Trata-se de chamada pública para concurso sobre educação profissional da Secretaria de Educação Profissional e Tecnológica (Setec/MEC) em parceria com a Comunidade dos Países de Língua Portuguesa (CPLP).</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/Edital_02_2018_BRAFF.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/edital_concurso_cplp_2017.pdf</t>
         </is>
       </c>
       <c r="F156" t="n">
@@ -4750,14 +4750,14 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 38/2018 - Trata do processo de seleção de propostas para credenciamento de instituições da Rede Federal, Faculdades de Tecnologia do Estado de São Paulo (Fatecs) e do Instituto Tecnológico de Aeronáutica (ITA) para atuação como Núcleo de Línguas (NucLi-IsF) no âmbito do Programa Idiomas sem Fronteiras (IsF).</t>
+          <t>Chamada Pública nº 02/2018 - Trata-se da chamada pública para seleção de servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) para a capacitação Brasileiros Formando Formadores (BraFF).</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/Editaln382018ChamadaPblicaparacredenciamentodeinstituiesdaRFEPCTdasFatecsedoITA.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/Edital_02_2018_BRAFF.pdf</t>
         </is>
       </c>
       <c r="F157" t="n">
@@ -4773,14 +4773,14 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 79/2016 - Trata-se de chamada pública para apresentação de propostas por instituição de educação profissional e tecnológica para a oferta de cursos de formação inicial e continuada ou de qualificação profissional e cursos técnicos de nível médio, presenciais ou à distância, sem transferência de recursos, no âmbito do PRONATEC, denominada “PROPOSTAS VOLUNTÁRIAS - PRONATEC”</t>
+          <t>Chamada Pública nº 38/2018 - Trata do processo de seleção de propostas para credenciamento de instituições da Rede Federal, Faculdades de Tecnologia do Estado de São Paulo (Fatecs) e do Instituto Tecnológico de Aeronáutica (ITA) para atuação como Núcleo de Línguas (NucLi-IsF) no âmbito do Programa Idiomas sem Fronteiras (IsF).</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/extrato_edital_79_2016_setec.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/Editaln382018ChamadaPblicaparacredenciamentodeinstituiesdaRFEPCTdasFatecsedoITA.pdf</t>
         </is>
       </c>
       <c r="F158" t="n">
@@ -4796,14 +4796,14 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Chamada Pública que estabelece os procedimentos para a autorização de oferta de cursos técnicos de nível médio por Instituições Privadas de Ensino Superior (IPES) para fins de habilitação ao Programa Juros por Educação, no âmbito do Programa de Pleno Pagamento de Dívidas dos Estados (Propag).</t>
+          <t>Chamada Pública nº 79/2016 - Trata-se de chamada pública para apresentação de propostas por instituição de educação profissional e tecnológica para a oferta de cursos de formação inicial e continuada ou de qualificação profissional e cursos técnicos de nível médio, presenciais ou à distância, sem transferência de recursos, no âmbito do PRONATEC, denominada “PROPOSTAS VOLUNTÁRIAS - PRONATEC”</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/FAQEdital6.2025.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/extrato_edital_79_2016_setec.pdf</t>
         </is>
       </c>
       <c r="F159" t="n">
@@ -4819,14 +4819,14 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Chamamento Público para credenciamento de profissionais no Banco de Especialistas para atuar no Projeto Assistec Inova, junto ao Ministério da Educação, no âmbito da Secretaria de Educação Profissional e Tecnológica.</t>
+          <t>Chamada Pública que estabelece os procedimentos para a autorização de oferta de cursos técnicos de nível médio por Instituições Privadas de Ensino Superior (IPES) para fins de habilitação ao Programa Juros por Educação, no âmbito do Programa de Pleno Pagamento de Dívidas dos Estados (Propag).</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/SEI_23000.035944_2024_89.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/FAQEdital6.2025.pdf</t>
         </is>
       </c>
       <c r="F160" t="n">
@@ -4842,14 +4842,14 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Edital 1/2026 - Chamada Pública de Adesão dos Institutos Federais de Educação, Ciência e Tecnologia, do Centro Federal de Educação Tecnológica Celso Suckow da Fonseca, do Centro Federal de Educação Tecnológica de Minas Gerais e do Colégio Pedro II, com objetivo de capacitação técnica para submissão de propostas em futuros editais de Unidades Embrapii.</t>
+          <t>Chamamento Público para credenciamento de profissionais no Banco de Especialistas para atuar no Projeto Assistec Inova, junto ao Ministério da Educação, no âmbito da Secretaria de Educação Profissional e Tecnológica.</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/edital12026.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/SEI_23000.035944_2024_89.pdf</t>
         </is>
       </c>
       <c r="F161" t="n">
@@ -4865,14 +4865,14 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Edital 84/2021 - Seleção de Projetos para desenvolvimento dos Ambientes de Promotores de Inovação na Rede Federal</t>
+          <t>Edital 1/2026 - Chamada Pública de Adesão dos Institutos Federais de Educação, Ciência e Tecnologia, do Centro Federal de Educação Tecnológica Celso Suckow da Fonseca, do Centro Federal de Educação Tecnológica de Minas Gerais e do Colégio Pedro II, com objetivo de capacitação técnica para submissão de propostas em futuros editais de Unidades Embrapii.</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/editais/2022/ResultadoetapaI.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/edital12026.pdf</t>
         </is>
       </c>
       <c r="F162" t="n">
@@ -4888,14 +4888,14 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Edital nº 01/2017 - APRESENTAÇÃO DE PROPOSTAS PARA A OFERTA DE VAGAS GRATUITAS EM CURSOS TÉCNICOS NA FORMA CONCOMITANTE, NO ÂMBITO DO PRONATEC/MEDIOTEC – 2º/2017 - A Secretária de Educação Profissional e Tecnológica do Ministério da Educação, no uso da atribuição que lhe confere o art. 13, Anexo I, do Decreto n° 7.690, de 02 de março de 2012, e considerando o disposto na Lei nº 12.513, de 26 de outubro de 2011, a Portaria nº 817, de 13 de agosto de 2015, a Portaria nº160, de 05 de março de 2013, alterada pela Portaria nº 701, de 13 de agosto de 2014, TORNA PÚBLICO os procedimentos e o cronograma para a apresentação de propostas visando a oferta de vagas gratuitas em cursos técnicos na forma concomitante e na modalidade presencial, no âmbito do Programa Nacional de Acesso ao Ensino Técnico e Emprego - PRONATEC, por meio da ação MEDIOTEC, para ingresso no segundo semestre de 2017.</t>
+          <t>Edital 84/2021 - Seleção de Projetos para desenvolvimento dos Ambientes de Promotores de Inovação na Rede Federal</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/edital_01_mediotec_2017.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/editais/2022/ResultadoetapaI.pdf</t>
         </is>
       </c>
       <c r="F163" t="n">
@@ -4911,14 +4911,14 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Edital nº 08/2024 - Chamamento Público visando à seleção de autores(as) para elaboração de capítulos de obra a ser publicada cuja temática central é a gestão de Núcleos de Inovação Tecnológica (NITs) e/ou de Agências de Inovação da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) Divulgação das Inscrições Homologadas</t>
+          <t>Edital nº 01/2017 - APRESENTAÇÃO DE PROPOSTAS PARA A OFERTA DE VAGAS GRATUITAS EM CURSOS TÉCNICOS NA FORMA CONCOMITANTE, NO ÂMBITO DO PRONATEC/MEDIOTEC – 2º/2017 - A Secretária de Educação Profissional e Tecnológica do Ministério da Educação, no uso da atribuição que lhe confere o art. 13, Anexo I, do Decreto n° 7.690, de 02 de março de 2012, e considerando o disposto na Lei nº 12.513, de 26 de outubro de 2011, a Portaria nº 817, de 13 de agosto de 2015, a Portaria nº160, de 05 de março de 2013, alterada pela Portaria nº 701, de 13 de agosto de 2014, TORNA PÚBLICO os procedimentos e o cronograma para a apresentação de propostas visando a oferta de vagas gratuitas em cursos técnicos na forma concomitante e na modalidade presencial, no âmbito do Programa Nacional de Acesso ao Ensino Técnico e Emprego - PRONATEC, por meio da ação MEDIOTEC, para ingresso no segundo semestre de 2017.</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/436.SEI_MEC5030251Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/edital_01_mediotec_2017.pdf</t>
         </is>
       </c>
       <c r="F164" t="n">
@@ -4934,14 +4934,14 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Edital nº 1/2023 - Seleção de proposta de selo comemorativo, em alusão aos 15 anos dos Institutos Federais.</t>
+          <t>Edital nº 08/2024 - Chamamento Público visando à seleção de autores(as) para elaboração de capítulos de obra a ser publicada cuja temática central é a gestão de Núcleos de Inovação Tecnológica (NITs) e/ou de Agências de Inovação da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) Divulgação das Inscrições Homologadas</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC4094376Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/436.SEI_MEC5030251Edital.pdf</t>
         </is>
       </c>
       <c r="F165" t="n">
@@ -4957,14 +4957,14 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Edital nº 100/2022 - Chamamento Público para a seleção de propostas para o Desafio Soutec</t>
+          <t>Edital nº 1/2023 - Seleção de proposta de selo comemorativo, em alusão aos 15 anos dos Institutos Federais.</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/secretarias/secretaria-de-educacao-profissional/editais-2022/SEI_MEC3570188Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC4094376Edital.pdf</t>
         </is>
       </c>
       <c r="F166" t="n">
@@ -4980,14 +4980,14 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Edital nº 109/2022 - Chamamento Público - Seleção de projetos voltados à promoção do empreendedorismo inovador, com foco na Economia 4.0, associados ao ensino, à pesquisa e à extensão, destinado às instituições integrantes da Rede Federal de Educação Profissional, Científica e Tecnológica</t>
+          <t>Edital nº 100/2022 - Chamamento Público para a seleção de propostas para o Desafio Soutec</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital109.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/secretarias/secretaria-de-educacao-profissional/editais-2022/SEI_MEC3570188Edital.pdf</t>
         </is>
       </c>
       <c r="F167" t="n">
@@ -5003,14 +5003,14 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Edital nº 11/2024 - Chamamento Público para a seleção de projetos aptos a integrarem a 4ª Semana Nacional de Educação Profissional e Tecnológica Retificação do</t>
+          <t>Edital nº 109/2022 - Chamamento Público - Seleção de projetos voltados à promoção do empreendedorismo inovador, com foco na Economia 4.0, associados ao ensino, à pesquisa e à extensão, destinado às instituições integrantes da Rede Federal de Educação Profissional, Científica e Tecnológica</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-2024-1/Edital_11.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital109.pdf</t>
         </is>
       </c>
       <c r="F168" t="n">
@@ -5026,14 +5026,14 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Edital nº 15/2023 - Chamada Pública para o Workshop para elaboração de Itinerários Formativos em economia circular na Educação Profissional e Tecnológica</t>
+          <t>Edital nº 11/2024 - Chamamento Público para a seleção de projetos aptos a integrarem a 4ª Semana Nacional de Educação Profissional e Tecnológica Retificação do</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/SEI_MEC3884064Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-2024-1/Edital_11.pdf</t>
         </is>
       </c>
       <c r="F169" t="n">
@@ -5049,14 +5049,14 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Edital nº 2/2020 - IFES, de chamada pública para a seleção de projetos voltados à implementação das Oficinas 4.0, aberto às autarquias da Rede Federal.</t>
+          <t>Edital nº 15/2023 - Chamada Pública para o Workshop para elaboração de Itinerários Formativos em economia circular na Educação Profissional e Tecnológica</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>https://www.ifes.edu.br/chamadas-publicas/19329-chamada-publica-2-2020-apoio-a-implementacao-de-oficinas-4-0</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/SEI_MEC3884064Edital.pdf</t>
         </is>
       </c>
       <c r="F170" t="n">
@@ -5072,14 +5072,14 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Edital nº 20/2021 – Seleção de servidores para atuação em Projetos de Colaboração Técnica junto ao Ministério da Educação.</t>
+          <t>Edital nº 2/2020 - IFES, de chamada pública para a seleção de projetos voltados à implementação das Oficinas 4.0, aberto às autarquias da Rede Federal.</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/SEI_MEC2573324Edital.pdf</t>
+          <t>https://www.ifes.edu.br/chamadas-publicas/19329-chamada-publica-2-2020-apoio-a-implementacao-de-oficinas-4-0</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -5095,14 +5095,14 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Edital nº 25/2023 - Chamada Pública destinada a selecionar equipes da Rede Federal de Educação Profissional, Científica e Tecnológica (EPCT) para participação no projeto de formação em criatividade, inovação e prototipagem do mercosul (Hackathon Mercosul). Retificação do Edital</t>
+          <t>Edital nº 20/2021 – Seleção de servidores para atuação em Projetos de Colaboração Técnica junto ao Ministério da Educação.</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/SEI_MEC3913111Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/SEI_MEC2573324Edital.pdf</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -5118,14 +5118,14 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Edital nº 26 versão consolidada</t>
+          <t>Edital nº 25/2023 - Chamada Pública destinada a selecionar equipes da Rede Federal de Educação Profissional, Científica e Tecnológica (EPCT) para participação no projeto de formação em criatividade, inovação e prototipagem do mercosul (Hackathon Mercosul). Retificação do Edital</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC3980995Documento.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/SEI_MEC3913111Edital.pdf</t>
         </is>
       </c>
       <c r="F173" t="n">
@@ -5141,14 +5141,14 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Edital nº 3/2021 – Chamada Pública para seleção de projetos de iniciação tecnológica com foco na Economia 4.0. Acesse o edital .</t>
+          <t>Edital nº 26 versão consolidada</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://www.ifes.edu.br/chamadas-publicas/19351-chamada-publica-3-2020-projetos-iniciacao-tecnologica-economia-4-0</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC3980995Documento.pdf</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -5164,24 +5164,20 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Edital nº 35/2020 - Chamada Pública - que tem como objetivo selecionar projetos voltados à criação de Laboratórios IFMaker junto aos Institutos Federais de Educação, Ciência e Tecnologia; Centros Federais de Educação Tecnológica Celso Suckow da Fonseca – Cefet-RJ e de Minas Gerais – Cefet-MG e o Colégio Pedro II, conforme especificado no Despacho SEI nº 2064854</t>
+          <t>Edital nº 3/2021 – Chamada Pública para seleção de projetos de iniciação tecnológica com foco na Economia 4.0. Acesse o edital .</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2020/SEI_MEC_2064339_Edital_Chamada_Publica.pdf</t>
+          <t>https://www.ifes.edu.br/chamadas-publicas/19351-chamada-publica-3-2020-projetos-iniciacao-tecnologica-economia-4-0</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>2</v>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>Retificação Edital nº 35/2020 - Chamada Pública - Seleção de projetos voltados à criação de Laboratórios Maker junto à Rede Federal de Educação Profissional, Científica e Tecnológica Retificação de Cronograma ​do | https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/AlteraodecronogramaRedeMakeredital35.pdf</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -5191,20 +5187,24 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Edital nº 46, de 20 de julho de 2020, que torna público edital para adesão de estados e Distrito Federal à oferta de Curso de Especialização Lato Sensu em Docência para a Educação Profissional e Tecnológica (DocentEPT) aos professores da rede pública estadual e distrital que atuam na oferta de cursos de Educação Profissional e Tecnológica</t>
+          <t>Edital nº 35/2020 - Chamada Pública - que tem como objetivo selecionar projetos voltados à criação de Laboratórios IFMaker junto aos Institutos Federais de Educação, Ciência e Tecnologia; Centros Federais de Educação Tecnológica Celso Suckow da Fonseca – Cefet-RJ e de Minas Gerais – Cefet-MG e o Colégio Pedro II, conforme especificado no Despacho SEI nº 2064854</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2020/Editaldeadeso_DOU.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2020/SEI_MEC_2064339_Edital_Chamada_Publica.pdf</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>1</v>
-      </c>
-      <c r="G176" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Retificação Edital nº 35/2020 - Chamada Pública - Seleção de projetos voltados à criação de Laboratórios Maker junto à Rede Federal de Educação Profissional, Científica e Tecnológica Retificação de Cronograma ​do | https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/AlteraodecronogramaRedeMakeredital35.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -5214,14 +5214,14 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Edital nº 47/2022 - Chamada Pública para oferta de cursos da Plataforma Aprenda Mais</t>
+          <t>Edital nº 46, de 20 de julho de 2020, que torna público edital para adesão de estados e Distrito Federal à oferta de Curso de Especialização Lato Sensu em Docência para a Educação Profissional e Tecnológica (DocentEPT) aos professores da rede pública estadual e distrital que atuam na oferta de cursos de Educação Profissional e Tecnológica</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/editais/2022/Editaln47.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2020/Editaldeadeso_DOU.pdf</t>
         </is>
       </c>
       <c r="F177" t="n">
@@ -5237,14 +5237,14 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Edital nº 48/2022 - Procedimentos para autorização da oferta de cursos técnicos de nível médio por Instituições Privadas de Ensino Superior – Anexos do</t>
+          <t>Edital nº 47/2022 - Chamada Pública para oferta de cursos da Plataforma Aprenda Mais</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/editais/2022/Editaln48.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/editais/2022/Editaln47.pdf</t>
         </is>
       </c>
       <c r="F178" t="n">
@@ -5260,14 +5260,14 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Edital nº 5 /2026 - Seleção de propostas de projetos de extensão voltados ao Acesso, à Permanência e ao Êxito no âmbito da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT).</t>
+          <t>Edital nº 48/2022 - Procedimentos para autorização da oferta de cursos técnicos de nível médio por Instituições Privadas de Ensino Superior – Anexos do</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2026/sei_7012727_edital_5.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/editais/2022/Editaln48.pdf</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -5283,14 +5283,14 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Edital nº 5/2020 – Chamada para seleção de projetos de apoio ao empreendedorismo inovador com foco na Economia 4.0. Acesse o edital .</t>
+          <t>Edital nº 5 /2026 - Seleção de propostas de projetos de extensão voltados ao Acesso, à Permanência e ao Êxito no âmbito da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT).</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>https://www.ifes.edu.br/chamadas-publicas/19384-chamada-publica-05-2020-selecao-de-projetos-de-apoio-ao-empreendedorismo-inovador-com-foco-na-economia-4-0</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2026/sei_7012727_edital_5.pdf</t>
         </is>
       </c>
       <c r="F180" t="n">
@@ -5306,14 +5306,14 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Edital nº 5/2021 – IF Mais Empreendedor Nacional : Adesão ao Programa IF Mais Empreendedor Nacional</t>
+          <t>Edital nº 5/2020 – Chamada para seleção de projetos de apoio ao empreendedorismo inovador com foco na Economia 4.0. Acesse o edital .</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/editais/2021/Edital05.2021IFEMPREENDEDORNACIONAL.pdf</t>
+          <t>https://www.ifes.edu.br/chamadas-publicas/19384-chamada-publica-05-2020-selecao-de-projetos-de-apoio-ao-empreendedorismo-inovador-com-foco-na-economia-4-0</t>
         </is>
       </c>
       <c r="F181" t="n">
@@ -5329,14 +5329,14 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Edital nº 5/2024 - Seleção de propostas de novos Cursos Abertos, On-line e Massivos (MOOCs), desenvolvidos pela Rede Federa de Educação Profissional, Científica e Tecnológica, a serem disponibilizados na Plataforma APRENDA MAIS.</t>
+          <t>Edital nº 5/2021 – IF Mais Empreendedor Nacional : Adesão ao Programa IF Mais Empreendedor Nacional</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC4659481Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/editais/2021/Edital05.2021IFEMPREENDEDORNACIONAL.pdf</t>
         </is>
       </c>
       <c r="F182" t="n">
@@ -5352,14 +5352,14 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Edital nº 52/2016 – que torna público, para conhecimento dos interessados, que será realizado na modalidade concurso, o PROJETO DESAFIO DA EDUCAÇÃO PROFISSIONAL E TECNOLÓGICA, na forma do REGULAMENTO anexo a este edital, com o objetivo de promover uma campanha nacional para aprimorar a Educação Profissional e Tecnológica estimulando a sociedade a enviar propostas de ações inovadoras e compartilhar experiências exitosas de implementação de ações.</t>
+          <t>Edital nº 5/2024 - Seleção de propostas de novos Cursos Abertos, On-line e Massivos (MOOCs), desenvolvidos pela Rede Federa de Educação Profissional, Científica e Tecnológica, a serem disponibilizados na Plataforma APRENDA MAIS.</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/edital_n_52_2016.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC4659481Edital.pdf</t>
         </is>
       </c>
       <c r="F183" t="n">
@@ -5375,14 +5375,14 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Edital nº 55/2016 , que torna público concurso PROJETO DESAFIO EDUCAÇÃO ZIKAZERO, na forma do REGULAMENTO anexo a este edital, com o objetivo de promover uma campanha nacional de mobilização para o enfrentamento ao Aedes aegyp e à microcefalia estimulando a sociedade a enviar propostas de ações inovadoras e compartilhar experiências exitosas de implementação de ações em prol do combate ao mosquito.</t>
+          <t>Edital nº 52/2016 – que torna público, para conhecimento dos interessados, que será realizado na modalidade concurso, o PROJETO DESAFIO DA EDUCAÇÃO PROFISSIONAL E TECNOLÓGICA, na forma do REGULAMENTO anexo a este edital, com o objetivo de promover uma campanha nacional para aprimorar a Educação Profissional e Tecnológica estimulando a sociedade a enviar propostas de ações inovadoras e compartilhar experiências exitosas de implementação de ações.</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/Edital_55_2016_SEI_MEC_0227936.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/edital_n_52_2016.pdf</t>
         </is>
       </c>
       <c r="F184" t="n">
@@ -5398,14 +5398,14 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Edital nº 6/2021 - Edital de Adesão das instituições ao Sistema Re-Saber</t>
+          <t>Edital nº 55/2016 , que torna público concurso PROJETO DESAFIO EDUCAÇÃO ZIKAZERO, na forma do REGULAMENTO anexo a este edital, com o objetivo de promover uma campanha nacional de mobilização para o enfrentamento ao Aedes aegyp e à microcefalia estimulando a sociedade a enviar propostas de ações inovadoras e compartilhar experiências exitosas de implementação de ações em prol do combate ao mosquito.</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/Edital_06_2021.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/Edital_55_2016_SEI_MEC_0227936.pdf</t>
         </is>
       </c>
       <c r="F185" t="n">
@@ -5421,14 +5421,14 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Edital nº 6/2024 - Edital visa selecionar a proposta de selo/logomarca que será utilizado em confecções comemorativas no contexto dos 115 anos da Rede Federal de Educação Profissional, Científica e Tecnológica, que poderá ser personalizado como selo postal, via Correios. *</t>
+          <t>Edital nº 6/2021 - Edital de Adesão das instituições ao Sistema Re-Saber</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-2024/325.SEI_MEC4985249Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/Edital_06_2021.pdf</t>
         </is>
       </c>
       <c r="F186" t="n">
@@ -5444,14 +5444,14 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Edital nº 61/2019 – Regulamento do Cadastro de Especialistas para compor o Banco de Avaliadores da Secretaria de Educação Profissional e Tecnológica.</t>
+          <t>Edital nº 6/2024 - Edital visa selecionar a proposta de selo/logomarca que será utilizado em confecções comemorativas no contexto dos 115 anos da Rede Federal de Educação Profissional, Científica e Tecnológica, que poderá ser personalizado como selo postal, via Correios. *</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2019/EDITALN612019.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-2024/325.SEI_MEC4985249Edital.pdf</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -5467,14 +5467,14 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Edital nº 63/2021- Seleção de Projetos de Promoção às Indicações Geográficas</t>
+          <t>Edital nº 61/2019 – Regulamento do Cadastro de Especialistas para compor o Banco de Avaliadores da Secretaria de Educação Profissional e Tecnológica.</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/editais/2021/Edital63.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2019/EDITALN612019.pdf</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -5490,14 +5490,14 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Edital nº 67/2021 - Chamada Pública de Projetos para apoio à implementação das Oficinas 4.0</t>
+          <t>Edital nº 63/2021- Seleção de Projetos de Promoção às Indicações Geográficas</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/SEI_MEC2898796Edital67.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/editais/2021/Edital63.pdf</t>
         </is>
       </c>
       <c r="F189" t="n">
@@ -5513,14 +5513,14 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Edital nº 68/2019 – Seleção de servidores para atuação em Projetos Educacionais de Colaboração Técnica junto ao Ministério da Educação.</t>
+          <t>Edital nº 67/2021 - Chamada Pública de Projetos para apoio à implementação das Oficinas 4.0</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2019/EDITALN682019.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/SEI_MEC2898796Edital67.pdf</t>
         </is>
       </c>
       <c r="F190" t="n">
@@ -5536,14 +5536,14 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Edital nº 83/2022 – Seleção de propostas de instituições da Rede Federal para a implementação de programa de capacitação de estudantes denominado Oficinas 4.0</t>
+          <t>Edital nº 68/2019 – Seleção de servidores para atuação em Projetos Educacionais de Colaboração Técnica junto ao Ministério da Educação.</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital83.2022.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2019/EDITALN682019.pdf</t>
         </is>
       </c>
       <c r="F191" t="n">
@@ -5559,14 +5559,14 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Edital nº 88/2022 – Seleção de projetos de iniciação tecnológica de instituições da RFEPCT para o desenvolvimento de ações de formação em programação e/ou robótica e/ou cultura maker para estudantes dos anos finais do ensino fundamental (6º ao 9º ano) das redes públicas de ensino. Retificação ​do</t>
+          <t>Edital nº 83/2022 – Seleção de propostas de instituições da Rede Federal para a implementação de programa de capacitação de estudantes denominado Oficinas 4.0</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital88.2022.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital83.2022.pdf</t>
         </is>
       </c>
       <c r="F192" t="n">
@@ -5582,14 +5582,14 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Edital nº 94/2022 – Chamada Pública para a capacitação de multiplicadores em bioeconomia para a Amazônia Legal. Chamada Pública para a Adesão de parceiros ofertantes da Rede Federal de Educação Profissional, Científica e Tecnológica – RFEPCT à linha de fomento Qualifica Mais EnergIFE, voltada à promoção da oferta de cursos na área das Energias Renováveis. Retificação do</t>
+          <t>Edital nº 88/2022 – Seleção de projetos de iniciação tecnológica de instituições da RFEPCT para o desenvolvimento de ações de formação em programação e/ou robótica e/ou cultura maker para estudantes dos anos finais do ensino fundamental (6º ao 9º ano) das redes públicas de ensino. Retificação ​do</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Editaln94.2022.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital88.2022.pdf</t>
         </is>
       </c>
       <c r="F193" t="n">
@@ -5605,14 +5605,14 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Edital nº 99/2022 - Chamamento Público para a seleção de projetos de inovação e trabalhos acadêmicos aptos a integrarem a Semana Nacional da Educação Profissional e Tecnológica Retificação do</t>
+          <t>Edital nº 94/2022 – Chamada Pública para a capacitação de multiplicadores em bioeconomia para a Amazônia Legal. Chamada Pública para a Adesão de parceiros ofertantes da Rede Federal de Educação Profissional, Científica e Tecnológica – RFEPCT à linha de fomento Qualifica Mais EnergIFE, voltada à promoção da oferta de cursos na área das Energias Renováveis. Retificação do</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/secretarias/secretaria-de-educacao-profissional/SEI_MEC3566713Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Editaln94.2022.pdf</t>
         </is>
       </c>
       <c r="F194" t="n">
@@ -5628,14 +5628,14 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Programa Setec-Capes/NOVA de capacitação para Professores da Rede Federal de Educação Profissional, Científica e Tecnológica . A Secretaria de Educação Profissional e Tecnológica (Setec) do Ministério da Educação, com apoio da Coordenação de Aperfeiçoamento de Pessoal de Nível Superior (Capes), lançam chamada pública de capacitação para professores de inglês em efetivo exercício na Rede Federal de Educação Profissional - Institutos Federais, Cefets, Escolas Técnicas vinculas às Universidades Federais e Colégio Pedro II. (Retificação publicada no Diário Oficial da União em 02 de junho de 2016)</t>
+          <t>Edital nº 99/2022 - Chamamento Público para a seleção de projetos de inovação e trabalhos acadêmicos aptos a integrarem a Semana Nacional da Educação Profissional e Tecnológica Retificação do</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2015/chamada_setec_capes_nova_extrato_dou.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/secretarias/secretaria-de-educacao-profissional/SEI_MEC3566713Edital.pdf</t>
         </is>
       </c>
       <c r="F195" t="n">
@@ -5651,24 +5651,20 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Republicação do Edital nº 76/2022 - Chamamento Público para seleção de projetos voltados ao fortalecimento de Núcleos de Inovação Tecnológica e/ou Agências de Inovação.</t>
+          <t>Programa Setec-Capes/NOVA de capacitação para Professores da Rede Federal de Educação Profissional, Científica e Tecnológica . A Secretaria de Educação Profissional e Tecnológica (Setec) do Ministério da Educação, com apoio da Coordenação de Aperfeiçoamento de Pessoal de Nível Superior (Capes), lançam chamada pública de capacitação para professores de inglês em efetivo exercício na Rede Federal de Educação Profissional - Institutos Federais, Cefets, Escolas Técnicas vinculas às Universidades Federais e Colégio Pedro II. (Retificação publicada no Diário Oficial da União em 02 de junho de 2016)</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Republicaodoedital76.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2015/chamada_setec_capes_nova_extrato_dou.pdf</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>2</v>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>Retificação do Edital nº 76/2022 – novo cronograma | https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/SEI_23000.006585_2022_91.pdf</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -5678,20 +5674,24 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições da Rede Federal de Educação Profissional, Científica e Tecnológica).</t>
+          <t>Republicação do Edital nº 76/2022 - Chamamento Público para seleção de projetos voltados ao fortalecimento de Núcleos de Inovação Tecnológica e/ou Agências de Inovação.</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/ResultadoEdital10.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Republicaodoedital76.pdf</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>1</v>
-      </c>
-      <c r="G197" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Retificação do Edital nº 76/2022 – novo cronograma | https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/SEI_23000.006585_2022_91.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -5701,14 +5701,14 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições Privadas de Ensino Superior que ofertam cursos técnicos e Escolas Técnicas Privadas).</t>
+          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições da Rede Federal de Educação Profissional, Científica e Tecnológica).</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/ResultadoEdital09.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/ResultadoEdital10.pdf</t>
         </is>
       </c>
       <c r="F198" t="n">
@@ -5724,20 +5724,43 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições Públicas Estaduais e Distrital de Educação Profissional e Tecnológica).</t>
+          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições Privadas de Ensino Superior que ofertam cursos técnicos e Escolas Técnicas Privadas).</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/ResultadoEdital09.pdf</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>1</v>
+      </c>
+      <c r="G199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>SETEC</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições Públicas Estaduais e Distrital de Educação Profissional e Tecnológica).</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr"/>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr">
+        <is>
           <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/2147-resultado-preliminar.pdf</t>
         </is>
       </c>
-      <c r="F199" t="n">
-        <v>1</v>
-      </c>
-      <c r="G199" t="inlineStr"/>
+      <c r="F200" t="n">
+        <v>1</v>
+      </c>
+      <c r="G200" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/editais.xlsx
+++ b/editais.xlsx
@@ -511,9 +511,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Chamada Pública CNPq/ERC (Conselho Europeu de Pesquisa) Nº 21/2026 | https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-21-2026/chamada-publica-cnpq-N-21-2026</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3526,9 +3530,13 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>1</v>
-      </c>
-      <c r="G108" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Edital Conjunto nº 5/2026 - Programa OBEDUC-EI, formato, pdf, 9,67mb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital-no-5.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4007,9 +4015,13 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>1</v>
-      </c>
-      <c r="G127" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Alteração Edital nº 23/2026 - Programa Nacional de Formação de Professores da Educação Básica (PARFOR), formato, pdf, 130kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2875930_edital_23_2026___alteracao.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">

--- a/editais.xlsx
+++ b/editais.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G200"/>
+  <dimension ref="A1:G205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1560,11 +1560,11 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alteração do edital nº 26/2025 - Política de Novação para Bolsistas e Ex-Bolsistas no Exterior, formato - pdf, 60,5kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11052026_Edital_2817202_SEI_2816655_Edital_n__26_2025___Alteracao.pdf</t>
+          <t>Edital nº 26/2025 - Alteração, formato, pdf, 114kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2878184_edital_26_2025___alteracao.pdf/@@display-file/file ; Alteração do edital nº 26/2025 - Política de Novação para Bolsistas e Ex-Bolsistas no Exterior, formato - pdf, 60,5kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11052026_Edital_2817202_SEI_2816655_Edital_n__26_2025___Alteracao.pdf</t>
         </is>
       </c>
     </row>
@@ -3569,20 +3569,24 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Edital nº 039/2013 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 400kb</t>
+          <t>Edital nº 02/2024 - Projetos de Cooperação entre Instituições para Qualificação de Profissionais de Nível Superior (PCI) - formato, pdf, 87kb</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_039_2013_PDPI.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/26022024_Edital_2328837_SEI_2326326_Edital_02_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1</v>
-      </c>
-      <c r="G110" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Alteração do Edital nº 02/2024 - Projetos de Cooperação entre Instituições para Qualificação de Profissionais de Nível Superior (PCI) - formato, pdf, 54kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/16052024_Edital_2379426_SEI_2379169_Edital_02_2024.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3592,24 +3596,20 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Edital nº 05/2023 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 473kb</t>
+          <t>Edital nº 039/2013 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 400kb</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15032023_Edital_1933938_Edital_5_2023.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_039_2013_PDPI.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>3</v>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>Alteração do Edital nº 05/2023 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 60kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400239_SEI_2399449_Edital_05_2023___ALTERACAO_II.pdf/@@display-file/file ; Relação das inscrições do Edital nº 05/2023 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 571kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/30052023_Lista_Listagem_1984677_Lista_de_inscritos_Math_Amsud_Edital_5.2023.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3619,22 +3619,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Edital nº 05/2024 - ProgramaCAPES/CLIMAT-AMSUD, formato - pdf, 239kb</t>
+          <t>Edital nº 05/2023 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 473kb</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20032024_Edital_2343766_SEI_2342530_Edital_05_2024.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15032023_Edital_1933938_Edital_5_2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Edital nº 05/2024 - ProgramaCAPES/STIC-AMSUD, formato - pdf, 239kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20032024_Edital_2343766_SEI_2342530_Edital_05_2024.pdf/@@display-file/file ; Alteração do Edital nº 05/2024 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 57kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07052024_Edital_2373417_SEI_2372656_Edital_05_2024.pdf/@@display-file/file ; Edital nº 05/2024 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 239kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20032024_Edital_2343766_SEI_2342530_Edital_05_2024.pdf/@@display-file/file</t>
+          <t>Alteração do Edital nº 05/2023 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 60kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400239_SEI_2399449_Edital_05_2023___ALTERACAO_II.pdf/@@display-file/file ; Relação das inscrições do Edital nº 05/2023 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 571kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/30052023_Lista_Listagem_1984677_Lista_de_inscritos_Math_Amsud_Edital_5.2023.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3646,22 +3646,22 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Edital nº 06/2023 - ProgramaCAPES/STIC-AMSUD, formato - pdf, 473kb</t>
+          <t>Edital nº 05/2024 - ProgramaCAPES/CLIMAT-AMSUD, formato - pdf, 239kb</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15032023_Edital_1933950_Edital_6_2023.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20032024_Edital_2343766_SEI_2342530_Edital_05_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alteração do Edital nº 06/2023 - Programa CAPES/STIC-AMSUD, formato - pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400119_SEI_2399429_Edital_6_2023___Alteracao_II.pdf/@@display-file/file ; Relação das inscrições do Edital nº 06/2023 - Programa CAPES/STIC-AMSUD, formato - pdf, 571kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/30052023_Lista_Listagem_1984493_Lista_de_inscritos_Stic_Amsud_Edital_6.2023.pdf/@@display-file/file</t>
+          <t>Edital nº 05/2024 - ProgramaCAPES/STIC-AMSUD, formato - pdf, 239kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20032024_Edital_2343766_SEI_2342530_Edital_05_2024.pdf/@@display-file/file ; Alteração do Edital nº 05/2024 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 57kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07052024_Edital_2373417_SEI_2372656_Edital_05_2024.pdf/@@display-file/file ; Edital nº 05/2024 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 239kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20032024_Edital_2343766_SEI_2342530_Edital_05_2024.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3673,22 +3673,22 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Edital nº 06/2024 - PDSE - formato, pdf, 133kb</t>
+          <t>Edital nº 06/2023 - ProgramaCAPES/STIC-AMSUD, formato - pdf, 473kb</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/21032024_Edital_2344636_SEI_2343579_Edital_6_2024.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15032023_Edital_1933950_Edital_6_2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Prorrogação do Edital nº 06/2024 - PDSE - formato, pdf, 55kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/10052024_Edital_2376323_SEI_2375557_Edital_6_2024.pdf/@@display-file/file</t>
+          <t>Alteração do Edital nº 06/2023 - Programa CAPES/STIC-AMSUD, formato - pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400119_SEI_2399429_Edital_6_2023___Alteracao_II.pdf/@@display-file/file ; Relação das inscrições do Edital nº 06/2023 - Programa CAPES/STIC-AMSUD, formato - pdf, 571kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/30052023_Lista_Listagem_1984493_Lista_de_inscritos_Stic_Amsud_Edital_6.2023.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3700,22 +3700,22 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Edital nº 07/2023 - ProgramaCAPES/CLIMAT-AMSUD, formato - pdf, 466kb</t>
+          <t>Edital nº 06/2024 - PDSE - formato, pdf, 133kb</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15032023_Edital_1933965_Edital_7_2023_.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/21032024_Edital_2344636_SEI_2343579_Edital_6_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alteração doEdital nº 07/2023 - ProgramaCAPES/CLIMAT-AMSUD, formato - pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400133_SEI_2399445_Edital_07_2023___ALTERACAO_II.pdf/@@display-file/file ; Relação das inscrições do Edital nº 07/2023 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 570kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/30052023_Lista_Listagem_1984693_Lista_de_inscritos_Climat_Amsud_Edital_7.2023.pdf/@@display-file/file</t>
+          <t>Prorrogação do Edital nº 06/2024 - PDSE - formato, pdf, 55kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/10052024_Edital_2376323_SEI_2375557_Edital_6_2024.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3727,22 +3727,22 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Edital nº 08/2023 - CAPES/Cofecub, formato, pdf, 495kb</t>
+          <t>Edital nº 07/2023 - ProgramaCAPES/CLIMAT-AMSUD, formato - pdf, 466kb</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/03042023_Edital_1946708_Edital_8_2022.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15032023_Edital_1933965_Edital_7_2023_.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alteração doEdital nº 08/2023 - CAPES/Cofecub, formato, pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20062024_Edital_2401059_SEI_2399441_Edital_08_2023___ALTERACAO_II.pdf/@@display-file/file</t>
+          <t>Alteração doEdital nº 07/2023 - ProgramaCAPES/CLIMAT-AMSUD, formato - pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400133_SEI_2399445_Edital_07_2023___ALTERACAO_II.pdf/@@display-file/file ; Relação das inscrições do Edital nº 07/2023 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 570kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/30052023_Lista_Listagem_1984693_Lista_de_inscritos_Climat_Amsud_Edital_7.2023.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3754,22 +3754,22 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Edital nº 08/2024 - CAPES/Cofecub, formato, pdf, 213kb</t>
+          <t>Edital nº 08/2023 - CAPES/Cofecub, formato, pdf, 495kb</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/22032024_Edital_2345736_SEI_2343959_Edital_8.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/03042023_Edital_1946708_Edital_8_2022.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alteração do Edital nº 08/2024 - Programa CAPES/Cofecub, formato, pdf, 54kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23122024_Edital_2517712_SEI_2516934_Edital_8_2024.pdf/@@display-file/file ; Prorrogação do Edital nº 08/2024 - CAPES/Cofecub, formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/02072024_Edital_2409554_SEI_2409272_Edital_08_2024___Prorrogacao.pdf/@@display-file/file ; Alteração do Edital nº 08/2024 - CAPES/Cofecub, formato, pdf, 57kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07052024_Edital_2373782_SEI_2372654_Edital_08_2024.pdf/@@display-file/file</t>
+          <t>Alteração doEdital nº 08/2023 - CAPES/Cofecub, formato, pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20062024_Edital_2401059_SEI_2399441_Edital_08_2023___ALTERACAO_II.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3781,20 +3781,24 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Edital nº 10/2022 - PDSE - formato, pdf, 337kb</t>
+          <t>Edital nº 08/2024 - CAPES/Cofecub, formato, pdf, 213kb</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/16022022_Edital10.22PDSE.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/22032024_Edital_2345736_SEI_2343959_Edital_8.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>1</v>
-      </c>
-      <c r="G118" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Alteração do Edital nº 08/2024 - Programa CAPES/Cofecub, formato, pdf, 54kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23122024_Edital_2517712_SEI_2516934_Edital_8_2024.pdf/@@display-file/file ; Prorrogação do Edital nº 08/2024 - CAPES/Cofecub, formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/02072024_Edital_2409554_SEI_2409272_Edital_08_2024___Prorrogacao.pdf/@@display-file/file ; Alteração do Edital nº 08/2024 - CAPES/Cofecub, formato, pdf, 57kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07052024_Edital_2373782_SEI_2372654_Edital_08_2024.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3804,24 +3808,20 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Edital nº 16/2025 - formato, pdf, 360kb</t>
+          <t>Edital nº 10/2022 - PDSE - formato, pdf, 337kb</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11082025_Edital_2654124.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/16022022_Edital10.22PDSE.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>2</v>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>Lista de inscritos no edital nº 16/2025 - formato, pdf, 207kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/29102025_Lista_Listagem_2693783_SEI___23038.003238_2025_21_buffalo.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3831,14 +3831,14 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Edital nº 16/2026 - Programa AURORA — Continuidade da Trajetória de Mães Cientistas</t>
+          <t>Edital nº 14/2025 - PCI - pdf, 83kb</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2818271_SEI_2817084_Edital_16_2026__1_.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/31072025_Edital_2646654_SEI_2644987_Edital_14_2025.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F120" t="n">
@@ -3854,20 +3854,24 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Edital nº 19/2017 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 315kb</t>
+          <t>Edital nº 16/2025 - formato, pdf, 360kb</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/31052017Edital192017PDPI.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11082025_Edital_2654124.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>1</v>
-      </c>
-      <c r="G121" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Lista de inscritos no edital nº 16/2025 - formato, pdf, 207kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/29102025_Lista_Listagem_2693783_SEI___23038.003238_2025_21_buffalo.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3877,14 +3881,14 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Edital nº 19/2026 - Programa Capes/Universidade em Buffalo (Capes/UB) - Professor Visitante - formato, pdf, 139kb</t>
+          <t>Edital nº 16/2026 - Programa AURORA — Continuidade da Trajetória de Mães Cientistas</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2843097_SEI_2842333_Edital_n__19_2026.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2818271_SEI_2817084_Edital_16_2026__1_.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F122" t="n">
@@ -3900,24 +3904,20 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Edital nº 20/2022 -Programa CAPES/STIC-AMSUD, formato, pdf - 286kb</t>
+          <t>Edital nº 19/2017 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 315kb</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07042022_Edital_1673688_EDITAL_20_2022_STIC_AMSUD.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/31052017Edital192017PDPI.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>3</v>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>Alteração do Edital nº 20/2022 -Programa CAPES/STIC-AMSUD, formato, pdf - 67kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400177_SEI_2399435_Edital_20_2022___ALTERACAO_I.pdf/@@display-file/file ; Relação das inscrições do Edital nº 20/2022 - Programa CAPES/STIC-AMSUD, formato - pdf, 358kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/06062022_Lista_Listagem_1727082_STIC.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3927,14 +3927,14 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Edital nº 21/2026 - Programa de Desenvolvimento da Pós-Graduação (PDPG) – Parcerias Estratégicas nos Estados VI – Rede de Pesquisa e Desenvolvimento da Região Nordeste, formato, pdf, 177kb</t>
+          <t>Edital nº 19/2026 - Programa Capes/Universidade em Buffalo (Capes/UB) - Professor Visitante - formato, pdf, 139kb</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2848691_sei_2847430_edital_n__21_2026.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2843097_SEI_2842333_Edital_n__19_2026.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F124" t="n">
@@ -3950,22 +3950,22 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Edital nº 22/2026 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 150kb</t>
+          <t>Edital nº 20/2022 -Programa CAPES/STIC-AMSUD, formato, pdf - 286kb</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/sei_2849220_edital_n__22_2026.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07042022_Edital_1673688_EDITAL_20_2022_STIC_AMSUD.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alteração Edital nº 22/2026 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 47,4kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2858430_sei_2857160_edital_22_2026___alteracao.pdf/@@display-file/file</t>
+          <t>Alteração do Edital nº 20/2022 -Programa CAPES/STIC-AMSUD, formato, pdf - 67kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400177_SEI_2399435_Edital_20_2022___ALTERACAO_I.pdf/@@display-file/file ; Relação das inscrições do Edital nº 20/2022 - Programa CAPES/STIC-AMSUD, formato - pdf, 358kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/06062022_Lista_Listagem_1727082_STIC.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3977,22 +3977,22 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Edital nº 23/2026 - Programa de Desenvolvimento Acadêmico Indígena (PDAI), formato, pdf, 168kb</t>
+          <t>Edital nº 21/2023 - Projetos de Cooperação entre Instituições para Qualificação de Profissionais de Nível Superior (PCI) - formato, pdf, 281kb</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2851776_sei_2851450_edital_n__23_2026.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/24082023_Edital_2043434_Edital_21_2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alteração Edital nº 23/2026 - Programa de Desenvolvimento Acadêmico Indígena (PDAI), formato, pdf, 102kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2872644_edital_conjunto_23_2026___alteracao.pdf/@@display-file/file</t>
+          <t>Retificação do Edital nº 21/2023 - Projetos de Cooperação entre Instituições para Qualificação de Profissionais de Nível Superior (PCI) - formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/01112023_Edital_2262651_SEI_2262236_Edital_21_2023.pdf/@@display-file/file ; Alteração do Edital nº 21/2023 - Projetos de Cooperação entre Instituições para Qualificação de Profissionais de Nível Superior (PCI) - formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/31102023_Edital_2261925_SEI_2261451_Edital_22_2023.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4004,24 +4004,20 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Edital nº 23/2026 - Programa Nacional de Formação de Professores da Educação Básica (PARFOR), formato, pdf, 168kb</t>
+          <t>Edital nº 21/2026 - Programa de Desenvolvimento da Pós-Graduação (PDPG) – Parcerias Estratégicas nos Estados VI – Rede de Pesquisa e Desenvolvimento da Região Nordeste, formato, pdf, 177kb</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2855421_sei_2854365_edital_n__23_2026.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2848691_sei_2847430_edital_n__21_2026.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>2</v>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>Alteração Edital nº 23/2026 - Programa Nacional de Formação de Professores da Educação Básica (PARFOR), formato, pdf, 130kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2875930_edital_23_2026___alteracao.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4031,22 +4027,22 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Edital nº 25/2022 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 353kb</t>
+          <t>Edital nº 22/2026 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 150kb</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/04052022_Edital_1698011_SEI_CAPES___1696119___Edital_25.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/sei_2849220_edital_n__22_2026.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alteração do edital nº 25/2022 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 67kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400217_SEI_2399433_Edital_25_2022___ALTERACAO_I.pdf/@@display-file/file ; Relação das inscrições do Edital nº 25/2022 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 353kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/06062022_Lista_Listagem_1727108_Climat.pdf/@@display-file/file</t>
+          <t>Alteração Edital nº 22/2026 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 47,4kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2858430_sei_2857160_edital_22_2026___alteracao.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4058,22 +4054,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Edital nº 26/2024 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE) - Retificação - formato, pdf, 48kb</t>
+          <t>Edital nº 23/2026 - Programa de Desenvolvimento Acadêmico Indígena (PDAI), formato, pdf, 168kb</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/14102024_Edital_2477735_SEI_2477608_Edital_N__26_2024.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2851776_sei_2851450_edital_n__23_2026.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alteração do Edital nº 26/2024 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE), formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/13032025_Edital_2560841_SEI_2559847_Edital_26_2024___ALTERACAO.pdf/@@display-file/file ; Edital nº 26/2024 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 135kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/08102024_Edital_2474014_SEI_2472849_Edital_26_2024.pdf/@@display-file/file</t>
+          <t>Alteração Edital nº 23/2026 - Programa de Desenvolvimento Acadêmico Indígena (PDAI), formato, pdf, 102kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2872644_edital_conjunto_23_2026___alteracao.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4085,14 +4081,14 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Edital nº 27/2024 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 157kb</t>
+          <t>Edital nº 23/2026 - Programa Nacional de Formação de Professores da Educação Básica (PARFOR), formato, pdf, 168kb</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/05112024_Edital_2490387_SEI_2489251_Edital_27_2024.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2855421_sei_2854365_edital_n__23_2026.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -4100,7 +4096,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alteração do Edital 27/2024 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa no EUA - PDPI - formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/02122024_Edital_2505290_SEI_2504109_Edital_27_2024__.pdf/@@display-file/file</t>
+          <t>Alteração Edital nº 23/2026 - Programa Nacional de Formação de Professores da Educação Básica (PARFOR), formato, pdf, 130kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2875930_edital_23_2026___alteracao.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4112,24 +4108,20 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Edital nº 30/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 110kb</t>
+          <t>Edital nº 24/2026 - Cooperação entre Instituições para</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/14022020_Edital_1145537_Edital_SITE.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2878169_edital_24_2026___pci.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>3</v>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>Reabertura e alteração do Edital nº 30/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 222kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/28042022_Edital_1691552_SEI_CAPES___1685746___Edital_30_2019.pdf/@@display-file/file ; Suspensão do Edital nº 30/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 111kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_1326070_Edital_Suspensao_site.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4139,14 +4131,14 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Edital nº 30/2023 - PDSE - formato, pdf, 125kb</t>
+          <t>Edital nº 25/2022 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 353kb</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/06112023_Edital_2263037_SEI_2261948_Edital_30_2023.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/04052022_Edital_1698011_SEI_CAPES___1696119___Edital_25.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -4154,7 +4146,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Prorrogação do Edital nº 30/2023 - PDSE - formato, pdf, 136kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11012024_Edital_2306448_SEI_CAPES___2305414___Edital_30_2023___Prorrogacao.pdf/@@display-file/file ; Alteração do Edital nº 30/2023 - PDSE - formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/18122023_Edital_2293491_SEI_2293429_Edital_30_2023_Alteracao.pdf/@@display-file/file</t>
+          <t>Alteração do edital nº 25/2022 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 67kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400217_SEI_2399433_Edital_25_2022___ALTERACAO_I.pdf/@@display-file/file ; Relação das inscrições do Edital nº 25/2022 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 353kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/06062022_Lista_Listagem_1727108_Climat.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4166,22 +4158,22 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Edital Nº 32/2022 - CAPES/Cofecub, formato, pdf, 225kb</t>
+          <t>Edital nº 25/2024 - Chamada Pública para envio de Proposta de Projeto de Cooperação entre Instituições para Qualificação de Profissionais de Nível Superior (PCI) - formato, pdf, 83kb</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29062022_EDITAL32_2022_COFECUB.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/17092024_Edital_2461148_SEI_2460992_Edital_25_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alteração do Edital Nº 32/2022 - CAPES/Cofecub, formato, pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400143_SEI_2399437_Edital_32_2022___ALTERACAO_III.pdf/@@display-file/file ; Relação de inscritos do Edital Nº 32/2022 - CAPES/Cofecub, formato, pdf, 65kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/25082022_Lista_Listagem_1783309_EDITAL_32_2022___CAPES_COFECUB_Relacao_de_Inscricoes.pdf/@@display-file/file</t>
+          <t>Alteração do Edital nº 25/2024 - Chamada Pública para envio de Proposta de Projeto de Cooperação entre Instituições para Qualificação de Profissionais de Nível Superior (PCI) - formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/10122024_Edital_2510251_SEI_2508924_Edital_25_2024___Alteracao.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4193,22 +4185,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Edital nº 32/2023 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 139kb</t>
+          <t>Edital nº 26/2024 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE) - Retificação - formato, pdf, 48kb</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/16112023_Edital_2271416_SEI_2268914_Edital_32_2023.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/14102024_Edital_2477735_SEI_2477608_Edital_N__26_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alteração do Edital nº 32/2023 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 57kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09022024_SEI_2321458_Edital_N__32_2023___ALTERACAOPDPI.pdf/@@display-file/file</t>
+          <t>Alteração do Edital nº 26/2024 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE), formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/13032025_Edital_2560841_SEI_2559847_Edital_26_2024___ALTERACAO.pdf/@@display-file/file ; Edital nº 26/2024 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 135kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/08102024_Edital_2474014_SEI_2472849_Edital_26_2024.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4220,20 +4212,24 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Edital nº 35/2011 - Certificação em Língua Inglesa - pdf, 615kb</t>
+          <t>Edital nº 27/2024 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 157kb</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_035_CertificacaoEUAprofLingIngl_Fulbright.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/05112024_Edital_2490387_SEI_2489251_Edital_27_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>1</v>
-      </c>
-      <c r="G135" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Alteração do Edital 27/2024 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa no EUA - PDPI - formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/02122024_Edital_2505290_SEI_2504109_Edital_27_2024__.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4243,20 +4239,24 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Edital nº 4/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 270kb</t>
+          <t>Edital nº 30/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 110kb</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/08022019Edital4.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/14022020_Edital_1145537_Edital_SITE.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>1</v>
-      </c>
-      <c r="G136" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Reabertura e alteração do Edital nº 30/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 222kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/28042022_Edital_1691552_SEI_CAPES___1685746___Edital_30_2019.pdf/@@display-file/file ; Suspensão do Edital nº 30/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 111kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_1326070_Edital_Suspensao_site.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4266,14 +4266,14 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Edital nº 44/2012 - Programa de Aperfeiçoamento para Professores de Língua Inglesa nos Eua, pdf, 272kb</t>
+          <t>Edital nº 30/2023 - PDSE - formato, pdf, 125kb</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_0442012_ProfLingIngl_EUA.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/06112023_Edital_2263037_SEI_2261948_Edital_30_2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F137" t="n">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Edital nº 44/2012 - Retificado - pdf, 528kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_0442012_ProfLIngRetif.pdf/@@display-file/file ; Retificação do Edital nº 44/2012 - pdf, 46kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/RetificacaoEdital442012_ProfLingInglEUA_01out12.pdf/@@display-file/file</t>
+          <t>Prorrogação do Edital nº 30/2023 - PDSE - formato, pdf, 136kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11012024_Edital_2306448_SEI_CAPES___2305414___Edital_30_2023___Prorrogacao.pdf/@@display-file/file ; Alteração do Edital nº 30/2023 - PDSE - formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/18122023_Edital_2293491_SEI_2293429_Edital_30_2023_Alteracao.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4293,22 +4293,22 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Edital nº 44/2022 - PDSE - formato, pdf, 337kb</t>
+          <t>Edital Nº 32/2022 - CAPES/Cofecub, formato, pdf, 225kb</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/22122022_Edital_1882688_Edital_44_2022.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29062022_EDITAL32_2022_COFECUB.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alteração do Edital nº 44/2022 - PDSE - formato, pdf, 146kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23052023_Edital_1981709_Edital_44_2023.pdf/@@display-file/file</t>
+          <t>Alteração do Edital Nº 32/2022 - CAPES/Cofecub, formato, pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400143_SEI_2399437_Edital_32_2022___ALTERACAO_III.pdf/@@display-file/file ; Relação de inscritos do Edital Nº 32/2022 - CAPES/Cofecub, formato, pdf, 65kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/25082022_Lista_Listagem_1783309_EDITAL_32_2022___CAPES_COFECUB_Relacao_de_Inscricoes.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4320,20 +4320,24 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Edital nº 52/2010 - Certificação em Língua Inglesa, pdf, 60kbDF</t>
+          <t>Edital nº 32/2023 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 139kb</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_52_Certificacao_LinguaInglesa2010.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/16112023_Edital_2271416_SEI_2268914_Edital_32_2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>1</v>
-      </c>
-      <c r="G139" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Alteração do Edital nº 32/2023 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 57kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09022024_SEI_2321458_Edital_N__32_2023___ALTERACAOPDPI.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4343,24 +4347,20 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Edital Nº09/2026 - Programa CAPES/BRAFITEC, formato, pdf, 209kb</t>
+          <t>Edital nº 35/2011 - Certificação em Língua Inglesa - pdf, 615kb</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2800035_SEI_2799041_Edital_9__de_2026.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_035_CertificacaoEUAprofLingIngl_Fulbright.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>2</v>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>Edital n° 9/2026 - Lista de Inscritos, formato, pdf, 398kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/lista_listagem_2864548_sei_2863010_edital_minuta__.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4370,24 +4370,20 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Lista de inscritos do Edital Conjunto nº 01/2024 - Programa Caminhos Amefricanos, formato, pdf, 407kb</t>
+          <t>Edital nº 4/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 270kb</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15052024_Lista_Listagem_2374115_Inscritos_MIR.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/08022019Edital4.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>2</v>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>Alteração do Edital Conjunto nº 01/2024 - Programa Caminhos Amefricanos, formato, pdf, 63kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29042024_Edital_2368101_SEI_2365347_Edital_Conjunto_n__1_CAPES_MIR.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4397,20 +4393,24 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Lista de inscritos do Edital nº 05/2024 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 46kb</t>
+          <t>Edital nº 44/2012 - Programa de Aperfeiçoamento para Professores de Língua Inglesa nos Eua, pdf, 272kb</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/10062024_Lista_Listagem_2390159_Lista_de_Inscritos_3.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_0442012_ProfLingIngl_EUA.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>1</v>
-      </c>
-      <c r="G142" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Edital nº 44/2012 - Retificado - pdf, 528kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_0442012_ProfLIngRetif.pdf/@@display-file/file ; Retificação do Edital nº 44/2012 - pdf, 46kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/RetificacaoEdital442012_ProfLingInglEUA_01out12.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4420,20 +4420,24 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Lista de inscritos doEdital nº 8/202 - CAPES/COFECUB, formato, pdf, 581kb</t>
+          <t>Edital nº 44/2022 - PDSE - formato, pdf, 337kb</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/14062023_Lista_Listagem_1990268_Inscricoes_cofecub_2023.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/22122022_Edital_1882688_Edital_44_2022.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>1</v>
-      </c>
-      <c r="G143" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Alteração do Edital nº 44/2022 - PDSE - formato, pdf, 146kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23052023_Edital_1981709_Edital_44_2023.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4443,24 +4447,20 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Lista de inscrições - Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 393kb</t>
+          <t>Edital nº 52/2010 - Certificação em Língua Inglesa, pdf, 60kbDF</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Lista_de_Inscricoes_Homologadas_PDSE___2020_REVISADA.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_52_Certificacao_LinguaInglesa2010.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>4</v>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>Lista de candidaturas - Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 417kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/documentos/diretoria-de-relacoes-internacionais/pdse/Lista_Listagem_1439062_Lista_de_Inscricoes_Homologadas_PDSE___2020.pdf/@@display-file/file ; Retificação do Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 244kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/EDITAL192020_PDSERETIFICAO.pdf/@@display-file/file ; Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE)- formato, pdf, 236kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09102020_edital-19-pdse.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4470,22 +4470,22 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Lista de inscrições do Edital nº 17/2025 - Primeira chamada Programa Institucional de Doutorado Sanduíche no Exterior (PDSE) - formato, pdf, 8,8mb</t>
+          <t>Edital Nº09/2026 - Programa CAPES/BRAFITEC, formato, pdf, 209kb</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/29102025_Lista_Listagem_2708089_PDSE.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2800035_SEI_2799041_Edital_9__de_2026.pdf</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lista de inscrições do Edital nº 17/2025 - Segunda chamada Programa Institucional de Doutorado Sanduíche no Exterior (PDSE) - formato, pdf, 1,4mb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/27042026_Lista_Listagem_2808119_Lista_de_inscricoes_homologadas_do_Edital_172025___PDSE___segunda_chamada___formato_pdf__2_.pdf/@@display-file/file ; Alteração do Edital nº 17/2025 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE), formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/08102025_Edital_2696973_SEI_2695934_Edital_17_2025__.pdf/@@display-file/file ; Edital nº 17/2025 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 142kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/21082025_Edital_2662823_SEI_2661209_Edital_n__17_2025.pdf/@@display-file/file</t>
+          <t>Edital n° 9/2026 - Lista de Inscritos, formato, pdf, 398kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/lista_listagem_2864548_sei_2863010_edital_minuta__.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4497,22 +4497,22 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Lista de instituições e cursos pré-aprovados para a 3ª fase do Edital nº 08/2022 - Parfor - formato, pdf, 715kb</t>
+          <t>Lista de inscritos do Edital Conjunto nº 01/2024 - Programa Caminhos Amefricanos, formato, pdf, 407kb</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/06052022_Relacao_1700579_LISTA_DE_IES_E_CURSOS_APROVADOS_PARA_A_3__ETAPA_DO_EDITAL_CAPES_N__08.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15052024_Lista_Listagem_2374115_Inscritos_MIR.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alteraçãodo Edital nº 08/2022 - Parfor - formato, xls, 119kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20122022_Edital_1880841_Edital_8_2022___PARFOR.pdf/@@display-file/file ; Alteração do Edital nº 08/2022 - Parfor - formato, pdf, 128kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09062022_Edital_1729649_EDITAL___8_2022.pdf/@@display-file/file ; Edital nº 08/2022 - Parfor - formato, pdf, 203kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07022022_Edital_1629612_SEI_CAPES___1628279___Edital_8.pdf/@@display-file/file</t>
+          <t>Alteração do Edital Conjunto nº 01/2024 - Programa Caminhos Amefricanos, formato, pdf, 63kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29042024_Edital_2368101_SEI_2365347_Edital_Conjunto_n__1_CAPES_MIR.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4524,24 +4524,20 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Lista e inscritos do Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 520kb</t>
+          <t>Lista de inscritos do Edital nº 05/2024 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 46kb</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/20022024_Lista_Listagem_2324280_SEI_2323841_Inscritos_MIR.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/10062024_Lista_Listagem_2390159_Lista_de_Inscritos_3.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>4</v>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>Alteração do Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 54kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/12062024_Edital_2395239_SEI_2389783_Edital_34_2023.pdf/@@display-file/file ; Prorrogação do Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 54kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/28122023_Edital_2301024_SEI_2300438_Edital_Conjunto_n__34_2023_Prorrogacao.pdf/@@display-file/file ; Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 129kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/04122024_Edital_2282364_SEI_2279471_Edital_Conjunto_n__34_2023.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4551,24 +4547,20 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Lista final de inscritos no Edital n° 33/2022 - Brafitec, formato, pdf, 372kb</t>
+          <t>Lista de inscritos doEdital nº 8/202 - CAPES/COFECUB, formato, pdf, 581kb</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/22092022_Lista_Listagem_1808291_Lista_inscritos_Brafitec_Edital_33_22.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/14062023_Lista_Listagem_1990268_Inscricoes_cofecub_2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>3</v>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>Alteração do Edital n° 33/2022 - Brafitec, formato, pdf, 193kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23022023_Edital_1920292_Edital_33_22.pdf/@@display-file/file ; Edital n° 33/2022 - Brafitec, formato, pdf, 428kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29062022_EDITAL33_2022_BRAFITEC.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4578,129 +4570,149 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Prorrogação do Edital nº 01/2024 - Programa Caminhos Amefricanos, formato, pdf, 69kb</t>
+          <t>Lista de inscrições - Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 393kb</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/30082024_Edital_2450719_SEI_2446271_Edital_Conjunto_1_2024.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Lista_de_Inscricoes_Homologadas_PDSE___2020_REVISADA.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
-      </c>
-      <c r="G149" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Lista de candidaturas - Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 417kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/documentos/diretoria-de-relacoes-internacionais/pdse/Lista_Listagem_1439062_Lista_de_Inscricoes_Homologadas_PDSE___2020.pdf/@@display-file/file ; Retificação do Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 244kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/EDITAL192020_PDSERETIFICAO.pdf/@@display-file/file ; Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE)- formato, pdf, 236kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09102020_edital-19-pdse.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>SETEC</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Chamada (documento Nº 6991254) para seleção de unidades da Rede Federal de Educação Profissional e Tecnológica e das redes públicas estaduais de Educação Profissional e Tecnológica, interessadas em receber apoio técnico para a implementação de programas de aprendizagem profissional articulados a cursos técnicos ou de qualificação profissional com componentes curriculares relacionados à sustentabilidade</t>
+          <t>Lista de inscrições do Edital nº 17/2025 - Primeira chamada Programa Institucional de Doutorado Sanduíche no Exterior (PDSE) - formato, pdf, 8,8mb</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2026/SEI_6991254_chamada.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/29102025_Lista_Listagem_2708089_PDSE.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>1</v>
-      </c>
-      <c r="G150" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Lista de inscrições do Edital nº 17/2025 - Segunda chamada Programa Institucional de Doutorado Sanduíche no Exterior (PDSE) - formato, pdf, 1,4mb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/27042026_Lista_Listagem_2808119_Lista_de_inscricoes_homologadas_do_Edital_172025___PDSE___segunda_chamada___formato_pdf__2_.pdf/@@display-file/file ; Alteração do Edital nº 17/2025 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE), formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/08102025_Edital_2696973_SEI_2695934_Edital_17_2025__.pdf/@@display-file/file ; Edital nº 17/2025 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 142kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/21082025_Edital_2662823_SEI_2661209_Edital_n__17_2025.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SETEC</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Chamada Pública com o objetivo de identificar, avaliar, cadastrar e disponibilizar metodologias, ferramentas e estudos sobre o mapeamento de demandas por Educação Profissional Técnica de Nível Médio, visando aprimorar a definição de ofertas de Educação Profissional Técnica de Nível Médio, no âmbito do Programa Juros por Educação.</t>
+          <t>Lista de instituições e cursos pré-aprovados para a 3ª fase do Edital nº 08/2022 - Parfor - formato, pdf, 715kb</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/SEI_6268868_Resultado_de_Edital.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/06052022_Relacao_1700579_LISTA_DE_IES_E_CURSOS_APROVADOS_PARA_A_3__ETAPA_DO_EDITAL_CAPES_N__08.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>1</v>
-      </c>
-      <c r="G151" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Alteraçãodo Edital nº 08/2022 - Parfor - formato, xls, 119kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20122022_Edital_1880841_Edital_8_2022___PARFOR.pdf/@@display-file/file ; Alteração do Edital nº 08/2022 - Parfor - formato, pdf, 128kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09062022_Edital_1729649_EDITAL___8_2022.pdf/@@display-file/file ; Edital nº 08/2022 - Parfor - formato, pdf, 203kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07022022_Edital_1629612_SEI_CAPES___1628279___Edital_8.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SETEC</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Chamada Pública de Adesão das Instituições da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT), com objetivo de capacitação técnica para submissão de propostas em futuros editais de unidades Embrapii.</t>
+          <t>Lista e inscritos do Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 520kb</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/edital-2025/SEI_MEC5650163ResultadodeEdital_.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/20022024_Lista_Listagem_2324280_SEI_2323841_Inscritos_MIR.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>1</v>
-      </c>
-      <c r="G152" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Alteração do Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 54kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/12062024_Edital_2395239_SEI_2389783_Edital_34_2023.pdf/@@display-file/file ; Prorrogação do Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 54kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/28122023_Edital_2301024_SEI_2300438_Edital_Conjunto_n__34_2023_Prorrogacao.pdf/@@display-file/file ; Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 129kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/04122024_Edital_2282364_SEI_2279471_Edital_Conjunto_n__34_2023.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>SETEC</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Chamada Pública de Adesão à linha de fomento Qualifica Mais EnergIFE</t>
+          <t>Lista final de inscritos no Edital n° 33/2022 - Brafitec, formato, pdf, 372kb</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/chamadapublica.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/22092022_Lista_Listagem_1808291_Lista_inscritos_Brafitec_Edital_33_22.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1</v>
-      </c>
-      <c r="G153" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Alteração do Edital n° 33/2022 - Brafitec, formato, pdf, 193kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23022023_Edital_1920292_Edital_33_22.pdf/@@display-file/file ; Edital n° 33/2022 - Brafitec, formato, pdf, 428kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29062022_EDITAL33_2022_BRAFITEC.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>SETEC</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 01/2017 - Trata-se de chamada pública para seleção de servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) para capacitação em Gestão da Inovação.</t>
+          <t>Prorrogação do Edital nº 01/2024 - Programa Caminhos Amefricanos, formato, pdf, 69kb</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/extrato_chamada_dou_cp_01_2017.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/30082024_Edital_2450719_SEI_2446271_Edital_Conjunto_1_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F154" t="n">
@@ -4716,14 +4728,14 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 01/2018 - Trata-se da chamada pública para seleção de propostas e servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) em efetivo exercício, para participarem da capacitação em Gestão da Inovação (GI - CSIRO).</t>
+          <t>Chamada (documento Nº 6991254) para seleção de unidades da Rede Federal de Educação Profissional e Tecnológica e das redes públicas estaduais de Educação Profissional e Tecnológica, interessadas em receber apoio técnico para a implementação de programas de aprendizagem profissional articulados a cursos técnicos ou de qualificação profissional com componentes curriculares relacionados à sustentabilidade</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/20181030Edital012018ChamadaPblicaGICSIRO.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2026/SEI_6991254_chamada.pdf</t>
         </is>
       </c>
       <c r="F155" t="n">
@@ -4739,14 +4751,14 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 02/2017 - Trata-se de chamada pública para concurso sobre educação profissional da Secretaria de Educação Profissional e Tecnológica (Setec/MEC) em parceria com a Comunidade dos Países de Língua Portuguesa (CPLP).</t>
+          <t>Chamada Pública com o objetivo de identificar, avaliar, cadastrar e disponibilizar metodologias, ferramentas e estudos sobre o mapeamento de demandas por Educação Profissional Técnica de Nível Médio, visando aprimorar a definição de ofertas de Educação Profissional Técnica de Nível Médio, no âmbito do Programa Juros por Educação.</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/edital_concurso_cplp_2017.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/SEI_6268868_Resultado_de_Edital.pdf</t>
         </is>
       </c>
       <c r="F156" t="n">
@@ -4762,14 +4774,14 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 02/2018 - Trata-se da chamada pública para seleção de servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) para a capacitação Brasileiros Formando Formadores (BraFF).</t>
+          <t>Chamada Pública de Adesão das Instituições da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT), com objetivo de capacitação técnica para submissão de propostas em futuros editais de unidades Embrapii.</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/Edital_02_2018_BRAFF.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/edital-2025/SEI_MEC5650163ResultadodeEdital_.pdf</t>
         </is>
       </c>
       <c r="F157" t="n">
@@ -4785,14 +4797,14 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 38/2018 - Trata do processo de seleção de propostas para credenciamento de instituições da Rede Federal, Faculdades de Tecnologia do Estado de São Paulo (Fatecs) e do Instituto Tecnológico de Aeronáutica (ITA) para atuação como Núcleo de Línguas (NucLi-IsF) no âmbito do Programa Idiomas sem Fronteiras (IsF).</t>
+          <t>Chamada Pública de Adesão à linha de fomento Qualifica Mais EnergIFE</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/Editaln382018ChamadaPblicaparacredenciamentodeinstituiesdaRFEPCTdasFatecsedoITA.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/chamadapublica.pdf</t>
         </is>
       </c>
       <c r="F158" t="n">
@@ -4808,14 +4820,14 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 79/2016 - Trata-se de chamada pública para apresentação de propostas por instituição de educação profissional e tecnológica para a oferta de cursos de formação inicial e continuada ou de qualificação profissional e cursos técnicos de nível médio, presenciais ou à distância, sem transferência de recursos, no âmbito do PRONATEC, denominada “PROPOSTAS VOLUNTÁRIAS - PRONATEC”</t>
+          <t>Chamada Pública nº 01/2017 - Trata-se de chamada pública para seleção de servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) para capacitação em Gestão da Inovação.</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/extrato_edital_79_2016_setec.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/extrato_chamada_dou_cp_01_2017.pdf</t>
         </is>
       </c>
       <c r="F159" t="n">
@@ -4831,14 +4843,14 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Chamada Pública que estabelece os procedimentos para a autorização de oferta de cursos técnicos de nível médio por Instituições Privadas de Ensino Superior (IPES) para fins de habilitação ao Programa Juros por Educação, no âmbito do Programa de Pleno Pagamento de Dívidas dos Estados (Propag).</t>
+          <t>Chamada Pública nº 01/2018 - Trata-se da chamada pública para seleção de propostas e servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) em efetivo exercício, para participarem da capacitação em Gestão da Inovação (GI - CSIRO).</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/FAQEdital6.2025.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/20181030Edital012018ChamadaPblicaGICSIRO.pdf</t>
         </is>
       </c>
       <c r="F160" t="n">
@@ -4854,14 +4866,14 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Chamamento Público para credenciamento de profissionais no Banco de Especialistas para atuar no Projeto Assistec Inova, junto ao Ministério da Educação, no âmbito da Secretaria de Educação Profissional e Tecnológica.</t>
+          <t>Chamada Pública nº 02/2017 - Trata-se de chamada pública para concurso sobre educação profissional da Secretaria de Educação Profissional e Tecnológica (Setec/MEC) em parceria com a Comunidade dos Países de Língua Portuguesa (CPLP).</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/SEI_23000.035944_2024_89.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/edital_concurso_cplp_2017.pdf</t>
         </is>
       </c>
       <c r="F161" t="n">
@@ -4877,14 +4889,14 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Edital 1/2026 - Chamada Pública de Adesão dos Institutos Federais de Educação, Ciência e Tecnologia, do Centro Federal de Educação Tecnológica Celso Suckow da Fonseca, do Centro Federal de Educação Tecnológica de Minas Gerais e do Colégio Pedro II, com objetivo de capacitação técnica para submissão de propostas em futuros editais de Unidades Embrapii.</t>
+          <t>Chamada Pública nº 02/2018 - Trata-se da chamada pública para seleção de servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) para a capacitação Brasileiros Formando Formadores (BraFF).</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/edital12026.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/Edital_02_2018_BRAFF.pdf</t>
         </is>
       </c>
       <c r="F162" t="n">
@@ -4900,14 +4912,14 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Edital 84/2021 - Seleção de Projetos para desenvolvimento dos Ambientes de Promotores de Inovação na Rede Federal</t>
+          <t>Chamada Pública nº 38/2018 - Trata do processo de seleção de propostas para credenciamento de instituições da Rede Federal, Faculdades de Tecnologia do Estado de São Paulo (Fatecs) e do Instituto Tecnológico de Aeronáutica (ITA) para atuação como Núcleo de Línguas (NucLi-IsF) no âmbito do Programa Idiomas sem Fronteiras (IsF).</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/editais/2022/ResultadoetapaI.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/Editaln382018ChamadaPblicaparacredenciamentodeinstituiesdaRFEPCTdasFatecsedoITA.pdf</t>
         </is>
       </c>
       <c r="F163" t="n">
@@ -4923,14 +4935,14 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Edital nº 01/2017 - APRESENTAÇÃO DE PROPOSTAS PARA A OFERTA DE VAGAS GRATUITAS EM CURSOS TÉCNICOS NA FORMA CONCOMITANTE, NO ÂMBITO DO PRONATEC/MEDIOTEC – 2º/2017 - A Secretária de Educação Profissional e Tecnológica do Ministério da Educação, no uso da atribuição que lhe confere o art. 13, Anexo I, do Decreto n° 7.690, de 02 de março de 2012, e considerando o disposto na Lei nº 12.513, de 26 de outubro de 2011, a Portaria nº 817, de 13 de agosto de 2015, a Portaria nº160, de 05 de março de 2013, alterada pela Portaria nº 701, de 13 de agosto de 2014, TORNA PÚBLICO os procedimentos e o cronograma para a apresentação de propostas visando a oferta de vagas gratuitas em cursos técnicos na forma concomitante e na modalidade presencial, no âmbito do Programa Nacional de Acesso ao Ensino Técnico e Emprego - PRONATEC, por meio da ação MEDIOTEC, para ingresso no segundo semestre de 2017.</t>
+          <t>Chamada Pública nº 79/2016 - Trata-se de chamada pública para apresentação de propostas por instituição de educação profissional e tecnológica para a oferta de cursos de formação inicial e continuada ou de qualificação profissional e cursos técnicos de nível médio, presenciais ou à distância, sem transferência de recursos, no âmbito do PRONATEC, denominada “PROPOSTAS VOLUNTÁRIAS - PRONATEC”</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/edital_01_mediotec_2017.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/extrato_edital_79_2016_setec.pdf</t>
         </is>
       </c>
       <c r="F164" t="n">
@@ -4946,14 +4958,14 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Edital nº 08/2024 - Chamamento Público visando à seleção de autores(as) para elaboração de capítulos de obra a ser publicada cuja temática central é a gestão de Núcleos de Inovação Tecnológica (NITs) e/ou de Agências de Inovação da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) Divulgação das Inscrições Homologadas</t>
+          <t>Chamada Pública que estabelece os procedimentos para a autorização de oferta de cursos técnicos de nível médio por Instituições Privadas de Ensino Superior (IPES) para fins de habilitação ao Programa Juros por Educação, no âmbito do Programa de Pleno Pagamento de Dívidas dos Estados (Propag).</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/436.SEI_MEC5030251Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/FAQEdital6.2025.pdf</t>
         </is>
       </c>
       <c r="F165" t="n">
@@ -4969,14 +4981,14 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Edital nº 1/2023 - Seleção de proposta de selo comemorativo, em alusão aos 15 anos dos Institutos Federais.</t>
+          <t>Chamamento Público para credenciamento de profissionais no Banco de Especialistas para atuar no Projeto Assistec Inova, junto ao Ministério da Educação, no âmbito da Secretaria de Educação Profissional e Tecnológica.</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC4094376Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/SEI_23000.035944_2024_89.pdf</t>
         </is>
       </c>
       <c r="F166" t="n">
@@ -4992,14 +5004,14 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Edital nº 100/2022 - Chamamento Público para a seleção de propostas para o Desafio Soutec</t>
+          <t>Edital 1/2026 - Chamada Pública de Adesão dos Institutos Federais de Educação, Ciência e Tecnologia, do Centro Federal de Educação Tecnológica Celso Suckow da Fonseca, do Centro Federal de Educação Tecnológica de Minas Gerais e do Colégio Pedro II, com objetivo de capacitação técnica para submissão de propostas em futuros editais de Unidades Embrapii.</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/secretarias/secretaria-de-educacao-profissional/editais-2022/SEI_MEC3570188Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/edital12026.pdf</t>
         </is>
       </c>
       <c r="F167" t="n">
@@ -5015,14 +5027,14 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Edital nº 109/2022 - Chamamento Público - Seleção de projetos voltados à promoção do empreendedorismo inovador, com foco na Economia 4.0, associados ao ensino, à pesquisa e à extensão, destinado às instituições integrantes da Rede Federal de Educação Profissional, Científica e Tecnológica</t>
+          <t>Edital 84/2021 - Seleção de Projetos para desenvolvimento dos Ambientes de Promotores de Inovação na Rede Federal</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital109.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/editais/2022/ResultadoetapaI.pdf</t>
         </is>
       </c>
       <c r="F168" t="n">
@@ -5038,14 +5050,14 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Edital nº 11/2024 - Chamamento Público para a seleção de projetos aptos a integrarem a 4ª Semana Nacional de Educação Profissional e Tecnológica Retificação do</t>
+          <t>Edital nº 01/2017 - APRESENTAÇÃO DE PROPOSTAS PARA A OFERTA DE VAGAS GRATUITAS EM CURSOS TÉCNICOS NA FORMA CONCOMITANTE, NO ÂMBITO DO PRONATEC/MEDIOTEC – 2º/2017 - A Secretária de Educação Profissional e Tecnológica do Ministério da Educação, no uso da atribuição que lhe confere o art. 13, Anexo I, do Decreto n° 7.690, de 02 de março de 2012, e considerando o disposto na Lei nº 12.513, de 26 de outubro de 2011, a Portaria nº 817, de 13 de agosto de 2015, a Portaria nº160, de 05 de março de 2013, alterada pela Portaria nº 701, de 13 de agosto de 2014, TORNA PÚBLICO os procedimentos e o cronograma para a apresentação de propostas visando a oferta de vagas gratuitas em cursos técnicos na forma concomitante e na modalidade presencial, no âmbito do Programa Nacional de Acesso ao Ensino Técnico e Emprego - PRONATEC, por meio da ação MEDIOTEC, para ingresso no segundo semestre de 2017.</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-2024-1/Edital_11.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/edital_01_mediotec_2017.pdf</t>
         </is>
       </c>
       <c r="F169" t="n">
@@ -5061,14 +5073,14 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Edital nº 15/2023 - Chamada Pública para o Workshop para elaboração de Itinerários Formativos em economia circular na Educação Profissional e Tecnológica</t>
+          <t>Edital nº 08/2024 - Chamamento Público visando à seleção de autores(as) para elaboração de capítulos de obra a ser publicada cuja temática central é a gestão de Núcleos de Inovação Tecnológica (NITs) e/ou de Agências de Inovação da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) Divulgação das Inscrições Homologadas</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/SEI_MEC3884064Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/436.SEI_MEC5030251Edital.pdf</t>
         </is>
       </c>
       <c r="F170" t="n">
@@ -5084,14 +5096,14 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Edital nº 2/2020 - IFES, de chamada pública para a seleção de projetos voltados à implementação das Oficinas 4.0, aberto às autarquias da Rede Federal.</t>
+          <t>Edital nº 1/2023 - Seleção de proposta de selo comemorativo, em alusão aos 15 anos dos Institutos Federais.</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://www.ifes.edu.br/chamadas-publicas/19329-chamada-publica-2-2020-apoio-a-implementacao-de-oficinas-4-0</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC4094376Edital.pdf</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -5107,14 +5119,14 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Edital nº 20/2021 – Seleção de servidores para atuação em Projetos de Colaboração Técnica junto ao Ministério da Educação.</t>
+          <t>Edital nº 100/2022 - Chamamento Público para a seleção de propostas para o Desafio Soutec</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/SEI_MEC2573324Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/secretarias/secretaria-de-educacao-profissional/editais-2022/SEI_MEC3570188Edital.pdf</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -5130,14 +5142,14 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Edital nº 25/2023 - Chamada Pública destinada a selecionar equipes da Rede Federal de Educação Profissional, Científica e Tecnológica (EPCT) para participação no projeto de formação em criatividade, inovação e prototipagem do mercosul (Hackathon Mercosul). Retificação do Edital</t>
+          <t>Edital nº 109/2022 - Chamamento Público - Seleção de projetos voltados à promoção do empreendedorismo inovador, com foco na Economia 4.0, associados ao ensino, à pesquisa e à extensão, destinado às instituições integrantes da Rede Federal de Educação Profissional, Científica e Tecnológica</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/SEI_MEC3913111Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital109.pdf</t>
         </is>
       </c>
       <c r="F173" t="n">
@@ -5153,14 +5165,14 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Edital nº 26 versão consolidada</t>
+          <t>Edital nº 11/2024 - Chamamento Público para a seleção de projetos aptos a integrarem a 4ª Semana Nacional de Educação Profissional e Tecnológica Retificação do</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC3980995Documento.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-2024-1/Edital_11.pdf</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -5176,14 +5188,14 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Edital nº 3/2021 – Chamada Pública para seleção de projetos de iniciação tecnológica com foco na Economia 4.0. Acesse o edital .</t>
+          <t>Edital nº 15/2023 - Chamada Pública para o Workshop para elaboração de Itinerários Formativos em economia circular na Educação Profissional e Tecnológica</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://www.ifes.edu.br/chamadas-publicas/19351-chamada-publica-3-2020-projetos-iniciacao-tecnologica-economia-4-0</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/SEI_MEC3884064Edital.pdf</t>
         </is>
       </c>
       <c r="F175" t="n">
@@ -5199,24 +5211,20 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Edital nº 35/2020 - Chamada Pública - que tem como objetivo selecionar projetos voltados à criação de Laboratórios IFMaker junto aos Institutos Federais de Educação, Ciência e Tecnologia; Centros Federais de Educação Tecnológica Celso Suckow da Fonseca – Cefet-RJ e de Minas Gerais – Cefet-MG e o Colégio Pedro II, conforme especificado no Despacho SEI nº 2064854</t>
+          <t>Edital nº 2/2020 - IFES, de chamada pública para a seleção de projetos voltados à implementação das Oficinas 4.0, aberto às autarquias da Rede Federal.</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2020/SEI_MEC_2064339_Edital_Chamada_Publica.pdf</t>
+          <t>https://www.ifes.edu.br/chamadas-publicas/19329-chamada-publica-2-2020-apoio-a-implementacao-de-oficinas-4-0</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>2</v>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>Retificação Edital nº 35/2020 - Chamada Pública - Seleção de projetos voltados à criação de Laboratórios Maker junto à Rede Federal de Educação Profissional, Científica e Tecnológica Retificação de Cronograma ​do | https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/AlteraodecronogramaRedeMakeredital35.pdf</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -5226,14 +5234,14 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Edital nº 46, de 20 de julho de 2020, que torna público edital para adesão de estados e Distrito Federal à oferta de Curso de Especialização Lato Sensu em Docência para a Educação Profissional e Tecnológica (DocentEPT) aos professores da rede pública estadual e distrital que atuam na oferta de cursos de Educação Profissional e Tecnológica</t>
+          <t>Edital nº 20/2021 – Seleção de servidores para atuação em Projetos de Colaboração Técnica junto ao Ministério da Educação.</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2020/Editaldeadeso_DOU.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/SEI_MEC2573324Edital.pdf</t>
         </is>
       </c>
       <c r="F177" t="n">
@@ -5249,14 +5257,14 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Edital nº 47/2022 - Chamada Pública para oferta de cursos da Plataforma Aprenda Mais</t>
+          <t>Edital nº 25/2023 - Chamada Pública destinada a selecionar equipes da Rede Federal de Educação Profissional, Científica e Tecnológica (EPCT) para participação no projeto de formação em criatividade, inovação e prototipagem do mercosul (Hackathon Mercosul). Retificação do Edital</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/editais/2022/Editaln47.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/SEI_MEC3913111Edital.pdf</t>
         </is>
       </c>
       <c r="F178" t="n">
@@ -5272,14 +5280,14 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Edital nº 48/2022 - Procedimentos para autorização da oferta de cursos técnicos de nível médio por Instituições Privadas de Ensino Superior – Anexos do</t>
+          <t>Edital nº 26 versão consolidada</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/editais/2022/Editaln48.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC3980995Documento.pdf</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -5295,14 +5303,14 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Edital nº 5 /2026 - Seleção de propostas de projetos de extensão voltados ao Acesso, à Permanência e ao Êxito no âmbito da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT).</t>
+          <t>Edital nº 3/2021 – Chamada Pública para seleção de projetos de iniciação tecnológica com foco na Economia 4.0. Acesse o edital .</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2026/sei_7012727_edital_5.pdf</t>
+          <t>https://www.ifes.edu.br/chamadas-publicas/19351-chamada-publica-3-2020-projetos-iniciacao-tecnologica-economia-4-0</t>
         </is>
       </c>
       <c r="F180" t="n">
@@ -5318,20 +5326,24 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Edital nº 5/2020 – Chamada para seleção de projetos de apoio ao empreendedorismo inovador com foco na Economia 4.0. Acesse o edital .</t>
+          <t>Edital nº 35/2020 - Chamada Pública - que tem como objetivo selecionar projetos voltados à criação de Laboratórios IFMaker junto aos Institutos Federais de Educação, Ciência e Tecnologia; Centros Federais de Educação Tecnológica Celso Suckow da Fonseca – Cefet-RJ e de Minas Gerais – Cefet-MG e o Colégio Pedro II, conforme especificado no Despacho SEI nº 2064854</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://www.ifes.edu.br/chamadas-publicas/19384-chamada-publica-05-2020-selecao-de-projetos-de-apoio-ao-empreendedorismo-inovador-com-foco-na-economia-4-0</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2020/SEI_MEC_2064339_Edital_Chamada_Publica.pdf</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>1</v>
-      </c>
-      <c r="G181" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Retificação Edital nº 35/2020 - Chamada Pública - Seleção de projetos voltados à criação de Laboratórios Maker junto à Rede Federal de Educação Profissional, Científica e Tecnológica Retificação de Cronograma ​do | https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/AlteraodecronogramaRedeMakeredital35.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -5341,14 +5353,14 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Edital nº 5/2021 – IF Mais Empreendedor Nacional : Adesão ao Programa IF Mais Empreendedor Nacional</t>
+          <t>Edital nº 46, de 20 de julho de 2020, que torna público edital para adesão de estados e Distrito Federal à oferta de Curso de Especialização Lato Sensu em Docência para a Educação Profissional e Tecnológica (DocentEPT) aos professores da rede pública estadual e distrital que atuam na oferta de cursos de Educação Profissional e Tecnológica</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/editais/2021/Edital05.2021IFEMPREENDEDORNACIONAL.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2020/Editaldeadeso_DOU.pdf</t>
         </is>
       </c>
       <c r="F182" t="n">
@@ -5364,14 +5376,14 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Edital nº 5/2024 - Seleção de propostas de novos Cursos Abertos, On-line e Massivos (MOOCs), desenvolvidos pela Rede Federa de Educação Profissional, Científica e Tecnológica, a serem disponibilizados na Plataforma APRENDA MAIS.</t>
+          <t>Edital nº 47/2022 - Chamada Pública para oferta de cursos da Plataforma Aprenda Mais</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC4659481Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/editais/2022/Editaln47.pdf</t>
         </is>
       </c>
       <c r="F183" t="n">
@@ -5387,14 +5399,14 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Edital nº 52/2016 – que torna público, para conhecimento dos interessados, que será realizado na modalidade concurso, o PROJETO DESAFIO DA EDUCAÇÃO PROFISSIONAL E TECNOLÓGICA, na forma do REGULAMENTO anexo a este edital, com o objetivo de promover uma campanha nacional para aprimorar a Educação Profissional e Tecnológica estimulando a sociedade a enviar propostas de ações inovadoras e compartilhar experiências exitosas de implementação de ações.</t>
+          <t>Edital nº 48/2022 - Procedimentos para autorização da oferta de cursos técnicos de nível médio por Instituições Privadas de Ensino Superior – Anexos do</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/edital_n_52_2016.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/editais/2022/Editaln48.pdf</t>
         </is>
       </c>
       <c r="F184" t="n">
@@ -5410,14 +5422,14 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Edital nº 55/2016 , que torna público concurso PROJETO DESAFIO EDUCAÇÃO ZIKAZERO, na forma do REGULAMENTO anexo a este edital, com o objetivo de promover uma campanha nacional de mobilização para o enfrentamento ao Aedes aegyp e à microcefalia estimulando a sociedade a enviar propostas de ações inovadoras e compartilhar experiências exitosas de implementação de ações em prol do combate ao mosquito.</t>
+          <t>Edital nº 5 /2026 - Seleção de propostas de projetos de extensão voltados ao Acesso, à Permanência e ao Êxito no âmbito da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT).</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/Edital_55_2016_SEI_MEC_0227936.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2026/sei_7012727_edital_5.pdf</t>
         </is>
       </c>
       <c r="F185" t="n">
@@ -5433,14 +5445,14 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Edital nº 6/2021 - Edital de Adesão das instituições ao Sistema Re-Saber</t>
+          <t>Edital nº 5/2020 – Chamada para seleção de projetos de apoio ao empreendedorismo inovador com foco na Economia 4.0. Acesse o edital .</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/Edital_06_2021.pdf</t>
+          <t>https://www.ifes.edu.br/chamadas-publicas/19384-chamada-publica-05-2020-selecao-de-projetos-de-apoio-ao-empreendedorismo-inovador-com-foco-na-economia-4-0</t>
         </is>
       </c>
       <c r="F186" t="n">
@@ -5456,14 +5468,14 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Edital nº 6/2024 - Edital visa selecionar a proposta de selo/logomarca que será utilizado em confecções comemorativas no contexto dos 115 anos da Rede Federal de Educação Profissional, Científica e Tecnológica, que poderá ser personalizado como selo postal, via Correios. *</t>
+          <t>Edital nº 5/2021 – IF Mais Empreendedor Nacional : Adesão ao Programa IF Mais Empreendedor Nacional</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-2024/325.SEI_MEC4985249Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/editais/2021/Edital05.2021IFEMPREENDEDORNACIONAL.pdf</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -5479,14 +5491,14 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Edital nº 61/2019 – Regulamento do Cadastro de Especialistas para compor o Banco de Avaliadores da Secretaria de Educação Profissional e Tecnológica.</t>
+          <t>Edital nº 5/2024 - Seleção de propostas de novos Cursos Abertos, On-line e Massivos (MOOCs), desenvolvidos pela Rede Federa de Educação Profissional, Científica e Tecnológica, a serem disponibilizados na Plataforma APRENDA MAIS.</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2019/EDITALN612019.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC4659481Edital.pdf</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -5502,14 +5514,14 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Edital nº 63/2021- Seleção de Projetos de Promoção às Indicações Geográficas</t>
+          <t>Edital nº 52/2016 – que torna público, para conhecimento dos interessados, que será realizado na modalidade concurso, o PROJETO DESAFIO DA EDUCAÇÃO PROFISSIONAL E TECNOLÓGICA, na forma do REGULAMENTO anexo a este edital, com o objetivo de promover uma campanha nacional para aprimorar a Educação Profissional e Tecnológica estimulando a sociedade a enviar propostas de ações inovadoras e compartilhar experiências exitosas de implementação de ações.</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/editais/2021/Edital63.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/edital_n_52_2016.pdf</t>
         </is>
       </c>
       <c r="F189" t="n">
@@ -5525,14 +5537,14 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Edital nº 67/2021 - Chamada Pública de Projetos para apoio à implementação das Oficinas 4.0</t>
+          <t>Edital nº 55/2016 , que torna público concurso PROJETO DESAFIO EDUCAÇÃO ZIKAZERO, na forma do REGULAMENTO anexo a este edital, com o objetivo de promover uma campanha nacional de mobilização para o enfrentamento ao Aedes aegyp e à microcefalia estimulando a sociedade a enviar propostas de ações inovadoras e compartilhar experiências exitosas de implementação de ações em prol do combate ao mosquito.</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/SEI_MEC2898796Edital67.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/Edital_55_2016_SEI_MEC_0227936.pdf</t>
         </is>
       </c>
       <c r="F190" t="n">
@@ -5548,14 +5560,14 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Edital nº 68/2019 – Seleção de servidores para atuação em Projetos Educacionais de Colaboração Técnica junto ao Ministério da Educação.</t>
+          <t>Edital nº 6/2021 - Edital de Adesão das instituições ao Sistema Re-Saber</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2019/EDITALN682019.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/Edital_06_2021.pdf</t>
         </is>
       </c>
       <c r="F191" t="n">
@@ -5571,14 +5583,14 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Edital nº 83/2022 – Seleção de propostas de instituições da Rede Federal para a implementação de programa de capacitação de estudantes denominado Oficinas 4.0</t>
+          <t>Edital nº 6/2024 - Edital visa selecionar a proposta de selo/logomarca que será utilizado em confecções comemorativas no contexto dos 115 anos da Rede Federal de Educação Profissional, Científica e Tecnológica, que poderá ser personalizado como selo postal, via Correios. *</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital83.2022.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-2024/325.SEI_MEC4985249Edital.pdf</t>
         </is>
       </c>
       <c r="F192" t="n">
@@ -5594,14 +5606,14 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Edital nº 88/2022 – Seleção de projetos de iniciação tecnológica de instituições da RFEPCT para o desenvolvimento de ações de formação em programação e/ou robótica e/ou cultura maker para estudantes dos anos finais do ensino fundamental (6º ao 9º ano) das redes públicas de ensino. Retificação ​do</t>
+          <t>Edital nº 61/2019 – Regulamento do Cadastro de Especialistas para compor o Banco de Avaliadores da Secretaria de Educação Profissional e Tecnológica.</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital88.2022.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2019/EDITALN612019.pdf</t>
         </is>
       </c>
       <c r="F193" t="n">
@@ -5617,14 +5629,14 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Edital nº 94/2022 – Chamada Pública para a capacitação de multiplicadores em bioeconomia para a Amazônia Legal. Chamada Pública para a Adesão de parceiros ofertantes da Rede Federal de Educação Profissional, Científica e Tecnológica – RFEPCT à linha de fomento Qualifica Mais EnergIFE, voltada à promoção da oferta de cursos na área das Energias Renováveis. Retificação do</t>
+          <t>Edital nº 63/2021- Seleção de Projetos de Promoção às Indicações Geográficas</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Editaln94.2022.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/editais/2021/Edital63.pdf</t>
         </is>
       </c>
       <c r="F194" t="n">
@@ -5640,14 +5652,14 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Edital nº 99/2022 - Chamamento Público para a seleção de projetos de inovação e trabalhos acadêmicos aptos a integrarem a Semana Nacional da Educação Profissional e Tecnológica Retificação do</t>
+          <t>Edital nº 67/2021 - Chamada Pública de Projetos para apoio à implementação das Oficinas 4.0</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/secretarias/secretaria-de-educacao-profissional/SEI_MEC3566713Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/SEI_MEC2898796Edital67.pdf</t>
         </is>
       </c>
       <c r="F195" t="n">
@@ -5663,14 +5675,14 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Programa Setec-Capes/NOVA de capacitação para Professores da Rede Federal de Educação Profissional, Científica e Tecnológica . A Secretaria de Educação Profissional e Tecnológica (Setec) do Ministério da Educação, com apoio da Coordenação de Aperfeiçoamento de Pessoal de Nível Superior (Capes), lançam chamada pública de capacitação para professores de inglês em efetivo exercício na Rede Federal de Educação Profissional - Institutos Federais, Cefets, Escolas Técnicas vinculas às Universidades Federais e Colégio Pedro II. (Retificação publicada no Diário Oficial da União em 02 de junho de 2016)</t>
+          <t>Edital nº 68/2019 – Seleção de servidores para atuação em Projetos Educacionais de Colaboração Técnica junto ao Ministério da Educação.</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2015/chamada_setec_capes_nova_extrato_dou.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2019/EDITALN682019.pdf</t>
         </is>
       </c>
       <c r="F196" t="n">
@@ -5686,24 +5698,20 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Republicação do Edital nº 76/2022 - Chamamento Público para seleção de projetos voltados ao fortalecimento de Núcleos de Inovação Tecnológica e/ou Agências de Inovação.</t>
+          <t>Edital nº 83/2022 – Seleção de propostas de instituições da Rede Federal para a implementação de programa de capacitação de estudantes denominado Oficinas 4.0</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Republicaodoedital76.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital83.2022.pdf</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>2</v>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>Retificação do Edital nº 76/2022 – novo cronograma | https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/SEI_23000.006585_2022_91.pdf</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -5713,14 +5721,14 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições da Rede Federal de Educação Profissional, Científica e Tecnológica).</t>
+          <t>Edital nº 88/2022 – Seleção de projetos de iniciação tecnológica de instituições da RFEPCT para o desenvolvimento de ações de formação em programação e/ou robótica e/ou cultura maker para estudantes dos anos finais do ensino fundamental (6º ao 9º ano) das redes públicas de ensino. Retificação ​do</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/ResultadoEdital10.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital88.2022.pdf</t>
         </is>
       </c>
       <c r="F198" t="n">
@@ -5736,14 +5744,14 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições Privadas de Ensino Superior que ofertam cursos técnicos e Escolas Técnicas Privadas).</t>
+          <t>Edital nº 94/2022 – Chamada Pública para a capacitação de multiplicadores em bioeconomia para a Amazônia Legal. Chamada Pública para a Adesão de parceiros ofertantes da Rede Federal de Educação Profissional, Científica e Tecnológica – RFEPCT à linha de fomento Qualifica Mais EnergIFE, voltada à promoção da oferta de cursos na área das Energias Renováveis. Retificação do</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/ResultadoEdital09.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Editaln94.2022.pdf</t>
         </is>
       </c>
       <c r="F199" t="n">
@@ -5759,20 +5767,139 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições Públicas Estaduais e Distrital de Educação Profissional e Tecnológica).</t>
+          <t>Edital nº 99/2022 - Chamamento Público para a seleção de projetos de inovação e trabalhos acadêmicos aptos a integrarem a Semana Nacional da Educação Profissional e Tecnológica Retificação do</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/secretarias/secretaria-de-educacao-profissional/SEI_MEC3566713Edital.pdf</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>1</v>
+      </c>
+      <c r="G200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>SETEC</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Programa Setec-Capes/NOVA de capacitação para Professores da Rede Federal de Educação Profissional, Científica e Tecnológica . A Secretaria de Educação Profissional e Tecnológica (Setec) do Ministério da Educação, com apoio da Coordenação de Aperfeiçoamento de Pessoal de Nível Superior (Capes), lançam chamada pública de capacitação para professores de inglês em efetivo exercício na Rede Federal de Educação Profissional - Institutos Federais, Cefets, Escolas Técnicas vinculas às Universidades Federais e Colégio Pedro II. (Retificação publicada no Diário Oficial da União em 02 de junho de 2016)</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr"/>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2015/chamada_setec_capes_nova_extrato_dou.pdf</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>1</v>
+      </c>
+      <c r="G201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>SETEC</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Republicação do Edital nº 76/2022 - Chamamento Público para seleção de projetos voltados ao fortalecimento de Núcleos de Inovação Tecnológica e/ou Agências de Inovação.</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr"/>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Republicaodoedital76.pdf</t>
+        </is>
+      </c>
+      <c r="F202" t="n">
+        <v>2</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Retificação do Edital nº 76/2022 – novo cronograma | https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/SEI_23000.006585_2022_91.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>SETEC</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições da Rede Federal de Educação Profissional, Científica e Tecnológica).</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr"/>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/ResultadoEdital10.pdf</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
+        <v>1</v>
+      </c>
+      <c r="G203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>SETEC</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições Privadas de Ensino Superior que ofertam cursos técnicos e Escolas Técnicas Privadas).</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr"/>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/ResultadoEdital09.pdf</t>
+        </is>
+      </c>
+      <c r="F204" t="n">
+        <v>1</v>
+      </c>
+      <c r="G204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>SETEC</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições Públicas Estaduais e Distrital de Educação Profissional e Tecnológica).</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr"/>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr">
+        <is>
           <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/2147-resultado-preliminar.pdf</t>
         </is>
       </c>
-      <c r="F200" t="n">
-        <v>1</v>
-      </c>
-      <c r="G200" t="inlineStr"/>
+      <c r="F205" t="n">
+        <v>1</v>
+      </c>
+      <c r="G205" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/editais.xlsx
+++ b/editais.xlsx
@@ -1560,11 +1560,11 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Edital nº 26/2025 - Alteração, formato, pdf, 114kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2878184_edital_26_2025___alteracao.pdf/@@display-file/file ; Alteração do edital nº 26/2025 - Política de Novação para Bolsistas e Ex-Bolsistas no Exterior, formato - pdf, 60,5kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11052026_Edital_2817202_SEI_2816655_Edital_n__26_2025___Alteracao.pdf</t>
+          <t>Edital nº 26/2025 - Alteração, formato, pdf, 114kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2878184_edital_26_2025___alteracao.pdf/@@display-file/file ; Retificação_Edital nº 26/2025 - Alteração, formato, pdf, 115kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2879083_edital_26_2025___retificacao.pdf/@@display-file/file ; Alteração do edital nº 26/2025 - Política de Novação para Bolsistas e Ex-Bolsistas no Exterior, formato - pdf, 60,5kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11052026_Edital_2817202_SEI_2816655_Edital_n__26_2025___Alteracao.pdf</t>
         </is>
       </c>
     </row>
@@ -1854,11 +1854,11 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Prorrogação Edital Conjunto nº 1/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México, formato pdf, 65,6kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2855428_sei_2855023_edital_conjunto_n__1_2026___prorrogacao.pdf/@@display-file/file ; Lista de inscritos Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Angola e México, formato pdf, 435kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/01042026_Lista_Listagem_2788855_Lista_de_inscritos_Angola_e_Mexico.pdf/@@display-file/file ; Lista de inscritos Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México, formato pdf, 421kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/12032026_Lista_Listagem_2780399_Lista_de_Inscritos_Panama.pdf/@@display-file/file ; Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México - Retificação do Cumprimento de decisão judicial, formato pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/13022026_Edital_2768872_SEI_2768349_Edital_Conjunto_n__1_2026____Retificacao_de_Decisao_Judicial.pdf/@@display-file/file ; Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México - Cumprimento de decisão judicial, formato pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11022026_Edital_2766993_SEI_2766572_Edital_Conjunto_1_2026_.pdf/@@display-file/file ; Alteração do edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México, formato pdf, 81kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/03022026_Edital_2762271_SEI_2757276_Edital_Conjunto_n__1_2026_CAPES_MIR_____1_.pdf/@@display-file/file ; Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México, formato pdf, 151kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09012026_Edital_2748950_SEI_2748603_Edital_Conjunto_n__1_2026.pdf/@@display-file/file ; Alteração do edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesPanamá, Angola e México, formato pdf, 81kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/03022026_Edital_2762271_SEI_2757276_Edital_Conjunto_n__1_2026_CAPES_MIR_____1_.pdf ; Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesPanamá, Angola e México - Cumprimento de decisão judicial, formato pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11022026_Edital_2766993_SEI_2766572_Edital_Conjunto_1_2026_.pdf ; Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesPanamá, Angola e México - Retificação do Cumprimento de decisão judicial, formato pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/13022026_Edital_2768872_SEI_2768349_Edital_Conjunto_n__1_2026____Retificacao_de_Decisao_Judicial.pdf ; Lista de inscritos Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesPanamá, Angola e México, formato pdf, 421kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/12032026_Lista_Listagem_2780399_Lista_de_Inscritos_Panama.pdf ; Lista de inscritos Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesAngola e México, formato pdf, 435kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/01042026_Lista_Listagem_2788855_Lista_de_inscritos_Angola_e_Mexico.pdf</t>
+          <t>Prorrogação Edital Conjunto nº 1/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México, formato pdf, 65,6kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2855428_sei_2855023_edital_conjunto_n__1_2026___prorrogacao.pdf/@@display-file/file ; Lista de inscritos Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Angola e México, formato pdf, 435kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/01042026_Lista_Listagem_2788855_Lista_de_inscritos_Angola_e_Mexico.pdf/@@display-file/file ; Lista de inscritos Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México, formato pdf, 421kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/12032026_Lista_Listagem_2780399_Lista_de_Inscritos_Panama.pdf/@@display-file/file ; Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México - Retificação do Cumprimento de decisão judicial, formato pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/13022026_Edital_2768872_SEI_2768349_Edital_Conjunto_n__1_2026____Retificacao_de_Decisao_Judicial.pdf/@@display-file/file ; Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México - Cumprimento de decisão judicial, formato pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11022026_Edital_2766993_SEI_2766572_Edital_Conjunto_1_2026_.pdf/@@display-file/file ; Alteração do edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México, formato pdf, 81kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/03022026_Edital_2762271_SEI_2757276_Edital_Conjunto_n__1_2026_CAPES_MIR_____1_.pdf/@@display-file/file ; Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México, formato pdf, 151kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09012026_Edital_2748950_SEI_2748603_Edital_Conjunto_n__1_2026.pdf/@@display-file/file ; Edital Conjunto nº 1/2026 - Prorrogação formato, pdf, 113kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2879086_edital_conjunto_1_2026___prorrogacao.pdf/@@display-file/file ; Alteração do edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesPanamá, Angola e México, formato pdf, 81kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/03022026_Edital_2762271_SEI_2757276_Edital_Conjunto_n__1_2026_CAPES_MIR_____1_.pdf ; Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesPanamá, Angola e México - Cumprimento de decisão judicial, formato pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11022026_Edital_2766993_SEI_2766572_Edital_Conjunto_1_2026_.pdf ; Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesPanamá, Angola e México - Retificação do Cumprimento de decisão judicial, formato pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/13022026_Edital_2768872_SEI_2768349_Edital_Conjunto_n__1_2026____Retificacao_de_Decisao_Judicial.pdf ; Lista de inscritos Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesPanamá, Angola e México, formato pdf, 421kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/12032026_Lista_Listagem_2780399_Lista_de_Inscritos_Panama.pdf ; Lista de inscritos Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesAngola e México, formato pdf, 435kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/01042026_Lista_Listagem_2788855_Lista_de_inscritos_Angola_e_Mexico.pdf</t>
         </is>
       </c>
     </row>
@@ -2009,9 +2009,13 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alteração - Edital nº 6/2026 Programa Rede de Pesquisa e Desenvolvimento da Amazônia Legal - formato, pdf, 125kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2879953_alteracao_edital_6_2026.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">

--- a/editais.xlsx
+++ b/editais.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G205"/>
+  <dimension ref="A1:G207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,27 +456,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5ª Chamada Pública Conjunta - Finep e Conselho Norueguês de Pesquisa (RCN)</t>
+          <t>Chamada Pública CNPq/CAPES Nº 30/2026 – Programa de Mestrado e Doutorado Acadêmico para Inovação – MAI/DAI</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>16/12/2026</t>
+          <t>11/12/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/1019381</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-30-2026/chamada-publica-cnpq-N-30-2026</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -492,57 +492,53 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Chamada Pública CNPq/ERC Nº 21/2026</t>
+          <t>Chamada Pública CNPq/SETEC/SETAD/MCTI/FNDCT Nº 29/2026 – RHAE IA – Recursos Humanos em Áreas Estratégicas – Pesquisador na Empresa – Inteligência Artificial</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-21-2026/chamada-publica-cnpq-N-21-2026</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-29-2026/chamada-publica-cnpq-N-29-2026</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Chamada Pública CNPq/ERC (Conselho Europeu de Pesquisa) Nº 21/2026 | https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-21-2026/chamada-publica-cnpq-N-21-2026</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CNPq</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Chamada CNPq/CT-Biotec/FNDCT/MCTI Nº 24/2026 - Apoio à Pesquisa, Desenvolvimento e Inovação em Biotecnologia</t>
+          <t>5ª Chamada Pública Conjunta - Finep e Conselho Norueguês de Pesquisa (RCN)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>16/12/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-24-2026/chamada-publica-cnpq-N-24-2026</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/1019381</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -553,58 +549,62 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FAPESB</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DIRETRIZES ESPECÍFICAS DA FAPESB – 1ª CHAMADA DA PARCERIA DE MATÉRIAS- PRIMAS PARA A TRANSIÇÃO VERDE E DIGITAL (RAMP) 2026-2027</t>
+          <t>Chamada Pública CNPq/ERC Nº 21/2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>15/02/2027</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/diretrizes-especificas-da-fapesb-1a-chamada-da-parceria-de-materias-primas-para-a-transicao-verde-e-digital-ramp-2026-2027/</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-21-2026/chamada-publica-cnpq-N-21-2026</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Chamada Pública CNPq/ERC (Conselho Europeu de Pesquisa) Nº 21/2026 | https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-21-2026/chamada-publica-cnpq-N-21-2026</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FAPESB</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CHAMADA CDTI ESPANHA (2026-2027) – DIRETRIZES ESPECÍFICAS DA FAPESB</t>
+          <t>Chamada CNPq/CT-Biotec/FNDCT/MCTI Nº 24/2026 - Apoio à Pesquisa, Desenvolvimento e Inovação em Biotecnologia</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/chamada-cdti-espanha-2026-2027-diretrizes-especificas-da-fapesb/</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-24-2026/chamada-publica-cnpq-N-24-2026</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -620,22 +620,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CHAMADA 2026- PROGRAMA DE AUXILIO PARA DOUTORANDOS COM BOLSA NACIONAL – DAAD</t>
+          <t>DIRETRIZES ESPECÍFICAS DA FAPESB – 1ª CHAMADA DA PARCERIA DE MATÉRIAS- PRIMAS PARA A TRANSIÇÃO VERDE E DIGITAL (RAMP) 2026-2027</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>15/02/2027</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/chamada-2026-programa-de-auxilio-para-doutorandos-com-bolsa-nacional-daad/</t>
+          <t>https://www.fapesb.ba.gov.br/diretrizes-especificas-da-fapesb-1a-chamada-da-parceria-de-materias-primas-para-a-transicao-verde-e-digital-ramp-2026-2027/</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -651,18 +651,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CHAMADA GCUB – MOB Nº 2026/2027 – PROGRAMA DE MOBILIDADE INTERNACIONAL DO GCUB (GCUB-MOB)</t>
+          <t>CHAMADA CDTI ESPANHA (2026-2027) – DIRETRIZES ESPECÍFICAS DA FAPESB</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>15/07/2026</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/chamada-gcub-mob-no-20262027-programa-de-mobilidade-internacional-do-gcub-gcub-mob/</t>
+          <t>https://www.fapesb.ba.gov.br/chamada-cdti-espanha-2026-2027-diretrizes-especificas-da-fapesb/</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -673,23 +677,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CNPq</t>
+          <t>FAPESB</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chamada CNPq/MCTI nº 25/2026 - Endometriose e Saúde Menstrual</t>
+          <t>CHAMADA 2026- PROGRAMA DE AUXILIO PARA DOUTORANDOS COM BOLSA NACIONAL – DAAD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-25-2026/chamada-publica-cnpq-N-25-2026</t>
+          <t>https://www.fapesb.ba.gov.br/chamada-2026-programa-de-auxilio-para-doutorandos-com-bolsa-nacional-daad/</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -705,18 +713,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EDITAL DE SELEÇÃO PÚBLICA Nº 017/ 2026 Subvenção Econômica à Pesquisa,Desenvolvimento e Inovação (P,D&amp;I) Soluções de Sistemas Inteligentes para a Administração Estadual – Rodada 2</t>
+          <t>CHAMADA GCUB – MOB Nº 2026/2027 – PROGRAMA DE MOBILIDADE INTERNACIONAL DO GCUB (GCUB-MOB)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/edital-de-selecao-publica-no-017-2026-subvencao-economica-a-pesquisadesenvolvimento-e-inovacao-pdi-solucoes-de-sistemas-inteligentes-para-a-administracao-estadual-rodada-2/</t>
+          <t>https://www.fapesb.ba.gov.br/chamada-gcub-mob-no-20262027-programa-de-mobilidade-internacional-do-gcub-gcub-mob/</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -727,23 +735,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FAPESB</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EDITAL FAPESB No 018/2026 – APOIO À PUBLICAÇÃO CIENTÍFICA, TECNOLÓGICA OU DE POPULARIZAÇÃO DAS CIÊNCIAS</t>
+          <t>Chamada CNPq/MCTI nº 25/2026 - Endometriose e Saúde Menstrual</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/edital-fapesb-no-0182026-apoio-a-publicacao-cientifica-tecnologica-ou-de-popularizacao-das-ciencias/</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-25-2026/chamada-publica-cnpq-N-25-2026</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -759,7 +767,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EDITAL FAPESB/SECTI – Nº 010/2026 – UNIVERSAL</t>
+          <t>EDITAL DE SELEÇÃO PÚBLICA Nº 017/ 2026 Subvenção Econômica à Pesquisa,Desenvolvimento e Inovação (P,D&amp;I) Soluções de Sistemas Inteligentes para a Administração Estadual – Rodada 2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -767,14 +775,10 @@
           <t>03/07/2026</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>03/09/2026</t>
-        </is>
-      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/edital-fapesbsecti-no-0102026-universal/</t>
+          <t>https://www.fapesb.ba.gov.br/edital-de-selecao-publica-no-017-2026-subvencao-economica-a-pesquisadesenvolvimento-e-inovacao-pdi-solucoes-de-sistemas-inteligentes-para-a-administracao-estadual-rodada-2/</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -790,7 +794,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EDITAL FAPESB/SECTI/CNPq/CAPES – No 11/2026 – PROFIX-CB</t>
+          <t>EDITAL FAPESB No 018/2026 – APOIO À PUBLICAÇÃO CIENTÍFICA, TECNOLÓGICA OU DE POPULARIZAÇÃO DAS CIÊNCIAS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -798,14 +802,10 @@
           <t>03/07/2026</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>17/08/2026</t>
-        </is>
-      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/edital-fapesbsecticnpqcapes-no-112026-profix-cb/</t>
+          <t>https://www.fapesb.ba.gov.br/edital-fapesb-no-0182026-apoio-a-publicacao-cientifica-tecnologica-ou-de-popularizacao-das-ciencias/</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -821,7 +821,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EDITAL Nº 019/2026 – CIÊNCIA NA MESA 5: BASE DE DADOS E SISTEMAS DE INFORMAÇÕES PARA TOMADA DE DECISÃO EM SOBERANIA ALIMENTAR E NUTRICIONAL</t>
+          <t>EDITAL FAPESB/SECTI – Nº 010/2026 – UNIVERSAL</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -829,10 +829,14 @@
           <t>03/07/2026</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/edital-no-0192026-ciencia-na-mesa-5-base-de-dados-e-sistemas-de-informacoes-para-tomada-de-decisao-em-soberania-alimentar-e-nutricional/</t>
+          <t>https://www.fapesb.ba.gov.br/edital-fapesbsecti-no-0102026-universal/</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -843,23 +847,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CNPq</t>
+          <t>FAPESB</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Chamamento Público CNPq/FNDCT/MCTI Nº 01/2026 Para Participação no Programa de Apoio à Popularização da Ciência nas Unidades da Federação</t>
+          <t>EDITAL FAPESB/SECTI/CNPq/CAPES – No 11/2026 – PROFIX-CB</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamamento-no-01-2026/chamamento-publico-01-2026</t>
+          <t>https://www.fapesb.ba.gov.br/edital-fapesbsecticnpqcapes-no-112026-profix-cb/</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -870,27 +878,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CNPq</t>
+          <t>FAPESB</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Chamada Pública CNPq/MMULHERES Nº 19/2026 - Programa Asas para o Futuro</t>
+          <t>EDITAL Nº 019/2026 – CIÊNCIA NA MESA 5: BASE DE DADOS E SISTEMAS DE INFORMAÇÕES PARA TOMADA DE DECISÃO EM SOBERANIA ALIMENTAR E NUTRICIONAL</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-19-2026/chamada-publica-cnpq-N-19-2026</t>
+          <t>https://www.fapesb.ba.gov.br/edital-no-0192026-ciencia-na-mesa-5-base-de-dados-e-sistemas-de-informacoes-para-tomada-de-decisao-em-soberania-alimentar-e-nutricional/</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -906,18 +910,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Chamada Pública MCTI/CNPq/MIR/MMulheres/MPI Nº 20/2026 Atlânticas - Programa Beatriz Nascimento de Mulheres na Ciência</t>
+          <t>Chamamento Público CNPq/FNDCT/MCTI Nº 01/2026 Para Participação no Programa de Apoio à Popularização da Ciência nas Unidades da Federação</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-20-2026/chamada-publica-cnpq-N-20-2026</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamamento-no-01-2026/chamamento-publico-01-2026</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -928,12 +932,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BRICs - CHAMADA PÚBLICA Cooperação Multilateral em Inovação</t>
+          <t>Chamada Pública CNPq/MMULHERES Nº 19/2026 - Programa Asas para o Futuro</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -943,12 +947,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/991625</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-19-2026/chamada-publica-cnpq-N-19-2026</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -964,22 +968,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Chamada Pública CNPq/CAPES/MRE N° 16/2026 - Programa de Estudantes-Convênio de Pós-Graduação (PEC-PG)</t>
+          <t>Chamada Pública MCTI/CNPq/MIR/MMulheres/MPI Nº 20/2026 Atlânticas - Programa Beatriz Nascimento de Mulheres na Ciência</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>13/08/2026</t>
-        </is>
-      </c>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-16-2026/chamada-publica-cnpq-N-16-2026</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-20-2026/chamada-publica-cnpq-N-20-2026</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -995,22 +995,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FIP Conexões Startups – 2026</t>
+          <t>BRICs - CHAMADA PÚBLICA Cooperação Multilateral em Inovação</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/986129</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/991625</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1026,22 +1026,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Chamada CNPq/MinC nº 17/2026 - Apoio ao funcionamento de incubadoras voltadas à Economia Criativa</t>
+          <t>Chamada Pública CNPq/CAPES/MRE N° 16/2026 - Programa de Estudantes-Convênio de Pós-Graduação (PEC-PG)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-17-2026/chamada-publica-cnpq-N-17-2026</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-16-2026/chamada-publica-cnpq-N-16-2026</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1057,22 +1057,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Subvenção Descentralizada Seleção de Parceiros em Fluxo Contínuo - Pró Amazônia Empreende</t>
+          <t>FIP Conexões Startups – 2026</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/972778</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/986129</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1088,22 +1088,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Chamada CNPq/FNDCT nº 06/2026 – UNIVERSAL</t>
+          <t>Chamada CNPq/MinC nº 17/2026 - Apoio ao funcionamento de incubadoras voltadas à Economia Criativa</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-06-2026/chamada-publica-cnpq-N-06-2026</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-17-2026/chamada-publica-cnpq-N-17-2026</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1119,22 +1119,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DESAFIO TECNOLÓGICO ELETROLISADOR NACIONAL</t>
+          <t>Subvenção Descentralizada Seleção de Parceiros em Fluxo Contínuo - Pró Amazônia Empreende</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/968467</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/972778</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1145,17 +1145,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CARTA CONVITE MCTI/FINEP - PROGRAMA TECNOVA 2026/2027</t>
+          <t>Chamada CNPq/FNDCT nº 06/2026 – UNIVERSAL</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/958302</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-06-2026/chamada-publica-cnpq-N-06-2026</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1176,23 +1176,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FAPESB</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DIRETRIZES ESPECÍFICAS DA FAPESB – CHAMADA MOBILITY CONFAP ITALY 2026</t>
+          <t>DESAFIO TECNOLÓGICO ELETROLISADOR NACIONAL</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/diretrizes-especificas-da-fapesb-chamada-mobility-confap-italy-2026/</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/968467</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1203,23 +1207,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FAPESB</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Edital 009/2026 – Apoio a Organização de Eventos</t>
+          <t>CARTA CONVITE MCTI/FINEP - PROGRAMA TECNOVA 2026/2027</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/edital-0092026-apoio-a-organizacao-de-eventos/</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/958302</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1230,27 +1238,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>FAPESB</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO UNIDADES DE PESQUISA MCTI – PROINFRA 2026</t>
+          <t>DIRETRIZES ESPECÍFICAS DA FAPESB – CHAMADA MOBILITY CONFAP ITALY 2026</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>07/07/2026</t>
-        </is>
-      </c>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/945796</t>
+          <t>https://www.fapesb.ba.gov.br/diretrizes-especificas-da-fapesb-chamada-mobility-confap-italy-2026/</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1261,27 +1265,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CNPq</t>
+          <t>FAPESB</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Chamada Pública CNPq N° 07/2026 - Programa Institucional de Bolsas de Pós-Graduação (PIBPG)</t>
+          <t>Edital 009/2026 – Apoio a Organização de Eventos</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>05/08/2026</t>
-        </is>
-      </c>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-07-2026/chamada-publica-cnpq-N-07-2026</t>
+          <t>https://www.fapesb.ba.gov.br/edital-0092026-apoio-a-organizacao-de-eventos/</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1297,22 +1297,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CARTA CONVITE MCTI/FINEP/FNDCT - PROMOÇÃO DA AUTONOMIA TECNOLÓGICA NA ÁREA DA DEFESA</t>
+          <t>MANUTENÇÃO UNIDADES DE PESQUISA MCTI – PROINFRA 2026</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/943682</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/945796</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1323,64 +1323,64 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Edital nº 10/2026 - Programas CAPES/MATH/STIC/CLIMAT-AMSUD, formato - pdf, 283kb</t>
+          <t>Chamada Pública CNPq N° 07/2026 - Programa Institucional de Bolsas de Pós-Graduação (PIBPG)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/copy2_of_15042026_Edital_2803264_SEI_2802205_Edital_10_2026.pdf</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-07-2026/chamada-publica-cnpq-N-07-2026</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Alteração Edital nº 10/2026 - Programas CAPES/MATH/STIC/CLIMAT-AMSUD, formato - pdf, 53,1kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/25052026_Edital_2826286_SEI_2825187_Edital_10_2026___alteracao.pdf ; Alteração do Edital  nº 10/2026 - Programas CAPES/MATH/STIC/CLIMAT-AMSUD, formato - pdf, 53,1kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/25052026_Edital_2826286_SEI_2825187_Edital_10_2026___alteracao.pdf</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Edital nº 12/2026 - Programa CAPES/MES-CUBA - Projetos , formato, pdf, 222kb</t>
+          <t>CARTA CONVITE MCTI/FINEP/FNDCT - PROMOÇÃO DA AUTONOMIA TECNOLÓGICA NA ÁREA DA DEFESA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23042026_Edital_2806973_SEI_2806062_Edital_12_2026.pdf</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/943682</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Lista de inscritos do Edital nº 12/2026 - Programa CAPES/MES-CUBA - Projetos, formato, pdf, 148kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/lista_listagem_2857109_lista_de_inscritos_projetos.pdf/@@display-file/file ; Alteração Edital nº 12/2026 - Programa CAPES/MES-CUBA - Projetos , formato, pdf, 53,1kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/25052026_Edital_2826296_SEI_2825183_Edital_12_2026___ALTERACAO.pdf</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1390,18 +1390,18 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Edital nº 13/2026 - Programa CAPES/MES-CUBA - Docentes , formato, pdf, 123kb</t>
+          <t>Edital nº 10/2026 - Programas CAPES/MATH/STIC/CLIMAT-AMSUD, formato - pdf, 283kb</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23042026_Edital_2806981_SEI_2806195_Edital_13_2026.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/copy2_of_15042026_Edital_2803264_SEI_2802205_Edital_10_2026.pdf</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1409,40 +1409,40 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Edital nº 13/2026 - Lista de Inscritos, formarto, pdf, 130kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/lista_listagem_2854147_lista_de_inscritos_docentes.pdf/@@display-file/file ; Alteração Edital nº 13/2026 - Programa CAPES/MES-CUBA - Docentes , formato, pdf, 123kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/25052026_Edital_2826299_SEI_2825184_Edital_13_2026___ALTERACAO.pdf</t>
+          <t>Alteração Edital nº 10/2026 - Programas CAPES/MATH/STIC/CLIMAT-AMSUD, formato - pdf, 53,1kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/25052026_Edital_2826286_SEI_2825187_Edital_10_2026___alteracao.pdf ; Alteração do Edital  nº 10/2026 - Programas CAPES/MATH/STIC/CLIMAT-AMSUD, formato - pdf, 53,1kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/25052026_Edital_2826286_SEI_2825187_Edital_10_2026___alteracao.pdf</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CNPq</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Chamada Pública CNPq/MCTI nº 15/2026 - Programa de Cooperação Afro-Brasileira em Ciência e Tecnologia - PROAFRICA</t>
+          <t>Edital nº 12/2026 - Programa CAPES/MES-CUBA - Projetos , formato, pdf, 222kb</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-15-2026/chamada-publica-cnpq-N-15-2026</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23042026_Edital_2806973_SEI_2806062_Edital_12_2026.pdf</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lista de inscritos do Edital nº 12/2026 - Programa CAPES/MES-CUBA - Projetos, formato, pdf, 148kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/lista_listagem_2857109_lista_de_inscritos_projetos.pdf/@@display-file/file ; Alteração Edital nº 12/2026 - Programa CAPES/MES-CUBA - Projetos , formato, pdf, 53,1kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/25052026_Edital_2826296_SEI_2825183_Edital_12_2026___ALTERACAO.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1452,59 +1452,59 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Edital Conjunto nº 4/2026, formato, pdf, 310kb</t>
+          <t>Edital nº 13/2026 - Programa CAPES/MES-CUBA - Docentes , formato, pdf, 123kb</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19052026_Edital_2823166_EDITAL_CONJUNTO_4_2026___CAPES_CFN.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23042026_Edital_2806981_SEI_2806195_Edital_13_2026.pdf</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Prorrogação - Edital Conjunto nº 4/2026, formato, pdf, 52,5kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/documentos/edital_2863852_sei_2863595_edital_conjunto_n__4_2026___prorrogacao.pdf/@@display-file/file</t>
+          <t>Edital nº 13/2026 - Lista de Inscritos, formarto, pdf, 130kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/lista_listagem_2854147_lista_de_inscritos_docentes.pdf/@@display-file/file ; Alteração Edital nº 13/2026 - Programa CAPES/MES-CUBA - Docentes , formato, pdf, 123kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/25052026_Edital_2826299_SEI_2825184_Edital_13_2026___ALTERACAO.pdf</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Edital CAPES Nº 18/2026 - Programa Cátedra Maison Du Brésil - pdf, 122kb</t>
+          <t>Chamada Pública CNPq/MCTI nº 15/2026 - Programa de Cooperação Afro-Brasileira em Ciência e Tecnologia - PROAFRICA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15052026_Edital_2821031_SEI_2819915_Edital_18_2026.pdf</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-15-2026/chamada-publica-cnpq-N-15-2026</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>3</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Alteração Edital CAPES Nº 18/2026 - Programa Cátedra Maison Du Brésil - pdf, 56,1kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2837190_SEI_2835880_Edital_18__2026___Alteracao.pdf ; Lista de inscritos Edital CAPES Nº 18/2026 - Programa Cátedra Maison Du Brésil - pdf, 116kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/lista_listagem_2853883_lista_de_inscritos.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1514,26 +1514,26 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Edital nº 17/2026 - seleção de projetos conjuntos de pesquisa por chamada no âmbito do Programa CAPES - AUGM</t>
+          <t>Edital Conjunto nº 4/2026, formato, pdf, 310kb</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/copy_of_13052026_Edital_2819298_SEI_2819065_Edital_17_2026.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19052026_Edital_2823166_EDITAL_CONJUNTO_4_2026___CAPES_CFN.pdf</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Edital nº 17/2026 - Relação das Inscrições Recebidas, formato, pdf, 178kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2865911_lista_de_inscritos.pdf/@@display-file/file ; Edital nº 17/2026 - Prorrogação, formato, pdf, 52,5kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2850525_sei_2848632_edital_n__17_2026.pdf/@@display-file/file</t>
+          <t>Prorrogação - Edital Conjunto nº 4/2026, formato, pdf, 52,5kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/documentos/edital_2863852_sei_2863595_edital_conjunto_n__4_2026___prorrogacao.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -1545,59 +1545,59 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Edital nº 26/2025 - Política de Novação para Bolsistas e Ex-Bolsistas no Exterior, formato - pdf, 96kb</t>
+          <t>Edital CAPES Nº 18/2026 - Programa Cátedra Maison Du Brésil - pdf, 122kb</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>22/12/2025</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/22122025_Edital_2740775.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15052026_Edital_2821031_SEI_2819915_Edital_18_2026.pdf</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Edital nº 26/2025 - Alteração, formato, pdf, 114kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2878184_edital_26_2025___alteracao.pdf/@@display-file/file ; Retificação_Edital nº 26/2025 - Alteração, formato, pdf, 115kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2879083_edital_26_2025___retificacao.pdf/@@display-file/file ; Alteração do edital nº 26/2025 - Política de Novação para Bolsistas e Ex-Bolsistas no Exterior, formato - pdf, 60,5kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11052026_Edital_2817202_SEI_2816655_Edital_n__26_2025___Alteracao.pdf</t>
+          <t>Alteração Edital CAPES Nº 18/2026 - Programa Cátedra Maison Du Brésil - pdf, 56,1kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2837190_SEI_2835880_Edital_18__2026___Alteracao.pdf ; Lista de inscritos Edital CAPES Nº 18/2026 - Programa Cátedra Maison Du Brésil - pdf, 116kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/lista_listagem_2853883_lista_de_inscritos.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FAPESB</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CHAMADA CONFAP/ERC 2026 – CALL RESEARCH OPPORTUNITIES IN EUROPE FOR ACTIVE PHD RESEARCHERS FROM BRAZIL</t>
+          <t>Edital nº 17/2026 - seleção de projetos conjuntos de pesquisa por chamada no âmbito do Programa CAPES - AUGM</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>10/07/2026</t>
-        </is>
-      </c>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/chamada-confaperc-2026-call-research-opportunities-in-europe-for-active-phd-researchers-from-brazil/</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/copy_of_13052026_Edital_2819298_SEI_2819065_Edital_17_2026.pdf</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Edital nº 17/2026 - Relação das Inscrições Recebidas, formato, pdf, 178kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2865911_lista_de_inscritos.pdf/@@display-file/file ; Edital nº 17/2026 - Prorrogação, formato, pdf, 52,5kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2850525_sei_2848632_edital_n__17_2026.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1607,76 +1607,80 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Edital nº 15/2026 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 134kb</t>
+          <t>Edital nº 26/2025 - Política de Novação para Bolsistas e Ex-Bolsistas no Exterior, formato - pdf, 96kb</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>22/12/2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/30042026_Edital_2811434_SEI_2811079_Edital_15_2026.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/22122025_Edital_2740775.pdf</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Edital nº 26/2025 - Alteração, formato, pdf, 114kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2878184_edital_26_2025___alteracao.pdf/@@display-file/file ; Retificação_Edital nº 26/2025 - Alteração, formato, pdf, 115kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2879083_edital_26_2025___retificacao.pdf/@@display-file/file ; Alteração do edital nº 26/2025 - Política de Novação para Bolsistas e Ex-Bolsistas no Exterior, formato - pdf, 60,5kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11052026_Edital_2817202_SEI_2816655_Edital_n__26_2025___Alteracao.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>FAPESB</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Edital conjunto ProEB e Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edição Moçambique nº 3/2026 - formato, pdf, 128kb</t>
+          <t>CHAMADA CONFAP/ERC 2026 – CALL RESEARCH OPPORTUNITIES IN EUROPE FOR ACTIVE PHD RESEARCHERS FROM BRAZIL</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/28042026_Edital_2809885_SEI_2804920_Edital_Conjunto_3_2026.pdf</t>
+          <t>https://www.fapesb.ba.gov.br/chamada-confaperc-2026-call-research-opportunities-in-europe-for-active-phd-researchers-from-brazil/</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>4</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Alteração - Edital Conjunto nº 3/2026 - ProEB e Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul - Edição Moçambique | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2827276_SEI_2826404_Edital_Conjunto_n__3_2026.pdf ; Retificação - Edital Conjunto nº 3/2026 - ProEB e Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul - Edição Moçambique | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2824561_Edital_Conjunto_n__03.2026.pdf ; Alteração - Edital conjunto ProEB e Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edição Moçambique nº 3/2026 - formato, pdf, 64,1kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2858440_sei_2857414_edital_conjunto_n__3_2026___alteracao.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CNPq</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Chamada CNPq/SETEC/MCTI N° 13/2026 - Apoio a Eventos de Promoção do Empreendedorismo e da Inovação no Brasil</t>
+          <t>Edital nº 15/2026 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 134kb</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-13-2026/chamada-publica-cnpq-N-13-2026</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/30042026_Edital_2811434_SEI_2811079_Edital_15_2026.pdf</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1692,55 +1696,55 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Edital nº 11/2026 - Programa Cátedra Jorge Amado, formato, pdf, 196kb</t>
+          <t>Edital conjunto ProEB e Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edição Moçambique nº 3/2026 - formato, pdf, 128kb</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23042026_Edital_2806958_SEI_2806040_Edital_11_2026.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/28042026_Edital_2809885_SEI_2804920_Edital_Conjunto_3_2026.pdf</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alteração - Edital Conjunto nº 3/2026 - ProEB e Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul - Edição Moçambique | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2827276_SEI_2826404_Edital_Conjunto_n__3_2026.pdf ; Retificação - Edital Conjunto nº 3/2026 - ProEB e Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul - Edição Moçambique | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2824561_Edital_Conjunto_n__03.2026.pdf ; Alteração - Edital conjunto ProEB e Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edição Moçambique nº 3/2026 - formato, pdf, 64,1kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2858440_sei_2857414_edital_conjunto_n__3_2026___alteracao.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Edital nº 5/2026 - Programa CAPES - PURDUE deProjetos conjuntos de pesquisa, formato, pdf, 257kb</t>
+          <t>Chamada CNPq/SETEC/MCTI N° 13/2026 - Apoio a Eventos de Promoção do Empreendedorismo e da Inovação no Brasil</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09032026_Edital_2780596_SEI_2779319_Edital_5__de_2026.pdf</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-13-2026/chamada-publica-cnpq-N-13-2026</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>5</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Lista de inscritos do Edital nº 5/2026 - Programa CAPES - PURDUE de Projetos conjuntos de pesquisa, formato, pdf, 144kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Lista_Listagem_2841625_Lista_de_inscritos.pdf/@@display-file/file ; Alteração do Edital nº 5/2026 - Programa CAPES - PURDUE de Projetos conjuntos de pesquisa, formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15042026_Edital_2803256_SEI_2801466_Edital_5__de_2026.pdf/@@display-file/file ; Edital nº 5/2026 - Programa CAPES - PURDUE de Projetos conjuntos de pesquisa, formato, pdf, 257kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09032026_Edital_2780596_SEI_2779319_Edital_5__de_2026.pdf/@@display-file/file ; Alteração do Edital nº 5/2026 - Programa CAPES - PURDUE deProjetos conjuntos de pesquisa,formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15042026_Edital_2803256_SEI_2801466_Edital_5__de_2026.pdf</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1750,59 +1754,55 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Edital CAPES/DAAD Probral nº 08/2026, formato - pdf, 214kb</t>
+          <t>Edital nº 11/2026 - Programa Cátedra Jorge Amado, formato, pdf, 196kb</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/01042026_Edital_2795382_SEI_2794361_Edital_8__de_2026.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23042026_Edital_2806958_SEI_2806040_Edital_11_2026.pdf</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>3</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Lista de Inscritos - Edital nº 08/2026, formato - pdf, 199 kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/lista_listagem_2841542_lista_de_inscritos.pdf/@@display-file/file ; Alteração do Edital CAPES/DAAD Probral nº 08/2026, formato - pdf, 48kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/13042026_Edital_2801456_SEI_2800616_Edital_8_2026.pdf</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FIP Startup Inteligência Artificial</t>
+          <t>Edital nº 5/2026 - Programa CAPES - PURDUE deProjetos conjuntos de pesquisa, formato, pdf, 257kb</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/756012</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09032026_Edital_2780596_SEI_2779319_Edital_5__de_2026.pdf</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Lista de inscritos do Edital nº 5/2026 - Programa CAPES - PURDUE de Projetos conjuntos de pesquisa, formato, pdf, 144kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Lista_Listagem_2841625_Lista_de_inscritos.pdf/@@display-file/file ; Alteração do Edital nº 5/2026 - Programa CAPES - PURDUE de Projetos conjuntos de pesquisa, formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15042026_Edital_2803256_SEI_2801466_Edital_5__de_2026.pdf/@@display-file/file ; Edital nº 5/2026 - Programa CAPES - PURDUE de Projetos conjuntos de pesquisa, formato, pdf, 257kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09032026_Edital_2780596_SEI_2779319_Edital_5__de_2026.pdf/@@display-file/file ; Alteração do Edital nº 5/2026 - Programa CAPES - PURDUE deProjetos conjuntos de pesquisa,formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15042026_Edital_2803256_SEI_2801466_Edital_5__de_2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1812,55 +1812,59 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Edital n° 14/2022 - formato, pdf, 380kb</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>Edital CAPES/DAAD Probral nº 08/2026, formato - pdf, 214kb</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/08062022_Lista_Listagem_1727316_Humboldt.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/01042026_Edital_2795382_SEI_2794361_Edital_8__de_2026.pdf</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lista de Inscritos no Edital nº 14/2022 do Programa de Bolsas para Pesquisa CAPES/Humboldt - 26° chamada | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Lista_de_inscritos_26_chamada.pdf/@@display-file/file ; Lista de inscritos - Chamada nª 23 do Edital n° 14/2022 - formato, pdf, 396kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/18122024_SEI_CAPES___2508050___Edital_Minuta_ok.pdf/@@display-file/file ; Lista de inscritos - Chamada nº 22 do Edital n° 14/2022 - formato, pdf, 99kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/17062024_Lista_Listagem_2395643_Lista_de_inscritos.pdf/@@display-file/file ; Lista de inscritos - Chamada nº 21 do Edital n° 14/2022 - formato, pdf, 151kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/22122023_Lista_Listagem_2297511_Lista_de_inscritos_21_.pdf/@@display-file/file ; Lista de inscritos - Chamada nª 20 do Edital 14/2022, formato , pdf, 391kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/Lista_Listagem_2001777_Lista_de_inscritos_final_2.pdf/@@display-file/file ; Relação final das inscrições recebidas - Chamada nº 19 do Edital n° 14/2022 - formato, pdf, 380kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/13122022_Lista_Listagem_1874367_Lista_Inscritos_Humboldt__1_.pdf/@@display-file/file ; Relação das inscrições recebidas do Editaln°14/2022 - formato, pdf, 372kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/20092022_Lista_Listagem_1805835_Lista_Final_Humboldt_pdf_para_word_edital_14_22.pdf/@@display-file/file ; Lista de Inscritos - Chamada nº 24 do Edital nº 14/2022 - formato, pdf, 150kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/17062025_Lista_Listagem_2616980_Lista_de_inscritos_24_chamada.pdf ; Lista de Inscritos - Chamada nº 25 do Edital nº 14/2022 - formato, pdf, 241kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/17122025_Lista_Listagem_2735806_SEI___23038.004870_2021_69_25__chamada.pdf ; Alteração do Edital n° 14/2022 - formato, pdf, 49kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/06042026_Edital_2797322_SEI_2796265_Edital_14__de_2022.pdf</t>
+          <t>Lista de Inscritos - Edital nº 08/2026, formato - pdf, 199 kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/lista_listagem_2841542_lista_de_inscritos.pdf/@@display-file/file ; Alteração do Edital CAPES/DAAD Probral nº 08/2026, formato - pdf, 48kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/13042026_Edital_2801456_SEI_2800616_Edital_8_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesPanamá, Angola e México, formato pdf, 151kb</t>
+          <t>FIP Startup Inteligência Artificial</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09012026_Edital_2748950_SEI_2748603_Edital_Conjunto_n__1_2026.pdf</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/756012</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>14</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Prorrogação Edital Conjunto nº 1/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México, formato pdf, 65,6kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2855428_sei_2855023_edital_conjunto_n__1_2026___prorrogacao.pdf/@@display-file/file ; Lista de inscritos Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Angola e México, formato pdf, 435kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/01042026_Lista_Listagem_2788855_Lista_de_inscritos_Angola_e_Mexico.pdf/@@display-file/file ; Lista de inscritos Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México, formato pdf, 421kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/12032026_Lista_Listagem_2780399_Lista_de_Inscritos_Panama.pdf/@@display-file/file ; Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México - Retificação do Cumprimento de decisão judicial, formato pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/13022026_Edital_2768872_SEI_2768349_Edital_Conjunto_n__1_2026____Retificacao_de_Decisao_Judicial.pdf/@@display-file/file ; Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México - Cumprimento de decisão judicial, formato pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11022026_Edital_2766993_SEI_2766572_Edital_Conjunto_1_2026_.pdf/@@display-file/file ; Alteração do edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México, formato pdf, 81kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/03022026_Edital_2762271_SEI_2757276_Edital_Conjunto_n__1_2026_CAPES_MIR_____1_.pdf/@@display-file/file ; Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México, formato pdf, 151kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09012026_Edital_2748950_SEI_2748603_Edital_Conjunto_n__1_2026.pdf/@@display-file/file ; Edital Conjunto nº 1/2026 - Prorrogação formato, pdf, 113kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2879086_edital_conjunto_1_2026___prorrogacao.pdf/@@display-file/file ; Alteração do edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesPanamá, Angola e México, formato pdf, 81kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/03022026_Edital_2762271_SEI_2757276_Edital_Conjunto_n__1_2026_CAPES_MIR_____1_.pdf ; Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesPanamá, Angola e México - Cumprimento de decisão judicial, formato pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11022026_Edital_2766993_SEI_2766572_Edital_Conjunto_1_2026_.pdf ; Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesPanamá, Angola e México - Retificação do Cumprimento de decisão judicial, formato pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/13022026_Edital_2768872_SEI_2768349_Edital_Conjunto_n__1_2026____Retificacao_de_Decisao_Judicial.pdf ; Lista de inscritos Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesPanamá, Angola e México, formato pdf, 421kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/12032026_Lista_Listagem_2780399_Lista_de_Inscritos_Panama.pdf ; Lista de inscritos Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesAngola e México, formato pdf, 435kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/01042026_Lista_Listagem_2788855_Lista_de_inscritos_Angola_e_Mexico.pdf</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1870,100 +1874,96 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Edital nº 07/2026 - CAPES/Cofecub, formato, pdf, 545kb</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>30/03/2026</t>
-        </is>
-      </c>
+          <t>Edital n° 14/2022 - formato, pdf, 380kb</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/30032026_EDITAL72026CAPESCOFECUB.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/08062022_Lista_Listagem_1727316_Humboldt.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alteração do Edital nº 07/2026 - CAPES/Cofecub, formato, pdf, 143kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2832325_EDITAL_7_2026___ALTERACAO.pdf ; Lista de inscritos  no Edital n° 7/2026 - Programa CAPES/COFECUB, formato, pdf, 116kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Lista_Listagem_2841501_Lista_de_inscritos.pdf/@@display-file/file</t>
+          <t>Lista de Inscritos no Edital nº 14/2022 do Programa de Bolsas para Pesquisa CAPES/Humboldt - 26° chamada | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Lista_de_inscritos_26_chamada.pdf/@@display-file/file ; Lista de inscritos - Chamada nª 23 do Edital n° 14/2022 - formato, pdf, 396kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/18122024_SEI_CAPES___2508050___Edital_Minuta_ok.pdf/@@display-file/file ; Lista de inscritos - Chamada nº 22 do Edital n° 14/2022 - formato, pdf, 99kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/17062024_Lista_Listagem_2395643_Lista_de_inscritos.pdf/@@display-file/file ; Lista de inscritos - Chamada nº 21 do Edital n° 14/2022 - formato, pdf, 151kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/22122023_Lista_Listagem_2297511_Lista_de_inscritos_21_.pdf/@@display-file/file ; Lista de inscritos - Chamada nª 20 do Edital 14/2022, formato , pdf, 391kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/Lista_Listagem_2001777_Lista_de_inscritos_final_2.pdf/@@display-file/file ; Relação final das inscrições recebidas - Chamada nº 19 do Edital n° 14/2022 - formato, pdf, 380kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/13122022_Lista_Listagem_1874367_Lista_Inscritos_Humboldt__1_.pdf/@@display-file/file ; Relação das inscrições recebidas do Editaln°14/2022 - formato, pdf, 372kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/20092022_Lista_Listagem_1805835_Lista_Final_Humboldt_pdf_para_word_edital_14_22.pdf/@@display-file/file ; Lista de Inscritos - Chamada nº 24 do Edital nº 14/2022 - formato, pdf, 150kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/17062025_Lista_Listagem_2616980_Lista_de_inscritos_24_chamada.pdf ; Lista de Inscritos - Chamada nº 25 do Edital nº 14/2022 - formato, pdf, 241kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/17122025_Lista_Listagem_2735806_SEI___23038.004870_2021_69_25__chamada.pdf ; Alteração do Edital n° 14/2022 - formato, pdf, 49kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/06042026_Edital_2797322_SEI_2796265_Edital_14__de_2022.pdf</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FAPESB</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DIRETRIZES ESPECÍFICAS DA FAPESB – CHAMADA 2026 CONFAP – BRASILLINOIS</t>
+          <t>Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesPanamá, Angola e México, formato pdf, 151kb</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
+          <t>09/01/2026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/diretrizes-especificas-da-fapesb-chamada-2026-confap-brasillinois/</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09012026_Edital_2748950_SEI_2748603_Edital_Conjunto_n__1_2026.pdf</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Prorrogação Edital Conjunto nº 1/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México, formato pdf, 65,6kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2855428_sei_2855023_edital_conjunto_n__1_2026___prorrogacao.pdf/@@display-file/file ; Lista de inscritos Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Angola e México, formato pdf, 435kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/01042026_Lista_Listagem_2788855_Lista_de_inscritos_Angola_e_Mexico.pdf/@@display-file/file ; Lista de inscritos Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México, formato pdf, 421kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/12032026_Lista_Listagem_2780399_Lista_de_Inscritos_Panama.pdf/@@display-file/file ; Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México - Retificação do Cumprimento de decisão judicial, formato pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/13022026_Edital_2768872_SEI_2768349_Edital_Conjunto_n__1_2026____Retificacao_de_Decisao_Judicial.pdf/@@display-file/file ; Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México - Cumprimento de decisão judicial, formato pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11022026_Edital_2766993_SEI_2766572_Edital_Conjunto_1_2026_.pdf/@@display-file/file ; Alteração do edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México, formato pdf, 81kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/03022026_Edital_2762271_SEI_2757276_Edital_Conjunto_n__1_2026_CAPES_MIR_____1_.pdf/@@display-file/file ; Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México, formato pdf, 151kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09012026_Edital_2748950_SEI_2748603_Edital_Conjunto_n__1_2026.pdf/@@display-file/file ; Edital Conjunto nº 1/2026 - Prorrogação formato, pdf, 113kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2879086_edital_conjunto_1_2026___prorrogacao.pdf/@@display-file/file ; Alteração do edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesPanamá, Angola e México, formato pdf, 81kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/03022026_Edital_2762271_SEI_2757276_Edital_Conjunto_n__1_2026_CAPES_MIR_____1_.pdf ; Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesPanamá, Angola e México - Cumprimento de decisão judicial, formato pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11022026_Edital_2766993_SEI_2766572_Edital_Conjunto_1_2026_.pdf ; Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesPanamá, Angola e México - Retificação do Cumprimento de decisão judicial, formato pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/13022026_Edital_2768872_SEI_2768349_Edital_Conjunto_n__1_2026____Retificacao_de_Decisao_Judicial.pdf ; Lista de inscritos Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesPanamá, Angola e México, formato pdf, 421kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/12032026_Lista_Listagem_2780399_Lista_de_Inscritos_Panama.pdf ; Lista de inscritos Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesAngola e México, formato pdf, 435kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/01042026_Lista_Listagem_2788855_Lista_de_inscritos_Angola_e_Mexico.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Agricultura familiar para ICTs 2026</t>
+          <t>Edital nº 07/2026 - CAPES/Cofecub, formato, pdf, 545kb</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/755892</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/30032026_EDITAL72026CAPESCOFECUB.pdf</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alteração do Edital nº 07/2026 - CAPES/Cofecub, formato, pdf, 143kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2832325_EDITAL_7_2026___ALTERACAO.pdf ; Lista de inscritos  no Edital n° 7/2026 - Programa CAPES/COFECUB, formato, pdf, 116kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Lista_Listagem_2841501_Lista_de_inscritos.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>FAPESB</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ecossistema Tecnológico de Biorrefino</t>
+          <t>DIRETRIZES ESPECÍFICAS DA FAPESB – CHAMADA 2026 CONFAP – BRASILLINOIS</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1973,12 +1973,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/755795</t>
+          <t>https://www.fapesb.ba.gov.br/diretrizes-especificas-da-fapesb-chamada-2026-confap-brasillinois/</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -1989,33 +1989,33 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Edital nº 06/2026 Programa Rede de Pesquisa e Desenvolvimento da Amazônia Legal - formato, pdf, 168kb</t>
+          <t>Agricultura familiar para ICTs 2026</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>25/03/2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20032026_Edital_2787827_SEI_2787352_Edital_6_2026.pdf</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/755892</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2</v>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Alteração - Edital nº 6/2026 Programa Rede de Pesquisa e Desenvolvimento da Amazônia Legal - formato, pdf, 125kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2879953_alteracao_edital_6_2026.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2025,22 +2025,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Prêmio Mulheres Inovadoras – 7ª edição – 2026</t>
+          <t>Ecossistema Tecnológico de Biorrefino</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/755727</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/755795</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2051,33 +2051,33 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Finep Mais Inovação Brasil - Rodada 2 – Tecnologias Digitais</t>
+          <t>Edital nº 06/2026 Programa Rede de Pesquisa e Desenvolvimento da Amazônia Legal - formato, pdf, 168kb</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/755485</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20032026_Edital_2787827_SEI_2787352_Edital_6_2026.pdf</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alteração - Edital nº 6/2026 Programa Rede de Pesquisa e Desenvolvimento da Amazônia Legal - formato, pdf, 125kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2879953_alteracao_edital_6_2026.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2087,22 +2087,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Finep Mais Inovação Brasil – Rodada 2 – Semicondutores</t>
+          <t>Prêmio Mulheres Inovadoras – 7ª edição – 2026</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/755605</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/755727</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2113,23 +2113,27 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FAPESB</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EDITAL FAPESB N° 05/2026 MOVE 2026 – PARTICIPAÇÃO DE PESQUISADORES EM EVENTOS NO EXTERIOR</t>
+          <t>Finep Mais Inovação Brasil - Rodada 2 – Tecnologias Digitais</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>12/03/2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/edital-fapesb-n-052026-move-2026-participacao-de-pesquisadores-em-eventos-no-exterior/</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/755485</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2145,22 +2149,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Finep Mais Inovação Brasil – Rodada 2 – Mobilidade Sustentável</t>
+          <t>Finep Mais Inovação Brasil – Rodada 2 – Semicondutores</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/755376</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/755605</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2176,18 +2180,18 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Chamada Fundação de Amparo à Pesquisa da Bahia/SECTI/SEMA/FGB nº 01/2026</t>
+          <t>EDITAL FAPESB N° 05/2026 MOVE 2026 – PARTICIPAÇÃO DE PESQUISADORES EM EVENTOS NO EXTERIOR</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/chamada-fundacao-de-amparo-a-pesquisa-da-bahiasectisemafgb-no-012026/</t>
+          <t>https://www.fapesb.ba.gov.br/edital-fapesb-n-052026-move-2026-participacao-de-pesquisadores-em-eventos-no-exterior/</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2198,23 +2202,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FAPESB</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>EDITAL FAPESB/SECTI/IEL nº 004/2026 – Chamada Estratégica FAPESB/SECTI/IEL</t>
+          <t>Finep Mais Inovação Brasil – Rodada 2 – Mobilidade Sustentável</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/edital-fapesbsectiiel-no-0042026-chamada-estrategica-fapesbsectiiel/</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/755376</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2225,58 +2233,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>FAPESB</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Edital nº 2/2026 - Pé-de-Meia Licenciaturas - formato, pdf, 81kb</t>
+          <t>Chamada Fundação de Amparo à Pesquisa da Bahia/SECTI/SEMA/FGB nº 01/2026</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>16/01/2026</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/16012026_Edital_2753123_SEI_2753038_Edital_2_2026.pdf</t>
+          <t>https://www.fapesb.ba.gov.br/chamada-fundacao-de-amparo-a-pesquisa-da-bahiasectisemafgb-no-012026/</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2</v>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Alteração do edital nº 2/2026 - Pé-de-Meia Licenciaturas - formato, pdf, 55kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19022026_Edital_2769828_SEI_2769557_Edital__2_2026.pdf</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>FAPESB</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Finep Mais Inovação Brasil – Rodada 2 – Economia Circular e Cidades Sustentáveis</t>
+          <t>EDITAL FAPESB/SECTI/IEL nº 004/2026 – Chamada Estratégica FAPESB/SECTI/IEL</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>13/02/2026</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
+          <t>04/03/2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/755213</t>
+          <t>https://www.fapesb.ba.gov.br/edital-fapesbsectiiel-no-0042026-chamada-estrategica-fapesbsectiiel/</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2287,33 +2287,33 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Finep Mais Inovação Brasil - Rodada 2 - Saúde / Empresas</t>
+          <t>Edital nº 2/2026 - Pé-de-Meia Licenciaturas - formato, pdf, 81kb</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
+          <t>16/01/2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/754704</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/16012026_Edital_2753123_SEI_2753038_Edital_2_2026.pdf</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1</v>
-      </c>
-      <c r="G63" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Alteração do edital nº 2/2026 - Pé-de-Meia Licenciaturas - formato, pdf, 55kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19022026_Edital_2769828_SEI_2769557_Edital__2_2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2323,22 +2323,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Finep Mais Inovação Brasil - Rodada 2 - Subvenção Econômica Regional</t>
+          <t>Finep Mais Inovação Brasil – Rodada 2 – Economia Circular e Cidades Sustentáveis</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>13/02/2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/755080</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/755213</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Finep Mais Inovação Brasil – Rodada 2 - Base Industrial de Defesa</t>
+          <t>Finep Mais Inovação Brasil - Rodada 2 - Saúde / Empresas</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/754961</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/754704</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Finep Mais Inovação Brasil – Rodada 2 – Cadeias Agroindustriais Sustentáveis</t>
+          <t>Finep Mais Inovação Brasil - Rodada 2 - Subvenção Econômica Regional</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/754839</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/755080</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Finep Mais Inovação Brasil – Rodada 2 – Transformação Mineral</t>
+          <t>Finep Mais Inovação Brasil – Rodada 2 - Base Industrial de Defesa</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2426,12 +2426,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/754473</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/754961</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Finep Mais Inovação Brasil – Rodada 2 – Transição Energética</t>
+          <t>Finep Mais Inovação Brasil – Rodada 2 – Cadeias Agroindustriais Sustentáveis</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2457,12 +2457,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/754567</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/754839</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -2473,23 +2473,27 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>FAPESB</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>DIRETRIZES ESPECÍFICAS DA FAPESB – Chamada para submissão de propostas do programa de Intercâmbio de Pessoal (MSCA SE) em coordenação com o Horizonte Europa</t>
+          <t>Finep Mais Inovação Brasil – Rodada 2 – Transformação Mineral</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/diretrizes-especificas-da-fapesb-chamada-para-submissao-de-propostas-do-programa-de-intercambio-de-pessoal-msca-se-em-coordenacao-com-o-horizonte-europa-2/</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/754473</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -2500,23 +2504,27 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FAPESB</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>EDITAL FAPESB/SECTI nº 003/2026 – Apoio a Pesquisas e Inovações para a Defesa Nacional e a Segurança Pública</t>
+          <t>Finep Mais Inovação Brasil – Rodada 2 – Transição Energética</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>20/01/2026</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/edital-fapesbsecti-no-0032026-apoio-a-pesquisas-e-inovacoes-para-a-defesa-nacional-e-a-seguranca-publica/</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/754567</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2527,23 +2535,23 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>FAPESB</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SELEÇÃO PÚBLICA MCTI/FINEP/FNDCT - Subvenção Econômica à Inovação - DESAFIOS TECNOLÓGICOS PARA AGRICULTURA FAMILIAR</t>
+          <t>DIRETRIZES ESPECÍFICAS DA FAPESB – Chamada para submissão de propostas do programa de Intercâmbio de Pessoal (MSCA SE) em coordenação com o Horizonte Europa</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>23/12/2025</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/754098</t>
+          <t>https://www.fapesb.ba.gov.br/diretrizes-especificas-da-fapesb-chamada-para-submissao-de-propostas-do-programa-de-intercambio-de-pessoal-msca-se-em-coordenacao-com-o-horizonte-europa-2/</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -2554,27 +2562,23 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>FAPESB</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Pesquisa Aplicada Em Centros Temáticos 2025</t>
+          <t>EDITAL FAPESB/SECTI nº 003/2026 – Apoio a Pesquisas e Inovações para a Defesa Nacional e a Segurança Pública</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>19/12/2025</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
+          <t>20/01/2026</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/753688</t>
+          <t>https://www.fapesb.ba.gov.br/edital-fapesbsecti-no-0032026-apoio-a-pesquisas-e-inovacoes-para-a-defesa-nacional-e-a-seguranca-publica/</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2590,18 +2594,18 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PROCESSO DE SELEÇÃO Nº 01/2025 PARA CELEBRAÇÃO DE CONVÊNIO COM ENTIDADE FECHADA DE PREVIDÊNCIA COMPLEMENTAR - EFPC</t>
+          <t>SELEÇÃO PÚBLICA MCTI/FINEP/FNDCT - Subvenção Econômica à Inovação - DESAFIOS TECNOLÓGICOS PARA AGRICULTURA FAMILIAR</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>23/12/2025</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/753680</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/754098</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -2612,23 +2616,27 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>FAPESB</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>EDITAL FAPESB Nº 030/2025 APOIO À PESQUISA CIENTÍFICA, TECNOLÓGICA E/OU DE INOVAÇÃO EM DOENÇAS E AGRAVOS PREVALENTES NA POPULAÇÃO NEGRA, COM ÊNFASE EM DOENÇA FALCIFORME E OS IMPACTOS DO RACISMO ESTRUTURAL NA SAÚDE – EDIÇÃO ANTÔNIA GARCIA</t>
+          <t>Pesquisa Aplicada Em Centros Temáticos 2025</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/edital-fapesb-no-0302025-apoio-a-pesquisa-cientifica-tecnologica-eou-de-inovacao-em-doencas-e-agravos-prevalentes-na-populacao-negra-com-enfase-em-doenca-falciforme-e-os-impactos-do-racismo-estrut/</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/753688</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2644,18 +2652,18 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>FIP Bioeconomia e Sustentabilidade</t>
+          <t>PROCESSO DE SELEÇÃO Nº 01/2025 PARA CELEBRAÇÃO DE CONVÊNIO COM ENTIDADE FECHADA DE PREVIDÊNCIA COMPLEMENTAR - EFPC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/752980</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/753680</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -2671,18 +2679,18 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Edital Nº 024/2025 Programa Nacional de Apoio à Geração de Empreendimentos Inovadores Programa Centelha 3 Bahia</t>
+          <t>EDITAL FAPESB Nº 030/2025 APOIO À PESQUISA CIENTÍFICA, TECNOLÓGICA E/OU DE INOVAÇÃO EM DOENÇAS E AGRAVOS PREVALENTES NA POPULAÇÃO NEGRA, COM ÊNFASE EM DOENÇA FALCIFORME E OS IMPACTOS DO RACISMO ESTRUTURAL NA SAÚDE – EDIÇÃO ANTÔNIA GARCIA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>06/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/edital-no-0242025-programa-nacional-de-apoio-a-geracao-de-empreendimentos-inovadores-programa-centelha-3-bahia/</t>
+          <t>https://www.fapesb.ba.gov.br/edital-fapesb-no-0302025-apoio-a-pesquisa-cientifica-tecnologica-eou-de-inovacao-em-doencas-e-agravos-prevalentes-na-populacao-negra-com-enfase-em-doenca-falciforme-e-os-impactos-do-racismo-estrut/</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -2693,60 +2701,56 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Edital Conjunto nº 04/2024 - Programa CAMINHOS AMEFRICANOS: PROGRAMA DE INTERCÂMBIOS SUL-SUL - EDIÇÃO PERU, EDIÇÃO ANGOLA e EDIÇÃO REPÚBLICA DOMINICANA, formato pdf, 146kb</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr"/>
+          <t>FIP Bioeconomia e Sustentabilidade</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>11/11/2025</t>
+        </is>
+      </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23122024_Edital_2517683_SEI_2515663_Edital_Conjunto_4_2024.pdf/@@display-file/file</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/752980</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>6</v>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>EDITAL CONJUNTO N° 4/2024 - ALTERAÇÃO - CAMINHOS AMEFRICANOS: PROGRAMA DE INTERCÂMBIOS SUL-SUL - EDIÇÕES PERU, ANGOLA E REPÚBLICA DOMINICANA, formato, pdf, 63kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2620581_SEI_2617290_Edital_Conjunto_4_2024.pdf/@@display-file/file ; Retificação do Edital Conjunto nº 04/2024 - Programa CAMINHOS AMEFRICANOS: PROGRAMA DE INTERCÂMBIOS SUL-SUL - EDIÇÃO PERU, EDIÇÃO ANGOLA e EDIÇÃO REPÚBLICA DOMINICANA, formato pdf, 71kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/16012025_Edital_2528145_SEI_2526246_Edital_Conjunto_N__4_2024___RETIFICACAO.pdf ; Lista de Inscritos do Edital Conjunto nº 04/2024 - Peru - Programa Programa CAMINHOS AMEFRICANOS: PROGRAMA DE INTERCÂMBIOS SUL-SUL - EDIÇÃO PERU, EDIÇÃO ANGOLA e EDIÇÃO REPÚBLICA DOMINICANA, formato pdf, 443kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/06032025_Lista_Listagem_2550258_MIR_lista_de_inscritos___alterado.pdf ; Lista de Inscritos do Edital Conjunto nº 04/2024 - Angola, República Dominicana - Programa Programa CAMINHOS AMEFRICANOS: PROGRAMA DE INTERCÂMBIOS SUL-SUL - EDIÇÃO PERU, EDIÇÃO ANGOLA e EDIÇÃO REPÚBLICA DOMINICANA, formato pdf, 264kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/17032025_Lista_Listagem_2557320_Lista_de_Inscritos_Angola_e_Rep_Dominicana.pdf ; Alteração do Edital Conjunto nº 04/2024 - Programa CAMINHOS AMEFRICANOS: PROGRAMA DE INTERCÂMBIOS SUL-SUL - EDIÇÃO PERU, EDIÇÃO ANGOLA e EDIÇÃO REPÚBLICA DOMINICANA, formato pdf, 63kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/14082025_EditalConjunto42024_Alterao.pdf</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>FAPESB</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Edital Nº 07/2025 - CAPES/Brafitec, formato, pdf, 207kb</t>
+          <t>Edital Nº 024/2025 Programa Nacional de Apoio à Geração de Empreendimentos Inovadores Programa Centelha 3 Bahia</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>03/04/2025</t>
+          <t>06/11/2025</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/03042025_Edital_2574246_SEI_2572796_Edital_n__7_2025.pdf</t>
+          <t>https://www.fapesb.ba.gov.br/edital-no-0242025-programa-nacional-de-apoio-a-geracao-de-empreendimentos-inovadores-programa-centelha-3-bahia/</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>4</v>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Alteração do Edital Nº 07/2025 - CAPES/Brafitec, formato, pdf, 65kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/25062025_Edital_2623304_SEI_2622327_Edital_n__7_2025___Alteracao.pdf ; Lista de Inscrições Recebidas no Programa CAPES-BRAFITEC - Edital nº 07/2025, formato, pdf, 173kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/23072025_Lista_Listagem_2636522_lista_de_inscritos___Brafitec.pdf ; Retificação da lista de Inscrições Recebidas no Programa CAPES-BRAFITEC - Edital nº 07/2025, formato, pdf, 201kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/04082025_Listagem_2643912_Lista_de_Inscritos.pdf</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2756,26 +2760,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Edital nº 09/2025 - CAPES/Cofecub, formato, pdf, 207kb</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>09/04/2025</t>
-        </is>
-      </c>
+          <t>Edital Conjunto nº 04/2024 - Programa CAMINHOS AMEFRICANOS: PROGRAMA DE INTERCÂMBIOS SUL-SUL - EDIÇÃO PERU, EDIÇÃO ANGOLA e EDIÇÃO REPÚBLICA DOMINICANA, formato pdf, 146kb</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09042025_Edital_2578055_SEI_2577896_Edital_n__9_2025.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23122024_Edital_2517683_SEI_2515663_Edital_Conjunto_4_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Relação das inscrições Recebidas do edital nº 09/2025, formato, pdf, 304kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/25062025_Lista_Listagem_2617939_Lista_de_inscritos_25.pdf</t>
+          <t>EDITAL CONJUNTO N° 4/2024 - ALTERAÇÃO - CAMINHOS AMEFRICANOS: PROGRAMA DE INTERCÂMBIOS SUL-SUL - EDIÇÕES PERU, ANGOLA E REPÚBLICA DOMINICANA, formato, pdf, 63kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2620581_SEI_2617290_Edital_Conjunto_4_2024.pdf/@@display-file/file ; Retificação do Edital Conjunto nº 04/2024 - Programa CAMINHOS AMEFRICANOS: PROGRAMA DE INTERCÂMBIOS SUL-SUL - EDIÇÃO PERU, EDIÇÃO ANGOLA e EDIÇÃO REPÚBLICA DOMINICANA, formato pdf, 71kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/16012025_Edital_2528145_SEI_2526246_Edital_Conjunto_N__4_2024___RETIFICACAO.pdf ; Lista de Inscritos do Edital Conjunto nº 04/2024 - Peru - Programa Programa CAMINHOS AMEFRICANOS: PROGRAMA DE INTERCÂMBIOS SUL-SUL - EDIÇÃO PERU, EDIÇÃO ANGOLA e EDIÇÃO REPÚBLICA DOMINICANA, formato pdf, 443kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/06032025_Lista_Listagem_2550258_MIR_lista_de_inscritos___alterado.pdf ; Lista de Inscritos do Edital Conjunto nº 04/2024 - Angola, República Dominicana - Programa Programa CAMINHOS AMEFRICANOS: PROGRAMA DE INTERCÂMBIOS SUL-SUL - EDIÇÃO PERU, EDIÇÃO ANGOLA e EDIÇÃO REPÚBLICA DOMINICANA, formato pdf, 264kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/17032025_Lista_Listagem_2557320_Lista_de_Inscritos_Angola_e_Rep_Dominicana.pdf ; Alteração do Edital Conjunto nº 04/2024 - Programa CAMINHOS AMEFRICANOS: PROGRAMA DE INTERCÂMBIOS SUL-SUL - EDIÇÃO PERU, EDIÇÃO ANGOLA e EDIÇÃO REPÚBLICA DOMINICANA, formato pdf, 63kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/14082025_EditalConjunto42024_Alterao.pdf</t>
         </is>
       </c>
     </row>
@@ -2787,51 +2787,59 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Edital nº 15/2024 - Política de Novação para Bolsistas e Ex-Bolsistas no Exterior, formato - pdf, 133kb</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr"/>
+          <t>Edital Nº 07/2025 - CAPES/Brafitec, formato, pdf, 207kb</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>03/04/2025</t>
+        </is>
+      </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/28062024_Edital_2407822_SEI_2407228_Edital_15_2024.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/03042025_Edital_2574246_SEI_2572796_Edital_n__7_2025.pdf</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Prorrogação do Edital nº 15/2024 - Política de Novação para Bolsistas e Ex-Bolsistas no Exterior, formato - pdf, 60kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29102024_Edital_2486324_SEI_2485381_Edital_15_2024.pdf/@@display-file/file ; Alteração do Edital nº 15/2024 - Política de Novação para Bolsistas e Ex-Bolsistas no Exterior, formato - pdf, 61kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/06062025_Publicacao_no_DOU_2612769_SEI_2611767_Edital_15_2024.pdf</t>
+          <t>Alteração do Edital Nº 07/2025 - CAPES/Brafitec, formato, pdf, 65kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/25062025_Edital_2623304_SEI_2622327_Edital_n__7_2025___Alteracao.pdf ; Lista de Inscrições Recebidas no Programa CAPES-BRAFITEC - Edital nº 07/2025, formato, pdf, 173kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/23072025_Lista_Listagem_2636522_lista_de_inscritos___Brafitec.pdf ; Retificação da lista de Inscrições Recebidas no Programa CAPES-BRAFITEC - Edital nº 07/2025, formato, pdf, 201kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/04082025_Listagem_2643912_Lista_de_Inscritos.pdf</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>FIP Transição Energética e Descarbonização</t>
+          <t>Edital nº 09/2025 - CAPES/Cofecub, formato, pdf, 207kb</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>04/06/2025</t>
+          <t>09/04/2025</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/752871</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09042025_Edital_2578055_SEI_2577896_Edital_n__9_2025.pdf</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1</v>
-      </c>
-      <c r="G81" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Relação das inscrições Recebidas do edital nº 09/2025, formato, pdf, 304kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/25062025_Lista_Listagem_2617939_Lista_de_inscritos_25.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2841,49 +2849,45 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Edital nº 05/2025 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 21kb</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>14/03/2025</t>
-        </is>
-      </c>
+          <t>Edital nº 15/2024 - Política de Novação para Bolsistas e Ex-Bolsistas no Exterior, formato - pdf, 133kb</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/14032025_Edital_2561854_SEI_2560981_Edital_5.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/28062024_Edital_2407822_SEI_2407228_Edital_15_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Edital nº 05/2025 - ProgramaCAPES/CLIMAT-AMSUD, formato - pdf, 21kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/14032025_Edital_2561854_SEI_2560981_Edital_5.pdf ; Edital nº 05/2025 - Programa CAPES/STIC-AMSUD, formato - pdf, 21kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/14032025_Edital_2561854_SEI_2560981_Edital_5.pdf ; Lista de inscritos do Edital nº 05/2025 - Programa CAPES/MATH-AMSUD, formato - pdf, 62kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/02062025_Lista_Listagem_2602780_amsud_2025.pdf ; Lista de inscritos do Edital nº 05/2025 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 62kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/02062025_Lista_Listagem_2602780_amsud_2025.pdf</t>
+          <t>Prorrogação do Edital nº 15/2024 - Política de Novação para Bolsistas e Ex-Bolsistas no Exterior, formato - pdf, 60kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29102024_Edital_2486324_SEI_2485381_Edital_15_2024.pdf/@@display-file/file ; Alteração do Edital nº 15/2024 - Política de Novação para Bolsistas e Ex-Bolsistas no Exterior, formato - pdf, 61kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/06062025_Publicacao_no_DOU_2612769_SEI_2611767_Edital_15_2024.pdf</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Edital nº 10/2025 - Política de Novação para Bolsistas e Ex-Bolsistas no Exterior, formato - pdf, 102kb</t>
+          <t>FIP Transição Energética e Descarbonização</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>30/04/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/30042025_Edital_2589477_SEI_2588226_Edital_n__10_2025.pdf</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/752871</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -2894,29 +2898,33 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Seleção de Gestor para o FIP Complexo da Saúde</t>
+          <t>Edital nº 05/2025 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 21kb</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>07/04/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/752474</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/14032025_Edital_2561854_SEI_2560981_Edital_5.pdf</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1</v>
-      </c>
-      <c r="G84" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Edital nº 05/2025 - ProgramaCAPES/CLIMAT-AMSUD, formato - pdf, 21kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/14032025_Edital_2561854_SEI_2560981_Edital_5.pdf ; Edital nº 05/2025 - Programa CAPES/STIC-AMSUD, formato - pdf, 21kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/14032025_Edital_2561854_SEI_2560981_Edital_5.pdf ; Lista de inscritos do Edital nº 05/2025 - Programa CAPES/MATH-AMSUD, formato - pdf, 62kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/02062025_Lista_Listagem_2602780_amsud_2025.pdf ; Lista de inscritos do Edital nº 05/2025 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 62kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/02062025_Lista_Listagem_2602780_amsud_2025.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2926,55 +2934,51 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Edital nº 1/2025 - Pé-de-Meia Licenciaturas - formato, pdf, 76kb</t>
+          <t>Edital nº 10/2025 - Política de Novação para Bolsistas e Ex-Bolsistas no Exterior, formato - pdf, 102kb</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>17/01/2025</t>
+          <t>30/04/2025</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/17012025_Edital_2529011_SEI_2528468_Edital_n__1_2025.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/30042025_Edital_2589477_SEI_2588226_Edital_n__10_2025.pdf</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>4</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Alteração do edital nº 1/2025 - Pé-de-Meia Licenciaturas - formato, pdf, 76kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07022025_Edital_2541491_SEI_2540577_Edital_1_2025.pdf ; Tornar sem efeito a alteração do edital nº 1/2025 - Pé-de-Meia Licenciaturas - formato, pdf, 142kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/17022025_Publicacao_no_DOU_2546770_EDITAL_1_2025__TORNAR_SEM_EFEITO_ALTERACAO.pdf ; Alteração do edital nº 1/2025 - Pé-de-Meia Licenciaturas - Segunda chamada - formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/04042025_Edital_2574981_SEI_2574897_Edital_1_2025.pdf</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Edital Nº 10/2023 - CAPES/Brafitec, formato, pdf, 429kb</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr"/>
+          <t>Seleção de Gestor para o FIP Complexo da Saúde</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>07/04/2025</t>
+        </is>
+      </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/13042023_Edital_1953404_Edital_10.2023.pdf/@@display-file/file</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/752474</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>3</v>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Lista de inscritosEdital Nº 10/2023 - CAPES/Brafitec, formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/18092023_Lista_Listagem_2234997_Lista_de_inscritos_2023.pdf/@@display-file/file ; Alteração do Edital n° 10/2023 - Brafitec, formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/27032025_Edital_2570257_SEI_2569933_Edital_N__10_2023___ALTERACAO.pdf</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2984,22 +2988,26 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Edital nº 11/2024 - CAPES/Brafitec, formato, pdf, 583kb</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr"/>
+          <t>Edital nº 1/2025 - Pé-de-Meia Licenciaturas - formato, pdf, 76kb</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>17/01/2025</t>
+        </is>
+      </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15042024_EDITAL112024PROGRAMABRAFITEC.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/17012025_Edital_2529011_SEI_2528468_Edital_n__1_2025.pdf</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lista de Inscrições Recebidas no Programa CAPES-BRAFITEC - Edital nº 11/2024, formato, pdf, 44kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/24092024_Lista_Listagem_2459366_Lista_de_Inscritos.pdf/@@display-file/file ; Alteração do Edital nº 11/2024 - CAPES/Brafitec, formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/27032025_Edital_2570314_SEI_2569939_Edital__N__11_2024___ALTERACAO.pdf</t>
+          <t>Alteração do edital nº 1/2025 - Pé-de-Meia Licenciaturas - formato, pdf, 76kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07022025_Edital_2541491_SEI_2540577_Edital_1_2025.pdf ; Tornar sem efeito a alteração do edital nº 1/2025 - Pé-de-Meia Licenciaturas - formato, pdf, 142kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/17022025_Publicacao_no_DOU_2546770_EDITAL_1_2025__TORNAR_SEM_EFEITO_ALTERACAO.pdf ; Alteração do edital nº 1/2025 - Pé-de-Meia Licenciaturas - Segunda chamada - formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/04042025_Edital_2574981_SEI_2574897_Edital_1_2025.pdf</t>
         </is>
       </c>
     </row>
@@ -3011,14 +3019,14 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Edital nº 16/2024 - Programa CAPES/AUGM, formato - pdf, 235kb</t>
+          <t>Edital Nº 10/2023 - CAPES/Brafitec, formato, pdf, 429kb</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/08072024_Edital_2413631_SEI_2413500_Edital_16_2024.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/13042023_Edital_1953404_Edital_10.2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F88" t="n">
@@ -3026,63 +3034,63 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lista de inscritos do Edital nº 16/2024, formato, pdf, 174kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/30092024_Lista_Listagem_2456928_Lista_de_inscritos.pdf/@@display-file/file ; Alteração do Edital nº 16/2024 - Programa CAPES/AUGM, formato - pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/24032025_Edital_2567485_SEI_2566349_Edital_n__16_2024___Alteracao_IV.pdf</t>
+          <t>Lista de inscritosEdital Nº 10/2023 - CAPES/Brafitec, formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/18092023_Lista_Listagem_2234997_Lista_de_inscritos_2023.pdf/@@display-file/file ; Alteração do Edital n° 10/2023 - Brafitec, formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/27032025_Edital_2570257_SEI_2569933_Edital_N__10_2023___ALTERACAO.pdf</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Conhecimento Brasil</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>07/08/2024</t>
-        </is>
-      </c>
+          <t>Edital nº 11/2024 - CAPES/Brafitec, formato, pdf, 583kb</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/749717</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15042024_EDITAL112024PROGRAMABRAFITEC.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
-      </c>
-      <c r="G89" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Lista de Inscrições Recebidas no Programa CAPES-BRAFITEC - Edital nº 11/2024, formato, pdf, 44kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/24092024_Lista_Listagem_2459366_Lista_de_Inscritos.pdf/@@display-file/file ; Alteração do Edital nº 11/2024 - CAPES/Brafitec, formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/27032025_Edital_2570314_SEI_2569939_Edital__N__11_2024___ALTERACAO.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Edital FIP Nordeste Capital Semente</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>10/07/2024</t>
-        </is>
-      </c>
+          <t>Edital nº 16/2024 - Programa CAPES/AUGM, formato - pdf, 235kb</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/749273</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/08072024_Edital_2413631_SEI_2413500_Edital_16_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>1</v>
-      </c>
-      <c r="G90" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Lista de inscritos do Edital nº 16/2024, formato, pdf, 174kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/30092024_Lista_Listagem_2456928_Lista_de_inscritos.pdf/@@display-file/file ; Alteração do Edital nº 16/2024 - Programa CAPES/AUGM, formato - pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/24032025_Edital_2567485_SEI_2566349_Edital_n__16_2024___Alteracao_IV.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3092,18 +3100,18 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SOLUÇÕES TECNOLÓGICAS PARA AUMENTO DA PRODUTIVIDADE NA AGRICULTURA FAMILIAR, AQUICULTURA E PESCA ARTESANAL</t>
+          <t>Conhecimento Brasil</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>08/07/2024</t>
+          <t>07/08/2024</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/748141</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/749717</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -3119,18 +3127,18 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Chamada pública conjunta Finep e Rede Eureka 2024</t>
+          <t>Edital FIP Nordeste Capital Semente</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>31/01/2024</t>
+          <t>10/07/2024</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/747009</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/749273</t>
         </is>
       </c>
       <c r="F92" t="n">
@@ -3146,18 +3154,18 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Programa de Investimento em Startups Inovadoras 2ª Rodada</t>
+          <t>SOLUÇÕES TECNOLÓGICAS PARA AUMENTO DA PRODUTIVIDADE NA AGRICULTURA FAMILIAR, AQUICULTURA E PESCA ARTESANAL</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>21/11/2017</t>
+          <t>08/07/2024</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/721708</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/748141</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -3173,18 +3181,18 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>COOPERAÇÃO ICT-EMPRESA – 01/2017</t>
+          <t>Chamada pública conjunta Finep e Rede Eureka 2024</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>08/05/2017</t>
+          <t>31/01/2024</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/721088</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/747009</t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -3200,18 +3208,18 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Finep / CDTI - COOPERAÇÃO ICT-EMPRESA – 01/2017</t>
+          <t>Programa de Investimento em Startups Inovadoras 2ª Rodada</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>07/05/2017</t>
+          <t>21/11/2017</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/721094</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/721708</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -3227,18 +3235,18 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Chamada Pública Bilateral Finep-CDTI</t>
+          <t>COOPERAÇÃO ICT-EMPRESA – 01/2017</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>13/10/2015</t>
+          <t>08/05/2017</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/719676</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/721088</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -3249,19 +3257,23 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Alteração do Edital CAPES/DAAD Probral nº 14/2019 - pdf, 60kb</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr"/>
+          <t>Finep / CDTI - COOPERAÇÃO ICT-EMPRESA – 01/2017</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>07/05/2017</t>
+        </is>
+      </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/24052024_Edital_2384178_SEI_2382892_Edital_14_2019___Alteracao_II.pdf/@@display-file/file</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/721094</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -3272,19 +3284,23 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Alteração do Edital Nº 12/2019 - CAPES/COFECUB - formato, pdf, 68kb</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr"/>
+          <t>Chamada Pública Bilateral Finep-CDTI</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>13/10/2015</t>
+        </is>
+      </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400250_SEI_2399447_Edital_12_2019___ALTERACAO_III.pdf/@@display-file/file</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/719676</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -3300,14 +3316,14 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Alteração do edital nº 19/2022 -ProgramaCAPES/MATH-AMSUD, formato - pdf, 60kb</t>
+          <t>Alteração do Edital CAPES/DAAD Probral nº 14/2019 - pdf, 60kb</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400204_SEI_2399434_Edital_19_2022___ALTERACAO_II.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/24052024_Edital_2384178_SEI_2382892_Edital_14_2019___Alteracao_II.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -3323,14 +3339,14 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Alteração do Edital nº 36/2017 - formato, pdf, 246kb</t>
+          <t>Alteração do Edital Nº 12/2019 - CAPES/COFECUB - formato, pdf, 68kb</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/EDITAL362017_HUMBOLDT_Alterao.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400250_SEI_2399447_Edital_12_2019___ALTERACAO_III.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -3346,14 +3362,14 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Alteração Edital nº 11 - Programa Cátedra Jorge Amado, formato, pdf, 53,3kb</t>
+          <t>Alteração do edital nº 19/2022 -ProgramaCAPES/MATH-AMSUD, formato - pdf, 60kb</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2845089_sei_2843522_edital_n__11_2026.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400204_SEI_2399434_Edital_19_2022___ALTERACAO_II.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -3369,14 +3385,14 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Alteração Edital nº 16/2026 - Programa AURORA, formato, pdf, 982kb</t>
+          <t>Alteração do Edital nº 36/2017 - formato, pdf, 246kb</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2853575_edital.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/EDITAL362017_HUMBOLDT_Alterao.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -3392,14 +3408,14 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Chamada Pública para Envio de Proposta de Curso Novo - Edital nº 20/2026</t>
+          <t>Alteração Edital nº 11 - Programa Cátedra Jorge Amado, formato, pdf, 53,3kb</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2844920.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2845089_sei_2843522_edital_n__11_2026.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -3415,24 +3431,20 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Edital CAPES/DAAD Probral nº 06/2021, formato, pdf, 254kb</t>
+          <t>Alteração Edital nº 16/2026 - Programa AURORA, formato, pdf, 982kb</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/EDITAL6PROBRAL.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2853575_edital.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>Alteração do Edital CAPES/DAAD Probral nº 06/2021, formato, pdf, 67kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400395_SEI_2398543_Edital_6_2021__1_.pdf/@@display-file/file ; Lista de inscritos do Edital CAPES/DAAD Probral nº 06/2021, formato, pdf, 47kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/18062021_Edital_6_2021_PROBRAL.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3442,24 +3454,20 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Edital CAPES/DAAD Probral nº 09/2023, formato - pdf, 472kb</t>
+          <t>Chamada Pública para Envio de Proposta de Curso Novo - Edital nº 20/2026</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/10042023_Edital_1950397_SEI_CAPES___1950165___Edital_9_2023.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2844920.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>4</v>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>Alteração do Edital CAPES/DAAD Probral nº 09/2023, formato - pdf, 60kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400189_SEI_2398591_Edital_21_2022.pdf/@@display-file/file ; Relação das inscrições do Edital CAPES/DAAD Probral nº 09/2023, formato, pdf, 412kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/19072023_Lista_Listagem_2018436_Probral_23.pdf/@@display-file/file ; Alteração do EditalCAPES/DAAD Probalnº9/2023, formato, pdf, 113kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/20062023_Edital_2001190_EDITAL_9_2023_SITE.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3469,14 +3477,14 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Edital CAPES/DAAD Probral nº 09/2024, formato - pdf, 630kb</t>
+          <t>Edital CAPES/DAAD Probral nº 06/2021, formato, pdf, 254kb</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/04042024_EDITAL9CAPESDAADPROBRAL.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/EDITAL6PROBRAL.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -3484,7 +3492,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lista de inscritos do Edital CAPES/DAAD Probral nº 09/2024, formato - pdf, 334kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/21062024_Lista_Listagem_2398276_probral.pdf/@@display-file/file ; Alteração do Edital CAPES/DAAD Probral nº 09/2024, formato - pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/03062024_Edital_2388049_SEI_2386684_Edital_9_2024.pdf/@@display-file/file</t>
+          <t>Alteração do Edital CAPES/DAAD Probral nº 06/2021, formato, pdf, 67kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400395_SEI_2398543_Edital_6_2021__1_.pdf/@@display-file/file ; Lista de inscritos do Edital CAPES/DAAD Probral nº 06/2021, formato, pdf, 47kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/18062021_Edital_6_2021_PROBRAL.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3496,22 +3504,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Edital CAPES/DAAD Probral nº 21/2022, formato, pdf, 376kb</t>
+          <t>Edital CAPES/DAAD Probral nº 09/2023, formato - pdf, 472kb</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/18042022_Edital_1681234_Edital_21.22.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/10042023_Edital_1950397_SEI_CAPES___1950165___Edital_9_2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alteração do Edital CAPES/DAAD Probral nº 21/2022, formato, pdf, 101kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400189_SEI_2398591_Edital_21_2022.pdf/@@display-file/file ; Relação das inscrições do Edital CAPES/DAAD Probral nº21/2022, formato, pdf, 78kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/13072022_Lista_Listagem_1748985_Probral.pdf/@@display-file/file</t>
+          <t>Alteração do Edital CAPES/DAAD Probral nº 09/2023, formato - pdf, 60kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400189_SEI_2398591_Edital_21_2022.pdf/@@display-file/file ; Relação das inscrições do Edital CAPES/DAAD Probral nº 09/2023, formato, pdf, 412kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/19072023_Lista_Listagem_2018436_Probral_23.pdf/@@display-file/file ; Alteração do EditalCAPES/DAAD Probalnº9/2023, formato, pdf, 113kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/20062023_Edital_2001190_EDITAL_9_2023_SITE.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3523,22 +3531,22 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Edital Conjunto nº 5/2026 - Programa OBEDUC-EI - Observatório da Educação Especial Inclusiva</t>
+          <t>Edital CAPES/DAAD Probral nº 09/2024, formato - pdf, 630kb</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital-no-5.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/04042024_EDITAL9CAPESDAADPROBRAL.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Edital Conjunto nº 5/2026 - Programa OBEDUC-EI, formato, pdf, 9,67mb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital-no-5.pdf/@@display-file/file</t>
+          <t>Lista de inscritos do Edital CAPES/DAAD Probral nº 09/2024, formato - pdf, 334kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/21062024_Lista_Listagem_2398276_probral.pdf/@@display-file/file ; Alteração do Edital CAPES/DAAD Probral nº 09/2024, formato - pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/03062024_Edital_2388049_SEI_2386684_Edital_9_2024.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3550,20 +3558,24 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Edital Conjunto nº 6/2026 - CAPES/CNJ - Apoio a Pesquisas Judiciárias, formato, pdf, 257kb</t>
+          <t>Edital CAPES/DAAD Probral nº 21/2022, formato, pdf, 376kb</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2873621_sei___23038-001405_2026_81.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/18042022_Edital_1681234_Edital_21.22.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
-      </c>
-      <c r="G109" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Alteração do Edital CAPES/DAAD Probral nº 21/2022, formato, pdf, 101kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400189_SEI_2398591_Edital_21_2022.pdf/@@display-file/file ; Relação das inscrições do Edital CAPES/DAAD Probral nº21/2022, formato, pdf, 78kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/13072022_Lista_Listagem_1748985_Probral.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3573,14 +3585,14 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Edital nº 02/2024 - Projetos de Cooperação entre Instituições para Qualificação de Profissionais de Nível Superior (PCI) - formato, pdf, 87kb</t>
+          <t>Edital Conjunto nº 5/2026 - Programa OBEDUC-EI - Observatório da Educação Especial Inclusiva</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/26022024_Edital_2328837_SEI_2326326_Edital_02_2024.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital-no-5.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -3588,7 +3600,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alteração do Edital nº 02/2024 - Projetos de Cooperação entre Instituições para Qualificação de Profissionais de Nível Superior (PCI) - formato, pdf, 54kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/16052024_Edital_2379426_SEI_2379169_Edital_02_2024.pdf/@@display-file/file</t>
+          <t>Edital Conjunto nº 5/2026 - Programa OBEDUC-EI, formato, pdf, 9,67mb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital-no-5.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3600,14 +3612,14 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Edital nº 039/2013 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 400kb</t>
+          <t>Edital Conjunto nº 6/2026 - CAPES/CNJ - Apoio a Pesquisas Judiciárias, formato, pdf, 257kb</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_039_2013_PDPI.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2873621_sei___23038-001405_2026_81.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -3623,22 +3635,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Edital nº 05/2023 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 473kb</t>
+          <t>Edital nº 02/2024 - Projetos de Cooperação entre Instituições para Qualificação de Profissionais de Nível Superior (PCI) - formato, pdf, 87kb</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15032023_Edital_1933938_Edital_5_2023.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/26022024_Edital_2328837_SEI_2326326_Edital_02_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alteração do Edital nº 05/2023 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 60kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400239_SEI_2399449_Edital_05_2023___ALTERACAO_II.pdf/@@display-file/file ; Relação das inscrições do Edital nº 05/2023 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 571kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/30052023_Lista_Listagem_1984677_Lista_de_inscritos_Math_Amsud_Edital_5.2023.pdf/@@display-file/file</t>
+          <t>Alteração do Edital nº 02/2024 - Projetos de Cooperação entre Instituições para Qualificação de Profissionais de Nível Superior (PCI) - formato, pdf, 54kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/16052024_Edital_2379426_SEI_2379169_Edital_02_2024.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3650,24 +3662,20 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Edital nº 05/2024 - ProgramaCAPES/CLIMAT-AMSUD, formato - pdf, 239kb</t>
+          <t>Edital nº 039/2013 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 400kb</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20032024_Edital_2343766_SEI_2342530_Edital_05_2024.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_039_2013_PDPI.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>4</v>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>Edital nº 05/2024 - ProgramaCAPES/STIC-AMSUD, formato - pdf, 239kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20032024_Edital_2343766_SEI_2342530_Edital_05_2024.pdf/@@display-file/file ; Alteração do Edital nº 05/2024 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 57kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07052024_Edital_2373417_SEI_2372656_Edital_05_2024.pdf/@@display-file/file ; Edital nº 05/2024 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 239kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20032024_Edital_2343766_SEI_2342530_Edital_05_2024.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3677,14 +3685,14 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Edital nº 06/2023 - ProgramaCAPES/STIC-AMSUD, formato - pdf, 473kb</t>
+          <t>Edital nº 05/2023 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 473kb</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15032023_Edital_1933950_Edital_6_2023.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15032023_Edital_1933938_Edital_5_2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -3692,7 +3700,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alteração do Edital nº 06/2023 - Programa CAPES/STIC-AMSUD, formato - pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400119_SEI_2399429_Edital_6_2023___Alteracao_II.pdf/@@display-file/file ; Relação das inscrições do Edital nº 06/2023 - Programa CAPES/STIC-AMSUD, formato - pdf, 571kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/30052023_Lista_Listagem_1984493_Lista_de_inscritos_Stic_Amsud_Edital_6.2023.pdf/@@display-file/file</t>
+          <t>Alteração do Edital nº 05/2023 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 60kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400239_SEI_2399449_Edital_05_2023___ALTERACAO_II.pdf/@@display-file/file ; Relação das inscrições do Edital nº 05/2023 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 571kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/30052023_Lista_Listagem_1984677_Lista_de_inscritos_Math_Amsud_Edital_5.2023.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3704,22 +3712,22 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Edital nº 06/2024 - PDSE - formato, pdf, 133kb</t>
+          <t>Edital nº 05/2024 - ProgramaCAPES/CLIMAT-AMSUD, formato - pdf, 239kb</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/21032024_Edital_2344636_SEI_2343579_Edital_6_2024.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20032024_Edital_2343766_SEI_2342530_Edital_05_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Prorrogação do Edital nº 06/2024 - PDSE - formato, pdf, 55kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/10052024_Edital_2376323_SEI_2375557_Edital_6_2024.pdf/@@display-file/file</t>
+          <t>Edital nº 05/2024 - ProgramaCAPES/STIC-AMSUD, formato - pdf, 239kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20032024_Edital_2343766_SEI_2342530_Edital_05_2024.pdf/@@display-file/file ; Alteração do Edital nº 05/2024 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 57kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07052024_Edital_2373417_SEI_2372656_Edital_05_2024.pdf/@@display-file/file ; Edital nº 05/2024 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 239kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20032024_Edital_2343766_SEI_2342530_Edital_05_2024.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3731,14 +3739,14 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Edital nº 07/2023 - ProgramaCAPES/CLIMAT-AMSUD, formato - pdf, 466kb</t>
+          <t>Edital nº 06/2023 - ProgramaCAPES/STIC-AMSUD, formato - pdf, 473kb</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15032023_Edital_1933965_Edital_7_2023_.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15032023_Edital_1933950_Edital_6_2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -3746,7 +3754,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alteração doEdital nº 07/2023 - ProgramaCAPES/CLIMAT-AMSUD, formato - pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400133_SEI_2399445_Edital_07_2023___ALTERACAO_II.pdf/@@display-file/file ; Relação das inscrições do Edital nº 07/2023 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 570kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/30052023_Lista_Listagem_1984693_Lista_de_inscritos_Climat_Amsud_Edital_7.2023.pdf/@@display-file/file</t>
+          <t>Alteração do Edital nº 06/2023 - Programa CAPES/STIC-AMSUD, formato - pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400119_SEI_2399429_Edital_6_2023___Alteracao_II.pdf/@@display-file/file ; Relação das inscrições do Edital nº 06/2023 - Programa CAPES/STIC-AMSUD, formato - pdf, 571kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/30052023_Lista_Listagem_1984493_Lista_de_inscritos_Stic_Amsud_Edital_6.2023.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3758,14 +3766,14 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Edital nº 08/2023 - CAPES/Cofecub, formato, pdf, 495kb</t>
+          <t>Edital nº 06/2024 - PDSE - formato, pdf, 133kb</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/03042023_Edital_1946708_Edital_8_2022.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/21032024_Edital_2344636_SEI_2343579_Edital_6_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -3773,7 +3781,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alteração doEdital nº 08/2023 - CAPES/Cofecub, formato, pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20062024_Edital_2401059_SEI_2399441_Edital_08_2023___ALTERACAO_II.pdf/@@display-file/file</t>
+          <t>Prorrogação do Edital nº 06/2024 - PDSE - formato, pdf, 55kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/10052024_Edital_2376323_SEI_2375557_Edital_6_2024.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3785,22 +3793,22 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Edital nº 08/2024 - CAPES/Cofecub, formato, pdf, 213kb</t>
+          <t>Edital nº 07/2023 - ProgramaCAPES/CLIMAT-AMSUD, formato - pdf, 466kb</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/22032024_Edital_2345736_SEI_2343959_Edital_8.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15032023_Edital_1933965_Edital_7_2023_.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alteração do Edital nº 08/2024 - Programa CAPES/Cofecub, formato, pdf, 54kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23122024_Edital_2517712_SEI_2516934_Edital_8_2024.pdf/@@display-file/file ; Prorrogação do Edital nº 08/2024 - CAPES/Cofecub, formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/02072024_Edital_2409554_SEI_2409272_Edital_08_2024___Prorrogacao.pdf/@@display-file/file ; Alteração do Edital nº 08/2024 - CAPES/Cofecub, formato, pdf, 57kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07052024_Edital_2373782_SEI_2372654_Edital_08_2024.pdf/@@display-file/file</t>
+          <t>Alteração doEdital nº 07/2023 - ProgramaCAPES/CLIMAT-AMSUD, formato - pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400133_SEI_2399445_Edital_07_2023___ALTERACAO_II.pdf/@@display-file/file ; Relação das inscrições do Edital nº 07/2023 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 570kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/30052023_Lista_Listagem_1984693_Lista_de_inscritos_Climat_Amsud_Edital_7.2023.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3812,20 +3820,24 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Edital nº 10/2022 - PDSE - formato, pdf, 337kb</t>
+          <t>Edital nº 08/2023 - CAPES/Cofecub, formato, pdf, 495kb</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/16022022_Edital10.22PDSE.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/03042023_Edital_1946708_Edital_8_2022.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>1</v>
-      </c>
-      <c r="G119" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Alteração doEdital nº 08/2023 - CAPES/Cofecub, formato, pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20062024_Edital_2401059_SEI_2399441_Edital_08_2023___ALTERACAO_II.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3835,20 +3847,24 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Edital nº 14/2025 - PCI - pdf, 83kb</t>
+          <t>Edital nº 08/2024 - CAPES/Cofecub, formato, pdf, 213kb</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/31072025_Edital_2646654_SEI_2644987_Edital_14_2025.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/22032024_Edital_2345736_SEI_2343959_Edital_8.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>1</v>
-      </c>
-      <c r="G120" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Alteração do Edital nº 08/2024 - Programa CAPES/Cofecub, formato, pdf, 54kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23122024_Edital_2517712_SEI_2516934_Edital_8_2024.pdf/@@display-file/file ; Prorrogação do Edital nº 08/2024 - CAPES/Cofecub, formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/02072024_Edital_2409554_SEI_2409272_Edital_08_2024___Prorrogacao.pdf/@@display-file/file ; Alteração do Edital nº 08/2024 - CAPES/Cofecub, formato, pdf, 57kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07052024_Edital_2373782_SEI_2372654_Edital_08_2024.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3858,24 +3874,20 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Edital nº 16/2025 - formato, pdf, 360kb</t>
+          <t>Edital nº 10/2022 - PDSE - formato, pdf, 337kb</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11082025_Edital_2654124.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/16022022_Edital10.22PDSE.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>2</v>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>Lista de inscritos no edital nº 16/2025 - formato, pdf, 207kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/29102025_Lista_Listagem_2693783_SEI___23038.003238_2025_21_buffalo.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3885,14 +3897,14 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Edital nº 16/2026 - Programa AURORA — Continuidade da Trajetória de Mães Cientistas</t>
+          <t>Edital nº 14/2025 - PCI - pdf, 83kb</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2818271_SEI_2817084_Edital_16_2026__1_.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/31072025_Edital_2646654_SEI_2644987_Edital_14_2025.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F122" t="n">
@@ -3908,20 +3920,24 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Edital nº 19/2017 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 315kb</t>
+          <t>Edital nº 16/2025 - formato, pdf, 360kb</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/31052017Edital192017PDPI.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11082025_Edital_2654124.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>1</v>
-      </c>
-      <c r="G123" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Lista de inscritos no edital nº 16/2025 - formato, pdf, 207kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/29102025_Lista_Listagem_2693783_SEI___23038.003238_2025_21_buffalo.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3931,14 +3947,14 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Edital nº 19/2026 - Programa Capes/Universidade em Buffalo (Capes/UB) - Professor Visitante - formato, pdf, 139kb</t>
+          <t>Edital nº 16/2026 - Programa AURORA — Continuidade da Trajetória de Mães Cientistas</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2843097_SEI_2842333_Edital_n__19_2026.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2818271_SEI_2817084_Edital_16_2026__1_.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F124" t="n">
@@ -3954,24 +3970,20 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Edital nº 20/2022 -Programa CAPES/STIC-AMSUD, formato, pdf - 286kb</t>
+          <t>Edital nº 19/2017 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 315kb</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07042022_Edital_1673688_EDITAL_20_2022_STIC_AMSUD.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/31052017Edital192017PDPI.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>3</v>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>Alteração do Edital nº 20/2022 -Programa CAPES/STIC-AMSUD, formato, pdf - 67kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400177_SEI_2399435_Edital_20_2022___ALTERACAO_I.pdf/@@display-file/file ; Relação das inscrições do Edital nº 20/2022 - Programa CAPES/STIC-AMSUD, formato - pdf, 358kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/06062022_Lista_Listagem_1727082_STIC.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3981,24 +3993,20 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Edital nº 21/2023 - Projetos de Cooperação entre Instituições para Qualificação de Profissionais de Nível Superior (PCI) - formato, pdf, 281kb</t>
+          <t>Edital nº 19/2026 - Programa Capes/Universidade em Buffalo (Capes/UB) - Professor Visitante - formato, pdf, 139kb</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/24082023_Edital_2043434_Edital_21_2023.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2843097_SEI_2842333_Edital_n__19_2026.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>3</v>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>Retificação do Edital nº 21/2023 - Projetos de Cooperação entre Instituições para Qualificação de Profissionais de Nível Superior (PCI) - formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/01112023_Edital_2262651_SEI_2262236_Edital_21_2023.pdf/@@display-file/file ; Alteração do Edital nº 21/2023 - Projetos de Cooperação entre Instituições para Qualificação de Profissionais de Nível Superior (PCI) - formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/31102023_Edital_2261925_SEI_2261451_Edital_22_2023.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4008,20 +4016,24 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Edital nº 21/2026 - Programa de Desenvolvimento da Pós-Graduação (PDPG) – Parcerias Estratégicas nos Estados VI – Rede de Pesquisa e Desenvolvimento da Região Nordeste, formato, pdf, 177kb</t>
+          <t>Edital nº 20/2022 -Programa CAPES/STIC-AMSUD, formato, pdf - 286kb</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2848691_sei_2847430_edital_n__21_2026.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07042022_Edital_1673688_EDITAL_20_2022_STIC_AMSUD.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>1</v>
-      </c>
-      <c r="G127" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Alteração do Edital nº 20/2022 -Programa CAPES/STIC-AMSUD, formato, pdf - 67kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400177_SEI_2399435_Edital_20_2022___ALTERACAO_I.pdf/@@display-file/file ; Relação das inscrições do Edital nº 20/2022 - Programa CAPES/STIC-AMSUD, formato - pdf, 358kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/06062022_Lista_Listagem_1727082_STIC.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4031,22 +4043,22 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Edital nº 22/2026 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 150kb</t>
+          <t>Edital nº 21/2023 - Projetos de Cooperação entre Instituições para Qualificação de Profissionais de Nível Superior (PCI) - formato, pdf, 281kb</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/sei_2849220_edital_n__22_2026.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/24082023_Edital_2043434_Edital_21_2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alteração Edital nº 22/2026 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 47,4kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2858430_sei_2857160_edital_22_2026___alteracao.pdf/@@display-file/file</t>
+          <t>Retificação do Edital nº 21/2023 - Projetos de Cooperação entre Instituições para Qualificação de Profissionais de Nível Superior (PCI) - formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/01112023_Edital_2262651_SEI_2262236_Edital_21_2023.pdf/@@display-file/file ; Alteração do Edital nº 21/2023 - Projetos de Cooperação entre Instituições para Qualificação de Profissionais de Nível Superior (PCI) - formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/31102023_Edital_2261925_SEI_2261451_Edital_22_2023.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4058,24 +4070,20 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Edital nº 23/2026 - Programa de Desenvolvimento Acadêmico Indígena (PDAI), formato, pdf, 168kb</t>
+          <t>Edital nº 21/2026 - Programa de Desenvolvimento da Pós-Graduação (PDPG) – Parcerias Estratégicas nos Estados VI – Rede de Pesquisa e Desenvolvimento da Região Nordeste, formato, pdf, 177kb</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2851776_sei_2851450_edital_n__23_2026.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2848691_sei_2847430_edital_n__21_2026.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>2</v>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>Alteração Edital nº 23/2026 - Programa de Desenvolvimento Acadêmico Indígena (PDAI), formato, pdf, 102kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2872644_edital_conjunto_23_2026___alteracao.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4085,14 +4093,14 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Edital nº 23/2026 - Programa Nacional de Formação de Professores da Educação Básica (PARFOR), formato, pdf, 168kb</t>
+          <t>Edital nº 22/2026 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 150kb</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2855421_sei_2854365_edital_n__23_2026.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/sei_2849220_edital_n__22_2026.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -4100,7 +4108,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alteração Edital nº 23/2026 - Programa Nacional de Formação de Professores da Educação Básica (PARFOR), formato, pdf, 130kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2875930_edital_23_2026___alteracao.pdf/@@display-file/file</t>
+          <t>Alteração Edital nº 22/2026 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 47,4kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2858430_sei_2857160_edital_22_2026___alteracao.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4112,20 +4120,24 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Edital nº 24/2026 - Cooperação entre Instituições para</t>
+          <t>Edital nº 23/2026 - Programa de Desenvolvimento Acadêmico Indígena (PDAI), formato, pdf, 168kb</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2878169_edital_24_2026___pci.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2851776_sei_2851450_edital_n__23_2026.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>1</v>
-      </c>
-      <c r="G131" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Alteração Edital nº 23/2026 - Programa de Desenvolvimento Acadêmico Indígena (PDAI), formato, pdf, 102kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2872644_edital_conjunto_23_2026___alteracao.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4135,22 +4147,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Edital nº 25/2022 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 353kb</t>
+          <t>Edital nº 23/2026 - Programa Nacional de Formação de Professores da Educação Básica (PARFOR), formato, pdf, 168kb</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/04052022_Edital_1698011_SEI_CAPES___1696119___Edital_25.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2855421_sei_2854365_edital_n__23_2026.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alteração do edital nº 25/2022 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 67kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400217_SEI_2399433_Edital_25_2022___ALTERACAO_I.pdf/@@display-file/file ; Relação das inscrições do Edital nº 25/2022 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 353kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/06062022_Lista_Listagem_1727108_Climat.pdf/@@display-file/file</t>
+          <t>Alteração Edital nº 23/2026 - Programa Nacional de Formação de Professores da Educação Básica (PARFOR), formato, pdf, 130kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2875930_edital_23_2026___alteracao.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4162,24 +4174,20 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Edital nº 25/2024 - Chamada Pública para envio de Proposta de Projeto de Cooperação entre Instituições para Qualificação de Profissionais de Nível Superior (PCI) - formato, pdf, 83kb</t>
+          <t>Edital nº 24/2026 - Cooperação entre Instituições para</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/17092024_Edital_2461148_SEI_2460992_Edital_25_2024.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2878169_edital_24_2026___pci.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>2</v>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>Alteração do Edital nº 25/2024 - Chamada Pública para envio de Proposta de Projeto de Cooperação entre Instituições para Qualificação de Profissionais de Nível Superior (PCI) - formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/10122024_Edital_2510251_SEI_2508924_Edital_25_2024___Alteracao.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4189,14 +4197,14 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Edital nº 26/2024 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE) - Retificação - formato, pdf, 48kb</t>
+          <t>Edital nº 25/2022 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 353kb</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/14102024_Edital_2477735_SEI_2477608_Edital_N__26_2024.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/04052022_Edital_1698011_SEI_CAPES___1696119___Edital_25.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -4204,7 +4212,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alteração do Edital nº 26/2024 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE), formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/13032025_Edital_2560841_SEI_2559847_Edital_26_2024___ALTERACAO.pdf/@@display-file/file ; Edital nº 26/2024 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 135kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/08102024_Edital_2474014_SEI_2472849_Edital_26_2024.pdf/@@display-file/file</t>
+          <t>Alteração do edital nº 25/2022 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 67kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400217_SEI_2399433_Edital_25_2022___ALTERACAO_I.pdf/@@display-file/file ; Relação das inscrições do Edital nº 25/2022 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 353kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/06062022_Lista_Listagem_1727108_Climat.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4216,14 +4224,14 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Edital nº 27/2024 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 157kb</t>
+          <t>Edital nº 25/2024 - Chamada Pública para envio de Proposta de Projeto de Cooperação entre Instituições para Qualificação de Profissionais de Nível Superior (PCI) - formato, pdf, 83kb</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/05112024_Edital_2490387_SEI_2489251_Edital_27_2024.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/17092024_Edital_2461148_SEI_2460992_Edital_25_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -4231,7 +4239,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alteração do Edital 27/2024 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa no EUA - PDPI - formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/02122024_Edital_2505290_SEI_2504109_Edital_27_2024__.pdf/@@display-file/file</t>
+          <t>Alteração do Edital nº 25/2024 - Chamada Pública para envio de Proposta de Projeto de Cooperação entre Instituições para Qualificação de Profissionais de Nível Superior (PCI) - formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/10122024_Edital_2510251_SEI_2508924_Edital_25_2024___Alteracao.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4243,14 +4251,14 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Edital nº 30/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 110kb</t>
+          <t>Edital nº 26/2024 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE) - Retificação - formato, pdf, 48kb</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/14022020_Edital_1145537_Edital_SITE.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/14102024_Edital_2477735_SEI_2477608_Edital_N__26_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F136" t="n">
@@ -4258,7 +4266,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Reabertura e alteração do Edital nº 30/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 222kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/28042022_Edital_1691552_SEI_CAPES___1685746___Edital_30_2019.pdf/@@display-file/file ; Suspensão do Edital nº 30/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 111kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_1326070_Edital_Suspensao_site.pdf/@@display-file/file</t>
+          <t>Alteração do Edital nº 26/2024 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE), formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/13032025_Edital_2560841_SEI_2559847_Edital_26_2024___ALTERACAO.pdf/@@display-file/file ; Edital nº 26/2024 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 135kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/08102024_Edital_2474014_SEI_2472849_Edital_26_2024.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4270,22 +4278,22 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Edital nº 30/2023 - PDSE - formato, pdf, 125kb</t>
+          <t>Edital nº 27/2024 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 157kb</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/06112023_Edital_2263037_SEI_2261948_Edital_30_2023.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/05112024_Edital_2490387_SEI_2489251_Edital_27_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Prorrogação do Edital nº 30/2023 - PDSE - formato, pdf, 136kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11012024_Edital_2306448_SEI_CAPES___2305414___Edital_30_2023___Prorrogacao.pdf/@@display-file/file ; Alteração do Edital nº 30/2023 - PDSE - formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/18122023_Edital_2293491_SEI_2293429_Edital_30_2023_Alteracao.pdf/@@display-file/file</t>
+          <t>Alteração do Edital 27/2024 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa no EUA - PDPI - formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/02122024_Edital_2505290_SEI_2504109_Edital_27_2024__.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4297,14 +4305,14 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Edital Nº 32/2022 - CAPES/Cofecub, formato, pdf, 225kb</t>
+          <t>Edital nº 30/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 110kb</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29062022_EDITAL32_2022_COFECUB.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/14022020_Edital_1145537_Edital_SITE.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F138" t="n">
@@ -4312,7 +4320,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alteração do Edital Nº 32/2022 - CAPES/Cofecub, formato, pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400143_SEI_2399437_Edital_32_2022___ALTERACAO_III.pdf/@@display-file/file ; Relação de inscritos do Edital Nº 32/2022 - CAPES/Cofecub, formato, pdf, 65kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/25082022_Lista_Listagem_1783309_EDITAL_32_2022___CAPES_COFECUB_Relacao_de_Inscricoes.pdf/@@display-file/file</t>
+          <t>Reabertura e alteração do Edital nº 30/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 222kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/28042022_Edital_1691552_SEI_CAPES___1685746___Edital_30_2019.pdf/@@display-file/file ; Suspensão do Edital nº 30/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 111kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_1326070_Edital_Suspensao_site.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4324,22 +4332,22 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Edital nº 32/2023 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 139kb</t>
+          <t>Edital nº 30/2023 - PDSE - formato, pdf, 125kb</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/16112023_Edital_2271416_SEI_2268914_Edital_32_2023.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/06112023_Edital_2263037_SEI_2261948_Edital_30_2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alteração do Edital nº 32/2023 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 57kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09022024_SEI_2321458_Edital_N__32_2023___ALTERACAOPDPI.pdf/@@display-file/file</t>
+          <t>Prorrogação do Edital nº 30/2023 - PDSE - formato, pdf, 136kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11012024_Edital_2306448_SEI_CAPES___2305414___Edital_30_2023___Prorrogacao.pdf/@@display-file/file ; Alteração do Edital nº 30/2023 - PDSE - formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/18122023_Edital_2293491_SEI_2293429_Edital_30_2023_Alteracao.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4351,20 +4359,24 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Edital nº 35/2011 - Certificação em Língua Inglesa - pdf, 615kb</t>
+          <t>Edital Nº 32/2022 - CAPES/Cofecub, formato, pdf, 225kb</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_035_CertificacaoEUAprofLingIngl_Fulbright.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29062022_EDITAL32_2022_COFECUB.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>1</v>
-      </c>
-      <c r="G140" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Alteração do Edital Nº 32/2022 - CAPES/Cofecub, formato, pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400143_SEI_2399437_Edital_32_2022___ALTERACAO_III.pdf/@@display-file/file ; Relação de inscritos do Edital Nº 32/2022 - CAPES/Cofecub, formato, pdf, 65kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/25082022_Lista_Listagem_1783309_EDITAL_32_2022___CAPES_COFECUB_Relacao_de_Inscricoes.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4374,20 +4386,24 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Edital nº 4/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 270kb</t>
+          <t>Edital nº 32/2023 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 139kb</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/08022019Edital4.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/16112023_Edital_2271416_SEI_2268914_Edital_32_2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>1</v>
-      </c>
-      <c r="G141" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Alteração do Edital nº 32/2023 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 57kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09022024_SEI_2321458_Edital_N__32_2023___ALTERACAOPDPI.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4397,24 +4413,20 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Edital nº 44/2012 - Programa de Aperfeiçoamento para Professores de Língua Inglesa nos Eua, pdf, 272kb</t>
+          <t>Edital nº 35/2011 - Certificação em Língua Inglesa - pdf, 615kb</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_0442012_ProfLingIngl_EUA.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_035_CertificacaoEUAprofLingIngl_Fulbright.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>3</v>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>Edital nº 44/2012 - Retificado - pdf, 528kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_0442012_ProfLIngRetif.pdf/@@display-file/file ; Retificação do Edital nº 44/2012 - pdf, 46kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/RetificacaoEdital442012_ProfLingInglEUA_01out12.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4424,24 +4436,20 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Edital nº 44/2022 - PDSE - formato, pdf, 337kb</t>
+          <t>Edital nº 4/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 270kb</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/22122022_Edital_1882688_Edital_44_2022.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/08022019Edital4.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>2</v>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>Alteração do Edital nº 44/2022 - PDSE - formato, pdf, 146kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23052023_Edital_1981709_Edital_44_2023.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4451,20 +4459,24 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Edital nº 52/2010 - Certificação em Língua Inglesa, pdf, 60kbDF</t>
+          <t>Edital nº 44/2012 - Programa de Aperfeiçoamento para Professores de Língua Inglesa nos Eua, pdf, 272kb</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_52_Certificacao_LinguaInglesa2010.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_0442012_ProfLingIngl_EUA.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>1</v>
-      </c>
-      <c r="G144" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Edital nº 44/2012 - Retificado - pdf, 528kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_0442012_ProfLIngRetif.pdf/@@display-file/file ; Retificação do Edital nº 44/2012 - pdf, 46kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/RetificacaoEdital442012_ProfLingInglEUA_01out12.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4474,14 +4486,14 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Edital Nº09/2026 - Programa CAPES/BRAFITEC, formato, pdf, 209kb</t>
+          <t>Edital nº 44/2022 - PDSE - formato, pdf, 337kb</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2800035_SEI_2799041_Edital_9__de_2026.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/22122022_Edital_1882688_Edital_44_2022.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F145" t="n">
@@ -4489,7 +4501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Edital n° 9/2026 - Lista de Inscritos, formato, pdf, 398kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/lista_listagem_2864548_sei_2863010_edital_minuta__.pdf/@@display-file/file</t>
+          <t>Alteração do Edital nº 44/2022 - PDSE - formato, pdf, 146kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23052023_Edital_1981709_Edital_44_2023.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4501,24 +4513,20 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Lista de inscritos do Edital Conjunto nº 01/2024 - Programa Caminhos Amefricanos, formato, pdf, 407kb</t>
+          <t>Edital nº 52/2010 - Certificação em Língua Inglesa, pdf, 60kbDF</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15052024_Lista_Listagem_2374115_Inscritos_MIR.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_52_Certificacao_LinguaInglesa2010.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>2</v>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>Alteração do Edital Conjunto nº 01/2024 - Programa Caminhos Amefricanos, formato, pdf, 63kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29042024_Edital_2368101_SEI_2365347_Edital_Conjunto_n__1_CAPES_MIR.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4528,20 +4536,24 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Lista de inscritos do Edital nº 05/2024 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 46kb</t>
+          <t>Edital Nº09/2026 - Programa CAPES/BRAFITEC, formato, pdf, 209kb</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/10062024_Lista_Listagem_2390159_Lista_de_Inscritos_3.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2800035_SEI_2799041_Edital_9__de_2026.pdf</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1</v>
-      </c>
-      <c r="G147" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Edital n° 9/2026 - Lista de Inscritos, formato, pdf, 398kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/lista_listagem_2864548_sei_2863010_edital_minuta__.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4551,20 +4563,24 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Lista de inscritos doEdital nº 8/202 - CAPES/COFECUB, formato, pdf, 581kb</t>
+          <t>Lista de inscritos do Edital Conjunto nº 01/2024 - Programa Caminhos Amefricanos, formato, pdf, 407kb</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/14062023_Lista_Listagem_1990268_Inscricoes_cofecub_2023.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15052024_Lista_Listagem_2374115_Inscritos_MIR.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1</v>
-      </c>
-      <c r="G148" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Alteração do Edital Conjunto nº 01/2024 - Programa Caminhos Amefricanos, formato, pdf, 63kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29042024_Edital_2368101_SEI_2365347_Edital_Conjunto_n__1_CAPES_MIR.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4574,24 +4590,20 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Lista de inscrições - Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 393kb</t>
+          <t>Lista de inscritos do Edital nº 05/2024 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 46kb</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Lista_de_Inscricoes_Homologadas_PDSE___2020_REVISADA.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/10062024_Lista_Listagem_2390159_Lista_de_Inscritos_3.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>4</v>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>Lista de candidaturas - Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 417kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/documentos/diretoria-de-relacoes-internacionais/pdse/Lista_Listagem_1439062_Lista_de_Inscricoes_Homologadas_PDSE___2020.pdf/@@display-file/file ; Retificação do Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 244kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/EDITAL192020_PDSERETIFICAO.pdf/@@display-file/file ; Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE)- formato, pdf, 236kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09102020_edital-19-pdse.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4601,24 +4613,20 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Lista de inscrições do Edital nº 17/2025 - Primeira chamada Programa Institucional de Doutorado Sanduíche no Exterior (PDSE) - formato, pdf, 8,8mb</t>
+          <t>Lista de inscritos doEdital nº 8/202 - CAPES/COFECUB, formato, pdf, 581kb</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/29102025_Lista_Listagem_2708089_PDSE.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/14062023_Lista_Listagem_1990268_Inscricoes_cofecub_2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>4</v>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>Lista de inscrições do Edital nº 17/2025 - Segunda chamada Programa Institucional de Doutorado Sanduíche no Exterior (PDSE) - formato, pdf, 1,4mb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/27042026_Lista_Listagem_2808119_Lista_de_inscricoes_homologadas_do_Edital_172025___PDSE___segunda_chamada___formato_pdf__2_.pdf/@@display-file/file ; Alteração do Edital nº 17/2025 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE), formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/08102025_Edital_2696973_SEI_2695934_Edital_17_2025__.pdf/@@display-file/file ; Edital nº 17/2025 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 142kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/21082025_Edital_2662823_SEI_2661209_Edital_n__17_2025.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4628,14 +4636,14 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Lista de instituições e cursos pré-aprovados para a 3ª fase do Edital nº 08/2022 - Parfor - formato, pdf, 715kb</t>
+          <t>Lista de inscrições - Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 393kb</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/06052022_Relacao_1700579_LISTA_DE_IES_E_CURSOS_APROVADOS_PARA_A_3__ETAPA_DO_EDITAL_CAPES_N__08.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Lista_de_Inscricoes_Homologadas_PDSE___2020_REVISADA.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -4643,7 +4651,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alteraçãodo Edital nº 08/2022 - Parfor - formato, xls, 119kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20122022_Edital_1880841_Edital_8_2022___PARFOR.pdf/@@display-file/file ; Alteração do Edital nº 08/2022 - Parfor - formato, pdf, 128kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09062022_Edital_1729649_EDITAL___8_2022.pdf/@@display-file/file ; Edital nº 08/2022 - Parfor - formato, pdf, 203kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07022022_Edital_1629612_SEI_CAPES___1628279___Edital_8.pdf/@@display-file/file</t>
+          <t>Lista de candidaturas - Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 417kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/documentos/diretoria-de-relacoes-internacionais/pdse/Lista_Listagem_1439062_Lista_de_Inscricoes_Homologadas_PDSE___2020.pdf/@@display-file/file ; Retificação do Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 244kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/EDITAL192020_PDSERETIFICAO.pdf/@@display-file/file ; Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE)- formato, pdf, 236kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09102020_edital-19-pdse.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4655,14 +4663,14 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Lista e inscritos do Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 520kb</t>
+          <t>Lista de inscrições do Edital nº 17/2025 - Primeira chamada Programa Institucional de Doutorado Sanduíche no Exterior (PDSE) - formato, pdf, 8,8mb</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/20022024_Lista_Listagem_2324280_SEI_2323841_Inscritos_MIR.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/29102025_Lista_Listagem_2708089_PDSE.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4670,7 +4678,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alteração do Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 54kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/12062024_Edital_2395239_SEI_2389783_Edital_34_2023.pdf/@@display-file/file ; Prorrogação do Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 54kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/28122023_Edital_2301024_SEI_2300438_Edital_Conjunto_n__34_2023_Prorrogacao.pdf/@@display-file/file ; Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 129kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/04122024_Edital_2282364_SEI_2279471_Edital_Conjunto_n__34_2023.pdf/@@display-file/file</t>
+          <t>Lista de inscrições do Edital nº 17/2025 - Segunda chamada Programa Institucional de Doutorado Sanduíche no Exterior (PDSE) - formato, pdf, 1,4mb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/27042026_Lista_Listagem_2808119_Lista_de_inscricoes_homologadas_do_Edital_172025___PDSE___segunda_chamada___formato_pdf__2_.pdf/@@display-file/file ; Alteração do Edital nº 17/2025 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE), formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/08102025_Edital_2696973_SEI_2695934_Edital_17_2025__.pdf/@@display-file/file ; Edital nº 17/2025 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 142kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/21082025_Edital_2662823_SEI_2661209_Edital_n__17_2025.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4682,22 +4690,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Lista final de inscritos no Edital n° 33/2022 - Brafitec, formato, pdf, 372kb</t>
+          <t>Lista de instituições e cursos pré-aprovados para a 3ª fase do Edital nº 08/2022 - Parfor - formato, pdf, 715kb</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/22092022_Lista_Listagem_1808291_Lista_inscritos_Brafitec_Edital_33_22.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/06052022_Relacao_1700579_LISTA_DE_IES_E_CURSOS_APROVADOS_PARA_A_3__ETAPA_DO_EDITAL_CAPES_N__08.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alteração do Edital n° 33/2022 - Brafitec, formato, pdf, 193kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23022023_Edital_1920292_Edital_33_22.pdf/@@display-file/file ; Edital n° 33/2022 - Brafitec, formato, pdf, 428kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29062022_EDITAL33_2022_BRAFITEC.pdf/@@display-file/file</t>
+          <t>Alteraçãodo Edital nº 08/2022 - Parfor - formato, xls, 119kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20122022_Edital_1880841_Edital_8_2022___PARFOR.pdf/@@display-file/file ; Alteração do Edital nº 08/2022 - Parfor - formato, pdf, 128kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09062022_Edital_1729649_EDITAL___8_2022.pdf/@@display-file/file ; Edital nº 08/2022 - Parfor - formato, pdf, 203kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07022022_Edital_1629612_SEI_CAPES___1628279___Edital_8.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4709,60 +4717,68 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Prorrogação do Edital nº 01/2024 - Programa Caminhos Amefricanos, formato, pdf, 69kb</t>
+          <t>Lista e inscritos do Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 520kb</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/30082024_Edital_2450719_SEI_2446271_Edital_Conjunto_1_2024.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/20022024_Lista_Listagem_2324280_SEI_2323841_Inscritos_MIR.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>1</v>
-      </c>
-      <c r="G154" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Alteração do Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 54kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/12062024_Edital_2395239_SEI_2389783_Edital_34_2023.pdf/@@display-file/file ; Prorrogação do Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 54kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/28122023_Edital_2301024_SEI_2300438_Edital_Conjunto_n__34_2023_Prorrogacao.pdf/@@display-file/file ; Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 129kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/04122024_Edital_2282364_SEI_2279471_Edital_Conjunto_n__34_2023.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>SETEC</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Chamada (documento Nº 6991254) para seleção de unidades da Rede Federal de Educação Profissional e Tecnológica e das redes públicas estaduais de Educação Profissional e Tecnológica, interessadas em receber apoio técnico para a implementação de programas de aprendizagem profissional articulados a cursos técnicos ou de qualificação profissional com componentes curriculares relacionados à sustentabilidade</t>
+          <t>Lista final de inscritos no Edital n° 33/2022 - Brafitec, formato, pdf, 372kb</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2026/SEI_6991254_chamada.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/22092022_Lista_Listagem_1808291_Lista_inscritos_Brafitec_Edital_33_22.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>1</v>
-      </c>
-      <c r="G155" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Alteração do Edital n° 33/2022 - Brafitec, formato, pdf, 193kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23022023_Edital_1920292_Edital_33_22.pdf/@@display-file/file ; Edital n° 33/2022 - Brafitec, formato, pdf, 428kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29062022_EDITAL33_2022_BRAFITEC.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SETEC</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Chamada Pública com o objetivo de identificar, avaliar, cadastrar e disponibilizar metodologias, ferramentas e estudos sobre o mapeamento de demandas por Educação Profissional Técnica de Nível Médio, visando aprimorar a definição de ofertas de Educação Profissional Técnica de Nível Médio, no âmbito do Programa Juros por Educação.</t>
+          <t>Prorrogação do Edital nº 01/2024 - Programa Caminhos Amefricanos, formato, pdf, 69kb</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/SEI_6268868_Resultado_de_Edital.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/30082024_Edital_2450719_SEI_2446271_Edital_Conjunto_1_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F156" t="n">
@@ -4778,14 +4794,14 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Chamada Pública de Adesão das Instituições da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT), com objetivo de capacitação técnica para submissão de propostas em futuros editais de unidades Embrapii.</t>
+          <t>Chamada (documento Nº 6991254) para seleção de unidades da Rede Federal de Educação Profissional e Tecnológica e das redes públicas estaduais de Educação Profissional e Tecnológica, interessadas em receber apoio técnico para a implementação de programas de aprendizagem profissional articulados a cursos técnicos ou de qualificação profissional com componentes curriculares relacionados à sustentabilidade</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/edital-2025/SEI_MEC5650163ResultadodeEdital_.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2026/SEI_6991254_chamada.pdf</t>
         </is>
       </c>
       <c r="F157" t="n">
@@ -4801,14 +4817,14 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Chamada Pública de Adesão à linha de fomento Qualifica Mais EnergIFE</t>
+          <t>Chamada Pública com o objetivo de identificar, avaliar, cadastrar e disponibilizar metodologias, ferramentas e estudos sobre o mapeamento de demandas por Educação Profissional Técnica de Nível Médio, visando aprimorar a definição de ofertas de Educação Profissional Técnica de Nível Médio, no âmbito do Programa Juros por Educação.</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/chamadapublica.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/SEI_6268868_Resultado_de_Edital.pdf</t>
         </is>
       </c>
       <c r="F158" t="n">
@@ -4824,14 +4840,14 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 01/2017 - Trata-se de chamada pública para seleção de servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) para capacitação em Gestão da Inovação.</t>
+          <t>Chamada Pública de Adesão das Instituições da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT), com objetivo de capacitação técnica para submissão de propostas em futuros editais de unidades Embrapii.</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/extrato_chamada_dou_cp_01_2017.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/edital-2025/SEI_MEC5650163ResultadodeEdital_.pdf</t>
         </is>
       </c>
       <c r="F159" t="n">
@@ -4847,14 +4863,14 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 01/2018 - Trata-se da chamada pública para seleção de propostas e servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) em efetivo exercício, para participarem da capacitação em Gestão da Inovação (GI - CSIRO).</t>
+          <t>Chamada Pública de Adesão à linha de fomento Qualifica Mais EnergIFE</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/20181030Edital012018ChamadaPblicaGICSIRO.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/chamadapublica.pdf</t>
         </is>
       </c>
       <c r="F160" t="n">
@@ -4870,14 +4886,14 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 02/2017 - Trata-se de chamada pública para concurso sobre educação profissional da Secretaria de Educação Profissional e Tecnológica (Setec/MEC) em parceria com a Comunidade dos Países de Língua Portuguesa (CPLP).</t>
+          <t>Chamada Pública nº 01/2017 - Trata-se de chamada pública para seleção de servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) para capacitação em Gestão da Inovação.</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/edital_concurso_cplp_2017.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/extrato_chamada_dou_cp_01_2017.pdf</t>
         </is>
       </c>
       <c r="F161" t="n">
@@ -4893,14 +4909,14 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 02/2018 - Trata-se da chamada pública para seleção de servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) para a capacitação Brasileiros Formando Formadores (BraFF).</t>
+          <t>Chamada Pública nº 01/2018 - Trata-se da chamada pública para seleção de propostas e servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) em efetivo exercício, para participarem da capacitação em Gestão da Inovação (GI - CSIRO).</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/Edital_02_2018_BRAFF.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/20181030Edital012018ChamadaPblicaGICSIRO.pdf</t>
         </is>
       </c>
       <c r="F162" t="n">
@@ -4916,14 +4932,14 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 38/2018 - Trata do processo de seleção de propostas para credenciamento de instituições da Rede Federal, Faculdades de Tecnologia do Estado de São Paulo (Fatecs) e do Instituto Tecnológico de Aeronáutica (ITA) para atuação como Núcleo de Línguas (NucLi-IsF) no âmbito do Programa Idiomas sem Fronteiras (IsF).</t>
+          <t>Chamada Pública nº 02/2017 - Trata-se de chamada pública para concurso sobre educação profissional da Secretaria de Educação Profissional e Tecnológica (Setec/MEC) em parceria com a Comunidade dos Países de Língua Portuguesa (CPLP).</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/Editaln382018ChamadaPblicaparacredenciamentodeinstituiesdaRFEPCTdasFatecsedoITA.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/edital_concurso_cplp_2017.pdf</t>
         </is>
       </c>
       <c r="F163" t="n">
@@ -4939,14 +4955,14 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 79/2016 - Trata-se de chamada pública para apresentação de propostas por instituição de educação profissional e tecnológica para a oferta de cursos de formação inicial e continuada ou de qualificação profissional e cursos técnicos de nível médio, presenciais ou à distância, sem transferência de recursos, no âmbito do PRONATEC, denominada “PROPOSTAS VOLUNTÁRIAS - PRONATEC”</t>
+          <t>Chamada Pública nº 02/2018 - Trata-se da chamada pública para seleção de servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) para a capacitação Brasileiros Formando Formadores (BraFF).</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/extrato_edital_79_2016_setec.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/Edital_02_2018_BRAFF.pdf</t>
         </is>
       </c>
       <c r="F164" t="n">
@@ -4962,14 +4978,14 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Chamada Pública que estabelece os procedimentos para a autorização de oferta de cursos técnicos de nível médio por Instituições Privadas de Ensino Superior (IPES) para fins de habilitação ao Programa Juros por Educação, no âmbito do Programa de Pleno Pagamento de Dívidas dos Estados (Propag).</t>
+          <t>Chamada Pública nº 38/2018 - Trata do processo de seleção de propostas para credenciamento de instituições da Rede Federal, Faculdades de Tecnologia do Estado de São Paulo (Fatecs) e do Instituto Tecnológico de Aeronáutica (ITA) para atuação como Núcleo de Línguas (NucLi-IsF) no âmbito do Programa Idiomas sem Fronteiras (IsF).</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/FAQEdital6.2025.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/Editaln382018ChamadaPblicaparacredenciamentodeinstituiesdaRFEPCTdasFatecsedoITA.pdf</t>
         </is>
       </c>
       <c r="F165" t="n">
@@ -4985,14 +5001,14 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Chamamento Público para credenciamento de profissionais no Banco de Especialistas para atuar no Projeto Assistec Inova, junto ao Ministério da Educação, no âmbito da Secretaria de Educação Profissional e Tecnológica.</t>
+          <t>Chamada Pública nº 79/2016 - Trata-se de chamada pública para apresentação de propostas por instituição de educação profissional e tecnológica para a oferta de cursos de formação inicial e continuada ou de qualificação profissional e cursos técnicos de nível médio, presenciais ou à distância, sem transferência de recursos, no âmbito do PRONATEC, denominada “PROPOSTAS VOLUNTÁRIAS - PRONATEC”</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/SEI_23000.035944_2024_89.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/extrato_edital_79_2016_setec.pdf</t>
         </is>
       </c>
       <c r="F166" t="n">
@@ -5008,14 +5024,14 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Edital 1/2026 - Chamada Pública de Adesão dos Institutos Federais de Educação, Ciência e Tecnologia, do Centro Federal de Educação Tecnológica Celso Suckow da Fonseca, do Centro Federal de Educação Tecnológica de Minas Gerais e do Colégio Pedro II, com objetivo de capacitação técnica para submissão de propostas em futuros editais de Unidades Embrapii.</t>
+          <t>Chamada Pública que estabelece os procedimentos para a autorização de oferta de cursos técnicos de nível médio por Instituições Privadas de Ensino Superior (IPES) para fins de habilitação ao Programa Juros por Educação, no âmbito do Programa de Pleno Pagamento de Dívidas dos Estados (Propag).</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/edital12026.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/FAQEdital6.2025.pdf</t>
         </is>
       </c>
       <c r="F167" t="n">
@@ -5031,14 +5047,14 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Edital 84/2021 - Seleção de Projetos para desenvolvimento dos Ambientes de Promotores de Inovação na Rede Federal</t>
+          <t>Chamamento Público para credenciamento de profissionais no Banco de Especialistas para atuar no Projeto Assistec Inova, junto ao Ministério da Educação, no âmbito da Secretaria de Educação Profissional e Tecnológica.</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/editais/2022/ResultadoetapaI.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/SEI_23000.035944_2024_89.pdf</t>
         </is>
       </c>
       <c r="F168" t="n">
@@ -5054,14 +5070,14 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Edital nº 01/2017 - APRESENTAÇÃO DE PROPOSTAS PARA A OFERTA DE VAGAS GRATUITAS EM CURSOS TÉCNICOS NA FORMA CONCOMITANTE, NO ÂMBITO DO PRONATEC/MEDIOTEC – 2º/2017 - A Secretária de Educação Profissional e Tecnológica do Ministério da Educação, no uso da atribuição que lhe confere o art. 13, Anexo I, do Decreto n° 7.690, de 02 de março de 2012, e considerando o disposto na Lei nº 12.513, de 26 de outubro de 2011, a Portaria nº 817, de 13 de agosto de 2015, a Portaria nº160, de 05 de março de 2013, alterada pela Portaria nº 701, de 13 de agosto de 2014, TORNA PÚBLICO os procedimentos e o cronograma para a apresentação de propostas visando a oferta de vagas gratuitas em cursos técnicos na forma concomitante e na modalidade presencial, no âmbito do Programa Nacional de Acesso ao Ensino Técnico e Emprego - PRONATEC, por meio da ação MEDIOTEC, para ingresso no segundo semestre de 2017.</t>
+          <t>Edital 1/2026 - Chamada Pública de Adesão dos Institutos Federais de Educação, Ciência e Tecnologia, do Centro Federal de Educação Tecnológica Celso Suckow da Fonseca, do Centro Federal de Educação Tecnológica de Minas Gerais e do Colégio Pedro II, com objetivo de capacitação técnica para submissão de propostas em futuros editais de Unidades Embrapii.</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/edital_01_mediotec_2017.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/edital12026.pdf</t>
         </is>
       </c>
       <c r="F169" t="n">
@@ -5077,14 +5093,14 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Edital nº 08/2024 - Chamamento Público visando à seleção de autores(as) para elaboração de capítulos de obra a ser publicada cuja temática central é a gestão de Núcleos de Inovação Tecnológica (NITs) e/ou de Agências de Inovação da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) Divulgação das Inscrições Homologadas</t>
+          <t>Edital 84/2021 - Seleção de Projetos para desenvolvimento dos Ambientes de Promotores de Inovação na Rede Federal</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/436.SEI_MEC5030251Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/editais/2022/ResultadoetapaI.pdf</t>
         </is>
       </c>
       <c r="F170" t="n">
@@ -5100,14 +5116,14 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Edital nº 1/2023 - Seleção de proposta de selo comemorativo, em alusão aos 15 anos dos Institutos Federais.</t>
+          <t>Edital nº 01/2017 - APRESENTAÇÃO DE PROPOSTAS PARA A OFERTA DE VAGAS GRATUITAS EM CURSOS TÉCNICOS NA FORMA CONCOMITANTE, NO ÂMBITO DO PRONATEC/MEDIOTEC – 2º/2017 - A Secretária de Educação Profissional e Tecnológica do Ministério da Educação, no uso da atribuição que lhe confere o art. 13, Anexo I, do Decreto n° 7.690, de 02 de março de 2012, e considerando o disposto na Lei nº 12.513, de 26 de outubro de 2011, a Portaria nº 817, de 13 de agosto de 2015, a Portaria nº160, de 05 de março de 2013, alterada pela Portaria nº 701, de 13 de agosto de 2014, TORNA PÚBLICO os procedimentos e o cronograma para a apresentação de propostas visando a oferta de vagas gratuitas em cursos técnicos na forma concomitante e na modalidade presencial, no âmbito do Programa Nacional de Acesso ao Ensino Técnico e Emprego - PRONATEC, por meio da ação MEDIOTEC, para ingresso no segundo semestre de 2017.</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC4094376Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/edital_01_mediotec_2017.pdf</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -5123,14 +5139,14 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Edital nº 100/2022 - Chamamento Público para a seleção de propostas para o Desafio Soutec</t>
+          <t>Edital nº 08/2024 - Chamamento Público visando à seleção de autores(as) para elaboração de capítulos de obra a ser publicada cuja temática central é a gestão de Núcleos de Inovação Tecnológica (NITs) e/ou de Agências de Inovação da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) Divulgação das Inscrições Homologadas</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/secretarias/secretaria-de-educacao-profissional/editais-2022/SEI_MEC3570188Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/436.SEI_MEC5030251Edital.pdf</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -5146,14 +5162,14 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Edital nº 109/2022 - Chamamento Público - Seleção de projetos voltados à promoção do empreendedorismo inovador, com foco na Economia 4.0, associados ao ensino, à pesquisa e à extensão, destinado às instituições integrantes da Rede Federal de Educação Profissional, Científica e Tecnológica</t>
+          <t>Edital nº 1/2023 - Seleção de proposta de selo comemorativo, em alusão aos 15 anos dos Institutos Federais.</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital109.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC4094376Edital.pdf</t>
         </is>
       </c>
       <c r="F173" t="n">
@@ -5169,14 +5185,14 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Edital nº 11/2024 - Chamamento Público para a seleção de projetos aptos a integrarem a 4ª Semana Nacional de Educação Profissional e Tecnológica Retificação do</t>
+          <t>Edital nº 100/2022 - Chamamento Público para a seleção de propostas para o Desafio Soutec</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-2024-1/Edital_11.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/secretarias/secretaria-de-educacao-profissional/editais-2022/SEI_MEC3570188Edital.pdf</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -5192,14 +5208,14 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Edital nº 15/2023 - Chamada Pública para o Workshop para elaboração de Itinerários Formativos em economia circular na Educação Profissional e Tecnológica</t>
+          <t>Edital nº 109/2022 - Chamamento Público - Seleção de projetos voltados à promoção do empreendedorismo inovador, com foco na Economia 4.0, associados ao ensino, à pesquisa e à extensão, destinado às instituições integrantes da Rede Federal de Educação Profissional, Científica e Tecnológica</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/SEI_MEC3884064Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital109.pdf</t>
         </is>
       </c>
       <c r="F175" t="n">
@@ -5215,14 +5231,14 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Edital nº 2/2020 - IFES, de chamada pública para a seleção de projetos voltados à implementação das Oficinas 4.0, aberto às autarquias da Rede Federal.</t>
+          <t>Edital nº 11/2024 - Chamamento Público para a seleção de projetos aptos a integrarem a 4ª Semana Nacional de Educação Profissional e Tecnológica Retificação do</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
-          <t>https://www.ifes.edu.br/chamadas-publicas/19329-chamada-publica-2-2020-apoio-a-implementacao-de-oficinas-4-0</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-2024-1/Edital_11.pdf</t>
         </is>
       </c>
       <c r="F176" t="n">
@@ -5238,14 +5254,14 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Edital nº 20/2021 – Seleção de servidores para atuação em Projetos de Colaboração Técnica junto ao Ministério da Educação.</t>
+          <t>Edital nº 15/2023 - Chamada Pública para o Workshop para elaboração de Itinerários Formativos em economia circular na Educação Profissional e Tecnológica</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/SEI_MEC2573324Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/SEI_MEC3884064Edital.pdf</t>
         </is>
       </c>
       <c r="F177" t="n">
@@ -5261,14 +5277,14 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Edital nº 25/2023 - Chamada Pública destinada a selecionar equipes da Rede Federal de Educação Profissional, Científica e Tecnológica (EPCT) para participação no projeto de formação em criatividade, inovação e prototipagem do mercosul (Hackathon Mercosul). Retificação do Edital</t>
+          <t>Edital nº 2/2020 - IFES, de chamada pública para a seleção de projetos voltados à implementação das Oficinas 4.0, aberto às autarquias da Rede Federal.</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/SEI_MEC3913111Edital.pdf</t>
+          <t>https://www.ifes.edu.br/chamadas-publicas/19329-chamada-publica-2-2020-apoio-a-implementacao-de-oficinas-4-0</t>
         </is>
       </c>
       <c r="F178" t="n">
@@ -5284,14 +5300,14 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Edital nº 26 versão consolidada</t>
+          <t>Edital nº 20/2021 – Seleção de servidores para atuação em Projetos de Colaboração Técnica junto ao Ministério da Educação.</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC3980995Documento.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/SEI_MEC2573324Edital.pdf</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -5307,14 +5323,14 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Edital nº 3/2021 – Chamada Pública para seleção de projetos de iniciação tecnológica com foco na Economia 4.0. Acesse o edital .</t>
+          <t>Edital nº 25/2023 - Chamada Pública destinada a selecionar equipes da Rede Federal de Educação Profissional, Científica e Tecnológica (EPCT) para participação no projeto de formação em criatividade, inovação e prototipagem do mercosul (Hackathon Mercosul). Retificação do Edital</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>https://www.ifes.edu.br/chamadas-publicas/19351-chamada-publica-3-2020-projetos-iniciacao-tecnologica-economia-4-0</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/SEI_MEC3913111Edital.pdf</t>
         </is>
       </c>
       <c r="F180" t="n">
@@ -5330,24 +5346,20 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Edital nº 35/2020 - Chamada Pública - que tem como objetivo selecionar projetos voltados à criação de Laboratórios IFMaker junto aos Institutos Federais de Educação, Ciência e Tecnologia; Centros Federais de Educação Tecnológica Celso Suckow da Fonseca – Cefet-RJ e de Minas Gerais – Cefet-MG e o Colégio Pedro II, conforme especificado no Despacho SEI nº 2064854</t>
+          <t>Edital nº 26 versão consolidada</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2020/SEI_MEC_2064339_Edital_Chamada_Publica.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC3980995Documento.pdf</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>2</v>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>Retificação Edital nº 35/2020 - Chamada Pública - Seleção de projetos voltados à criação de Laboratórios Maker junto à Rede Federal de Educação Profissional, Científica e Tecnológica Retificação de Cronograma ​do | https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/AlteraodecronogramaRedeMakeredital35.pdf</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -5357,14 +5369,14 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Edital nº 46, de 20 de julho de 2020, que torna público edital para adesão de estados e Distrito Federal à oferta de Curso de Especialização Lato Sensu em Docência para a Educação Profissional e Tecnológica (DocentEPT) aos professores da rede pública estadual e distrital que atuam na oferta de cursos de Educação Profissional e Tecnológica</t>
+          <t>Edital nº 3/2021 – Chamada Pública para seleção de projetos de iniciação tecnológica com foco na Economia 4.0. Acesse o edital .</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2020/Editaldeadeso_DOU.pdf</t>
+          <t>https://www.ifes.edu.br/chamadas-publicas/19351-chamada-publica-3-2020-projetos-iniciacao-tecnologica-economia-4-0</t>
         </is>
       </c>
       <c r="F182" t="n">
@@ -5380,20 +5392,24 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Edital nº 47/2022 - Chamada Pública para oferta de cursos da Plataforma Aprenda Mais</t>
+          <t>Edital nº 35/2020 - Chamada Pública - que tem como objetivo selecionar projetos voltados à criação de Laboratórios IFMaker junto aos Institutos Federais de Educação, Ciência e Tecnologia; Centros Federais de Educação Tecnológica Celso Suckow da Fonseca – Cefet-RJ e de Minas Gerais – Cefet-MG e o Colégio Pedro II, conforme especificado no Despacho SEI nº 2064854</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/editais/2022/Editaln47.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2020/SEI_MEC_2064339_Edital_Chamada_Publica.pdf</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>1</v>
-      </c>
-      <c r="G183" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Retificação Edital nº 35/2020 - Chamada Pública - Seleção de projetos voltados à criação de Laboratórios Maker junto à Rede Federal de Educação Profissional, Científica e Tecnológica Retificação de Cronograma ​do | https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/AlteraodecronogramaRedeMakeredital35.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -5403,14 +5419,14 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Edital nº 48/2022 - Procedimentos para autorização da oferta de cursos técnicos de nível médio por Instituições Privadas de Ensino Superior – Anexos do</t>
+          <t>Edital nº 46, de 20 de julho de 2020, que torna público edital para adesão de estados e Distrito Federal à oferta de Curso de Especialização Lato Sensu em Docência para a Educação Profissional e Tecnológica (DocentEPT) aos professores da rede pública estadual e distrital que atuam na oferta de cursos de Educação Profissional e Tecnológica</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/editais/2022/Editaln48.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2020/Editaldeadeso_DOU.pdf</t>
         </is>
       </c>
       <c r="F184" t="n">
@@ -5426,14 +5442,14 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Edital nº 5 /2026 - Seleção de propostas de projetos de extensão voltados ao Acesso, à Permanência e ao Êxito no âmbito da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT).</t>
+          <t>Edital nº 47/2022 - Chamada Pública para oferta de cursos da Plataforma Aprenda Mais</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2026/sei_7012727_edital_5.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/editais/2022/Editaln47.pdf</t>
         </is>
       </c>
       <c r="F185" t="n">
@@ -5449,14 +5465,14 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Edital nº 5/2020 – Chamada para seleção de projetos de apoio ao empreendedorismo inovador com foco na Economia 4.0. Acesse o edital .</t>
+          <t>Edital nº 48/2022 - Procedimentos para autorização da oferta de cursos técnicos de nível médio por Instituições Privadas de Ensino Superior – Anexos do</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
-          <t>https://www.ifes.edu.br/chamadas-publicas/19384-chamada-publica-05-2020-selecao-de-projetos-de-apoio-ao-empreendedorismo-inovador-com-foco-na-economia-4-0</t>
+          <t>https://www.gov.br/mec/pt-br/media/editais/2022/Editaln48.pdf</t>
         </is>
       </c>
       <c r="F186" t="n">
@@ -5472,14 +5488,14 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Edital nº 5/2021 – IF Mais Empreendedor Nacional : Adesão ao Programa IF Mais Empreendedor Nacional</t>
+          <t>Edital nº 5 /2026 - Seleção de propostas de projetos de extensão voltados ao Acesso, à Permanência e ao Êxito no âmbito da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT).</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/editais/2021/Edital05.2021IFEMPREENDEDORNACIONAL.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2026/sei_7012727_edital_5.pdf</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -5495,14 +5511,14 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Edital nº 5/2024 - Seleção de propostas de novos Cursos Abertos, On-line e Massivos (MOOCs), desenvolvidos pela Rede Federa de Educação Profissional, Científica e Tecnológica, a serem disponibilizados na Plataforma APRENDA MAIS.</t>
+          <t>Edital nº 5/2020 – Chamada para seleção de projetos de apoio ao empreendedorismo inovador com foco na Economia 4.0. Acesse o edital .</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC4659481Edital.pdf</t>
+          <t>https://www.ifes.edu.br/chamadas-publicas/19384-chamada-publica-05-2020-selecao-de-projetos-de-apoio-ao-empreendedorismo-inovador-com-foco-na-economia-4-0</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -5518,14 +5534,14 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Edital nº 52/2016 – que torna público, para conhecimento dos interessados, que será realizado na modalidade concurso, o PROJETO DESAFIO DA EDUCAÇÃO PROFISSIONAL E TECNOLÓGICA, na forma do REGULAMENTO anexo a este edital, com o objetivo de promover uma campanha nacional para aprimorar a Educação Profissional e Tecnológica estimulando a sociedade a enviar propostas de ações inovadoras e compartilhar experiências exitosas de implementação de ações.</t>
+          <t>Edital nº 5/2021 – IF Mais Empreendedor Nacional : Adesão ao Programa IF Mais Empreendedor Nacional</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/edital_n_52_2016.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/editais/2021/Edital05.2021IFEMPREENDEDORNACIONAL.pdf</t>
         </is>
       </c>
       <c r="F189" t="n">
@@ -5541,14 +5557,14 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Edital nº 55/2016 , que torna público concurso PROJETO DESAFIO EDUCAÇÃO ZIKAZERO, na forma do REGULAMENTO anexo a este edital, com o objetivo de promover uma campanha nacional de mobilização para o enfrentamento ao Aedes aegyp e à microcefalia estimulando a sociedade a enviar propostas de ações inovadoras e compartilhar experiências exitosas de implementação de ações em prol do combate ao mosquito.</t>
+          <t>Edital nº 5/2024 - Seleção de propostas de novos Cursos Abertos, On-line e Massivos (MOOCs), desenvolvidos pela Rede Federa de Educação Profissional, Científica e Tecnológica, a serem disponibilizados na Plataforma APRENDA MAIS.</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/Edital_55_2016_SEI_MEC_0227936.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC4659481Edital.pdf</t>
         </is>
       </c>
       <c r="F190" t="n">
@@ -5564,14 +5580,14 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Edital nº 6/2021 - Edital de Adesão das instituições ao Sistema Re-Saber</t>
+          <t>Edital nº 52/2016 – que torna público, para conhecimento dos interessados, que será realizado na modalidade concurso, o PROJETO DESAFIO DA EDUCAÇÃO PROFISSIONAL E TECNOLÓGICA, na forma do REGULAMENTO anexo a este edital, com o objetivo de promover uma campanha nacional para aprimorar a Educação Profissional e Tecnológica estimulando a sociedade a enviar propostas de ações inovadoras e compartilhar experiências exitosas de implementação de ações.</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/Edital_06_2021.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/edital_n_52_2016.pdf</t>
         </is>
       </c>
       <c r="F191" t="n">
@@ -5587,14 +5603,14 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Edital nº 6/2024 - Edital visa selecionar a proposta de selo/logomarca que será utilizado em confecções comemorativas no contexto dos 115 anos da Rede Federal de Educação Profissional, Científica e Tecnológica, que poderá ser personalizado como selo postal, via Correios. *</t>
+          <t>Edital nº 55/2016 , que torna público concurso PROJETO DESAFIO EDUCAÇÃO ZIKAZERO, na forma do REGULAMENTO anexo a este edital, com o objetivo de promover uma campanha nacional de mobilização para o enfrentamento ao Aedes aegyp e à microcefalia estimulando a sociedade a enviar propostas de ações inovadoras e compartilhar experiências exitosas de implementação de ações em prol do combate ao mosquito.</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-2024/325.SEI_MEC4985249Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/Edital_55_2016_SEI_MEC_0227936.pdf</t>
         </is>
       </c>
       <c r="F192" t="n">
@@ -5610,14 +5626,14 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Edital nº 61/2019 – Regulamento do Cadastro de Especialistas para compor o Banco de Avaliadores da Secretaria de Educação Profissional e Tecnológica.</t>
+          <t>Edital nº 6/2021 - Edital de Adesão das instituições ao Sistema Re-Saber</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2019/EDITALN612019.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/Edital_06_2021.pdf</t>
         </is>
       </c>
       <c r="F193" t="n">
@@ -5633,14 +5649,14 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Edital nº 63/2021- Seleção de Projetos de Promoção às Indicações Geográficas</t>
+          <t>Edital nº 6/2024 - Edital visa selecionar a proposta de selo/logomarca que será utilizado em confecções comemorativas no contexto dos 115 anos da Rede Federal de Educação Profissional, Científica e Tecnológica, que poderá ser personalizado como selo postal, via Correios. *</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/editais/2021/Edital63.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-2024/325.SEI_MEC4985249Edital.pdf</t>
         </is>
       </c>
       <c r="F194" t="n">
@@ -5656,14 +5672,14 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Edital nº 67/2021 - Chamada Pública de Projetos para apoio à implementação das Oficinas 4.0</t>
+          <t>Edital nº 61/2019 – Regulamento do Cadastro de Especialistas para compor o Banco de Avaliadores da Secretaria de Educação Profissional e Tecnológica.</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/SEI_MEC2898796Edital67.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2019/EDITALN612019.pdf</t>
         </is>
       </c>
       <c r="F195" t="n">
@@ -5679,14 +5695,14 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Edital nº 68/2019 – Seleção de servidores para atuação em Projetos Educacionais de Colaboração Técnica junto ao Ministério da Educação.</t>
+          <t>Edital nº 63/2021- Seleção de Projetos de Promoção às Indicações Geográficas</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2019/EDITALN682019.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/editais/2021/Edital63.pdf</t>
         </is>
       </c>
       <c r="F196" t="n">
@@ -5702,14 +5718,14 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Edital nº 83/2022 – Seleção de propostas de instituições da Rede Federal para a implementação de programa de capacitação de estudantes denominado Oficinas 4.0</t>
+          <t>Edital nº 67/2021 - Chamada Pública de Projetos para apoio à implementação das Oficinas 4.0</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital83.2022.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/SEI_MEC2898796Edital67.pdf</t>
         </is>
       </c>
       <c r="F197" t="n">
@@ -5725,14 +5741,14 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Edital nº 88/2022 – Seleção de projetos de iniciação tecnológica de instituições da RFEPCT para o desenvolvimento de ações de formação em programação e/ou robótica e/ou cultura maker para estudantes dos anos finais do ensino fundamental (6º ao 9º ano) das redes públicas de ensino. Retificação ​do</t>
+          <t>Edital nº 68/2019 – Seleção de servidores para atuação em Projetos Educacionais de Colaboração Técnica junto ao Ministério da Educação.</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital88.2022.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2019/EDITALN682019.pdf</t>
         </is>
       </c>
       <c r="F198" t="n">
@@ -5748,14 +5764,14 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Edital nº 94/2022 – Chamada Pública para a capacitação de multiplicadores em bioeconomia para a Amazônia Legal. Chamada Pública para a Adesão de parceiros ofertantes da Rede Federal de Educação Profissional, Científica e Tecnológica – RFEPCT à linha de fomento Qualifica Mais EnergIFE, voltada à promoção da oferta de cursos na área das Energias Renováveis. Retificação do</t>
+          <t>Edital nº 83/2022 – Seleção de propostas de instituições da Rede Federal para a implementação de programa de capacitação de estudantes denominado Oficinas 4.0</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Editaln94.2022.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital83.2022.pdf</t>
         </is>
       </c>
       <c r="F199" t="n">
@@ -5771,14 +5787,14 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Edital nº 99/2022 - Chamamento Público para a seleção de projetos de inovação e trabalhos acadêmicos aptos a integrarem a Semana Nacional da Educação Profissional e Tecnológica Retificação do</t>
+          <t>Edital nº 88/2022 – Seleção de projetos de iniciação tecnológica de instituições da RFEPCT para o desenvolvimento de ações de formação em programação e/ou robótica e/ou cultura maker para estudantes dos anos finais do ensino fundamental (6º ao 9º ano) das redes públicas de ensino. Retificação ​do</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/secretarias/secretaria-de-educacao-profissional/SEI_MEC3566713Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital88.2022.pdf</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -5794,14 +5810,14 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Programa Setec-Capes/NOVA de capacitação para Professores da Rede Federal de Educação Profissional, Científica e Tecnológica . A Secretaria de Educação Profissional e Tecnológica (Setec) do Ministério da Educação, com apoio da Coordenação de Aperfeiçoamento de Pessoal de Nível Superior (Capes), lançam chamada pública de capacitação para professores de inglês em efetivo exercício na Rede Federal de Educação Profissional - Institutos Federais, Cefets, Escolas Técnicas vinculas às Universidades Federais e Colégio Pedro II. (Retificação publicada no Diário Oficial da União em 02 de junho de 2016)</t>
+          <t>Edital nº 94/2022 – Chamada Pública para a capacitação de multiplicadores em bioeconomia para a Amazônia Legal. Chamada Pública para a Adesão de parceiros ofertantes da Rede Federal de Educação Profissional, Científica e Tecnológica – RFEPCT à linha de fomento Qualifica Mais EnergIFE, voltada à promoção da oferta de cursos na área das Energias Renováveis. Retificação do</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2015/chamada_setec_capes_nova_extrato_dou.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Editaln94.2022.pdf</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -5817,24 +5833,20 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Republicação do Edital nº 76/2022 - Chamamento Público para seleção de projetos voltados ao fortalecimento de Núcleos de Inovação Tecnológica e/ou Agências de Inovação.</t>
+          <t>Edital nº 99/2022 - Chamamento Público para a seleção de projetos de inovação e trabalhos acadêmicos aptos a integrarem a Semana Nacional da Educação Profissional e Tecnológica Retificação do</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Republicaodoedital76.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/secretarias/secretaria-de-educacao-profissional/SEI_MEC3566713Edital.pdf</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>2</v>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>Retificação do Edital nº 76/2022 – novo cronograma | https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/SEI_23000.006585_2022_91.pdf</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -5844,14 +5856,14 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições da Rede Federal de Educação Profissional, Científica e Tecnológica).</t>
+          <t>Programa Setec-Capes/NOVA de capacitação para Professores da Rede Federal de Educação Profissional, Científica e Tecnológica . A Secretaria de Educação Profissional e Tecnológica (Setec) do Ministério da Educação, com apoio da Coordenação de Aperfeiçoamento de Pessoal de Nível Superior (Capes), lançam chamada pública de capacitação para professores de inglês em efetivo exercício na Rede Federal de Educação Profissional - Institutos Federais, Cefets, Escolas Técnicas vinculas às Universidades Federais e Colégio Pedro II. (Retificação publicada no Diário Oficial da União em 02 de junho de 2016)</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/ResultadoEdital10.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2015/chamada_setec_capes_nova_extrato_dou.pdf</t>
         </is>
       </c>
       <c r="F203" t="n">
@@ -5867,20 +5879,24 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições Privadas de Ensino Superior que ofertam cursos técnicos e Escolas Técnicas Privadas).</t>
+          <t>Republicação do Edital nº 76/2022 - Chamamento Público para seleção de projetos voltados ao fortalecimento de Núcleos de Inovação Tecnológica e/ou Agências de Inovação.</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/ResultadoEdital09.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Republicaodoedital76.pdf</t>
         </is>
       </c>
       <c r="F204" t="n">
-        <v>1</v>
-      </c>
-      <c r="G204" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Retificação do Edital nº 76/2022 – novo cronograma | https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/SEI_23000.006585_2022_91.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -5890,20 +5906,66 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições Públicas Estaduais e Distrital de Educação Profissional e Tecnológica).</t>
+          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições da Rede Federal de Educação Profissional, Científica e Tecnológica).</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/ResultadoEdital10.pdf</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
+        <v>1</v>
+      </c>
+      <c r="G205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>SETEC</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições Privadas de Ensino Superior que ofertam cursos técnicos e Escolas Técnicas Privadas).</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr"/>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/ResultadoEdital09.pdf</t>
+        </is>
+      </c>
+      <c r="F206" t="n">
+        <v>1</v>
+      </c>
+      <c r="G206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>SETEC</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições Públicas Estaduais e Distrital de Educação Profissional e Tecnológica).</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr"/>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr">
+        <is>
           <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/2147-resultado-preliminar.pdf</t>
         </is>
       </c>
-      <c r="F205" t="n">
-        <v>1</v>
-      </c>
-      <c r="G205" t="inlineStr"/>
+      <c r="F207" t="n">
+        <v>1</v>
+      </c>
+      <c r="G207" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/editais.xlsx
+++ b/editais.xlsx
@@ -4131,11 +4131,11 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alteração Edital nº 23/2026 - Programa de Desenvolvimento Acadêmico Indígena (PDAI), formato, pdf, 102kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2872644_edital_conjunto_23_2026___alteracao.pdf/@@display-file/file</t>
+          <t>Alteração Edital nº 23/2026 - Programa de Desenvolvimento Acadêmico Indígena (PDAI), formato, pdf, 102kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2872644_edital_conjunto_23_2026___alteracao.pdf/@@display-file/file ; Relação dos Programas de Pós-Graduação (PPGs) - Edital nº 23/2026 - Programa de Desenvolvimento Acadêmico Indígena (PDAI), formato, pdf, 1.836kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/resultado_2881142_pdai_divulgacao_ppgs_bolsas_v-final_13-08-2026.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>

--- a/editais.xlsx
+++ b/editais.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G207"/>
+  <dimension ref="A1:G208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4817,14 +4817,14 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Chamada Pública com o objetivo de identificar, avaliar, cadastrar e disponibilizar metodologias, ferramentas e estudos sobre o mapeamento de demandas por Educação Profissional Técnica de Nível Médio, visando aprimorar a definição de ofertas de Educação Profissional Técnica de Nível Médio, no âmbito do Programa Juros por Educação.</t>
+          <t>Chamada (documento Nº 6991254) para seleção de unidades da Rede Federal de Educação Profissional e Tecnológica e das redes públicas estaduais de Educação Profissional e Tecnológica, interessadas em receber apoio técnico para a implementação de programas de aprendizagem profissional articulados a cursos técnicos ou de qualificação profissional com componentes curriculares relacionados à sustentabilidade.</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/SEI_6268868_Resultado_de_Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2026/SEI_6991254_chamada.pdf</t>
         </is>
       </c>
       <c r="F158" t="n">
@@ -4840,14 +4840,14 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Chamada Pública de Adesão das Instituições da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT), com objetivo de capacitação técnica para submissão de propostas em futuros editais de unidades Embrapii.</t>
+          <t>Chamada Pública com o objetivo de identificar, avaliar, cadastrar e disponibilizar metodologias, ferramentas e estudos sobre o mapeamento de demandas por Educação Profissional Técnica de Nível Médio, visando aprimorar a definição de ofertas de Educação Profissional Técnica de Nível Médio, no âmbito do Programa Juros por Educação.</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/edital-2025/SEI_MEC5650163ResultadodeEdital_.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/SEI_6268868_Resultado_de_Edital.pdf</t>
         </is>
       </c>
       <c r="F159" t="n">
@@ -4863,14 +4863,14 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Chamada Pública de Adesão à linha de fomento Qualifica Mais EnergIFE</t>
+          <t>Chamada Pública de Adesão das Instituições da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT), com objetivo de capacitação técnica para submissão de propostas em futuros editais de unidades Embrapii.</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/chamadapublica.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/edital-2025/SEI_MEC5650163ResultadodeEdital_.pdf</t>
         </is>
       </c>
       <c r="F160" t="n">
@@ -4886,14 +4886,14 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 01/2017 - Trata-se de chamada pública para seleção de servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) para capacitação em Gestão da Inovação.</t>
+          <t>Chamada Pública de Adesão à linha de fomento Qualifica Mais EnergIFE</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/extrato_chamada_dou_cp_01_2017.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/chamadapublica.pdf</t>
         </is>
       </c>
       <c r="F161" t="n">
@@ -4909,14 +4909,14 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 01/2018 - Trata-se da chamada pública para seleção de propostas e servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) em efetivo exercício, para participarem da capacitação em Gestão da Inovação (GI - CSIRO).</t>
+          <t>Chamada Pública nº 01/2017 - Trata-se de chamada pública para seleção de servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) para capacitação em Gestão da Inovação.</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/20181030Edital012018ChamadaPblicaGICSIRO.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/extrato_chamada_dou_cp_01_2017.pdf</t>
         </is>
       </c>
       <c r="F162" t="n">
@@ -4932,14 +4932,14 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 02/2017 - Trata-se de chamada pública para concurso sobre educação profissional da Secretaria de Educação Profissional e Tecnológica (Setec/MEC) em parceria com a Comunidade dos Países de Língua Portuguesa (CPLP).</t>
+          <t>Chamada Pública nº 01/2018 - Trata-se da chamada pública para seleção de propostas e servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) em efetivo exercício, para participarem da capacitação em Gestão da Inovação (GI - CSIRO).</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/edital_concurso_cplp_2017.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/20181030Edital012018ChamadaPblicaGICSIRO.pdf</t>
         </is>
       </c>
       <c r="F163" t="n">
@@ -4955,14 +4955,14 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 02/2018 - Trata-se da chamada pública para seleção de servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) para a capacitação Brasileiros Formando Formadores (BraFF).</t>
+          <t>Chamada Pública nº 02/2017 - Trata-se de chamada pública para concurso sobre educação profissional da Secretaria de Educação Profissional e Tecnológica (Setec/MEC) em parceria com a Comunidade dos Países de Língua Portuguesa (CPLP).</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/Edital_02_2018_BRAFF.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/edital_concurso_cplp_2017.pdf</t>
         </is>
       </c>
       <c r="F164" t="n">
@@ -4978,14 +4978,14 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 38/2018 - Trata do processo de seleção de propostas para credenciamento de instituições da Rede Federal, Faculdades de Tecnologia do Estado de São Paulo (Fatecs) e do Instituto Tecnológico de Aeronáutica (ITA) para atuação como Núcleo de Línguas (NucLi-IsF) no âmbito do Programa Idiomas sem Fronteiras (IsF).</t>
+          <t>Chamada Pública nº 02/2018 - Trata-se da chamada pública para seleção de servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) para a capacitação Brasileiros Formando Formadores (BraFF).</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/Editaln382018ChamadaPblicaparacredenciamentodeinstituiesdaRFEPCTdasFatecsedoITA.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/Edital_02_2018_BRAFF.pdf</t>
         </is>
       </c>
       <c r="F165" t="n">
@@ -5001,14 +5001,14 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 79/2016 - Trata-se de chamada pública para apresentação de propostas por instituição de educação profissional e tecnológica para a oferta de cursos de formação inicial e continuada ou de qualificação profissional e cursos técnicos de nível médio, presenciais ou à distância, sem transferência de recursos, no âmbito do PRONATEC, denominada “PROPOSTAS VOLUNTÁRIAS - PRONATEC”</t>
+          <t>Chamada Pública nº 38/2018 - Trata do processo de seleção de propostas para credenciamento de instituições da Rede Federal, Faculdades de Tecnologia do Estado de São Paulo (Fatecs) e do Instituto Tecnológico de Aeronáutica (ITA) para atuação como Núcleo de Línguas (NucLi-IsF) no âmbito do Programa Idiomas sem Fronteiras (IsF).</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/extrato_edital_79_2016_setec.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/Editaln382018ChamadaPblicaparacredenciamentodeinstituiesdaRFEPCTdasFatecsedoITA.pdf</t>
         </is>
       </c>
       <c r="F166" t="n">
@@ -5024,14 +5024,14 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Chamada Pública que estabelece os procedimentos para a autorização de oferta de cursos técnicos de nível médio por Instituições Privadas de Ensino Superior (IPES) para fins de habilitação ao Programa Juros por Educação, no âmbito do Programa de Pleno Pagamento de Dívidas dos Estados (Propag).</t>
+          <t>Chamada Pública nº 79/2016 - Trata-se de chamada pública para apresentação de propostas por instituição de educação profissional e tecnológica para a oferta de cursos de formação inicial e continuada ou de qualificação profissional e cursos técnicos de nível médio, presenciais ou à distância, sem transferência de recursos, no âmbito do PRONATEC, denominada “PROPOSTAS VOLUNTÁRIAS - PRONATEC”</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/FAQEdital6.2025.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/extrato_edital_79_2016_setec.pdf</t>
         </is>
       </c>
       <c r="F167" t="n">
@@ -5047,14 +5047,14 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Chamamento Público para credenciamento de profissionais no Banco de Especialistas para atuar no Projeto Assistec Inova, junto ao Ministério da Educação, no âmbito da Secretaria de Educação Profissional e Tecnológica.</t>
+          <t>Chamada Pública que estabelece os procedimentos para a autorização de oferta de cursos técnicos de nível médio por Instituições Privadas de Ensino Superior (IPES) para fins de habilitação ao Programa Juros por Educação, no âmbito do Programa de Pleno Pagamento de Dívidas dos Estados (Propag).</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/SEI_23000.035944_2024_89.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/FAQEdital6.2025.pdf</t>
         </is>
       </c>
       <c r="F168" t="n">
@@ -5070,14 +5070,14 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Edital 1/2026 - Chamada Pública de Adesão dos Institutos Federais de Educação, Ciência e Tecnologia, do Centro Federal de Educação Tecnológica Celso Suckow da Fonseca, do Centro Federal de Educação Tecnológica de Minas Gerais e do Colégio Pedro II, com objetivo de capacitação técnica para submissão de propostas em futuros editais de Unidades Embrapii.</t>
+          <t>Chamamento Público para credenciamento de profissionais no Banco de Especialistas para atuar no Projeto Assistec Inova, junto ao Ministério da Educação, no âmbito da Secretaria de Educação Profissional e Tecnológica.</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/edital12026.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/SEI_23000.035944_2024_89.pdf</t>
         </is>
       </c>
       <c r="F169" t="n">
@@ -5093,14 +5093,14 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Edital 84/2021 - Seleção de Projetos para desenvolvimento dos Ambientes de Promotores de Inovação na Rede Federal</t>
+          <t>Edital 1/2026 - Chamada Pública de Adesão dos Institutos Federais de Educação, Ciência e Tecnologia, do Centro Federal de Educação Tecnológica Celso Suckow da Fonseca, do Centro Federal de Educação Tecnológica de Minas Gerais e do Colégio Pedro II, com objetivo de capacitação técnica para submissão de propostas em futuros editais de Unidades Embrapii.</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/editais/2022/ResultadoetapaI.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/edital12026.pdf</t>
         </is>
       </c>
       <c r="F170" t="n">
@@ -5116,14 +5116,14 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Edital nº 01/2017 - APRESENTAÇÃO DE PROPOSTAS PARA A OFERTA DE VAGAS GRATUITAS EM CURSOS TÉCNICOS NA FORMA CONCOMITANTE, NO ÂMBITO DO PRONATEC/MEDIOTEC – 2º/2017 - A Secretária de Educação Profissional e Tecnológica do Ministério da Educação, no uso da atribuição que lhe confere o art. 13, Anexo I, do Decreto n° 7.690, de 02 de março de 2012, e considerando o disposto na Lei nº 12.513, de 26 de outubro de 2011, a Portaria nº 817, de 13 de agosto de 2015, a Portaria nº160, de 05 de março de 2013, alterada pela Portaria nº 701, de 13 de agosto de 2014, TORNA PÚBLICO os procedimentos e o cronograma para a apresentação de propostas visando a oferta de vagas gratuitas em cursos técnicos na forma concomitante e na modalidade presencial, no âmbito do Programa Nacional de Acesso ao Ensino Técnico e Emprego - PRONATEC, por meio da ação MEDIOTEC, para ingresso no segundo semestre de 2017.</t>
+          <t>Edital 84/2021 - Seleção de Projetos para desenvolvimento dos Ambientes de Promotores de Inovação na Rede Federal</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/edital_01_mediotec_2017.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/editais/2022/ResultadoetapaI.pdf</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -5139,14 +5139,14 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Edital nº 08/2024 - Chamamento Público visando à seleção de autores(as) para elaboração de capítulos de obra a ser publicada cuja temática central é a gestão de Núcleos de Inovação Tecnológica (NITs) e/ou de Agências de Inovação da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) Divulgação das Inscrições Homologadas</t>
+          <t>Edital nº 01/2017 - APRESENTAÇÃO DE PROPOSTAS PARA A OFERTA DE VAGAS GRATUITAS EM CURSOS TÉCNICOS NA FORMA CONCOMITANTE, NO ÂMBITO DO PRONATEC/MEDIOTEC – 2º/2017 - A Secretária de Educação Profissional e Tecnológica do Ministério da Educação, no uso da atribuição que lhe confere o art. 13, Anexo I, do Decreto n° 7.690, de 02 de março de 2012, e considerando o disposto na Lei nº 12.513, de 26 de outubro de 2011, a Portaria nº 817, de 13 de agosto de 2015, a Portaria nº160, de 05 de março de 2013, alterada pela Portaria nº 701, de 13 de agosto de 2014, TORNA PÚBLICO os procedimentos e o cronograma para a apresentação de propostas visando a oferta de vagas gratuitas em cursos técnicos na forma concomitante e na modalidade presencial, no âmbito do Programa Nacional de Acesso ao Ensino Técnico e Emprego - PRONATEC, por meio da ação MEDIOTEC, para ingresso no segundo semestre de 2017.</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/436.SEI_MEC5030251Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/edital_01_mediotec_2017.pdf</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -5162,14 +5162,14 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Edital nº 1/2023 - Seleção de proposta de selo comemorativo, em alusão aos 15 anos dos Institutos Federais.</t>
+          <t>Edital nº 08/2024 - Chamamento Público visando à seleção de autores(as) para elaboração de capítulos de obra a ser publicada cuja temática central é a gestão de Núcleos de Inovação Tecnológica (NITs) e/ou de Agências de Inovação da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) Divulgação das Inscrições Homologadas</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC4094376Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/436.SEI_MEC5030251Edital.pdf</t>
         </is>
       </c>
       <c r="F173" t="n">
@@ -5185,14 +5185,14 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Edital nº 100/2022 - Chamamento Público para a seleção de propostas para o Desafio Soutec</t>
+          <t>Edital nº 1/2023 - Seleção de proposta de selo comemorativo, em alusão aos 15 anos dos Institutos Federais.</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/secretarias/secretaria-de-educacao-profissional/editais-2022/SEI_MEC3570188Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC4094376Edital.pdf</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -5208,14 +5208,14 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Edital nº 109/2022 - Chamamento Público - Seleção de projetos voltados à promoção do empreendedorismo inovador, com foco na Economia 4.0, associados ao ensino, à pesquisa e à extensão, destinado às instituições integrantes da Rede Federal de Educação Profissional, Científica e Tecnológica</t>
+          <t>Edital nº 100/2022 - Chamamento Público para a seleção de propostas para o Desafio Soutec</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital109.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/secretarias/secretaria-de-educacao-profissional/editais-2022/SEI_MEC3570188Edital.pdf</t>
         </is>
       </c>
       <c r="F175" t="n">
@@ -5231,14 +5231,14 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Edital nº 11/2024 - Chamamento Público para a seleção de projetos aptos a integrarem a 4ª Semana Nacional de Educação Profissional e Tecnológica Retificação do</t>
+          <t>Edital nº 109/2022 - Chamamento Público - Seleção de projetos voltados à promoção do empreendedorismo inovador, com foco na Economia 4.0, associados ao ensino, à pesquisa e à extensão, destinado às instituições integrantes da Rede Federal de Educação Profissional, Científica e Tecnológica</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-2024-1/Edital_11.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital109.pdf</t>
         </is>
       </c>
       <c r="F176" t="n">
@@ -5254,14 +5254,14 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Edital nº 15/2023 - Chamada Pública para o Workshop para elaboração de Itinerários Formativos em economia circular na Educação Profissional e Tecnológica</t>
+          <t>Edital nº 11/2024 - Chamamento Público para a seleção de projetos aptos a integrarem a 4ª Semana Nacional de Educação Profissional e Tecnológica Retificação do</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/SEI_MEC3884064Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-2024-1/Edital_11.pdf</t>
         </is>
       </c>
       <c r="F177" t="n">
@@ -5277,14 +5277,14 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Edital nº 2/2020 - IFES, de chamada pública para a seleção de projetos voltados à implementação das Oficinas 4.0, aberto às autarquias da Rede Federal.</t>
+          <t>Edital nº 15/2023 - Chamada Pública para o Workshop para elaboração de Itinerários Formativos em economia circular na Educação Profissional e Tecnológica</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
-          <t>https://www.ifes.edu.br/chamadas-publicas/19329-chamada-publica-2-2020-apoio-a-implementacao-de-oficinas-4-0</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/SEI_MEC3884064Edital.pdf</t>
         </is>
       </c>
       <c r="F178" t="n">
@@ -5300,14 +5300,14 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Edital nº 20/2021 – Seleção de servidores para atuação em Projetos de Colaboração Técnica junto ao Ministério da Educação.</t>
+          <t>Edital nº 2/2020 - IFES, de chamada pública para a seleção de projetos voltados à implementação das Oficinas 4.0, aberto às autarquias da Rede Federal.</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/SEI_MEC2573324Edital.pdf</t>
+          <t>https://www.ifes.edu.br/chamadas-publicas/19329-chamada-publica-2-2020-apoio-a-implementacao-de-oficinas-4-0</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -5323,14 +5323,14 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Edital nº 25/2023 - Chamada Pública destinada a selecionar equipes da Rede Federal de Educação Profissional, Científica e Tecnológica (EPCT) para participação no projeto de formação em criatividade, inovação e prototipagem do mercosul (Hackathon Mercosul). Retificação do Edital</t>
+          <t>Edital nº 20/2021 – Seleção de servidores para atuação em Projetos de Colaboração Técnica junto ao Ministério da Educação.</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/SEI_MEC3913111Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/SEI_MEC2573324Edital.pdf</t>
         </is>
       </c>
       <c r="F180" t="n">
@@ -5346,14 +5346,14 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Edital nº 26 versão consolidada</t>
+          <t>Edital nº 25/2023 - Chamada Pública destinada a selecionar equipes da Rede Federal de Educação Profissional, Científica e Tecnológica (EPCT) para participação no projeto de formação em criatividade, inovação e prototipagem do mercosul (Hackathon Mercosul). Retificação do Edital</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC3980995Documento.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/SEI_MEC3913111Edital.pdf</t>
         </is>
       </c>
       <c r="F181" t="n">
@@ -5369,14 +5369,14 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Edital nº 3/2021 – Chamada Pública para seleção de projetos de iniciação tecnológica com foco na Economia 4.0. Acesse o edital .</t>
+          <t>Edital nº 26 versão consolidada</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
-          <t>https://www.ifes.edu.br/chamadas-publicas/19351-chamada-publica-3-2020-projetos-iniciacao-tecnologica-economia-4-0</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC3980995Documento.pdf</t>
         </is>
       </c>
       <c r="F182" t="n">
@@ -5392,24 +5392,20 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Edital nº 35/2020 - Chamada Pública - que tem como objetivo selecionar projetos voltados à criação de Laboratórios IFMaker junto aos Institutos Federais de Educação, Ciência e Tecnologia; Centros Federais de Educação Tecnológica Celso Suckow da Fonseca – Cefet-RJ e de Minas Gerais – Cefet-MG e o Colégio Pedro II, conforme especificado no Despacho SEI nº 2064854</t>
+          <t>Edital nº 3/2021 – Chamada Pública para seleção de projetos de iniciação tecnológica com foco na Economia 4.0. Acesse o edital .</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2020/SEI_MEC_2064339_Edital_Chamada_Publica.pdf</t>
+          <t>https://www.ifes.edu.br/chamadas-publicas/19351-chamada-publica-3-2020-projetos-iniciacao-tecnologica-economia-4-0</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>2</v>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>Retificação Edital nº 35/2020 - Chamada Pública - Seleção de projetos voltados à criação de Laboratórios Maker junto à Rede Federal de Educação Profissional, Científica e Tecnológica Retificação de Cronograma ​do | https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/AlteraodecronogramaRedeMakeredital35.pdf</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -5419,20 +5415,24 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Edital nº 46, de 20 de julho de 2020, que torna público edital para adesão de estados e Distrito Federal à oferta de Curso de Especialização Lato Sensu em Docência para a Educação Profissional e Tecnológica (DocentEPT) aos professores da rede pública estadual e distrital que atuam na oferta de cursos de Educação Profissional e Tecnológica</t>
+          <t>Edital nº 35/2020 - Chamada Pública - que tem como objetivo selecionar projetos voltados à criação de Laboratórios IFMaker junto aos Institutos Federais de Educação, Ciência e Tecnologia; Centros Federais de Educação Tecnológica Celso Suckow da Fonseca – Cefet-RJ e de Minas Gerais – Cefet-MG e o Colégio Pedro II, conforme especificado no Despacho SEI nº 2064854</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2020/Editaldeadeso_DOU.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2020/SEI_MEC_2064339_Edital_Chamada_Publica.pdf</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>1</v>
-      </c>
-      <c r="G184" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Retificação Edital nº 35/2020 - Chamada Pública - Seleção de projetos voltados à criação de Laboratórios Maker junto à Rede Federal de Educação Profissional, Científica e Tecnológica Retificação de Cronograma ​do | https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/AlteraodecronogramaRedeMakeredital35.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -5442,14 +5442,14 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Edital nº 47/2022 - Chamada Pública para oferta de cursos da Plataforma Aprenda Mais</t>
+          <t>Edital nº 46, de 20 de julho de 2020, que torna público edital para adesão de estados e Distrito Federal à oferta de Curso de Especialização Lato Sensu em Docência para a Educação Profissional e Tecnológica (DocentEPT) aos professores da rede pública estadual e distrital que atuam na oferta de cursos de Educação Profissional e Tecnológica</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/editais/2022/Editaln47.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2020/Editaldeadeso_DOU.pdf</t>
         </is>
       </c>
       <c r="F185" t="n">
@@ -5465,14 +5465,14 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Edital nº 48/2022 - Procedimentos para autorização da oferta de cursos técnicos de nível médio por Instituições Privadas de Ensino Superior – Anexos do</t>
+          <t>Edital nº 47/2022 - Chamada Pública para oferta de cursos da Plataforma Aprenda Mais</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/editais/2022/Editaln48.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/editais/2022/Editaln47.pdf</t>
         </is>
       </c>
       <c r="F186" t="n">
@@ -5488,14 +5488,14 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Edital nº 5 /2026 - Seleção de propostas de projetos de extensão voltados ao Acesso, à Permanência e ao Êxito no âmbito da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT).</t>
+          <t>Edital nº 48/2022 - Procedimentos para autorização da oferta de cursos técnicos de nível médio por Instituições Privadas de Ensino Superior – Anexos do</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2026/sei_7012727_edital_5.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/editais/2022/Editaln48.pdf</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -5511,14 +5511,14 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Edital nº 5/2020 – Chamada para seleção de projetos de apoio ao empreendedorismo inovador com foco na Economia 4.0. Acesse o edital .</t>
+          <t>Edital nº 5 /2026 - Seleção de propostas de projetos de extensão voltados ao Acesso, à Permanência e ao Êxito no âmbito da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT).</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
-          <t>https://www.ifes.edu.br/chamadas-publicas/19384-chamada-publica-05-2020-selecao-de-projetos-de-apoio-ao-empreendedorismo-inovador-com-foco-na-economia-4-0</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2026/sei_7012727_edital_5.pdf</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -5534,14 +5534,14 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Edital nº 5/2021 – IF Mais Empreendedor Nacional : Adesão ao Programa IF Mais Empreendedor Nacional</t>
+          <t>Edital nº 5/2020 – Chamada para seleção de projetos de apoio ao empreendedorismo inovador com foco na Economia 4.0. Acesse o edital .</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/editais/2021/Edital05.2021IFEMPREENDEDORNACIONAL.pdf</t>
+          <t>https://www.ifes.edu.br/chamadas-publicas/19384-chamada-publica-05-2020-selecao-de-projetos-de-apoio-ao-empreendedorismo-inovador-com-foco-na-economia-4-0</t>
         </is>
       </c>
       <c r="F189" t="n">
@@ -5557,14 +5557,14 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Edital nº 5/2024 - Seleção de propostas de novos Cursos Abertos, On-line e Massivos (MOOCs), desenvolvidos pela Rede Federa de Educação Profissional, Científica e Tecnológica, a serem disponibilizados na Plataforma APRENDA MAIS.</t>
+          <t>Edital nº 5/2021 – IF Mais Empreendedor Nacional : Adesão ao Programa IF Mais Empreendedor Nacional</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC4659481Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/editais/2021/Edital05.2021IFEMPREENDEDORNACIONAL.pdf</t>
         </is>
       </c>
       <c r="F190" t="n">
@@ -5580,14 +5580,14 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Edital nº 52/2016 – que torna público, para conhecimento dos interessados, que será realizado na modalidade concurso, o PROJETO DESAFIO DA EDUCAÇÃO PROFISSIONAL E TECNOLÓGICA, na forma do REGULAMENTO anexo a este edital, com o objetivo de promover uma campanha nacional para aprimorar a Educação Profissional e Tecnológica estimulando a sociedade a enviar propostas de ações inovadoras e compartilhar experiências exitosas de implementação de ações.</t>
+          <t>Edital nº 5/2024 - Seleção de propostas de novos Cursos Abertos, On-line e Massivos (MOOCs), desenvolvidos pela Rede Federa de Educação Profissional, Científica e Tecnológica, a serem disponibilizados na Plataforma APRENDA MAIS.</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/edital_n_52_2016.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC4659481Edital.pdf</t>
         </is>
       </c>
       <c r="F191" t="n">
@@ -5603,14 +5603,14 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Edital nº 55/2016 , que torna público concurso PROJETO DESAFIO EDUCAÇÃO ZIKAZERO, na forma do REGULAMENTO anexo a este edital, com o objetivo de promover uma campanha nacional de mobilização para o enfrentamento ao Aedes aegyp e à microcefalia estimulando a sociedade a enviar propostas de ações inovadoras e compartilhar experiências exitosas de implementação de ações em prol do combate ao mosquito.</t>
+          <t>Edital nº 52/2016 – que torna público, para conhecimento dos interessados, que será realizado na modalidade concurso, o PROJETO DESAFIO DA EDUCAÇÃO PROFISSIONAL E TECNOLÓGICA, na forma do REGULAMENTO anexo a este edital, com o objetivo de promover uma campanha nacional para aprimorar a Educação Profissional e Tecnológica estimulando a sociedade a enviar propostas de ações inovadoras e compartilhar experiências exitosas de implementação de ações.</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/Edital_55_2016_SEI_MEC_0227936.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/edital_n_52_2016.pdf</t>
         </is>
       </c>
       <c r="F192" t="n">
@@ -5626,14 +5626,14 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Edital nº 6/2021 - Edital de Adesão das instituições ao Sistema Re-Saber</t>
+          <t>Edital nº 55/2016 , que torna público concurso PROJETO DESAFIO EDUCAÇÃO ZIKAZERO, na forma do REGULAMENTO anexo a este edital, com o objetivo de promover uma campanha nacional de mobilização para o enfrentamento ao Aedes aegyp e à microcefalia estimulando a sociedade a enviar propostas de ações inovadoras e compartilhar experiências exitosas de implementação de ações em prol do combate ao mosquito.</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/Edital_06_2021.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/Edital_55_2016_SEI_MEC_0227936.pdf</t>
         </is>
       </c>
       <c r="F193" t="n">
@@ -5649,14 +5649,14 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Edital nº 6/2024 - Edital visa selecionar a proposta de selo/logomarca que será utilizado em confecções comemorativas no contexto dos 115 anos da Rede Federal de Educação Profissional, Científica e Tecnológica, que poderá ser personalizado como selo postal, via Correios. *</t>
+          <t>Edital nº 6/2021 - Edital de Adesão das instituições ao Sistema Re-Saber</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-2024/325.SEI_MEC4985249Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/Edital_06_2021.pdf</t>
         </is>
       </c>
       <c r="F194" t="n">
@@ -5672,14 +5672,14 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Edital nº 61/2019 – Regulamento do Cadastro de Especialistas para compor o Banco de Avaliadores da Secretaria de Educação Profissional e Tecnológica.</t>
+          <t>Edital nº 6/2024 - Edital visa selecionar a proposta de selo/logomarca que será utilizado em confecções comemorativas no contexto dos 115 anos da Rede Federal de Educação Profissional, Científica e Tecnológica, que poderá ser personalizado como selo postal, via Correios. *</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2019/EDITALN612019.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-2024/325.SEI_MEC4985249Edital.pdf</t>
         </is>
       </c>
       <c r="F195" t="n">
@@ -5695,14 +5695,14 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Edital nº 63/2021- Seleção de Projetos de Promoção às Indicações Geográficas</t>
+          <t>Edital nº 61/2019 – Regulamento do Cadastro de Especialistas para compor o Banco de Avaliadores da Secretaria de Educação Profissional e Tecnológica.</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/editais/2021/Edital63.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2019/EDITALN612019.pdf</t>
         </is>
       </c>
       <c r="F196" t="n">
@@ -5718,14 +5718,14 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Edital nº 67/2021 - Chamada Pública de Projetos para apoio à implementação das Oficinas 4.0</t>
+          <t>Edital nº 63/2021- Seleção de Projetos de Promoção às Indicações Geográficas</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/SEI_MEC2898796Edital67.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/editais/2021/Edital63.pdf</t>
         </is>
       </c>
       <c r="F197" t="n">
@@ -5741,14 +5741,14 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Edital nº 68/2019 – Seleção de servidores para atuação em Projetos Educacionais de Colaboração Técnica junto ao Ministério da Educação.</t>
+          <t>Edital nº 67/2021 - Chamada Pública de Projetos para apoio à implementação das Oficinas 4.0</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2019/EDITALN682019.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/SEI_MEC2898796Edital67.pdf</t>
         </is>
       </c>
       <c r="F198" t="n">
@@ -5764,14 +5764,14 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Edital nº 83/2022 – Seleção de propostas de instituições da Rede Federal para a implementação de programa de capacitação de estudantes denominado Oficinas 4.0</t>
+          <t>Edital nº 68/2019 – Seleção de servidores para atuação em Projetos Educacionais de Colaboração Técnica junto ao Ministério da Educação.</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital83.2022.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2019/EDITALN682019.pdf</t>
         </is>
       </c>
       <c r="F199" t="n">
@@ -5787,14 +5787,14 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Edital nº 88/2022 – Seleção de projetos de iniciação tecnológica de instituições da RFEPCT para o desenvolvimento de ações de formação em programação e/ou robótica e/ou cultura maker para estudantes dos anos finais do ensino fundamental (6º ao 9º ano) das redes públicas de ensino. Retificação ​do</t>
+          <t>Edital nº 83/2022 – Seleção de propostas de instituições da Rede Federal para a implementação de programa de capacitação de estudantes denominado Oficinas 4.0</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital88.2022.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital83.2022.pdf</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -5810,14 +5810,14 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Edital nº 94/2022 – Chamada Pública para a capacitação de multiplicadores em bioeconomia para a Amazônia Legal. Chamada Pública para a Adesão de parceiros ofertantes da Rede Federal de Educação Profissional, Científica e Tecnológica – RFEPCT à linha de fomento Qualifica Mais EnergIFE, voltada à promoção da oferta de cursos na área das Energias Renováveis. Retificação do</t>
+          <t>Edital nº 88/2022 – Seleção de projetos de iniciação tecnológica de instituições da RFEPCT para o desenvolvimento de ações de formação em programação e/ou robótica e/ou cultura maker para estudantes dos anos finais do ensino fundamental (6º ao 9º ano) das redes públicas de ensino. Retificação ​do</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Editaln94.2022.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital88.2022.pdf</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -5833,14 +5833,14 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Edital nº 99/2022 - Chamamento Público para a seleção de projetos de inovação e trabalhos acadêmicos aptos a integrarem a Semana Nacional da Educação Profissional e Tecnológica Retificação do</t>
+          <t>Edital nº 94/2022 – Chamada Pública para a capacitação de multiplicadores em bioeconomia para a Amazônia Legal. Chamada Pública para a Adesão de parceiros ofertantes da Rede Federal de Educação Profissional, Científica e Tecnológica – RFEPCT à linha de fomento Qualifica Mais EnergIFE, voltada à promoção da oferta de cursos na área das Energias Renováveis. Retificação do</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/secretarias/secretaria-de-educacao-profissional/SEI_MEC3566713Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Editaln94.2022.pdf</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -5856,14 +5856,14 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Programa Setec-Capes/NOVA de capacitação para Professores da Rede Federal de Educação Profissional, Científica e Tecnológica . A Secretaria de Educação Profissional e Tecnológica (Setec) do Ministério da Educação, com apoio da Coordenação de Aperfeiçoamento de Pessoal de Nível Superior (Capes), lançam chamada pública de capacitação para professores de inglês em efetivo exercício na Rede Federal de Educação Profissional - Institutos Federais, Cefets, Escolas Técnicas vinculas às Universidades Federais e Colégio Pedro II. (Retificação publicada no Diário Oficial da União em 02 de junho de 2016)</t>
+          <t>Edital nº 99/2022 - Chamamento Público para a seleção de projetos de inovação e trabalhos acadêmicos aptos a integrarem a Semana Nacional da Educação Profissional e Tecnológica Retificação do</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2015/chamada_setec_capes_nova_extrato_dou.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/secretarias/secretaria-de-educacao-profissional/SEI_MEC3566713Edital.pdf</t>
         </is>
       </c>
       <c r="F203" t="n">
@@ -5879,24 +5879,20 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Republicação do Edital nº 76/2022 - Chamamento Público para seleção de projetos voltados ao fortalecimento de Núcleos de Inovação Tecnológica e/ou Agências de Inovação.</t>
+          <t>Programa Setec-Capes/NOVA de capacitação para Professores da Rede Federal de Educação Profissional, Científica e Tecnológica . A Secretaria de Educação Profissional e Tecnológica (Setec) do Ministério da Educação, com apoio da Coordenação de Aperfeiçoamento de Pessoal de Nível Superior (Capes), lançam chamada pública de capacitação para professores de inglês em efetivo exercício na Rede Federal de Educação Profissional - Institutos Federais, Cefets, Escolas Técnicas vinculas às Universidades Federais e Colégio Pedro II. (Retificação publicada no Diário Oficial da União em 02 de junho de 2016)</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Republicaodoedital76.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2015/chamada_setec_capes_nova_extrato_dou.pdf</t>
         </is>
       </c>
       <c r="F204" t="n">
-        <v>2</v>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>Retificação do Edital nº 76/2022 – novo cronograma | https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/SEI_23000.006585_2022_91.pdf</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -5906,20 +5902,24 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições da Rede Federal de Educação Profissional, Científica e Tecnológica).</t>
+          <t>Republicação do Edital nº 76/2022 - Chamamento Público para seleção de projetos voltados ao fortalecimento de Núcleos de Inovação Tecnológica e/ou Agências de Inovação.</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/ResultadoEdital10.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Republicaodoedital76.pdf</t>
         </is>
       </c>
       <c r="F205" t="n">
-        <v>1</v>
-      </c>
-      <c r="G205" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Retificação do Edital nº 76/2022 – novo cronograma | https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/SEI_23000.006585_2022_91.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -5929,14 +5929,14 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições Privadas de Ensino Superior que ofertam cursos técnicos e Escolas Técnicas Privadas).</t>
+          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições da Rede Federal de Educação Profissional, Científica e Tecnológica).</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/ResultadoEdital09.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/ResultadoEdital10.pdf</t>
         </is>
       </c>
       <c r="F206" t="n">
@@ -5952,20 +5952,43 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições Públicas Estaduais e Distrital de Educação Profissional e Tecnológica).</t>
+          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições Privadas de Ensino Superior que ofertam cursos técnicos e Escolas Técnicas Privadas).</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr">
         <is>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/ResultadoEdital09.pdf</t>
+        </is>
+      </c>
+      <c r="F207" t="n">
+        <v>1</v>
+      </c>
+      <c r="G207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>SETEC</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições Públicas Estaduais e Distrital de Educação Profissional e Tecnológica).</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr"/>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr">
+        <is>
           <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/2147-resultado-preliminar.pdf</t>
         </is>
       </c>
-      <c r="F207" t="n">
-        <v>1</v>
-      </c>
-      <c r="G207" t="inlineStr"/>
+      <c r="F208" t="n">
+        <v>1</v>
+      </c>
+      <c r="G208" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/editais.xlsx
+++ b/editais.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G208"/>
+  <dimension ref="A1:G214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4251,24 +4251,20 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Edital nº 26/2024 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE) - Retificação - formato, pdf, 48kb</t>
+          <t>Edital nº 25/2026 - Edição 2027, formato, pdf, 145kb</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/14102024_Edital_2477735_SEI_2477608_Edital_N__26_2024.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2886643_sei_2886062_edital_n___25_2026.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>3</v>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>Alteração do Edital nº 26/2024 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE), formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/13032025_Edital_2560841_SEI_2559847_Edital_26_2024___ALTERACAO.pdf/@@display-file/file ; Edital nº 26/2024 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 135kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/08102024_Edital_2474014_SEI_2472849_Edital_26_2024.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4278,22 +4274,22 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Edital nº 27/2024 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 157kb</t>
+          <t>Edital nº 26/2024 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE) - Retificação - formato, pdf, 48kb</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/05112024_Edital_2490387_SEI_2489251_Edital_27_2024.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/14102024_Edital_2477735_SEI_2477608_Edital_N__26_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alteração do Edital 27/2024 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa no EUA - PDPI - formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/02122024_Edital_2505290_SEI_2504109_Edital_27_2024__.pdf/@@display-file/file</t>
+          <t>Alteração do Edital nº 26/2024 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE), formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/13032025_Edital_2560841_SEI_2559847_Edital_26_2024___ALTERACAO.pdf/@@display-file/file ; Edital nº 26/2024 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 135kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/08102024_Edital_2474014_SEI_2472849_Edital_26_2024.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4305,22 +4301,22 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Edital nº 30/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 110kb</t>
+          <t>Edital nº 27/2024 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 157kb</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/14022020_Edital_1145537_Edital_SITE.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/05112024_Edital_2490387_SEI_2489251_Edital_27_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Reabertura e alteração do Edital nº 30/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 222kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/28042022_Edital_1691552_SEI_CAPES___1685746___Edital_30_2019.pdf/@@display-file/file ; Suspensão do Edital nº 30/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 111kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_1326070_Edital_Suspensao_site.pdf/@@display-file/file</t>
+          <t>Alteração do Edital 27/2024 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa no EUA - PDPI - formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/02122024_Edital_2505290_SEI_2504109_Edital_27_2024__.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4332,14 +4328,14 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Edital nº 30/2023 - PDSE - formato, pdf, 125kb</t>
+          <t>Edital nº 30/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 110kb</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/06112023_Edital_2263037_SEI_2261948_Edital_30_2023.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/14022020_Edital_1145537_Edital_SITE.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F139" t="n">
@@ -4347,7 +4343,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Prorrogação do Edital nº 30/2023 - PDSE - formato, pdf, 136kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11012024_Edital_2306448_SEI_CAPES___2305414___Edital_30_2023___Prorrogacao.pdf/@@display-file/file ; Alteração do Edital nº 30/2023 - PDSE - formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/18122023_Edital_2293491_SEI_2293429_Edital_30_2023_Alteracao.pdf/@@display-file/file</t>
+          <t>Reabertura e alteração do Edital nº 30/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 222kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/28042022_Edital_1691552_SEI_CAPES___1685746___Edital_30_2019.pdf/@@display-file/file ; Suspensão do Edital nº 30/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 111kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_1326070_Edital_Suspensao_site.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4359,14 +4355,14 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Edital Nº 32/2022 - CAPES/Cofecub, formato, pdf, 225kb</t>
+          <t>Edital nº 30/2023 - PDSE - formato, pdf, 125kb</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29062022_EDITAL32_2022_COFECUB.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/06112023_Edital_2263037_SEI_2261948_Edital_30_2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F140" t="n">
@@ -4374,7 +4370,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alteração do Edital Nº 32/2022 - CAPES/Cofecub, formato, pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400143_SEI_2399437_Edital_32_2022___ALTERACAO_III.pdf/@@display-file/file ; Relação de inscritos do Edital Nº 32/2022 - CAPES/Cofecub, formato, pdf, 65kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/25082022_Lista_Listagem_1783309_EDITAL_32_2022___CAPES_COFECUB_Relacao_de_Inscricoes.pdf/@@display-file/file</t>
+          <t>Prorrogação do Edital nº 30/2023 - PDSE - formato, pdf, 136kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11012024_Edital_2306448_SEI_CAPES___2305414___Edital_30_2023___Prorrogacao.pdf/@@display-file/file ; Alteração do Edital nº 30/2023 - PDSE - formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/18122023_Edital_2293491_SEI_2293429_Edital_30_2023_Alteracao.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4386,22 +4382,22 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Edital nº 32/2023 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 139kb</t>
+          <t>Edital Nº 32/2022 - CAPES/Cofecub, formato, pdf, 225kb</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/16112023_Edital_2271416_SEI_2268914_Edital_32_2023.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29062022_EDITAL32_2022_COFECUB.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alteração do Edital nº 32/2023 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 57kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09022024_SEI_2321458_Edital_N__32_2023___ALTERACAOPDPI.pdf/@@display-file/file</t>
+          <t>Alteração do Edital Nº 32/2022 - CAPES/Cofecub, formato, pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400143_SEI_2399437_Edital_32_2022___ALTERACAO_III.pdf/@@display-file/file ; Relação de inscritos do Edital Nº 32/2022 - CAPES/Cofecub, formato, pdf, 65kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/25082022_Lista_Listagem_1783309_EDITAL_32_2022___CAPES_COFECUB_Relacao_de_Inscricoes.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4413,20 +4409,24 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Edital nº 35/2011 - Certificação em Língua Inglesa - pdf, 615kb</t>
+          <t>Edital nº 32/2023 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 139kb</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_035_CertificacaoEUAprofLingIngl_Fulbright.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/16112023_Edital_2271416_SEI_2268914_Edital_32_2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>1</v>
-      </c>
-      <c r="G142" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Alteração do Edital nº 32/2023 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 57kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09022024_SEI_2321458_Edital_N__32_2023___ALTERACAOPDPI.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4436,14 +4436,14 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Edital nº 4/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 270kb</t>
+          <t>Edital nº 35/2011 - Certificação em Língua Inglesa - pdf, 615kb</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/08022019Edital4.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_035_CertificacaoEUAprofLingIngl_Fulbright.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F143" t="n">
@@ -4459,24 +4459,20 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Edital nº 44/2012 - Programa de Aperfeiçoamento para Professores de Língua Inglesa nos Eua, pdf, 272kb</t>
+          <t>Edital nº 4/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 270kb</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_0442012_ProfLingIngl_EUA.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/08022019Edital4.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>3</v>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>Edital nº 44/2012 - Retificado - pdf, 528kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_0442012_ProfLIngRetif.pdf/@@display-file/file ; Retificação do Edital nº 44/2012 - pdf, 46kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/RetificacaoEdital442012_ProfLingInglEUA_01out12.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4486,22 +4482,22 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Edital nº 44/2022 - PDSE - formato, pdf, 337kb</t>
+          <t>Edital nº 44/2012 - Programa de Aperfeiçoamento para Professores de Língua Inglesa nos Eua, pdf, 272kb</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/22122022_Edital_1882688_Edital_44_2022.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_0442012_ProfLingIngl_EUA.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alteração do Edital nº 44/2022 - PDSE - formato, pdf, 146kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23052023_Edital_1981709_Edital_44_2023.pdf/@@display-file/file</t>
+          <t>Edital nº 44/2012 - Retificado - pdf, 528kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_0442012_ProfLIngRetif.pdf/@@display-file/file ; Retificação do Edital nº 44/2012 - pdf, 46kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/RetificacaoEdital442012_ProfLingInglEUA_01out12.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4513,20 +4509,24 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Edital nº 52/2010 - Certificação em Língua Inglesa, pdf, 60kbDF</t>
+          <t>Edital nº 44/2022 - PDSE - formato, pdf, 337kb</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_52_Certificacao_LinguaInglesa2010.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/22122022_Edital_1882688_Edital_44_2022.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>1</v>
-      </c>
-      <c r="G146" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Alteração do Edital nº 44/2022 - PDSE - formato, pdf, 146kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23052023_Edital_1981709_Edital_44_2023.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4536,24 +4536,20 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Edital Nº09/2026 - Programa CAPES/BRAFITEC, formato, pdf, 209kb</t>
+          <t>Edital nº 52/2010 - Certificação em Língua Inglesa, pdf, 60kbDF</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2800035_SEI_2799041_Edital_9__de_2026.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_52_Certificacao_LinguaInglesa2010.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>2</v>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>Edital n° 9/2026 - Lista de Inscritos, formato, pdf, 398kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/lista_listagem_2864548_sei_2863010_edital_minuta__.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4563,14 +4559,14 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Lista de inscritos do Edital Conjunto nº 01/2024 - Programa Caminhos Amefricanos, formato, pdf, 407kb</t>
+          <t>Edital Nº09/2026 - Programa CAPES/BRAFITEC, formato, pdf, 209kb</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15052024_Lista_Listagem_2374115_Inscritos_MIR.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2800035_SEI_2799041_Edital_9__de_2026.pdf</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4578,7 +4574,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alteração do Edital Conjunto nº 01/2024 - Programa Caminhos Amefricanos, formato, pdf, 63kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29042024_Edital_2368101_SEI_2365347_Edital_Conjunto_n__1_CAPES_MIR.pdf/@@display-file/file</t>
+          <t>Edital n° 9/2026 - Lista de Inscritos, formato, pdf, 398kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/lista_listagem_2864548_sei_2863010_edital_minuta__.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4590,20 +4586,24 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Lista de inscritos do Edital nº 05/2024 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 46kb</t>
+          <t>Edital PAEP nº 06/2022 - formato, pdf, 331kb</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/10062024_Lista_Listagem_2390159_Lista_de_Inscritos_3.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/02022022_Edital_1626836_SEI_CAPES___1626182___Edita_6.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
-      </c>
-      <c r="G149" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Alteração do Edital PAEP nº 06/2022 - formato, pdf, 80kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15062022_Edital_1733665_Edital_6_2022.pdf/@@display-file/file ; Reabertura do Edital PAEP nº 06/2022 - formato, pdf, 112kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/24032022_Edital_1661092_Edital_6.2022_reabertura.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4613,20 +4613,24 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Lista de inscritos doEdital nº 8/202 - CAPES/COFECUB, formato, pdf, 581kb</t>
+          <t>Edital PAEP nº 11/2023 - formato, pdf, 264kb</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/14062023_Lista_Listagem_1990268_Inscricoes_cofecub_2023.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20042023_Edital_1959492_SEI_CAPES___1959158___Edital_11_2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>1</v>
-      </c>
-      <c r="G150" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Alteração doEdital PAEP nº 11/2023 - formato, pdf, 154kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/08092023_EDITAL112023ALTERAO.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4636,22 +4640,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Lista de inscrições - Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 393kb</t>
+          <t>Edital PAEP nº 19/2025 - formato, pdf, 136kb</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Lista_de_Inscricoes_Homologadas_PDSE___2020_REVISADA.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/12092025_Edital_2679718_SEI_2669828_Edital_19_2025.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lista de candidaturas - Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 417kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/documentos/diretoria-de-relacoes-internacionais/pdse/Lista_Listagem_1439062_Lista_de_Inscricoes_Homologadas_PDSE___2020.pdf/@@display-file/file ; Retificação do Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 244kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/EDITAL192020_PDSERETIFICAO.pdf/@@display-file/file ; Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE)- formato, pdf, 236kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09102020_edital-19-pdse.pdf/@@display-file/file</t>
+          <t>Alteração do edital PAEP nº 19/2025 - formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23102025_Edital_2706985_SEI_2706736_Edital_n__19_2025___ALTERACAO.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4663,22 +4667,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Lista de inscrições do Edital nº 17/2025 - Primeira chamada Programa Institucional de Doutorado Sanduíche no Exterior (PDSE) - formato, pdf, 8,8mb</t>
+          <t>Edital PAEP nº 22/2024 - Alteração - formato, pdf, 47kb</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/29102025_Lista_Listagem_2708089_PDSE.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2473082_SEI_2472594_Edital_22_2024___ALTERACAO.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lista de inscrições do Edital nº 17/2025 - Segunda chamada Programa Institucional de Doutorado Sanduíche no Exterior (PDSE) - formato, pdf, 1,4mb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/27042026_Lista_Listagem_2808119_Lista_de_inscricoes_homologadas_do_Edital_172025___PDSE___segunda_chamada___formato_pdf__2_.pdf/@@display-file/file ; Alteração do Edital nº 17/2025 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE), formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/08102025_Edital_2696973_SEI_2695934_Edital_17_2025__.pdf/@@display-file/file ; Edital nº 17/2025 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 142kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/21082025_Edital_2662823_SEI_2661209_Edital_n__17_2025.pdf/@@display-file/file</t>
+          <t>Edital PAEP nº 22/2024 - formato, pdf, 126kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/10092024_Edital_2457107_SEI_2457028_Edital_22_2024.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4690,24 +4694,20 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Lista de instituições e cursos pré-aprovados para a 3ª fase do Edital nº 08/2022 - Parfor - formato, pdf, 715kb</t>
+          <t>Edital PAEP nº 37/2023 - formato, pdf, 264kb</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/06052022_Relacao_1700579_LISTA_DE_IES_E_CURSOS_APROVADOS_PARA_A_3__ETAPA_DO_EDITAL_CAPES_N__08.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20122023_Edital_2295422_SEI_2295394_Edital_37_2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>4</v>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>Alteraçãodo Edital nº 08/2022 - Parfor - formato, xls, 119kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20122022_Edital_1880841_Edital_8_2022___PARFOR.pdf/@@display-file/file ; Alteração do Edital nº 08/2022 - Parfor - formato, pdf, 128kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09062022_Edital_1729649_EDITAL___8_2022.pdf/@@display-file/file ; Edital nº 08/2022 - Parfor - formato, pdf, 203kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07022022_Edital_1629612_SEI_CAPES___1628279___Edital_8.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4717,22 +4717,22 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Lista e inscritos do Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 520kb</t>
+          <t>Lista de inscritos do Edital Conjunto nº 01/2024 - Programa Caminhos Amefricanos, formato, pdf, 407kb</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/20022024_Lista_Listagem_2324280_SEI_2323841_Inscritos_MIR.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15052024_Lista_Listagem_2374115_Inscritos_MIR.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alteração do Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 54kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/12062024_Edital_2395239_SEI_2389783_Edital_34_2023.pdf/@@display-file/file ; Prorrogação do Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 54kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/28122023_Edital_2301024_SEI_2300438_Edital_Conjunto_n__34_2023_Prorrogacao.pdf/@@display-file/file ; Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 129kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/04122024_Edital_2282364_SEI_2279471_Edital_Conjunto_n__34_2023.pdf/@@display-file/file</t>
+          <t>Alteração do Edital Conjunto nº 01/2024 - Programa Caminhos Amefricanos, formato, pdf, 63kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29042024_Edital_2368101_SEI_2365347_Edital_Conjunto_n__1_CAPES_MIR.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4744,24 +4744,20 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Lista final de inscritos no Edital n° 33/2022 - Brafitec, formato, pdf, 372kb</t>
+          <t>Lista de inscritos do Edital nº 05/2024 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 46kb</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/22092022_Lista_Listagem_1808291_Lista_inscritos_Brafitec_Edital_33_22.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/10062024_Lista_Listagem_2390159_Lista_de_Inscritos_3.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>3</v>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>Alteração do Edital n° 33/2022 - Brafitec, formato, pdf, 193kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23022023_Edital_1920292_Edital_33_22.pdf/@@display-file/file ; Edital n° 33/2022 - Brafitec, formato, pdf, 428kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29062022_EDITAL33_2022_BRAFITEC.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4771,14 +4767,14 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Prorrogação do Edital nº 01/2024 - Programa Caminhos Amefricanos, formato, pdf, 69kb</t>
+          <t>Lista de inscritos doEdital nº 8/202 - CAPES/COFECUB, formato, pdf, 581kb</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/30082024_Edital_2450719_SEI_2446271_Edital_Conjunto_1_2024.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/14062023_Lista_Listagem_1990268_Inscricoes_cofecub_2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F156" t="n">
@@ -4789,134 +4785,154 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SETEC</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Chamada (documento Nº 6991254) para seleção de unidades da Rede Federal de Educação Profissional e Tecnológica e das redes públicas estaduais de Educação Profissional e Tecnológica, interessadas em receber apoio técnico para a implementação de programas de aprendizagem profissional articulados a cursos técnicos ou de qualificação profissional com componentes curriculares relacionados à sustentabilidade</t>
+          <t>Lista de inscrições - Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 393kb</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2026/SEI_6991254_chamada.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Lista_de_Inscricoes_Homologadas_PDSE___2020_REVISADA.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>1</v>
-      </c>
-      <c r="G157" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Lista de candidaturas - Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 417kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/documentos/diretoria-de-relacoes-internacionais/pdse/Lista_Listagem_1439062_Lista_de_Inscricoes_Homologadas_PDSE___2020.pdf/@@display-file/file ; Retificação do Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 244kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/EDITAL192020_PDSERETIFICAO.pdf/@@display-file/file ; Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE)- formato, pdf, 236kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09102020_edital-19-pdse.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>SETEC</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Chamada (documento Nº 6991254) para seleção de unidades da Rede Federal de Educação Profissional e Tecnológica e das redes públicas estaduais de Educação Profissional e Tecnológica, interessadas em receber apoio técnico para a implementação de programas de aprendizagem profissional articulados a cursos técnicos ou de qualificação profissional com componentes curriculares relacionados à sustentabilidade.</t>
+          <t>Lista de inscrições do Edital nº 17/2025 - Primeira chamada Programa Institucional de Doutorado Sanduíche no Exterior (PDSE) - formato, pdf, 8,8mb</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2026/SEI_6991254_chamada.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/29102025_Lista_Listagem_2708089_PDSE.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>1</v>
-      </c>
-      <c r="G158" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Lista de inscrições do Edital nº 17/2025 - Segunda chamada Programa Institucional de Doutorado Sanduíche no Exterior (PDSE) - formato, pdf, 1,4mb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/27042026_Lista_Listagem_2808119_Lista_de_inscricoes_homologadas_do_Edital_172025___PDSE___segunda_chamada___formato_pdf__2_.pdf/@@display-file/file ; Alteração do Edital nº 17/2025 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE), formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/08102025_Edital_2696973_SEI_2695934_Edital_17_2025__.pdf/@@display-file/file ; Edital nº 17/2025 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 142kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/21082025_Edital_2662823_SEI_2661209_Edital_n__17_2025.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>SETEC</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Chamada Pública com o objetivo de identificar, avaliar, cadastrar e disponibilizar metodologias, ferramentas e estudos sobre o mapeamento de demandas por Educação Profissional Técnica de Nível Médio, visando aprimorar a definição de ofertas de Educação Profissional Técnica de Nível Médio, no âmbito do Programa Juros por Educação.</t>
+          <t>Lista de instituições e cursos pré-aprovados para a 3ª fase do Edital nº 08/2022 - Parfor - formato, pdf, 715kb</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/SEI_6268868_Resultado_de_Edital.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/06052022_Relacao_1700579_LISTA_DE_IES_E_CURSOS_APROVADOS_PARA_A_3__ETAPA_DO_EDITAL_CAPES_N__08.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>1</v>
-      </c>
-      <c r="G159" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Alteraçãodo Edital nº 08/2022 - Parfor - formato, xls, 119kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20122022_Edital_1880841_Edital_8_2022___PARFOR.pdf/@@display-file/file ; Alteração do Edital nº 08/2022 - Parfor - formato, pdf, 128kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09062022_Edital_1729649_EDITAL___8_2022.pdf/@@display-file/file ; Edital nº 08/2022 - Parfor - formato, pdf, 203kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07022022_Edital_1629612_SEI_CAPES___1628279___Edital_8.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>SETEC</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Chamada Pública de Adesão das Instituições da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT), com objetivo de capacitação técnica para submissão de propostas em futuros editais de unidades Embrapii.</t>
+          <t>Lista e inscritos do Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 520kb</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/edital-2025/SEI_MEC5650163ResultadodeEdital_.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/20022024_Lista_Listagem_2324280_SEI_2323841_Inscritos_MIR.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>1</v>
-      </c>
-      <c r="G160" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Alteração do Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 54kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/12062024_Edital_2395239_SEI_2389783_Edital_34_2023.pdf/@@display-file/file ; Prorrogação do Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 54kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/28122023_Edital_2301024_SEI_2300438_Edital_Conjunto_n__34_2023_Prorrogacao.pdf/@@display-file/file ; Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 129kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/04122024_Edital_2282364_SEI_2279471_Edital_Conjunto_n__34_2023.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>SETEC</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Chamada Pública de Adesão à linha de fomento Qualifica Mais EnergIFE</t>
+          <t>Lista final de inscritos no Edital n° 33/2022 - Brafitec, formato, pdf, 372kb</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/chamadapublica.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/22092022_Lista_Listagem_1808291_Lista_inscritos_Brafitec_Edital_33_22.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>1</v>
-      </c>
-      <c r="G161" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Alteração do Edital n° 33/2022 - Brafitec, formato, pdf, 193kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23022023_Edital_1920292_Edital_33_22.pdf/@@display-file/file ; Edital n° 33/2022 - Brafitec, formato, pdf, 428kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29062022_EDITAL33_2022_BRAFITEC.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>SETEC</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 01/2017 - Trata-se de chamada pública para seleção de servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) para capacitação em Gestão da Inovação.</t>
+          <t>Prorrogação do Edital nº 01/2024 - Programa Caminhos Amefricanos, formato, pdf, 69kb</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/extrato_chamada_dou_cp_01_2017.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/30082024_Edital_2450719_SEI_2446271_Edital_Conjunto_1_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F162" t="n">
@@ -4932,14 +4948,14 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 01/2018 - Trata-se da chamada pública para seleção de propostas e servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) em efetivo exercício, para participarem da capacitação em Gestão da Inovação (GI - CSIRO).</t>
+          <t>Chamada (documento Nº 6991254) para seleção de unidades da Rede Federal de Educação Profissional e Tecnológica e das redes públicas estaduais de Educação Profissional e Tecnológica, interessadas em receber apoio técnico para a implementação de programas de aprendizagem profissional articulados a cursos técnicos ou de qualificação profissional com componentes curriculares relacionados à sustentabilidade</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/20181030Edital012018ChamadaPblicaGICSIRO.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2026/SEI_6991254_chamada.pdf</t>
         </is>
       </c>
       <c r="F163" t="n">
@@ -4955,14 +4971,14 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 02/2017 - Trata-se de chamada pública para concurso sobre educação profissional da Secretaria de Educação Profissional e Tecnológica (Setec/MEC) em parceria com a Comunidade dos Países de Língua Portuguesa (CPLP).</t>
+          <t>Chamada (documento Nº 6991254) para seleção de unidades da Rede Federal de Educação Profissional e Tecnológica e das redes públicas estaduais de Educação Profissional e Tecnológica, interessadas em receber apoio técnico para a implementação de programas de aprendizagem profissional articulados a cursos técnicos ou de qualificação profissional com componentes curriculares relacionados à sustentabilidade.</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/edital_concurso_cplp_2017.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2026/SEI_6991254_chamada.pdf</t>
         </is>
       </c>
       <c r="F164" t="n">
@@ -4978,14 +4994,14 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 02/2018 - Trata-se da chamada pública para seleção de servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) para a capacitação Brasileiros Formando Formadores (BraFF).</t>
+          <t>Chamada Pública com o objetivo de identificar, avaliar, cadastrar e disponibilizar metodologias, ferramentas e estudos sobre o mapeamento de demandas por Educação Profissional Técnica de Nível Médio, visando aprimorar a definição de ofertas de Educação Profissional Técnica de Nível Médio, no âmbito do Programa Juros por Educação.</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/Edital_02_2018_BRAFF.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/SEI_6268868_Resultado_de_Edital.pdf</t>
         </is>
       </c>
       <c r="F165" t="n">
@@ -5001,14 +5017,14 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 38/2018 - Trata do processo de seleção de propostas para credenciamento de instituições da Rede Federal, Faculdades de Tecnologia do Estado de São Paulo (Fatecs) e do Instituto Tecnológico de Aeronáutica (ITA) para atuação como Núcleo de Línguas (NucLi-IsF) no âmbito do Programa Idiomas sem Fronteiras (IsF).</t>
+          <t>Chamada Pública de Adesão das Instituições da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT), com objetivo de capacitação técnica para submissão de propostas em futuros editais de unidades Embrapii.</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/Editaln382018ChamadaPblicaparacredenciamentodeinstituiesdaRFEPCTdasFatecsedoITA.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/edital-2025/SEI_MEC5650163ResultadodeEdital_.pdf</t>
         </is>
       </c>
       <c r="F166" t="n">
@@ -5024,14 +5040,14 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 79/2016 - Trata-se de chamada pública para apresentação de propostas por instituição de educação profissional e tecnológica para a oferta de cursos de formação inicial e continuada ou de qualificação profissional e cursos técnicos de nível médio, presenciais ou à distância, sem transferência de recursos, no âmbito do PRONATEC, denominada “PROPOSTAS VOLUNTÁRIAS - PRONATEC”</t>
+          <t>Chamada Pública de Adesão à linha de fomento Qualifica Mais EnergIFE</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/extrato_edital_79_2016_setec.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/chamadapublica.pdf</t>
         </is>
       </c>
       <c r="F167" t="n">
@@ -5047,14 +5063,14 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Chamada Pública que estabelece os procedimentos para a autorização de oferta de cursos técnicos de nível médio por Instituições Privadas de Ensino Superior (IPES) para fins de habilitação ao Programa Juros por Educação, no âmbito do Programa de Pleno Pagamento de Dívidas dos Estados (Propag).</t>
+          <t>Chamada Pública nº 01/2017 - Trata-se de chamada pública para seleção de servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) para capacitação em Gestão da Inovação.</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/FAQEdital6.2025.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/extrato_chamada_dou_cp_01_2017.pdf</t>
         </is>
       </c>
       <c r="F168" t="n">
@@ -5070,14 +5086,14 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Chamamento Público para credenciamento de profissionais no Banco de Especialistas para atuar no Projeto Assistec Inova, junto ao Ministério da Educação, no âmbito da Secretaria de Educação Profissional e Tecnológica.</t>
+          <t>Chamada Pública nº 01/2018 - Trata-se da chamada pública para seleção de propostas e servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) em efetivo exercício, para participarem da capacitação em Gestão da Inovação (GI - CSIRO).</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/SEI_23000.035944_2024_89.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/20181030Edital012018ChamadaPblicaGICSIRO.pdf</t>
         </is>
       </c>
       <c r="F169" t="n">
@@ -5093,14 +5109,14 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Edital 1/2026 - Chamada Pública de Adesão dos Institutos Federais de Educação, Ciência e Tecnologia, do Centro Federal de Educação Tecnológica Celso Suckow da Fonseca, do Centro Federal de Educação Tecnológica de Minas Gerais e do Colégio Pedro II, com objetivo de capacitação técnica para submissão de propostas em futuros editais de Unidades Embrapii.</t>
+          <t>Chamada Pública nº 02/2017 - Trata-se de chamada pública para concurso sobre educação profissional da Secretaria de Educação Profissional e Tecnológica (Setec/MEC) em parceria com a Comunidade dos Países de Língua Portuguesa (CPLP).</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/edital12026.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/edital_concurso_cplp_2017.pdf</t>
         </is>
       </c>
       <c r="F170" t="n">
@@ -5116,14 +5132,14 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Edital 84/2021 - Seleção de Projetos para desenvolvimento dos Ambientes de Promotores de Inovação na Rede Federal</t>
+          <t>Chamada Pública nº 02/2018 - Trata-se da chamada pública para seleção de servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) para a capacitação Brasileiros Formando Formadores (BraFF).</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/editais/2022/ResultadoetapaI.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/Edital_02_2018_BRAFF.pdf</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -5139,14 +5155,14 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Edital nº 01/2017 - APRESENTAÇÃO DE PROPOSTAS PARA A OFERTA DE VAGAS GRATUITAS EM CURSOS TÉCNICOS NA FORMA CONCOMITANTE, NO ÂMBITO DO PRONATEC/MEDIOTEC – 2º/2017 - A Secretária de Educação Profissional e Tecnológica do Ministério da Educação, no uso da atribuição que lhe confere o art. 13, Anexo I, do Decreto n° 7.690, de 02 de março de 2012, e considerando o disposto na Lei nº 12.513, de 26 de outubro de 2011, a Portaria nº 817, de 13 de agosto de 2015, a Portaria nº160, de 05 de março de 2013, alterada pela Portaria nº 701, de 13 de agosto de 2014, TORNA PÚBLICO os procedimentos e o cronograma para a apresentação de propostas visando a oferta de vagas gratuitas em cursos técnicos na forma concomitante e na modalidade presencial, no âmbito do Programa Nacional de Acesso ao Ensino Técnico e Emprego - PRONATEC, por meio da ação MEDIOTEC, para ingresso no segundo semestre de 2017.</t>
+          <t>Chamada Pública nº 38/2018 - Trata do processo de seleção de propostas para credenciamento de instituições da Rede Federal, Faculdades de Tecnologia do Estado de São Paulo (Fatecs) e do Instituto Tecnológico de Aeronáutica (ITA) para atuação como Núcleo de Línguas (NucLi-IsF) no âmbito do Programa Idiomas sem Fronteiras (IsF).</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/edital_01_mediotec_2017.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/Editaln382018ChamadaPblicaparacredenciamentodeinstituiesdaRFEPCTdasFatecsedoITA.pdf</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -5162,14 +5178,14 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Edital nº 08/2024 - Chamamento Público visando à seleção de autores(as) para elaboração de capítulos de obra a ser publicada cuja temática central é a gestão de Núcleos de Inovação Tecnológica (NITs) e/ou de Agências de Inovação da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) Divulgação das Inscrições Homologadas</t>
+          <t>Chamada Pública nº 79/2016 - Trata-se de chamada pública para apresentação de propostas por instituição de educação profissional e tecnológica para a oferta de cursos de formação inicial e continuada ou de qualificação profissional e cursos técnicos de nível médio, presenciais ou à distância, sem transferência de recursos, no âmbito do PRONATEC, denominada “PROPOSTAS VOLUNTÁRIAS - PRONATEC”</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/436.SEI_MEC5030251Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/extrato_edital_79_2016_setec.pdf</t>
         </is>
       </c>
       <c r="F173" t="n">
@@ -5185,14 +5201,14 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Edital nº 1/2023 - Seleção de proposta de selo comemorativo, em alusão aos 15 anos dos Institutos Federais.</t>
+          <t>Chamada Pública que estabelece os procedimentos para a autorização de oferta de cursos técnicos de nível médio por Instituições Privadas de Ensino Superior (IPES) para fins de habilitação ao Programa Juros por Educação, no âmbito do Programa de Pleno Pagamento de Dívidas dos Estados (Propag).</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC4094376Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/FAQEdital6.2025.pdf</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -5208,14 +5224,14 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Edital nº 100/2022 - Chamamento Público para a seleção de propostas para o Desafio Soutec</t>
+          <t>Chamamento Público para credenciamento de profissionais no Banco de Especialistas para atuar no Projeto Assistec Inova, junto ao Ministério da Educação, no âmbito da Secretaria de Educação Profissional e Tecnológica.</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/secretarias/secretaria-de-educacao-profissional/editais-2022/SEI_MEC3570188Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/SEI_23000.035944_2024_89.pdf</t>
         </is>
       </c>
       <c r="F175" t="n">
@@ -5231,14 +5247,14 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Edital nº 109/2022 - Chamamento Público - Seleção de projetos voltados à promoção do empreendedorismo inovador, com foco na Economia 4.0, associados ao ensino, à pesquisa e à extensão, destinado às instituições integrantes da Rede Federal de Educação Profissional, Científica e Tecnológica</t>
+          <t>Edital 1/2026 - Chamada Pública de Adesão dos Institutos Federais de Educação, Ciência e Tecnologia, do Centro Federal de Educação Tecnológica Celso Suckow da Fonseca, do Centro Federal de Educação Tecnológica de Minas Gerais e do Colégio Pedro II, com objetivo de capacitação técnica para submissão de propostas em futuros editais de Unidades Embrapii.</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital109.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/edital12026.pdf</t>
         </is>
       </c>
       <c r="F176" t="n">
@@ -5254,14 +5270,14 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Edital nº 11/2024 - Chamamento Público para a seleção de projetos aptos a integrarem a 4ª Semana Nacional de Educação Profissional e Tecnológica Retificação do</t>
+          <t>Edital 84/2021 - Seleção de Projetos para desenvolvimento dos Ambientes de Promotores de Inovação na Rede Federal</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-2024-1/Edital_11.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/editais/2022/ResultadoetapaI.pdf</t>
         </is>
       </c>
       <c r="F177" t="n">
@@ -5277,14 +5293,14 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Edital nº 15/2023 - Chamada Pública para o Workshop para elaboração de Itinerários Formativos em economia circular na Educação Profissional e Tecnológica</t>
+          <t>Edital nº 01/2017 - APRESENTAÇÃO DE PROPOSTAS PARA A OFERTA DE VAGAS GRATUITAS EM CURSOS TÉCNICOS NA FORMA CONCOMITANTE, NO ÂMBITO DO PRONATEC/MEDIOTEC – 2º/2017 - A Secretária de Educação Profissional e Tecnológica do Ministério da Educação, no uso da atribuição que lhe confere o art. 13, Anexo I, do Decreto n° 7.690, de 02 de março de 2012, e considerando o disposto na Lei nº 12.513, de 26 de outubro de 2011, a Portaria nº 817, de 13 de agosto de 2015, a Portaria nº160, de 05 de março de 2013, alterada pela Portaria nº 701, de 13 de agosto de 2014, TORNA PÚBLICO os procedimentos e o cronograma para a apresentação de propostas visando a oferta de vagas gratuitas em cursos técnicos na forma concomitante e na modalidade presencial, no âmbito do Programa Nacional de Acesso ao Ensino Técnico e Emprego - PRONATEC, por meio da ação MEDIOTEC, para ingresso no segundo semestre de 2017.</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/SEI_MEC3884064Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/edital_01_mediotec_2017.pdf</t>
         </is>
       </c>
       <c r="F178" t="n">
@@ -5300,14 +5316,14 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Edital nº 2/2020 - IFES, de chamada pública para a seleção de projetos voltados à implementação das Oficinas 4.0, aberto às autarquias da Rede Federal.</t>
+          <t>Edital nº 08/2024 - Chamamento Público visando à seleção de autores(as) para elaboração de capítulos de obra a ser publicada cuja temática central é a gestão de Núcleos de Inovação Tecnológica (NITs) e/ou de Agências de Inovação da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) Divulgação das Inscrições Homologadas</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://www.ifes.edu.br/chamadas-publicas/19329-chamada-publica-2-2020-apoio-a-implementacao-de-oficinas-4-0</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/436.SEI_MEC5030251Edital.pdf</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -5323,14 +5339,14 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Edital nº 20/2021 – Seleção de servidores para atuação em Projetos de Colaboração Técnica junto ao Ministério da Educação.</t>
+          <t>Edital nº 1/2023 - Seleção de proposta de selo comemorativo, em alusão aos 15 anos dos Institutos Federais.</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/SEI_MEC2573324Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC4094376Edital.pdf</t>
         </is>
       </c>
       <c r="F180" t="n">
@@ -5346,14 +5362,14 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Edital nº 25/2023 - Chamada Pública destinada a selecionar equipes da Rede Federal de Educação Profissional, Científica e Tecnológica (EPCT) para participação no projeto de formação em criatividade, inovação e prototipagem do mercosul (Hackathon Mercosul). Retificação do Edital</t>
+          <t>Edital nº 100/2022 - Chamamento Público para a seleção de propostas para o Desafio Soutec</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/SEI_MEC3913111Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/secretarias/secretaria-de-educacao-profissional/editais-2022/SEI_MEC3570188Edital.pdf</t>
         </is>
       </c>
       <c r="F181" t="n">
@@ -5369,14 +5385,14 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Edital nº 26 versão consolidada</t>
+          <t>Edital nº 109/2022 - Chamamento Público - Seleção de projetos voltados à promoção do empreendedorismo inovador, com foco na Economia 4.0, associados ao ensino, à pesquisa e à extensão, destinado às instituições integrantes da Rede Federal de Educação Profissional, Científica e Tecnológica</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC3980995Documento.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital109.pdf</t>
         </is>
       </c>
       <c r="F182" t="n">
@@ -5392,14 +5408,14 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Edital nº 3/2021 – Chamada Pública para seleção de projetos de iniciação tecnológica com foco na Economia 4.0. Acesse o edital .</t>
+          <t>Edital nº 11/2024 - Chamamento Público para a seleção de projetos aptos a integrarem a 4ª Semana Nacional de Educação Profissional e Tecnológica Retificação do</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
-          <t>https://www.ifes.edu.br/chamadas-publicas/19351-chamada-publica-3-2020-projetos-iniciacao-tecnologica-economia-4-0</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-2024-1/Edital_11.pdf</t>
         </is>
       </c>
       <c r="F183" t="n">
@@ -5415,24 +5431,20 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Edital nº 35/2020 - Chamada Pública - que tem como objetivo selecionar projetos voltados à criação de Laboratórios IFMaker junto aos Institutos Federais de Educação, Ciência e Tecnologia; Centros Federais de Educação Tecnológica Celso Suckow da Fonseca – Cefet-RJ e de Minas Gerais – Cefet-MG e o Colégio Pedro II, conforme especificado no Despacho SEI nº 2064854</t>
+          <t>Edital nº 15/2023 - Chamada Pública para o Workshop para elaboração de Itinerários Formativos em economia circular na Educação Profissional e Tecnológica</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2020/SEI_MEC_2064339_Edital_Chamada_Publica.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/SEI_MEC3884064Edital.pdf</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>2</v>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>Retificação Edital nº 35/2020 - Chamada Pública - Seleção de projetos voltados à criação de Laboratórios Maker junto à Rede Federal de Educação Profissional, Científica e Tecnológica Retificação de Cronograma ​do | https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/AlteraodecronogramaRedeMakeredital35.pdf</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -5442,14 +5454,14 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Edital nº 46, de 20 de julho de 2020, que torna público edital para adesão de estados e Distrito Federal à oferta de Curso de Especialização Lato Sensu em Docência para a Educação Profissional e Tecnológica (DocentEPT) aos professores da rede pública estadual e distrital que atuam na oferta de cursos de Educação Profissional e Tecnológica</t>
+          <t>Edital nº 2/2020 - IFES, de chamada pública para a seleção de projetos voltados à implementação das Oficinas 4.0, aberto às autarquias da Rede Federal.</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2020/Editaldeadeso_DOU.pdf</t>
+          <t>https://www.ifes.edu.br/chamadas-publicas/19329-chamada-publica-2-2020-apoio-a-implementacao-de-oficinas-4-0</t>
         </is>
       </c>
       <c r="F185" t="n">
@@ -5465,14 +5477,14 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Edital nº 47/2022 - Chamada Pública para oferta de cursos da Plataforma Aprenda Mais</t>
+          <t>Edital nº 20/2021 – Seleção de servidores para atuação em Projetos de Colaboração Técnica junto ao Ministério da Educação.</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/editais/2022/Editaln47.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/SEI_MEC2573324Edital.pdf</t>
         </is>
       </c>
       <c r="F186" t="n">
@@ -5488,14 +5500,14 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Edital nº 48/2022 - Procedimentos para autorização da oferta de cursos técnicos de nível médio por Instituições Privadas de Ensino Superior – Anexos do</t>
+          <t>Edital nº 25/2023 - Chamada Pública destinada a selecionar equipes da Rede Federal de Educação Profissional, Científica e Tecnológica (EPCT) para participação no projeto de formação em criatividade, inovação e prototipagem do mercosul (Hackathon Mercosul). Retificação do Edital</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/editais/2022/Editaln48.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/SEI_MEC3913111Edital.pdf</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -5511,14 +5523,14 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Edital nº 5 /2026 - Seleção de propostas de projetos de extensão voltados ao Acesso, à Permanência e ao Êxito no âmbito da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT).</t>
+          <t>Edital nº 26 versão consolidada</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2026/sei_7012727_edital_5.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC3980995Documento.pdf</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -5534,14 +5546,14 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Edital nº 5/2020 – Chamada para seleção de projetos de apoio ao empreendedorismo inovador com foco na Economia 4.0. Acesse o edital .</t>
+          <t>Edital nº 3/2021 – Chamada Pública para seleção de projetos de iniciação tecnológica com foco na Economia 4.0. Acesse o edital .</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr">
         <is>
-          <t>https://www.ifes.edu.br/chamadas-publicas/19384-chamada-publica-05-2020-selecao-de-projetos-de-apoio-ao-empreendedorismo-inovador-com-foco-na-economia-4-0</t>
+          <t>https://www.ifes.edu.br/chamadas-publicas/19351-chamada-publica-3-2020-projetos-iniciacao-tecnologica-economia-4-0</t>
         </is>
       </c>
       <c r="F189" t="n">
@@ -5557,20 +5569,24 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Edital nº 5/2021 – IF Mais Empreendedor Nacional : Adesão ao Programa IF Mais Empreendedor Nacional</t>
+          <t>Edital nº 35/2020 - Chamada Pública - que tem como objetivo selecionar projetos voltados à criação de Laboratórios IFMaker junto aos Institutos Federais de Educação, Ciência e Tecnologia; Centros Federais de Educação Tecnológica Celso Suckow da Fonseca – Cefet-RJ e de Minas Gerais – Cefet-MG e o Colégio Pedro II, conforme especificado no Despacho SEI nº 2064854</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/editais/2021/Edital05.2021IFEMPREENDEDORNACIONAL.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2020/SEI_MEC_2064339_Edital_Chamada_Publica.pdf</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>1</v>
-      </c>
-      <c r="G190" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Retificação Edital nº 35/2020 - Chamada Pública - Seleção de projetos voltados à criação de Laboratórios Maker junto à Rede Federal de Educação Profissional, Científica e Tecnológica Retificação de Cronograma ​do | https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/AlteraodecronogramaRedeMakeredital35.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -5580,14 +5596,14 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Edital nº 5/2024 - Seleção de propostas de novos Cursos Abertos, On-line e Massivos (MOOCs), desenvolvidos pela Rede Federa de Educação Profissional, Científica e Tecnológica, a serem disponibilizados na Plataforma APRENDA MAIS.</t>
+          <t>Edital nº 46, de 20 de julho de 2020, que torna público edital para adesão de estados e Distrito Federal à oferta de Curso de Especialização Lato Sensu em Docência para a Educação Profissional e Tecnológica (DocentEPT) aos professores da rede pública estadual e distrital que atuam na oferta de cursos de Educação Profissional e Tecnológica</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC4659481Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2020/Editaldeadeso_DOU.pdf</t>
         </is>
       </c>
       <c r="F191" t="n">
@@ -5603,14 +5619,14 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Edital nº 52/2016 – que torna público, para conhecimento dos interessados, que será realizado na modalidade concurso, o PROJETO DESAFIO DA EDUCAÇÃO PROFISSIONAL E TECNOLÓGICA, na forma do REGULAMENTO anexo a este edital, com o objetivo de promover uma campanha nacional para aprimorar a Educação Profissional e Tecnológica estimulando a sociedade a enviar propostas de ações inovadoras e compartilhar experiências exitosas de implementação de ações.</t>
+          <t>Edital nº 47/2022 - Chamada Pública para oferta de cursos da Plataforma Aprenda Mais</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/edital_n_52_2016.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/editais/2022/Editaln47.pdf</t>
         </is>
       </c>
       <c r="F192" t="n">
@@ -5626,14 +5642,14 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Edital nº 55/2016 , que torna público concurso PROJETO DESAFIO EDUCAÇÃO ZIKAZERO, na forma do REGULAMENTO anexo a este edital, com o objetivo de promover uma campanha nacional de mobilização para o enfrentamento ao Aedes aegyp e à microcefalia estimulando a sociedade a enviar propostas de ações inovadoras e compartilhar experiências exitosas de implementação de ações em prol do combate ao mosquito.</t>
+          <t>Edital nº 48/2022 - Procedimentos para autorização da oferta de cursos técnicos de nível médio por Instituições Privadas de Ensino Superior – Anexos do</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/Edital_55_2016_SEI_MEC_0227936.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/editais/2022/Editaln48.pdf</t>
         </is>
       </c>
       <c r="F193" t="n">
@@ -5649,14 +5665,14 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Edital nº 6/2021 - Edital de Adesão das instituições ao Sistema Re-Saber</t>
+          <t>Edital nº 5 /2026 - Seleção de propostas de projetos de extensão voltados ao Acesso, à Permanência e ao Êxito no âmbito da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT).</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/Edital_06_2021.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2026/sei_7012727_edital_5.pdf</t>
         </is>
       </c>
       <c r="F194" t="n">
@@ -5672,14 +5688,14 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Edital nº 6/2024 - Edital visa selecionar a proposta de selo/logomarca que será utilizado em confecções comemorativas no contexto dos 115 anos da Rede Federal de Educação Profissional, Científica e Tecnológica, que poderá ser personalizado como selo postal, via Correios. *</t>
+          <t>Edital nº 5/2020 – Chamada para seleção de projetos de apoio ao empreendedorismo inovador com foco na Economia 4.0. Acesse o edital .</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-2024/325.SEI_MEC4985249Edital.pdf</t>
+          <t>https://www.ifes.edu.br/chamadas-publicas/19384-chamada-publica-05-2020-selecao-de-projetos-de-apoio-ao-empreendedorismo-inovador-com-foco-na-economia-4-0</t>
         </is>
       </c>
       <c r="F195" t="n">
@@ -5695,14 +5711,14 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Edital nº 61/2019 – Regulamento do Cadastro de Especialistas para compor o Banco de Avaliadores da Secretaria de Educação Profissional e Tecnológica.</t>
+          <t>Edital nº 5/2021 – IF Mais Empreendedor Nacional : Adesão ao Programa IF Mais Empreendedor Nacional</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2019/EDITALN612019.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/editais/2021/Edital05.2021IFEMPREENDEDORNACIONAL.pdf</t>
         </is>
       </c>
       <c r="F196" t="n">
@@ -5718,14 +5734,14 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Edital nº 63/2021- Seleção de Projetos de Promoção às Indicações Geográficas</t>
+          <t>Edital nº 5/2024 - Seleção de propostas de novos Cursos Abertos, On-line e Massivos (MOOCs), desenvolvidos pela Rede Federa de Educação Profissional, Científica e Tecnológica, a serem disponibilizados na Plataforma APRENDA MAIS.</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/editais/2021/Edital63.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC4659481Edital.pdf</t>
         </is>
       </c>
       <c r="F197" t="n">
@@ -5741,14 +5757,14 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Edital nº 67/2021 - Chamada Pública de Projetos para apoio à implementação das Oficinas 4.0</t>
+          <t>Edital nº 52/2016 – que torna público, para conhecimento dos interessados, que será realizado na modalidade concurso, o PROJETO DESAFIO DA EDUCAÇÃO PROFISSIONAL E TECNOLÓGICA, na forma do REGULAMENTO anexo a este edital, com o objetivo de promover uma campanha nacional para aprimorar a Educação Profissional e Tecnológica estimulando a sociedade a enviar propostas de ações inovadoras e compartilhar experiências exitosas de implementação de ações.</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/SEI_MEC2898796Edital67.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/edital_n_52_2016.pdf</t>
         </is>
       </c>
       <c r="F198" t="n">
@@ -5764,14 +5780,14 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Edital nº 68/2019 – Seleção de servidores para atuação em Projetos Educacionais de Colaboração Técnica junto ao Ministério da Educação.</t>
+          <t>Edital nº 55/2016 , que torna público concurso PROJETO DESAFIO EDUCAÇÃO ZIKAZERO, na forma do REGULAMENTO anexo a este edital, com o objetivo de promover uma campanha nacional de mobilização para o enfrentamento ao Aedes aegyp e à microcefalia estimulando a sociedade a enviar propostas de ações inovadoras e compartilhar experiências exitosas de implementação de ações em prol do combate ao mosquito.</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2019/EDITALN682019.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/Edital_55_2016_SEI_MEC_0227936.pdf</t>
         </is>
       </c>
       <c r="F199" t="n">
@@ -5787,14 +5803,14 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Edital nº 83/2022 – Seleção de propostas de instituições da Rede Federal para a implementação de programa de capacitação de estudantes denominado Oficinas 4.0</t>
+          <t>Edital nº 6/2021 - Edital de Adesão das instituições ao Sistema Re-Saber</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital83.2022.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/Edital_06_2021.pdf</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -5810,14 +5826,14 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Edital nº 88/2022 – Seleção de projetos de iniciação tecnológica de instituições da RFEPCT para o desenvolvimento de ações de formação em programação e/ou robótica e/ou cultura maker para estudantes dos anos finais do ensino fundamental (6º ao 9º ano) das redes públicas de ensino. Retificação ​do</t>
+          <t>Edital nº 6/2024 - Edital visa selecionar a proposta de selo/logomarca que será utilizado em confecções comemorativas no contexto dos 115 anos da Rede Federal de Educação Profissional, Científica e Tecnológica, que poderá ser personalizado como selo postal, via Correios. *</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital88.2022.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-2024/325.SEI_MEC4985249Edital.pdf</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -5833,14 +5849,14 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Edital nº 94/2022 – Chamada Pública para a capacitação de multiplicadores em bioeconomia para a Amazônia Legal. Chamada Pública para a Adesão de parceiros ofertantes da Rede Federal de Educação Profissional, Científica e Tecnológica – RFEPCT à linha de fomento Qualifica Mais EnergIFE, voltada à promoção da oferta de cursos na área das Energias Renováveis. Retificação do</t>
+          <t>Edital nº 61/2019 – Regulamento do Cadastro de Especialistas para compor o Banco de Avaliadores da Secretaria de Educação Profissional e Tecnológica.</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Editaln94.2022.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2019/EDITALN612019.pdf</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -5856,14 +5872,14 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Edital nº 99/2022 - Chamamento Público para a seleção de projetos de inovação e trabalhos acadêmicos aptos a integrarem a Semana Nacional da Educação Profissional e Tecnológica Retificação do</t>
+          <t>Edital nº 63/2021- Seleção de Projetos de Promoção às Indicações Geográficas</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/secretarias/secretaria-de-educacao-profissional/SEI_MEC3566713Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/editais/2021/Edital63.pdf</t>
         </is>
       </c>
       <c r="F203" t="n">
@@ -5879,14 +5895,14 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Programa Setec-Capes/NOVA de capacitação para Professores da Rede Federal de Educação Profissional, Científica e Tecnológica . A Secretaria de Educação Profissional e Tecnológica (Setec) do Ministério da Educação, com apoio da Coordenação de Aperfeiçoamento de Pessoal de Nível Superior (Capes), lançam chamada pública de capacitação para professores de inglês em efetivo exercício na Rede Federal de Educação Profissional - Institutos Federais, Cefets, Escolas Técnicas vinculas às Universidades Federais e Colégio Pedro II. (Retificação publicada no Diário Oficial da União em 02 de junho de 2016)</t>
+          <t>Edital nº 67/2021 - Chamada Pública de Projetos para apoio à implementação das Oficinas 4.0</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2015/chamada_setec_capes_nova_extrato_dou.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/SEI_MEC2898796Edital67.pdf</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -5902,24 +5918,20 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Republicação do Edital nº 76/2022 - Chamamento Público para seleção de projetos voltados ao fortalecimento de Núcleos de Inovação Tecnológica e/ou Agências de Inovação.</t>
+          <t>Edital nº 68/2019 – Seleção de servidores para atuação em Projetos Educacionais de Colaboração Técnica junto ao Ministério da Educação.</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Republicaodoedital76.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2019/EDITALN682019.pdf</t>
         </is>
       </c>
       <c r="F205" t="n">
-        <v>2</v>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>Retificação do Edital nº 76/2022 – novo cronograma | https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/SEI_23000.006585_2022_91.pdf</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -5929,14 +5941,14 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições da Rede Federal de Educação Profissional, Científica e Tecnológica).</t>
+          <t>Edital nº 83/2022 – Seleção de propostas de instituições da Rede Federal para a implementação de programa de capacitação de estudantes denominado Oficinas 4.0</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/ResultadoEdital10.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital83.2022.pdf</t>
         </is>
       </c>
       <c r="F206" t="n">
@@ -5952,14 +5964,14 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições Privadas de Ensino Superior que ofertam cursos técnicos e Escolas Técnicas Privadas).</t>
+          <t>Edital nº 88/2022 – Seleção de projetos de iniciação tecnológica de instituições da RFEPCT para o desenvolvimento de ações de formação em programação e/ou robótica e/ou cultura maker para estudantes dos anos finais do ensino fundamental (6º ao 9º ano) das redes públicas de ensino. Retificação ​do</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/ResultadoEdital09.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital88.2022.pdf</t>
         </is>
       </c>
       <c r="F207" t="n">
@@ -5975,20 +5987,162 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições Públicas Estaduais e Distrital de Educação Profissional e Tecnológica).</t>
+          <t>Edital nº 94/2022 – Chamada Pública para a capacitação de multiplicadores em bioeconomia para a Amazônia Legal. Chamada Pública para a Adesão de parceiros ofertantes da Rede Federal de Educação Profissional, Científica e Tecnológica – RFEPCT à linha de fomento Qualifica Mais EnergIFE, voltada à promoção da oferta de cursos na área das Energias Renováveis. Retificação do</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr">
         <is>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Editaln94.2022.pdf</t>
+        </is>
+      </c>
+      <c r="F208" t="n">
+        <v>1</v>
+      </c>
+      <c r="G208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>SETEC</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Edital nº 99/2022 - Chamamento Público para a seleção de projetos de inovação e trabalhos acadêmicos aptos a integrarem a Semana Nacional da Educação Profissional e Tecnológica Retificação do</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr"/>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/secretarias/secretaria-de-educacao-profissional/SEI_MEC3566713Edital.pdf</t>
+        </is>
+      </c>
+      <c r="F209" t="n">
+        <v>1</v>
+      </c>
+      <c r="G209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>SETEC</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Programa Setec-Capes/NOVA de capacitação para Professores da Rede Federal de Educação Profissional, Científica e Tecnológica . A Secretaria de Educação Profissional e Tecnológica (Setec) do Ministério da Educação, com apoio da Coordenação de Aperfeiçoamento de Pessoal de Nível Superior (Capes), lançam chamada pública de capacitação para professores de inglês em efetivo exercício na Rede Federal de Educação Profissional - Institutos Federais, Cefets, Escolas Técnicas vinculas às Universidades Federais e Colégio Pedro II. (Retificação publicada no Diário Oficial da União em 02 de junho de 2016)</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr"/>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2015/chamada_setec_capes_nova_extrato_dou.pdf</t>
+        </is>
+      </c>
+      <c r="F210" t="n">
+        <v>1</v>
+      </c>
+      <c r="G210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>SETEC</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Republicação do Edital nº 76/2022 - Chamamento Público para seleção de projetos voltados ao fortalecimento de Núcleos de Inovação Tecnológica e/ou Agências de Inovação.</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr"/>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Republicaodoedital76.pdf</t>
+        </is>
+      </c>
+      <c r="F211" t="n">
+        <v>2</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Retificação do Edital nº 76/2022 – novo cronograma | https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/SEI_23000.006585_2022_91.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>SETEC</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições da Rede Federal de Educação Profissional, Científica e Tecnológica).</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr"/>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/ResultadoEdital10.pdf</t>
+        </is>
+      </c>
+      <c r="F212" t="n">
+        <v>1</v>
+      </c>
+      <c r="G212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>SETEC</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições Privadas de Ensino Superior que ofertam cursos técnicos e Escolas Técnicas Privadas).</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr"/>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/ResultadoEdital09.pdf</t>
+        </is>
+      </c>
+      <c r="F213" t="n">
+        <v>1</v>
+      </c>
+      <c r="G213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>SETEC</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições Públicas Estaduais e Distrital de Educação Profissional e Tecnológica).</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr"/>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr">
+        <is>
           <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/2147-resultado-preliminar.pdf</t>
         </is>
       </c>
-      <c r="F208" t="n">
-        <v>1</v>
-      </c>
-      <c r="G208" t="inlineStr"/>
+      <c r="F214" t="n">
+        <v>1</v>
+      </c>
+      <c r="G214" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/editais.xlsx
+++ b/editais.xlsx
@@ -3108,7 +3108,11 @@
           <t>07/08/2024</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>https://www.finep.gov.br/e/chamada-publica/222684/749717</t>

--- a/editais.xlsx
+++ b/editais.xlsx
@@ -1529,11 +1529,11 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Prorrogação - Edital Conjunto nº 4/2026, formato, pdf, 52,5kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/documentos/edital_2863852_sei_2863595_edital_conjunto_n__4_2026___prorrogacao.pdf/@@display-file/file</t>
+          <t>Prorrogação - Edital Conjunto nº 4/2026, formato, pdf, 52,5kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/documentos/edital_2863852_sei_2863595_edital_conjunto_n__4_2026___prorrogacao.pdf/@@display-file/file ; Alteração - Edital Conjunto nº 4/2026, formato, pdf, 52,6kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2888100_sei_2886868_edital_conjunto_n__4_2026___alteracao.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4721,22 +4721,22 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Lista de inscritos do Edital Conjunto nº 01/2024 - Programa Caminhos Amefricanos, formato, pdf, 407kb</t>
+          <t>Edital PDSE nº 17/2025 – segunda chamada – relação de aprovadas na análise técnica após a análise dos recursos - formato, pdf, 1,438kb</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15052024_Lista_Listagem_2374115_Inscritos_MIR.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/lista_listagem_2878471_listagem_resultado_final_pdse_segunda_chamada.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alteração do Edital Conjunto nº 01/2024 - Programa Caminhos Amefricanos, formato, pdf, 63kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29042024_Edital_2368101_SEI_2365347_Edital_Conjunto_n__1_CAPES_MIR.pdf/@@display-file/file</t>
+          <t>Lista de inscrições do Edital nº 17/2025 - Segunda chamada Programa Institucional de Doutorado Sanduíche no Exterior (PDSE) - formato, pdf, 1,4mb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/27042026_Lista_Listagem_2808119_Lista_de_inscricoes_homologadas_do_Edital_172025___PDSE___segunda_chamada___formato_pdf__2_.pdf/@@display-file/file ; Lista de inscrições do Edital nº 17/2025 - Primeira chamada Programa Institucional de Doutorado Sanduíche no Exterior (PDSE) - formato, pdf, 8,8mb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/29102025_Lista_Listagem_2708089_PDSE.pdf/@@display-file/file ; Alteração do Edital nº 17/2025 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE), formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/08102025_Edital_2696973_SEI_2695934_Edital_17_2025__.pdf/@@display-file/file ; Edital nº 17/2025 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 142kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/21082025_Edital_2662823_SEI_2661209_Edital_n__17_2025.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4748,20 +4748,24 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Lista de inscritos do Edital nº 05/2024 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 46kb</t>
+          <t>Lista de inscritos do Edital Conjunto nº 01/2024 - Programa Caminhos Amefricanos, formato, pdf, 407kb</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/10062024_Lista_Listagem_2390159_Lista_de_Inscritos_3.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15052024_Lista_Listagem_2374115_Inscritos_MIR.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>1</v>
-      </c>
-      <c r="G155" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Alteração do Edital Conjunto nº 01/2024 - Programa Caminhos Amefricanos, formato, pdf, 63kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29042024_Edital_2368101_SEI_2365347_Edital_Conjunto_n__1_CAPES_MIR.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4771,14 +4775,14 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Lista de inscritos doEdital nº 8/202 - CAPES/COFECUB, formato, pdf, 581kb</t>
+          <t>Lista de inscritos do Edital nº 05/2024 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 46kb</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/14062023_Lista_Listagem_1990268_Inscricoes_cofecub_2023.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/10062024_Lista_Listagem_2390159_Lista_de_Inscritos_3.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F156" t="n">
@@ -4794,24 +4798,20 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Lista de inscrições - Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 393kb</t>
+          <t>Lista de inscritos doEdital nº 8/202 - CAPES/COFECUB, formato, pdf, 581kb</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Lista_de_Inscricoes_Homologadas_PDSE___2020_REVISADA.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/14062023_Lista_Listagem_1990268_Inscricoes_cofecub_2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>4</v>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>Lista de candidaturas - Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 417kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/documentos/diretoria-de-relacoes-internacionais/pdse/Lista_Listagem_1439062_Lista_de_Inscricoes_Homologadas_PDSE___2020.pdf/@@display-file/file ; Retificação do Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 244kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/EDITAL192020_PDSERETIFICAO.pdf/@@display-file/file ; Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE)- formato, pdf, 236kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09102020_edital-19-pdse.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4821,14 +4821,14 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Lista de inscrições do Edital nº 17/2025 - Primeira chamada Programa Institucional de Doutorado Sanduíche no Exterior (PDSE) - formato, pdf, 8,8mb</t>
+          <t>Lista de inscrições - Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 393kb</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/29102025_Lista_Listagem_2708089_PDSE.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Lista_de_Inscricoes_Homologadas_PDSE___2020_REVISADA.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F158" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lista de inscrições do Edital nº 17/2025 - Segunda chamada Programa Institucional de Doutorado Sanduíche no Exterior (PDSE) - formato, pdf, 1,4mb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/27042026_Lista_Listagem_2808119_Lista_de_inscricoes_homologadas_do_Edital_172025___PDSE___segunda_chamada___formato_pdf__2_.pdf/@@display-file/file ; Alteração do Edital nº 17/2025 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE), formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/08102025_Edital_2696973_SEI_2695934_Edital_17_2025__.pdf/@@display-file/file ; Edital nº 17/2025 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 142kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/21082025_Edital_2662823_SEI_2661209_Edital_n__17_2025.pdf/@@display-file/file</t>
+          <t>Lista de candidaturas - Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 417kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/documentos/diretoria-de-relacoes-internacionais/pdse/Lista_Listagem_1439062_Lista_de_Inscricoes_Homologadas_PDSE___2020.pdf/@@display-file/file ; Retificação do Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 244kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/EDITAL192020_PDSERETIFICAO.pdf/@@display-file/file ; Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE)- formato, pdf, 236kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09102020_edital-19-pdse.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>

--- a/editais.xlsx
+++ b/editais.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G214"/>
+  <dimension ref="A1:G215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,22 +461,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Chamada Pública CNPq/CAPES Nº 30/2026 – Programa de Mestrado e Doutorado Acadêmico para Inovação – MAI/DAI</t>
+          <t>Chamada Pública MCTI/CNPq/ANR N° 32/2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11/12/2026</t>
+          <t>31/03/2027</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-30-2026/chamada-publica-cnpq-N-30-2026</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-32-2026/chamada-publica-cnpq-N-32-2026</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -492,7 +492,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Chamada Pública CNPq/SETEC/SETAD/MCTI/FNDCT Nº 29/2026 – RHAE IA – Recursos Humanos em Áreas Estratégicas – Pesquisador na Empresa – Inteligência Artificial</t>
+          <t>Chamada Pública CNPq/CAPES Nº 30/2026 – Programa de Mestrado e Doutorado Acadêmico para Inovação – MAI/DAI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -502,12 +502,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/12/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-29-2026/chamada-publica-cnpq-N-29-2026</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-30-2026/chamada-publica-cnpq-N-30-2026</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -518,27 +518,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5ª Chamada Pública Conjunta - Finep e Conselho Norueguês de Pesquisa (RCN)</t>
+          <t>Chamada Pública CNPq/SETEC/SETAD/MCTI/FNDCT Nº 29/2026 – RHAE IA – Recursos Humanos em Áreas Estratégicas – Pesquisador na Empresa – Inteligência Artificial</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>16/12/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/1019381</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-29-2026/chamada-publica-cnpq-N-29-2026</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -549,37 +549,33 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CNPq</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Chamada Pública CNPq/ERC Nº 21/2026</t>
+          <t>5ª Chamada Pública Conjunta - Finep e Conselho Norueguês de Pesquisa (RCN)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>16/12/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-21-2026/chamada-publica-cnpq-N-21-2026</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/1019381</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Chamada Pública CNPq/ERC (Conselho Europeu de Pesquisa) Nº 21/2026 | https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-21-2026/chamada-publica-cnpq-N-21-2026</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -589,53 +585,57 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Chamada CNPq/CT-Biotec/FNDCT/MCTI Nº 24/2026 - Apoio à Pesquisa, Desenvolvimento e Inovação em Biotecnologia</t>
+          <t>Chamada Pública CNPq/ERC Nº 21/2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-24-2026/chamada-publica-cnpq-N-24-2026</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-21-2026/chamada-publica-cnpq-N-21-2026</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Chamada Pública CNPq/ERC (Conselho Europeu de Pesquisa) Nº 21/2026 | https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-21-2026/chamada-publica-cnpq-N-21-2026</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FAPESB</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DIRETRIZES ESPECÍFICAS DA FAPESB – 1ª CHAMADA DA PARCERIA DE MATÉRIAS- PRIMAS PARA A TRANSIÇÃO VERDE E DIGITAL (RAMP) 2026-2027</t>
+          <t>Chamada CNPq/CT-Biotec/FNDCT/MCTI Nº 24/2026 - Apoio à Pesquisa, Desenvolvimento e Inovação em Biotecnologia</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>15/02/2027</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/diretrizes-especificas-da-fapesb-1a-chamada-da-parceria-de-materias-primas-para-a-transicao-verde-e-digital-ramp-2026-2027/</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-24-2026/chamada-publica-cnpq-N-24-2026</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -651,22 +651,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CHAMADA CDTI ESPANHA (2026-2027) – DIRETRIZES ESPECÍFICAS DA FAPESB</t>
+          <t>DIRETRIZES ESPECÍFICAS DA FAPESB – 1ª CHAMADA DA PARCERIA DE MATÉRIAS- PRIMAS PARA A TRANSIÇÃO VERDE E DIGITAL (RAMP) 2026-2027</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>15/02/2027</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/chamada-cdti-espanha-2026-2027-diretrizes-especificas-da-fapesb/</t>
+          <t>https://www.fapesb.ba.gov.br/diretrizes-especificas-da-fapesb-1a-chamada-da-parceria-de-materias-primas-para-a-transicao-verde-e-digital-ramp-2026-2027/</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -682,22 +682,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CHAMADA 2026- PROGRAMA DE AUXILIO PARA DOUTORANDOS COM BOLSA NACIONAL – DAAD</t>
+          <t>CHAMADA CDTI ESPANHA (2026-2027) – DIRETRIZES ESPECÍFICAS DA FAPESB</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/chamada-2026-programa-de-auxilio-para-doutorandos-com-bolsa-nacional-daad/</t>
+          <t>https://www.fapesb.ba.gov.br/chamada-cdti-espanha-2026-2027-diretrizes-especificas-da-fapesb/</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -713,7 +713,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CHAMADA GCUB – MOB Nº 2026/2027 – PROGRAMA DE MOBILIDADE INTERNACIONAL DO GCUB (GCUB-MOB)</t>
+          <t>CHAMADA 2026- PROGRAMA DE AUXILIO PARA DOUTORANDOS COM BOLSA NACIONAL – DAAD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -721,10 +721,14 @@
           <t>13/07/2026</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/chamada-gcub-mob-no-20262027-programa-de-mobilidade-internacional-do-gcub-gcub-mob/</t>
+          <t>https://www.fapesb.ba.gov.br/chamada-2026-programa-de-auxilio-para-doutorandos-com-bolsa-nacional-daad/</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -735,23 +739,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CNPq</t>
+          <t>FAPESB</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chamada CNPq/MCTI nº 25/2026 - Endometriose e Saúde Menstrual</t>
+          <t>CHAMADA GCUB – MOB Nº 2026/2027 – PROGRAMA DE MOBILIDADE INTERNACIONAL DO GCUB (GCUB-MOB)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-25-2026/chamada-publica-cnpq-N-25-2026</t>
+          <t>https://www.fapesb.ba.gov.br/chamada-gcub-mob-no-20262027-programa-de-mobilidade-internacional-do-gcub-gcub-mob/</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -762,23 +766,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FAPESB</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EDITAL DE SELEÇÃO PÚBLICA Nº 017/ 2026 Subvenção Econômica à Pesquisa,Desenvolvimento e Inovação (P,D&amp;I) Soluções de Sistemas Inteligentes para a Administração Estadual – Rodada 2</t>
+          <t>Chamada CNPq/MCTI nº 25/2026 - Endometriose e Saúde Menstrual</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/edital-de-selecao-publica-no-017-2026-subvencao-economica-a-pesquisadesenvolvimento-e-inovacao-pdi-solucoes-de-sistemas-inteligentes-para-a-administracao-estadual-rodada-2/</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-25-2026/chamada-publica-cnpq-N-25-2026</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -794,7 +798,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EDITAL FAPESB No 018/2026 – APOIO À PUBLICAÇÃO CIENTÍFICA, TECNOLÓGICA OU DE POPULARIZAÇÃO DAS CIÊNCIAS</t>
+          <t>EDITAL DE SELEÇÃO PÚBLICA Nº 017/ 2026 Subvenção Econômica à Pesquisa,Desenvolvimento e Inovação (P,D&amp;I) Soluções de Sistemas Inteligentes para a Administração Estadual – Rodada 2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -805,7 +809,7 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/edital-fapesb-no-0182026-apoio-a-publicacao-cientifica-tecnologica-ou-de-popularizacao-das-ciencias/</t>
+          <t>https://www.fapesb.ba.gov.br/edital-de-selecao-publica-no-017-2026-subvencao-economica-a-pesquisadesenvolvimento-e-inovacao-pdi-solucoes-de-sistemas-inteligentes-para-a-administracao-estadual-rodada-2/</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -821,7 +825,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EDITAL FAPESB/SECTI – Nº 010/2026 – UNIVERSAL</t>
+          <t>EDITAL FAPESB No 018/2026 – APOIO À PUBLICAÇÃO CIENTÍFICA, TECNOLÓGICA OU DE POPULARIZAÇÃO DAS CIÊNCIAS</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -829,14 +833,10 @@
           <t>03/07/2026</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>03/09/2026</t>
-        </is>
-      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/edital-fapesbsecti-no-0102026-universal/</t>
+          <t>https://www.fapesb.ba.gov.br/edital-fapesb-no-0182026-apoio-a-publicacao-cientifica-tecnologica-ou-de-popularizacao-das-ciencias/</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -852,7 +852,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EDITAL FAPESB/SECTI/CNPq/CAPES – No 11/2026 – PROFIX-CB</t>
+          <t>EDITAL FAPESB/SECTI – Nº 010/2026 – UNIVERSAL</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -862,12 +862,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/edital-fapesbsecticnpqcapes-no-112026-profix-cb/</t>
+          <t>https://www.fapesb.ba.gov.br/edital-fapesbsecti-no-0102026-universal/</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -883,7 +883,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EDITAL Nº 019/2026 – CIÊNCIA NA MESA 5: BASE DE DADOS E SISTEMAS DE INFORMAÇÕES PARA TOMADA DE DECISÃO EM SOBERANIA ALIMENTAR E NUTRICIONAL</t>
+          <t>EDITAL FAPESB/SECTI/CNPq/CAPES – No 11/2026 – PROFIX-CB</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -891,10 +891,14 @@
           <t>03/07/2026</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/edital-no-0192026-ciencia-na-mesa-5-base-de-dados-e-sistemas-de-informacoes-para-tomada-de-decisao-em-soberania-alimentar-e-nutricional/</t>
+          <t>https://www.fapesb.ba.gov.br/edital-fapesbsecticnpqcapes-no-112026-profix-cb/</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -905,23 +909,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CNPq</t>
+          <t>FAPESB</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Chamamento Público CNPq/FNDCT/MCTI Nº 01/2026 Para Participação no Programa de Apoio à Popularização da Ciência nas Unidades da Federação</t>
+          <t>EDITAL Nº 019/2026 – CIÊNCIA NA MESA 5: BASE DE DADOS E SISTEMAS DE INFORMAÇÕES PARA TOMADA DE DECISÃO EM SOBERANIA ALIMENTAR E NUTRICIONAL</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamamento-no-01-2026/chamamento-publico-01-2026</t>
+          <t>https://www.fapesb.ba.gov.br/edital-no-0192026-ciencia-na-mesa-5-base-de-dados-e-sistemas-de-informacoes-para-tomada-de-decisao-em-soberania-alimentar-e-nutricional/</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -937,22 +941,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Chamada Pública CNPq/MMULHERES Nº 19/2026 - Programa Asas para o Futuro</t>
+          <t>Chamamento Público CNPq/FNDCT/MCTI Nº 01/2026 Para Participação no Programa de Apoio à Popularização da Ciência nas Unidades da Federação</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-19-2026/chamada-publica-cnpq-N-19-2026</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamamento-no-01-2026/chamamento-publico-01-2026</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -968,7 +968,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Chamada Pública MCTI/CNPq/MIR/MMulheres/MPI Nº 20/2026 Atlânticas - Programa Beatriz Nascimento de Mulheres na Ciência</t>
+          <t>Chamada Pública CNPq/MMULHERES Nº 19/2026 - Programa Asas para o Futuro</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -976,10 +976,14 @@
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-20-2026/chamada-publica-cnpq-N-20-2026</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-19-2026/chamada-publica-cnpq-N-19-2026</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -990,12 +994,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BRICs - CHAMADA PÚBLICA Cooperação Multilateral em Inovação</t>
+          <t>Chamada Pública MCTI/CNPq/MIR/MMulheres/MPI Nº 20/2026 Atlânticas - Programa Beatriz Nascimento de Mulheres na Ciência</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1003,14 +1007,10 @@
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>14/08/2026</t>
-        </is>
-      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/991625</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-20-2026/chamada-publica-cnpq-N-20-2026</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1021,27 +1021,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CNPq</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Chamada Pública CNPq/CAPES/MRE N° 16/2026 - Programa de Estudantes-Convênio de Pós-Graduação (PEC-PG)</t>
+          <t>BRICs - CHAMADA PÚBLICA Cooperação Multilateral em Inovação</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-16-2026/chamada-publica-cnpq-N-16-2026</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/991625</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1052,27 +1052,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FIP Conexões Startups – 2026</t>
+          <t>Chamada Pública CNPq/CAPES/MRE N° 16/2026 - Programa de Estudantes-Convênio de Pós-Graduação (PEC-PG)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/986129</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-16-2026/chamada-publica-cnpq-N-16-2026</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1083,27 +1083,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CNPq</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Chamada CNPq/MinC nº 17/2026 - Apoio ao funcionamento de incubadoras voltadas à Economia Criativa</t>
+          <t>FIP Conexões Startups – 2026</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-17-2026/chamada-publica-cnpq-N-17-2026</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/986129</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1114,27 +1114,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Subvenção Descentralizada Seleção de Parceiros em Fluxo Contínuo - Pró Amazônia Empreende</t>
+          <t>Chamada CNPq/MinC nº 17/2026 - Apoio ao funcionamento de incubadoras voltadas à Economia Criativa</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/972778</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-17-2026/chamada-publica-cnpq-N-17-2026</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1145,27 +1145,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CNPq</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Chamada CNPq/FNDCT nº 06/2026 – UNIVERSAL</t>
+          <t>Subvenção Descentralizada Seleção de Parceiros em Fluxo Contínuo - Pró Amazônia Empreende</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-06-2026/chamada-publica-cnpq-N-06-2026</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/972778</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1176,27 +1176,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DESAFIO TECNOLÓGICO ELETROLISADOR NACIONAL</t>
+          <t>Chamada CNPq/FNDCT nº 06/2026 – UNIVERSAL</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/968467</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-06-2026/chamada-publica-cnpq-N-06-2026</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1212,22 +1212,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CARTA CONVITE MCTI/FINEP - PROGRAMA TECNOVA 2026/2027</t>
+          <t>DESAFIO TECNOLÓGICO ELETROLISADOR NACIONAL</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/958302</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/968467</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1238,23 +1238,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FAPESB</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DIRETRIZES ESPECÍFICAS DA FAPESB – CHAMADA MOBILITY CONFAP ITALY 2026</t>
+          <t>CARTA CONVITE MCTI/FINEP - PROGRAMA TECNOVA 2026/2027</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/diretrizes-especificas-da-fapesb-chamada-mobility-confap-italy-2026/</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/958302</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1270,18 +1274,18 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Edital 009/2026 – Apoio a Organização de Eventos</t>
+          <t>DIRETRIZES ESPECÍFICAS DA FAPESB – CHAMADA MOBILITY CONFAP ITALY 2026</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/edital-0092026-apoio-a-organizacao-de-eventos/</t>
+          <t>https://www.fapesb.ba.gov.br/diretrizes-especificas-da-fapesb-chamada-mobility-confap-italy-2026/</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1292,27 +1296,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>FAPESB</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO UNIDADES DE PESQUISA MCTI – PROINFRA 2026</t>
+          <t>Edital 009/2026 – Apoio a Organização de Eventos</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>07/07/2026</t>
-        </is>
-      </c>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/945796</t>
+          <t>https://www.fapesb.ba.gov.br/edital-0092026-apoio-a-organizacao-de-eventos/</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1323,27 +1323,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CNPq</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Chamada Pública CNPq N° 07/2026 - Programa Institucional de Bolsas de Pós-Graduação (PIBPG)</t>
+          <t>MANUTENÇÃO UNIDADES DE PESQUISA MCTI – PROINFRA 2026</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-07-2026/chamada-publica-cnpq-N-07-2026</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/945796</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1354,27 +1354,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CARTA CONVITE MCTI/FINEP/FNDCT - PROMOÇÃO DA AUTONOMIA TECNOLÓGICA NA ÁREA DA DEFESA</t>
+          <t>Chamada Pública CNPq N° 07/2026 - Programa Institucional de Bolsas de Pós-Graduação (PIBPG)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/943682</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-07-2026/chamada-publica-cnpq-N-07-2026</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1385,33 +1385,33 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Edital nº 10/2026 - Programas CAPES/MATH/STIC/CLIMAT-AMSUD, formato - pdf, 283kb</t>
+          <t>CARTA CONVITE MCTI/FINEP/FNDCT - PROMOÇÃO DA AUTONOMIA TECNOLÓGICA NA ÁREA DA DEFESA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/copy2_of_15042026_Edital_2803264_SEI_2802205_Edital_10_2026.pdf</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/943682</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Alteração Edital nº 10/2026 - Programas CAPES/MATH/STIC/CLIMAT-AMSUD, formato - pdf, 53,1kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/25052026_Edital_2826286_SEI_2825187_Edital_10_2026___alteracao.pdf ; Alteração do Edital  nº 10/2026 - Programas CAPES/MATH/STIC/CLIMAT-AMSUD, formato - pdf, 53,1kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/25052026_Edital_2826286_SEI_2825187_Edital_10_2026___alteracao.pdf</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1421,18 +1421,18 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Edital nº 12/2026 - Programa CAPES/MES-CUBA - Projetos , formato, pdf, 222kb</t>
+          <t>Edital nº 10/2026 - Programas CAPES/MATH/STIC/CLIMAT-AMSUD, formato - pdf, 283kb</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23042026_Edital_2806973_SEI_2806062_Edital_12_2026.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/copy2_of_15042026_Edital_2803264_SEI_2802205_Edital_10_2026.pdf</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lista de inscritos do Edital nº 12/2026 - Programa CAPES/MES-CUBA - Projetos, formato, pdf, 148kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/lista_listagem_2857109_lista_de_inscritos_projetos.pdf/@@display-file/file ; Alteração Edital nº 12/2026 - Programa CAPES/MES-CUBA - Projetos , formato, pdf, 53,1kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/25052026_Edital_2826296_SEI_2825183_Edital_12_2026___ALTERACAO.pdf</t>
+          <t>Alteração Edital nº 10/2026 - Programas CAPES/MATH/STIC/CLIMAT-AMSUD, formato - pdf, 53,1kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/25052026_Edital_2826286_SEI_2825187_Edital_10_2026___alteracao.pdf ; Alteração do Edital  nº 10/2026 - Programas CAPES/MATH/STIC/CLIMAT-AMSUD, formato - pdf, 53,1kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/25052026_Edital_2826286_SEI_2825187_Edital_10_2026___alteracao.pdf</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Edital nº 13/2026 - Programa CAPES/MES-CUBA - Docentes , formato, pdf, 123kb</t>
+          <t>Edital nº 12/2026 - Programa CAPES/MES-CUBA - Projetos , formato, pdf, 222kb</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1463,7 +1463,7 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23042026_Edital_2806981_SEI_2806195_Edital_13_2026.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23042026_Edital_2806973_SEI_2806062_Edital_12_2026.pdf</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1471,71 +1471,71 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Edital nº 13/2026 - Lista de Inscritos, formarto, pdf, 130kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/lista_listagem_2854147_lista_de_inscritos_docentes.pdf/@@display-file/file ; Alteração Edital nº 13/2026 - Programa CAPES/MES-CUBA - Docentes , formato, pdf, 123kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/25052026_Edital_2826299_SEI_2825184_Edital_13_2026___ALTERACAO.pdf</t>
+          <t>Lista de inscritos do Edital nº 12/2026 - Programa CAPES/MES-CUBA - Projetos, formato, pdf, 148kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/lista_listagem_2857109_lista_de_inscritos_projetos.pdf/@@display-file/file ; Alteração Edital nº 12/2026 - Programa CAPES/MES-CUBA - Projetos , formato, pdf, 53,1kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/25052026_Edital_2826296_SEI_2825183_Edital_12_2026___ALTERACAO.pdf</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CNPq</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Chamada Pública CNPq/MCTI nº 15/2026 - Programa de Cooperação Afro-Brasileira em Ciência e Tecnologia - PROAFRICA</t>
+          <t>Edital nº 13/2026 - Programa CAPES/MES-CUBA - Docentes , formato, pdf, 123kb</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-15-2026/chamada-publica-cnpq-N-15-2026</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23042026_Edital_2806981_SEI_2806195_Edital_13_2026.pdf</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Edital nº 13/2026 - Lista de Inscritos, formarto, pdf, 130kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/lista_listagem_2854147_lista_de_inscritos_docentes.pdf/@@display-file/file ; Alteração Edital nº 13/2026 - Programa CAPES/MES-CUBA - Docentes , formato, pdf, 123kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/25052026_Edital_2826299_SEI_2825184_Edital_13_2026___ALTERACAO.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Edital Conjunto nº 4/2026, formato, pdf, 310kb</t>
+          <t>Chamada Pública CNPq/MCTI nº 15/2026 - Programa de Cooperação Afro-Brasileira em Ciência e Tecnologia - PROAFRICA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19052026_Edital_2823166_EDITAL_CONJUNTO_4_2026___CAPES_CFN.pdf</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-15-2026/chamada-publica-cnpq-N-15-2026</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Prorrogação - Edital Conjunto nº 4/2026, formato, pdf, 52,5kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/documentos/edital_2863852_sei_2863595_edital_conjunto_n__4_2026___prorrogacao.pdf/@@display-file/file ; Alteração - Edital Conjunto nº 4/2026, formato, pdf, 52,6kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2888100_sei_2886868_edital_conjunto_n__4_2026___alteracao.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1545,18 +1545,18 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Edital CAPES Nº 18/2026 - Programa Cátedra Maison Du Brésil - pdf, 122kb</t>
+          <t>Edital Conjunto nº 4/2026, formato, pdf, 310kb</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15052026_Edital_2821031_SEI_2819915_Edital_18_2026.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19052026_Edital_2823166_EDITAL_CONJUNTO_4_2026___CAPES_CFN.pdf</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alteração Edital CAPES Nº 18/2026 - Programa Cátedra Maison Du Brésil - pdf, 56,1kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2837190_SEI_2835880_Edital_18__2026___Alteracao.pdf ; Lista de inscritos Edital CAPES Nº 18/2026 - Programa Cátedra Maison Du Brésil - pdf, 116kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/lista_listagem_2853883_lista_de_inscritos.pdf/@@display-file/file</t>
+          <t>Prorrogação - Edital Conjunto nº 4/2026, formato, pdf, 52,5kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/documentos/edital_2863852_sei_2863595_edital_conjunto_n__4_2026___prorrogacao.pdf/@@display-file/file ; Alteração - Edital Conjunto nº 4/2026, formato, pdf, 52,6kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2888100_sei_2886868_edital_conjunto_n__4_2026___alteracao.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -1576,18 +1576,18 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Edital nº 17/2026 - seleção de projetos conjuntos de pesquisa por chamada no âmbito do Programa CAPES - AUGM</t>
+          <t>Edital CAPES Nº 18/2026 - Programa Cátedra Maison Du Brésil - pdf, 122kb</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/copy_of_13052026_Edital_2819298_SEI_2819065_Edital_17_2026.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15052026_Edital_2821031_SEI_2819915_Edital_18_2026.pdf</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Edital nº 17/2026 - Relação das Inscrições Recebidas, formato, pdf, 178kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2865911_lista_de_inscritos.pdf/@@display-file/file ; Edital nº 17/2026 - Prorrogação, formato, pdf, 52,5kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2850525_sei_2848632_edital_n__17_2026.pdf/@@display-file/file</t>
+          <t>Alteração Edital CAPES Nº 18/2026 - Programa Cátedra Maison Du Brésil - pdf, 56,1kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2837190_SEI_2835880_Edital_18__2026___Alteracao.pdf ; Lista de inscritos Edital CAPES Nº 18/2026 - Programa Cátedra Maison Du Brésil - pdf, 116kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/lista_listagem_2853883_lista_de_inscritos.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -1607,80 +1607,84 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Edital nº 26/2025 - Política de Novação para Bolsistas e Ex-Bolsistas no Exterior, formato - pdf, 96kb</t>
+          <t>Edital nº 17/2026 - seleção de projetos conjuntos de pesquisa por chamada no âmbito do Programa CAPES - AUGM</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>22/12/2025</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/22122025_Edital_2740775.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/copy_of_13052026_Edital_2819298_SEI_2819065_Edital_17_2026.pdf</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Edital nº 26/2025 - Alteração, formato, pdf, 114kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2878184_edital_26_2025___alteracao.pdf/@@display-file/file ; Retificação_Edital nº 26/2025 - Alteração, formato, pdf, 115kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2879083_edital_26_2025___retificacao.pdf/@@display-file/file ; Alteração do edital nº 26/2025 - Política de Novação para Bolsistas e Ex-Bolsistas no Exterior, formato - pdf, 60,5kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11052026_Edital_2817202_SEI_2816655_Edital_n__26_2025___Alteracao.pdf</t>
+          <t>Edital nº 17/2026 - Relação das Inscrições Recebidas, formato, pdf, 178kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2865911_lista_de_inscritos.pdf/@@display-file/file ; Edital nº 17/2026 - Prorrogação, formato, pdf, 52,5kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2850525_sei_2848632_edital_n__17_2026.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FAPESB</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CHAMADA CONFAP/ERC 2026 – CALL RESEARCH OPPORTUNITIES IN EUROPE FOR ACTIVE PHD RESEARCHERS FROM BRAZIL</t>
+          <t>Edital nº 26/2025 - Política de Novação para Bolsistas e Ex-Bolsistas no Exterior, formato - pdf, 96kb</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>10/07/2026</t>
-        </is>
-      </c>
+          <t>22/12/2025</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/chamada-confaperc-2026-call-research-opportunities-in-europe-for-active-phd-researchers-from-brazil/</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/22122025_Edital_2740775.pdf</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Edital nº 26/2025 - Alteração, formato, pdf, 114kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2878184_edital_26_2025___alteracao.pdf/@@display-file/file ; Retificação_Edital nº 26/2025 - Alteração, formato, pdf, 115kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2879083_edital_26_2025___retificacao.pdf/@@display-file/file ; Alteração do edital nº 26/2025 - Política de Novação para Bolsistas e Ex-Bolsistas no Exterior, formato - pdf, 60,5kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11052026_Edital_2817202_SEI_2816655_Edital_n__26_2025___Alteracao.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>FAPESB</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Edital nº 15/2026 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 134kb</t>
+          <t>CHAMADA CONFAP/ERC 2026 – CALL RESEARCH OPPORTUNITIES IN EUROPE FOR ACTIVE PHD RESEARCHERS FROM BRAZIL</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/30042026_Edital_2811434_SEI_2811079_Edital_15_2026.pdf</t>
+          <t>https://www.fapesb.ba.gov.br/chamada-confaperc-2026-call-research-opportunities-in-europe-for-active-phd-researchers-from-brazil/</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1696,38 +1700,34 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Edital conjunto ProEB e Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edição Moçambique nº 3/2026 - formato, pdf, 128kb</t>
+          <t>Edital nº 15/2026 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 134kb</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/28042026_Edital_2809885_SEI_2804920_Edital_Conjunto_3_2026.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/30042026_Edital_2811434_SEI_2811079_Edital_15_2026.pdf</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>4</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Alteração - Edital Conjunto nº 3/2026 - ProEB e Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul - Edição Moçambique | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2827276_SEI_2826404_Edital_Conjunto_n__3_2026.pdf ; Retificação - Edital Conjunto nº 3/2026 - ProEB e Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul - Edição Moçambique | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2824561_Edital_Conjunto_n__03.2026.pdf ; Alteração - Edital conjunto ProEB e Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edição Moçambique nº 3/2026 - formato, pdf, 64,1kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2858440_sei_2857414_edital_conjunto_n__3_2026___alteracao.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CNPq</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Chamada CNPq/SETEC/MCTI N° 13/2026 - Apoio a Eventos de Promoção do Empreendedorismo e da Inovação no Brasil</t>
+          <t>Edital conjunto ProEB e Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edição Moçambique nº 3/2026 - formato, pdf, 128kb</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1738,34 +1738,38 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-13-2026/chamada-publica-cnpq-N-13-2026</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/28042026_Edital_2809885_SEI_2804920_Edital_Conjunto_3_2026.pdf</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alteração - Edital Conjunto nº 3/2026 - ProEB e Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul - Edição Moçambique | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2827276_SEI_2826404_Edital_Conjunto_n__3_2026.pdf ; Retificação - Edital Conjunto nº 3/2026 - ProEB e Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul - Edição Moçambique | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2824561_Edital_Conjunto_n__03.2026.pdf ; Alteração - Edital conjunto ProEB e Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edição Moçambique nº 3/2026 - formato, pdf, 64,1kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2858440_sei_2857414_edital_conjunto_n__3_2026___alteracao.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Edital nº 11/2026 - Programa Cátedra Jorge Amado, formato, pdf, 196kb</t>
+          <t>Chamada CNPq/SETEC/MCTI N° 13/2026 - Apoio a Eventos de Promoção do Empreendedorismo e da Inovação no Brasil</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23042026_Edital_2806958_SEI_2806040_Edital_11_2026.pdf</t>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-13-2026/chamada-publica-cnpq-N-13-2026</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1781,28 +1785,24 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Edital nº 5/2026 - Programa CAPES - PURDUE deProjetos conjuntos de pesquisa, formato, pdf, 257kb</t>
+          <t>Edital nº 11/2026 - Programa Cátedra Jorge Amado, formato, pdf, 196kb</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09032026_Edital_2780596_SEI_2779319_Edital_5__de_2026.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23042026_Edital_2806958_SEI_2806040_Edital_11_2026.pdf</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>5</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Lista de inscritos do Edital nº 5/2026 - Programa CAPES - PURDUE de Projetos conjuntos de pesquisa, formato, pdf, 144kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Lista_Listagem_2841625_Lista_de_inscritos.pdf/@@display-file/file ; Alteração do Edital nº 5/2026 - Programa CAPES - PURDUE de Projetos conjuntos de pesquisa, formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15042026_Edital_2803256_SEI_2801466_Edital_5__de_2026.pdf/@@display-file/file ; Edital nº 5/2026 - Programa CAPES - PURDUE de Projetos conjuntos de pesquisa, formato, pdf, 257kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09032026_Edital_2780596_SEI_2779319_Edital_5__de_2026.pdf/@@display-file/file ; Alteração do Edital nº 5/2026 - Programa CAPES - PURDUE deProjetos conjuntos de pesquisa,formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15042026_Edital_2803256_SEI_2801466_Edital_5__de_2026.pdf</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1812,86 +1812,90 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Edital CAPES/DAAD Probral nº 08/2026, formato - pdf, 214kb</t>
+          <t>Edital nº 5/2026 - Programa CAPES - PURDUE deProjetos conjuntos de pesquisa, formato, pdf, 257kb</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/01042026_Edital_2795382_SEI_2794361_Edital_8__de_2026.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09032026_Edital_2780596_SEI_2779319_Edital_5__de_2026.pdf</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lista de Inscritos - Edital nº 08/2026, formato - pdf, 199 kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/lista_listagem_2841542_lista_de_inscritos.pdf/@@display-file/file ; Alteração do Edital CAPES/DAAD Probral nº 08/2026, formato - pdf, 48kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/13042026_Edital_2801456_SEI_2800616_Edital_8_2026.pdf</t>
+          <t>Lista de inscritos do Edital nº 5/2026 - Programa CAPES - PURDUE de Projetos conjuntos de pesquisa, formato, pdf, 144kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Lista_Listagem_2841625_Lista_de_inscritos.pdf/@@display-file/file ; Alteração do Edital nº 5/2026 - Programa CAPES - PURDUE de Projetos conjuntos de pesquisa, formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15042026_Edital_2803256_SEI_2801466_Edital_5__de_2026.pdf/@@display-file/file ; Edital nº 5/2026 - Programa CAPES - PURDUE de Projetos conjuntos de pesquisa, formato, pdf, 257kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09032026_Edital_2780596_SEI_2779319_Edital_5__de_2026.pdf/@@display-file/file ; Alteração do Edital nº 5/2026 - Programa CAPES - PURDUE deProjetos conjuntos de pesquisa,formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15042026_Edital_2803256_SEI_2801466_Edital_5__de_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FIP Startup Inteligência Artificial</t>
+          <t>Edital CAPES/DAAD Probral nº 08/2026, formato - pdf, 214kb</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/756012</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/01042026_Edital_2795382_SEI_2794361_Edital_8__de_2026.pdf</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Lista de Inscritos - Edital nº 08/2026, formato - pdf, 199 kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/lista_listagem_2841542_lista_de_inscritos.pdf/@@display-file/file ; Alteração do Edital CAPES/DAAD Probral nº 08/2026, formato - pdf, 48kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/13042026_Edital_2801456_SEI_2800616_Edital_8_2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Edital n° 14/2022 - formato, pdf, 380kb</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
+          <t>FIP Startup Inteligência Artificial</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/08062022_Lista_Listagem_1727316_Humboldt.pdf/@@display-file/file</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/756012</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>11</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Lista de Inscritos no Edital nº 14/2022 do Programa de Bolsas para Pesquisa CAPES/Humboldt - 26° chamada | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Lista_de_inscritos_26_chamada.pdf/@@display-file/file ; Lista de inscritos - Chamada nª 23 do Edital n° 14/2022 - formato, pdf, 396kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/18122024_SEI_CAPES___2508050___Edital_Minuta_ok.pdf/@@display-file/file ; Lista de inscritos - Chamada nº 22 do Edital n° 14/2022 - formato, pdf, 99kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/17062024_Lista_Listagem_2395643_Lista_de_inscritos.pdf/@@display-file/file ; Lista de inscritos - Chamada nº 21 do Edital n° 14/2022 - formato, pdf, 151kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/22122023_Lista_Listagem_2297511_Lista_de_inscritos_21_.pdf/@@display-file/file ; Lista de inscritos - Chamada nª 20 do Edital 14/2022, formato , pdf, 391kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/Lista_Listagem_2001777_Lista_de_inscritos_final_2.pdf/@@display-file/file ; Relação final das inscrições recebidas - Chamada nº 19 do Edital n° 14/2022 - formato, pdf, 380kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/13122022_Lista_Listagem_1874367_Lista_Inscritos_Humboldt__1_.pdf/@@display-file/file ; Relação das inscrições recebidas do Editaln°14/2022 - formato, pdf, 372kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/20092022_Lista_Listagem_1805835_Lista_Final_Humboldt_pdf_para_word_edital_14_22.pdf/@@display-file/file ; Lista de Inscritos - Chamada nº 24 do Edital nº 14/2022 - formato, pdf, 150kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/17062025_Lista_Listagem_2616980_Lista_de_inscritos_24_chamada.pdf ; Lista de Inscritos - Chamada nº 25 do Edital nº 14/2022 - formato, pdf, 241kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/17122025_Lista_Listagem_2735806_SEI___23038.004870_2021_69_25__chamada.pdf ; Alteração do Edital n° 14/2022 - formato, pdf, 49kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/06042026_Edital_2797322_SEI_2796265_Edital_14__de_2022.pdf</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1901,26 +1905,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesPanamá, Angola e México, formato pdf, 151kb</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>09/01/2026</t>
-        </is>
-      </c>
+          <t>Edital n° 14/2022 - formato, pdf, 380kb</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09012026_Edital_2748950_SEI_2748603_Edital_Conjunto_n__1_2026.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/08062022_Lista_Listagem_1727316_Humboldt.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Prorrogação Edital Conjunto nº 1/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México, formato pdf, 65,6kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2855428_sei_2855023_edital_conjunto_n__1_2026___prorrogacao.pdf/@@display-file/file ; Lista de inscritos Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Angola e México, formato pdf, 435kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/01042026_Lista_Listagem_2788855_Lista_de_inscritos_Angola_e_Mexico.pdf/@@display-file/file ; Lista de inscritos Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México, formato pdf, 421kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/12032026_Lista_Listagem_2780399_Lista_de_Inscritos_Panama.pdf/@@display-file/file ; Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México - Retificação do Cumprimento de decisão judicial, formato pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/13022026_Edital_2768872_SEI_2768349_Edital_Conjunto_n__1_2026____Retificacao_de_Decisao_Judicial.pdf/@@display-file/file ; Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México - Cumprimento de decisão judicial, formato pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11022026_Edital_2766993_SEI_2766572_Edital_Conjunto_1_2026_.pdf/@@display-file/file ; Alteração do edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México, formato pdf, 81kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/03022026_Edital_2762271_SEI_2757276_Edital_Conjunto_n__1_2026_CAPES_MIR_____1_.pdf/@@display-file/file ; Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México, formato pdf, 151kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09012026_Edital_2748950_SEI_2748603_Edital_Conjunto_n__1_2026.pdf/@@display-file/file ; Edital Conjunto nº 1/2026 - Prorrogação formato, pdf, 113kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2879086_edital_conjunto_1_2026___prorrogacao.pdf/@@display-file/file ; Alteração do edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesPanamá, Angola e México, formato pdf, 81kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/03022026_Edital_2762271_SEI_2757276_Edital_Conjunto_n__1_2026_CAPES_MIR_____1_.pdf ; Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesPanamá, Angola e México - Cumprimento de decisão judicial, formato pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11022026_Edital_2766993_SEI_2766572_Edital_Conjunto_1_2026_.pdf ; Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesPanamá, Angola e México - Retificação do Cumprimento de decisão judicial, formato pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/13022026_Edital_2768872_SEI_2768349_Edital_Conjunto_n__1_2026____Retificacao_de_Decisao_Judicial.pdf ; Lista de inscritos Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesPanamá, Angola e México, formato pdf, 421kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/12032026_Lista_Listagem_2780399_Lista_de_Inscritos_Panama.pdf ; Lista de inscritos Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesAngola e México, formato pdf, 435kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/01042026_Lista_Listagem_2788855_Lista_de_inscritos_Angola_e_Mexico.pdf</t>
+          <t>Lista de Inscritos no Edital nº 14/2022 do Programa de Bolsas para Pesquisa CAPES/Humboldt - 26° chamada | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Lista_de_inscritos_26_chamada.pdf/@@display-file/file ; Lista de inscritos - Chamada nª 23 do Edital n° 14/2022 - formato, pdf, 396kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/18122024_SEI_CAPES___2508050___Edital_Minuta_ok.pdf/@@display-file/file ; Lista de inscritos - Chamada nº 22 do Edital n° 14/2022 - formato, pdf, 99kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/17062024_Lista_Listagem_2395643_Lista_de_inscritos.pdf/@@display-file/file ; Lista de inscritos - Chamada nº 21 do Edital n° 14/2022 - formato, pdf, 151kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/22122023_Lista_Listagem_2297511_Lista_de_inscritos_21_.pdf/@@display-file/file ; Lista de inscritos - Chamada nª 20 do Edital 14/2022, formato , pdf, 391kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/Lista_Listagem_2001777_Lista_de_inscritos_final_2.pdf/@@display-file/file ; Relação final das inscrições recebidas - Chamada nº 19 do Edital n° 14/2022 - formato, pdf, 380kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/13122022_Lista_Listagem_1874367_Lista_Inscritos_Humboldt__1_.pdf/@@display-file/file ; Relação das inscrições recebidas do Editaln°14/2022 - formato, pdf, 372kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/20092022_Lista_Listagem_1805835_Lista_Final_Humboldt_pdf_para_word_edital_14_22.pdf/@@display-file/file ; Lista de Inscritos - Chamada nº 24 do Edital nº 14/2022 - formato, pdf, 150kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/17062025_Lista_Listagem_2616980_Lista_de_inscritos_24_chamada.pdf ; Lista de Inscritos - Chamada nº 25 do Edital nº 14/2022 - formato, pdf, 241kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/17122025_Lista_Listagem_2735806_SEI___23038.004870_2021_69_25__chamada.pdf ; Alteração do Edital n° 14/2022 - formato, pdf, 49kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/06042026_Edital_2797322_SEI_2796265_Edital_14__de_2022.pdf</t>
         </is>
       </c>
     </row>
@@ -1932,69 +1932,69 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Edital nº 07/2026 - CAPES/Cofecub, formato, pdf, 545kb</t>
+          <t>Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesPanamá, Angola e México, formato pdf, 151kb</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/30032026_EDITAL72026CAPESCOFECUB.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09012026_Edital_2748950_SEI_2748603_Edital_Conjunto_n__1_2026.pdf</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alteração do Edital nº 07/2026 - CAPES/Cofecub, formato, pdf, 143kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2832325_EDITAL_7_2026___ALTERACAO.pdf ; Lista de inscritos  no Edital n° 7/2026 - Programa CAPES/COFECUB, formato, pdf, 116kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Lista_Listagem_2841501_Lista_de_inscritos.pdf/@@display-file/file</t>
+          <t>Prorrogação Edital Conjunto nº 1/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México, formato pdf, 65,6kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2855428_sei_2855023_edital_conjunto_n__1_2026___prorrogacao.pdf/@@display-file/file ; Lista de inscritos Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Angola e México, formato pdf, 435kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/01042026_Lista_Listagem_2788855_Lista_de_inscritos_Angola_e_Mexico.pdf/@@display-file/file ; Lista de inscritos Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México, formato pdf, 421kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/12032026_Lista_Listagem_2780399_Lista_de_Inscritos_Panama.pdf/@@display-file/file ; Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México - Retificação do Cumprimento de decisão judicial, formato pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/13022026_Edital_2768872_SEI_2768349_Edital_Conjunto_n__1_2026____Retificacao_de_Decisao_Judicial.pdf/@@display-file/file ; Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México - Cumprimento de decisão judicial, formato pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11022026_Edital_2766993_SEI_2766572_Edital_Conjunto_1_2026_.pdf/@@display-file/file ; Alteração do edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México, formato pdf, 81kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/03022026_Edital_2762271_SEI_2757276_Edital_Conjunto_n__1_2026_CAPES_MIR_____1_.pdf/@@display-file/file ; Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  Edições Panamá, Angola e México, formato pdf, 151kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09012026_Edital_2748950_SEI_2748603_Edital_Conjunto_n__1_2026.pdf/@@display-file/file ; Edital Conjunto nº 1/2026 - Prorrogação formato, pdf, 113kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2879086_edital_conjunto_1_2026___prorrogacao.pdf/@@display-file/file ; Alteração do edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesPanamá, Angola e México, formato pdf, 81kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/03022026_Edital_2762271_SEI_2757276_Edital_Conjunto_n__1_2026_CAPES_MIR_____1_.pdf ; Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesPanamá, Angola e México - Cumprimento de decisão judicial, formato pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11022026_Edital_2766993_SEI_2766572_Edital_Conjunto_1_2026_.pdf ; Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesPanamá, Angola e México - Retificação do Cumprimento de decisão judicial, formato pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/13022026_Edital_2768872_SEI_2768349_Edital_Conjunto_n__1_2026____Retificacao_de_Decisao_Judicial.pdf ; Lista de inscritos Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesPanamá, Angola e México, formato pdf, 421kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/12032026_Lista_Listagem_2780399_Lista_de_Inscritos_Panama.pdf ; Lista de inscritos Edital Conjunto nº 01/2026 - Programa Caminhos Amefricanos: Programa de Intercâmbios Sul-Sul -  EdiçõesAngola e México, formato pdf, 435kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/01042026_Lista_Listagem_2788855_Lista_de_inscritos_Angola_e_Mexico.pdf</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FAPESB</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DIRETRIZES ESPECÍFICAS DA FAPESB – CHAMADA 2026 CONFAP – BRASILLINOIS</t>
+          <t>Edital nº 07/2026 - CAPES/Cofecub, formato, pdf, 545kb</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/diretrizes-especificas-da-fapesb-chamada-2026-confap-brasillinois/</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/30032026_EDITAL72026CAPESCOFECUB.pdf</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alteração do Edital nº 07/2026 - CAPES/Cofecub, formato, pdf, 143kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2832325_EDITAL_7_2026___ALTERACAO.pdf ; Lista de inscritos  no Edital n° 7/2026 - Programa CAPES/COFECUB, formato, pdf, 116kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Lista_Listagem_2841501_Lista_de_inscritos.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>FAPESB</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Agricultura familiar para ICTs 2026</t>
+          <t>DIRETRIZES ESPECÍFICAS DA FAPESB – CHAMADA 2026 CONFAP – BRASILLINOIS</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2004,12 +2004,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/755892</t>
+          <t>https://www.fapesb.ba.gov.br/diretrizes-especificas-da-fapesb-chamada-2026-confap-brasillinois/</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ecossistema Tecnológico de Biorrefino</t>
+          <t>Agricultura familiar para ICTs 2026</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2035,12 +2035,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/755795</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/755892</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2051,64 +2051,64 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Edital nº 06/2026 Programa Rede de Pesquisa e Desenvolvimento da Amazônia Legal - formato, pdf, 168kb</t>
+          <t>Ecossistema Tecnológico de Biorrefino</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>25/03/2026</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20032026_Edital_2787827_SEI_2787352_Edital_6_2026.pdf</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/755795</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Alteração - Edital nº 6/2026 Programa Rede de Pesquisa e Desenvolvimento da Amazônia Legal - formato, pdf, 125kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2879953_alteracao_edital_6_2026.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Prêmio Mulheres Inovadoras – 7ª edição – 2026</t>
+          <t>Edital nº 06/2026 Programa Rede de Pesquisa e Desenvolvimento da Amazônia Legal - formato, pdf, 168kb</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/755727</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20032026_Edital_2787827_SEI_2787352_Edital_6_2026.pdf</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
-      </c>
-      <c r="G56" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alteração - Edital nº 6/2026 Programa Rede de Pesquisa e Desenvolvimento da Amazônia Legal - formato, pdf, 125kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2879953_alteracao_edital_6_2026.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2118,22 +2118,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Finep Mais Inovação Brasil - Rodada 2 – Tecnologias Digitais</t>
+          <t>Prêmio Mulheres Inovadoras – 7ª edição – 2026</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/755485</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/755727</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Finep Mais Inovação Brasil – Rodada 2 – Semicondutores</t>
+          <t>Finep Mais Inovação Brasil - Rodada 2 – Tecnologias Digitais</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/755605</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/755485</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2175,23 +2175,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FAPESB</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EDITAL FAPESB N° 05/2026 MOVE 2026 – PARTICIPAÇÃO DE PESQUISADORES EM EVENTOS NO EXTERIOR</t>
+          <t>Finep Mais Inovação Brasil – Rodada 2 – Semicondutores</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>12/03/2026</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/edital-fapesb-n-052026-move-2026-participacao-de-pesquisadores-em-eventos-no-exterior/</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/755605</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2202,27 +2206,23 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>FAPESB</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Finep Mais Inovação Brasil – Rodada 2 – Mobilidade Sustentável</t>
+          <t>EDITAL FAPESB N° 05/2026 MOVE 2026 – PARTICIPAÇÃO DE PESQUISADORES EM EVENTOS NO EXTERIOR</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/755376</t>
+          <t>https://www.fapesb.ba.gov.br/edital-fapesb-n-052026-move-2026-participacao-de-pesquisadores-em-eventos-no-exterior/</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2233,23 +2233,27 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FAPESB</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Chamada Fundação de Amparo à Pesquisa da Bahia/SECTI/SEMA/FGB nº 01/2026</t>
+          <t>Finep Mais Inovação Brasil – Rodada 2 – Mobilidade Sustentável</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/chamada-fundacao-de-amparo-a-pesquisa-da-bahiasectisemafgb-no-012026/</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/755376</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2265,7 +2269,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EDITAL FAPESB/SECTI/IEL nº 004/2026 – Chamada Estratégica FAPESB/SECTI/IEL</t>
+          <t>Chamada Fundação de Amparo à Pesquisa da Bahia/SECTI/SEMA/FGB nº 01/2026</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2276,7 +2280,7 @@
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/edital-fapesbsectiiel-no-0042026-chamada-estrategica-fapesbsectiiel/</t>
+          <t>https://www.fapesb.ba.gov.br/chamada-fundacao-de-amparo-a-pesquisa-da-bahiasectisemafgb-no-012026/</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2287,64 +2291,60 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>FAPESB</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Edital nº 2/2026 - Pé-de-Meia Licenciaturas - formato, pdf, 81kb</t>
+          <t>EDITAL FAPESB/SECTI/IEL nº 004/2026 – Chamada Estratégica FAPESB/SECTI/IEL</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>16/01/2026</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/16012026_Edital_2753123_SEI_2753038_Edital_2_2026.pdf</t>
+          <t>https://www.fapesb.ba.gov.br/edital-fapesbsectiiel-no-0042026-chamada-estrategica-fapesbsectiiel/</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Alteração do edital nº 2/2026 - Pé-de-Meia Licenciaturas - formato, pdf, 55kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19022026_Edital_2769828_SEI_2769557_Edital__2_2026.pdf</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Finep Mais Inovação Brasil – Rodada 2 – Economia Circular e Cidades Sustentáveis</t>
+          <t>Edital nº 2/2026 - Pé-de-Meia Licenciaturas - formato, pdf, 81kb</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>13/02/2026</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
+          <t>16/01/2026</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/755213</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/16012026_Edital_2753123_SEI_2753038_Edital_2_2026.pdf</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1</v>
-      </c>
-      <c r="G64" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Alteração do edital nº 2/2026 - Pé-de-Meia Licenciaturas - formato, pdf, 55kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19022026_Edital_2769828_SEI_2769557_Edital__2_2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Finep Mais Inovação Brasil - Rodada 2 - Saúde / Empresas</t>
+          <t>Finep Mais Inovação Brasil – Rodada 2 – Economia Circular e Cidades Sustentáveis</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>13/02/2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/754704</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/755213</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Finep Mais Inovação Brasil - Rodada 2 - Subvenção Econômica Regional</t>
+          <t>Finep Mais Inovação Brasil - Rodada 2 - Saúde / Empresas</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/755080</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/754704</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Finep Mais Inovação Brasil – Rodada 2 - Base Industrial de Defesa</t>
+          <t>Finep Mais Inovação Brasil - Rodada 2 - Subvenção Econômica Regional</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2426,12 +2426,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/754961</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/755080</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Finep Mais Inovação Brasil – Rodada 2 – Cadeias Agroindustriais Sustentáveis</t>
+          <t>Finep Mais Inovação Brasil – Rodada 2 - Base Industrial de Defesa</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/754839</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/754961</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Finep Mais Inovação Brasil – Rodada 2 – Transformação Mineral</t>
+          <t>Finep Mais Inovação Brasil – Rodada 2 – Cadeias Agroindustriais Sustentáveis</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2488,12 +2488,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/754473</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/754839</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Finep Mais Inovação Brasil – Rodada 2 – Transição Energética</t>
+          <t>Finep Mais Inovação Brasil – Rodada 2 – Transformação Mineral</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/754567</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/754473</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2535,23 +2535,27 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FAPESB</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>DIRETRIZES ESPECÍFICAS DA FAPESB – Chamada para submissão de propostas do programa de Intercâmbio de Pessoal (MSCA SE) em coordenação com o Horizonte Europa</t>
+          <t>Finep Mais Inovação Brasil – Rodada 2 – Transição Energética</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/diretrizes-especificas-da-fapesb-chamada-para-submissao-de-propostas-do-programa-de-intercambio-de-pessoal-msca-se-em-coordenacao-com-o-horizonte-europa-2/</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/754567</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -2567,18 +2571,18 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>EDITAL FAPESB/SECTI nº 003/2026 – Apoio a Pesquisas e Inovações para a Defesa Nacional e a Segurança Pública</t>
+          <t>DIRETRIZES ESPECÍFICAS DA FAPESB – Chamada para submissão de propostas do programa de Intercâmbio de Pessoal (MSCA SE) em coordenação com o Horizonte Europa</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>20/01/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/edital-fapesbsecti-no-0032026-apoio-a-pesquisas-e-inovacoes-para-a-defesa-nacional-e-a-seguranca-publica/</t>
+          <t>https://www.fapesb.ba.gov.br/diretrizes-especificas-da-fapesb-chamada-para-submissao-de-propostas-do-programa-de-intercambio-de-pessoal-msca-se-em-coordenacao-com-o-horizonte-europa-2/</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2589,23 +2593,23 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>FAPESB</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SELEÇÃO PÚBLICA MCTI/FINEP/FNDCT - Subvenção Econômica à Inovação - DESAFIOS TECNOLÓGICOS PARA AGRICULTURA FAMILIAR</t>
+          <t>EDITAL FAPESB/SECTI nº 003/2026 – Apoio a Pesquisas e Inovações para a Defesa Nacional e a Segurança Pública</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>23/12/2025</t>
+          <t>20/01/2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/754098</t>
+          <t>https://www.fapesb.ba.gov.br/edital-fapesbsecti-no-0032026-apoio-a-pesquisas-e-inovacoes-para-a-defesa-nacional-e-a-seguranca-publica/</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -2621,22 +2625,18 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Pesquisa Aplicada Em Centros Temáticos 2025</t>
+          <t>SELEÇÃO PÚBLICA MCTI/FINEP/FNDCT - Subvenção Econômica à Inovação - DESAFIOS TECNOLÓGICOS PARA AGRICULTURA FAMILIAR</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>19/12/2025</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
+          <t>23/12/2025</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/753688</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/754098</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2652,18 +2652,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PROCESSO DE SELEÇÃO Nº 01/2025 PARA CELEBRAÇÃO DE CONVÊNIO COM ENTIDADE FECHADA DE PREVIDÊNCIA COMPLEMENTAR - EFPC</t>
+          <t>Pesquisa Aplicada Em Centros Temáticos 2025</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/753680</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/753688</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -2674,23 +2678,23 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FAPESB</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>EDITAL FAPESB Nº 030/2025 APOIO À PESQUISA CIENTÍFICA, TECNOLÓGICA E/OU DE INOVAÇÃO EM DOENÇAS E AGRAVOS PREVALENTES NA POPULAÇÃO NEGRA, COM ÊNFASE EM DOENÇA FALCIFORME E OS IMPACTOS DO RACISMO ESTRUTURAL NA SAÚDE – EDIÇÃO ANTÔNIA GARCIA</t>
+          <t>PROCESSO DE SELEÇÃO Nº 01/2025 PARA CELEBRAÇÃO DE CONVÊNIO COM ENTIDADE FECHADA DE PREVIDÊNCIA COMPLEMENTAR - EFPC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/edital-fapesb-no-0302025-apoio-a-pesquisa-cientifica-tecnologica-eou-de-inovacao-em-doencas-e-agravos-prevalentes-na-populacao-negra-com-enfase-em-doenca-falciforme-e-os-impactos-do-racismo-estrut/</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/753680</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -2701,23 +2705,23 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>FAPESB</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>FIP Bioeconomia e Sustentabilidade</t>
+          <t>EDITAL FAPESB Nº 030/2025 APOIO À PESQUISA CIENTÍFICA, TECNOLÓGICA E/OU DE INOVAÇÃO EM DOENÇAS E AGRAVOS PREVALENTES NA POPULAÇÃO NEGRA, COM ÊNFASE EM DOENÇA FALCIFORME E OS IMPACTOS DO RACISMO ESTRUTURAL NA SAÚDE – EDIÇÃO ANTÔNIA GARCIA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/752980</t>
+          <t>https://www.fapesb.ba.gov.br/edital-fapesb-no-0302025-apoio-a-pesquisa-cientifica-tecnologica-eou-de-inovacao-em-doencas-e-agravos-prevalentes-na-populacao-negra-com-enfase-em-doenca-falciforme-e-os-impactos-do-racismo-estrut/</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -2728,23 +2732,23 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>FAPESB</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Edital Nº 024/2025 Programa Nacional de Apoio à Geração de Empreendimentos Inovadores Programa Centelha 3 Bahia</t>
+          <t>FIP Bioeconomia e Sustentabilidade</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>06/11/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://www.fapesb.ba.gov.br/edital-no-0242025-programa-nacional-de-apoio-a-geracao-de-empreendimentos-inovadores-programa-centelha-3-bahia/</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/752980</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -2755,29 +2759,29 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>FAPESB</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Edital Conjunto nº 04/2024 - Programa CAMINHOS AMEFRICANOS: PROGRAMA DE INTERCÂMBIOS SUL-SUL - EDIÇÃO PERU, EDIÇÃO ANGOLA e EDIÇÃO REPÚBLICA DOMINICANA, formato pdf, 146kb</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr"/>
+          <t>Edital Nº 024/2025 Programa Nacional de Apoio à Geração de Empreendimentos Inovadores Programa Centelha 3 Bahia</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>06/11/2025</t>
+        </is>
+      </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23122024_Edital_2517683_SEI_2515663_Edital_Conjunto_4_2024.pdf/@@display-file/file</t>
+          <t>https://www.fapesb.ba.gov.br/edital-no-0242025-programa-nacional-de-apoio-a-geracao-de-empreendimentos-inovadores-programa-centelha-3-bahia/</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>6</v>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>EDITAL CONJUNTO N° 4/2024 - ALTERAÇÃO - CAMINHOS AMEFRICANOS: PROGRAMA DE INTERCÂMBIOS SUL-SUL - EDIÇÕES PERU, ANGOLA E REPÚBLICA DOMINICANA, formato, pdf, 63kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2620581_SEI_2617290_Edital_Conjunto_4_2024.pdf/@@display-file/file ; Retificação do Edital Conjunto nº 04/2024 - Programa CAMINHOS AMEFRICANOS: PROGRAMA DE INTERCÂMBIOS SUL-SUL - EDIÇÃO PERU, EDIÇÃO ANGOLA e EDIÇÃO REPÚBLICA DOMINICANA, formato pdf, 71kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/16012025_Edital_2528145_SEI_2526246_Edital_Conjunto_N__4_2024___RETIFICACAO.pdf ; Lista de Inscritos do Edital Conjunto nº 04/2024 - Peru - Programa Programa CAMINHOS AMEFRICANOS: PROGRAMA DE INTERCÂMBIOS SUL-SUL - EDIÇÃO PERU, EDIÇÃO ANGOLA e EDIÇÃO REPÚBLICA DOMINICANA, formato pdf, 443kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/06032025_Lista_Listagem_2550258_MIR_lista_de_inscritos___alterado.pdf ; Lista de Inscritos do Edital Conjunto nº 04/2024 - Angola, República Dominicana - Programa Programa CAMINHOS AMEFRICANOS: PROGRAMA DE INTERCÂMBIOS SUL-SUL - EDIÇÃO PERU, EDIÇÃO ANGOLA e EDIÇÃO REPÚBLICA DOMINICANA, formato pdf, 264kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/17032025_Lista_Listagem_2557320_Lista_de_Inscritos_Angola_e_Rep_Dominicana.pdf ; Alteração do Edital Conjunto nº 04/2024 - Programa CAMINHOS AMEFRICANOS: PROGRAMA DE INTERCÂMBIOS SUL-SUL - EDIÇÃO PERU, EDIÇÃO ANGOLA e EDIÇÃO REPÚBLICA DOMINICANA, formato pdf, 63kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/14082025_EditalConjunto42024_Alterao.pdf</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2787,26 +2791,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Edital Nº 07/2025 - CAPES/Brafitec, formato, pdf, 207kb</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>03/04/2025</t>
-        </is>
-      </c>
+          <t>Edital Conjunto nº 04/2024 - Programa CAMINHOS AMEFRICANOS: PROGRAMA DE INTERCÂMBIOS SUL-SUL - EDIÇÃO PERU, EDIÇÃO ANGOLA e EDIÇÃO REPÚBLICA DOMINICANA, formato pdf, 146kb</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/03042025_Edital_2574246_SEI_2572796_Edital_n__7_2025.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23122024_Edital_2517683_SEI_2515663_Edital_Conjunto_4_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alteração do Edital Nº 07/2025 - CAPES/Brafitec, formato, pdf, 65kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/25062025_Edital_2623304_SEI_2622327_Edital_n__7_2025___Alteracao.pdf ; Lista de Inscrições Recebidas no Programa CAPES-BRAFITEC - Edital nº 07/2025, formato, pdf, 173kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/23072025_Lista_Listagem_2636522_lista_de_inscritos___Brafitec.pdf ; Retificação da lista de Inscrições Recebidas no Programa CAPES-BRAFITEC - Edital nº 07/2025, formato, pdf, 201kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/04082025_Listagem_2643912_Lista_de_Inscritos.pdf</t>
+          <t>EDITAL CONJUNTO N° 4/2024 - ALTERAÇÃO - CAMINHOS AMEFRICANOS: PROGRAMA DE INTERCÂMBIOS SUL-SUL - EDIÇÕES PERU, ANGOLA E REPÚBLICA DOMINICANA, formato, pdf, 63kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2620581_SEI_2617290_Edital_Conjunto_4_2024.pdf/@@display-file/file ; Retificação do Edital Conjunto nº 04/2024 - Programa CAMINHOS AMEFRICANOS: PROGRAMA DE INTERCÂMBIOS SUL-SUL - EDIÇÃO PERU, EDIÇÃO ANGOLA e EDIÇÃO REPÚBLICA DOMINICANA, formato pdf, 71kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/16012025_Edital_2528145_SEI_2526246_Edital_Conjunto_N__4_2024___RETIFICACAO.pdf ; Lista de Inscritos do Edital Conjunto nº 04/2024 - Peru - Programa Programa CAMINHOS AMEFRICANOS: PROGRAMA DE INTERCÂMBIOS SUL-SUL - EDIÇÃO PERU, EDIÇÃO ANGOLA e EDIÇÃO REPÚBLICA DOMINICANA, formato pdf, 443kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/06032025_Lista_Listagem_2550258_MIR_lista_de_inscritos___alterado.pdf ; Lista de Inscritos do Edital Conjunto nº 04/2024 - Angola, República Dominicana - Programa Programa CAMINHOS AMEFRICANOS: PROGRAMA DE INTERCÂMBIOS SUL-SUL - EDIÇÃO PERU, EDIÇÃO ANGOLA e EDIÇÃO REPÚBLICA DOMINICANA, formato pdf, 264kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/17032025_Lista_Listagem_2557320_Lista_de_Inscritos_Angola_e_Rep_Dominicana.pdf ; Alteração do Edital Conjunto nº 04/2024 - Programa CAMINHOS AMEFRICANOS: PROGRAMA DE INTERCÂMBIOS SUL-SUL - EDIÇÃO PERU, EDIÇÃO ANGOLA e EDIÇÃO REPÚBLICA DOMINICANA, formato pdf, 63kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/14082025_EditalConjunto42024_Alterao.pdf</t>
         </is>
       </c>
     </row>
@@ -2818,26 +2818,26 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Edital nº 09/2025 - CAPES/Cofecub, formato, pdf, 207kb</t>
+          <t>Edital Nº 07/2025 - CAPES/Brafitec, formato, pdf, 207kb</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>09/04/2025</t>
+          <t>03/04/2025</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09042025_Edital_2578055_SEI_2577896_Edital_n__9_2025.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/03042025_Edital_2574246_SEI_2572796_Edital_n__7_2025.pdf</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Relação das inscrições Recebidas do edital nº 09/2025, formato, pdf, 304kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/25062025_Lista_Listagem_2617939_Lista_de_inscritos_25.pdf</t>
+          <t>Alteração do Edital Nº 07/2025 - CAPES/Brafitec, formato, pdf, 65kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/25062025_Edital_2623304_SEI_2622327_Edital_n__7_2025___Alteracao.pdf ; Lista de Inscrições Recebidas no Programa CAPES-BRAFITEC - Edital nº 07/2025, formato, pdf, 173kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/23072025_Lista_Listagem_2636522_lista_de_inscritos___Brafitec.pdf ; Retificação da lista de Inscrições Recebidas no Programa CAPES-BRAFITEC - Edital nº 07/2025, formato, pdf, 201kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/04082025_Listagem_2643912_Lista_de_Inscritos.pdf</t>
         </is>
       </c>
     </row>
@@ -2849,82 +2849,82 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Edital nº 15/2024 - Política de Novação para Bolsistas e Ex-Bolsistas no Exterior, formato - pdf, 133kb</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr"/>
+          <t>Edital nº 09/2025 - CAPES/Cofecub, formato, pdf, 207kb</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>09/04/2025</t>
+        </is>
+      </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/28062024_Edital_2407822_SEI_2407228_Edital_15_2024.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09042025_Edital_2578055_SEI_2577896_Edital_n__9_2025.pdf</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Prorrogação do Edital nº 15/2024 - Política de Novação para Bolsistas e Ex-Bolsistas no Exterior, formato - pdf, 60kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29102024_Edital_2486324_SEI_2485381_Edital_15_2024.pdf/@@display-file/file ; Alteração do Edital nº 15/2024 - Política de Novação para Bolsistas e Ex-Bolsistas no Exterior, formato - pdf, 61kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/06062025_Publicacao_no_DOU_2612769_SEI_2611767_Edital_15_2024.pdf</t>
+          <t>Relação das inscrições Recebidas do edital nº 09/2025, formato, pdf, 304kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/25062025_Lista_Listagem_2617939_Lista_de_inscritos_25.pdf</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>FIP Transição Energética e Descarbonização</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>04/06/2025</t>
-        </is>
-      </c>
+          <t>Edital nº 15/2024 - Política de Novação para Bolsistas e Ex-Bolsistas no Exterior, formato - pdf, 133kb</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/752871</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/28062024_Edital_2407822_SEI_2407228_Edital_15_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Prorrogação do Edital nº 15/2024 - Política de Novação para Bolsistas e Ex-Bolsistas no Exterior, formato - pdf, 60kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29102024_Edital_2486324_SEI_2485381_Edital_15_2024.pdf/@@display-file/file ; Alteração do Edital nº 15/2024 - Política de Novação para Bolsistas e Ex-Bolsistas no Exterior, formato - pdf, 61kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/06062025_Publicacao_no_DOU_2612769_SEI_2611767_Edital_15_2024.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Edital nº 05/2025 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 21kb</t>
+          <t>FIP Transição Energética e Descarbonização</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/14032025_Edital_2561854_SEI_2560981_Edital_5.pdf</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/752871</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>5</v>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Edital nº 05/2025 - ProgramaCAPES/CLIMAT-AMSUD, formato - pdf, 21kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/14032025_Edital_2561854_SEI_2560981_Edital_5.pdf ; Edital nº 05/2025 - Programa CAPES/STIC-AMSUD, formato - pdf, 21kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/14032025_Edital_2561854_SEI_2560981_Edital_5.pdf ; Lista de inscritos do Edital nº 05/2025 - Programa CAPES/MATH-AMSUD, formato - pdf, 62kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/02062025_Lista_Listagem_2602780_amsud_2025.pdf ; Lista de inscritos do Edital nº 05/2025 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 62kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/02062025_Lista_Listagem_2602780_amsud_2025.pdf</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2934,45 +2934,49 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Edital nº 10/2025 - Política de Novação para Bolsistas e Ex-Bolsistas no Exterior, formato - pdf, 102kb</t>
+          <t>Edital nº 05/2025 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 21kb</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>30/04/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/30042025_Edital_2589477_SEI_2588226_Edital_n__10_2025.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/14032025_Edital_2561854_SEI_2560981_Edital_5.pdf</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1</v>
-      </c>
-      <c r="G85" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Edital nº 05/2025 - ProgramaCAPES/CLIMAT-AMSUD, formato - pdf, 21kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/14032025_Edital_2561854_SEI_2560981_Edital_5.pdf ; Edital nº 05/2025 - Programa CAPES/STIC-AMSUD, formato - pdf, 21kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/14032025_Edital_2561854_SEI_2560981_Edital_5.pdf ; Lista de inscritos do Edital nº 05/2025 - Programa CAPES/MATH-AMSUD, formato - pdf, 62kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/02062025_Lista_Listagem_2602780_amsud_2025.pdf ; Lista de inscritos do Edital nº 05/2025 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 62kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/02062025_Lista_Listagem_2602780_amsud_2025.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Seleção de Gestor para o FIP Complexo da Saúde</t>
+          <t>Edital nº 10/2025 - Política de Novação para Bolsistas e Ex-Bolsistas no Exterior, formato - pdf, 102kb</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>07/04/2025</t>
+          <t>30/04/2025</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/752474</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/30042025_Edital_2589477_SEI_2588226_Edital_n__10_2025.pdf</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -2983,33 +2987,29 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Edital nº 1/2025 - Pé-de-Meia Licenciaturas - formato, pdf, 76kb</t>
+          <t>Seleção de Gestor para o FIP Complexo da Saúde</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>17/01/2025</t>
+          <t>07/04/2025</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/17012025_Edital_2529011_SEI_2528468_Edital_n__1_2025.pdf</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/752474</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>4</v>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Alteração do edital nº 1/2025 - Pé-de-Meia Licenciaturas - formato, pdf, 76kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07022025_Edital_2541491_SEI_2540577_Edital_1_2025.pdf ; Tornar sem efeito a alteração do edital nº 1/2025 - Pé-de-Meia Licenciaturas - formato, pdf, 142kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/17022025_Publicacao_no_DOU_2546770_EDITAL_1_2025__TORNAR_SEM_EFEITO_ALTERACAO.pdf ; Alteração do edital nº 1/2025 - Pé-de-Meia Licenciaturas - Segunda chamada - formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/04042025_Edital_2574981_SEI_2574897_Edital_1_2025.pdf</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3019,22 +3019,26 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Edital Nº 10/2023 - CAPES/Brafitec, formato, pdf, 429kb</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr"/>
+          <t>Edital nº 1/2025 - Pé-de-Meia Licenciaturas - formato, pdf, 76kb</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>17/01/2025</t>
+        </is>
+      </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/13042023_Edital_1953404_Edital_10.2023.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/17012025_Edital_2529011_SEI_2528468_Edital_n__1_2025.pdf</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lista de inscritosEdital Nº 10/2023 - CAPES/Brafitec, formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/18092023_Lista_Listagem_2234997_Lista_de_inscritos_2023.pdf/@@display-file/file ; Alteração do Edital n° 10/2023 - Brafitec, formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/27032025_Edital_2570257_SEI_2569933_Edital_N__10_2023___ALTERACAO.pdf</t>
+          <t>Alteração do edital nº 1/2025 - Pé-de-Meia Licenciaturas - formato, pdf, 76kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07022025_Edital_2541491_SEI_2540577_Edital_1_2025.pdf ; Tornar sem efeito a alteração do edital nº 1/2025 - Pé-de-Meia Licenciaturas - formato, pdf, 142kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/17022025_Publicacao_no_DOU_2546770_EDITAL_1_2025__TORNAR_SEM_EFEITO_ALTERACAO.pdf ; Alteração do edital nº 1/2025 - Pé-de-Meia Licenciaturas - Segunda chamada - formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/04042025_Edital_2574981_SEI_2574897_Edital_1_2025.pdf</t>
         </is>
       </c>
     </row>
@@ -3046,14 +3050,14 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Edital nº 11/2024 - CAPES/Brafitec, formato, pdf, 583kb</t>
+          <t>Edital Nº 10/2023 - CAPES/Brafitec, formato, pdf, 429kb</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15042024_EDITAL112024PROGRAMABRAFITEC.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/13042023_Edital_1953404_Edital_10.2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -3061,7 +3065,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lista de Inscrições Recebidas no Programa CAPES-BRAFITEC - Edital nº 11/2024, formato, pdf, 44kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/24092024_Lista_Listagem_2459366_Lista_de_Inscritos.pdf/@@display-file/file ; Alteração do Edital nº 11/2024 - CAPES/Brafitec, formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/27032025_Edital_2570314_SEI_2569939_Edital__N__11_2024___ALTERACAO.pdf</t>
+          <t>Lista de inscritosEdital Nº 10/2023 - CAPES/Brafitec, formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/18092023_Lista_Listagem_2234997_Lista_de_inscritos_2023.pdf/@@display-file/file ; Alteração do Edital n° 10/2023 - Brafitec, formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/27032025_Edital_2570257_SEI_2569933_Edital_N__10_2023___ALTERACAO.pdf</t>
         </is>
       </c>
     </row>
@@ -3073,14 +3077,14 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Edital nº 16/2024 - Programa CAPES/AUGM, formato - pdf, 235kb</t>
+          <t>Edital nº 11/2024 - CAPES/Brafitec, formato, pdf, 583kb</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/08072024_Edital_2413631_SEI_2413500_Edital_16_2024.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15042024_EDITAL112024PROGRAMABRAFITEC.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F90" t="n">
@@ -3088,40 +3092,36 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lista de inscritos do Edital nº 16/2024, formato, pdf, 174kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/30092024_Lista_Listagem_2456928_Lista_de_inscritos.pdf/@@display-file/file ; Alteração do Edital nº 16/2024 - Programa CAPES/AUGM, formato - pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/24032025_Edital_2567485_SEI_2566349_Edital_n__16_2024___Alteracao_IV.pdf</t>
+          <t>Lista de Inscrições Recebidas no Programa CAPES-BRAFITEC - Edital nº 11/2024, formato, pdf, 44kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/24092024_Lista_Listagem_2459366_Lista_de_Inscritos.pdf/@@display-file/file ; Alteração do Edital nº 11/2024 - CAPES/Brafitec, formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/27032025_Edital_2570314_SEI_2569939_Edital__N__11_2024___ALTERACAO.pdf</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Conhecimento Brasil</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>07/08/2024</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>11/09/2026</t>
-        </is>
-      </c>
+          <t>Edital nº 16/2024 - Programa CAPES/AUGM, formato - pdf, 235kb</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/749717</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/08072024_Edital_2413631_SEI_2413500_Edital_16_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>1</v>
-      </c>
-      <c r="G91" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Lista de inscritos do Edital nº 16/2024, formato, pdf, 174kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/30092024_Lista_Listagem_2456928_Lista_de_inscritos.pdf/@@display-file/file ; Alteração do Edital nº 16/2024 - Programa CAPES/AUGM, formato - pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/24032025_Edital_2567485_SEI_2566349_Edital_n__16_2024___Alteracao_IV.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3131,18 +3131,22 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Edital FIP Nordeste Capital Semente</t>
+          <t>Conhecimento Brasil</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>10/07/2024</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr"/>
+          <t>07/08/2024</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/749273</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/749717</t>
         </is>
       </c>
       <c r="F92" t="n">
@@ -3158,18 +3162,18 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SOLUÇÕES TECNOLÓGICAS PARA AUMENTO DA PRODUTIVIDADE NA AGRICULTURA FAMILIAR, AQUICULTURA E PESCA ARTESANAL</t>
+          <t>Edital FIP Nordeste Capital Semente</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>08/07/2024</t>
+          <t>10/07/2024</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/748141</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/749273</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -3185,18 +3189,18 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Chamada pública conjunta Finep e Rede Eureka 2024</t>
+          <t>SOLUÇÕES TECNOLÓGICAS PARA AUMENTO DA PRODUTIVIDADE NA AGRICULTURA FAMILIAR, AQUICULTURA E PESCA ARTESANAL</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>31/01/2024</t>
+          <t>08/07/2024</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/747009</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/748141</t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -3212,18 +3216,18 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Programa de Investimento em Startups Inovadoras 2ª Rodada</t>
+          <t>Chamada pública conjunta Finep e Rede Eureka 2024</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>21/11/2017</t>
+          <t>31/01/2024</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/721708</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/747009</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -3239,18 +3243,18 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>COOPERAÇÃO ICT-EMPRESA – 01/2017</t>
+          <t>Programa de Investimento em Startups Inovadoras 2ª Rodada</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>08/05/2017</t>
+          <t>21/11/2017</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/721088</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/721708</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -3266,18 +3270,18 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Finep / CDTI - COOPERAÇÃO ICT-EMPRESA – 01/2017</t>
+          <t>COOPERAÇÃO ICT-EMPRESA – 01/2017</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>07/05/2017</t>
+          <t>08/05/2017</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/721094</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/721088</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -3293,18 +3297,18 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Chamada Pública Bilateral Finep-CDTI</t>
+          <t>Finep / CDTI - COOPERAÇÃO ICT-EMPRESA – 01/2017</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>13/10/2015</t>
+          <t>07/05/2017</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://www.finep.gov.br/e/chamada-publica/222684/719676</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/721094</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -3315,19 +3319,23 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Alteração do Edital CAPES/DAAD Probral nº 14/2019 - pdf, 60kb</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr"/>
+          <t>Chamada Pública Bilateral Finep-CDTI</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>13/10/2015</t>
+        </is>
+      </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/24052024_Edital_2384178_SEI_2382892_Edital_14_2019___Alteracao_II.pdf/@@display-file/file</t>
+          <t>https://www.finep.gov.br/e/chamada-publica/222684/719676</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -3343,14 +3351,14 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Alteração do Edital Nº 12/2019 - CAPES/COFECUB - formato, pdf, 68kb</t>
+          <t>Alteração do Edital CAPES/DAAD Probral nº 14/2019 - pdf, 60kb</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400250_SEI_2399447_Edital_12_2019___ALTERACAO_III.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/24052024_Edital_2384178_SEI_2382892_Edital_14_2019___Alteracao_II.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -3366,14 +3374,14 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Alteração do edital nº 19/2022 -ProgramaCAPES/MATH-AMSUD, formato - pdf, 60kb</t>
+          <t>Alteração do Edital Nº 12/2019 - CAPES/COFECUB - formato, pdf, 68kb</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400204_SEI_2399434_Edital_19_2022___ALTERACAO_II.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400250_SEI_2399447_Edital_12_2019___ALTERACAO_III.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -3389,14 +3397,14 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Alteração do Edital nº 36/2017 - formato, pdf, 246kb</t>
+          <t>Alteração do edital nº 19/2022 -ProgramaCAPES/MATH-AMSUD, formato - pdf, 60kb</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/EDITAL362017_HUMBOLDT_Alterao.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400204_SEI_2399434_Edital_19_2022___ALTERACAO_II.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -3412,14 +3420,14 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Alteração Edital nº 11 - Programa Cátedra Jorge Amado, formato, pdf, 53,3kb</t>
+          <t>Alteração do Edital nº 36/2017 - formato, pdf, 246kb</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2845089_sei_2843522_edital_n__11_2026.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/EDITAL362017_HUMBOLDT_Alterao.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -3435,14 +3443,14 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Alteração Edital nº 16/2026 - Programa AURORA, formato, pdf, 982kb</t>
+          <t>Alteração Edital nº 11 - Programa Cátedra Jorge Amado, formato, pdf, 53,3kb</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2853575_edital.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2845089_sei_2843522_edital_n__11_2026.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -3458,14 +3466,14 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Chamada Pública para Envio de Proposta de Curso Novo - Edital nº 20/2026</t>
+          <t>Alteração Edital nº 16/2026 - Programa AURORA, formato, pdf, 982kb</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2844920.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2853575_edital.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F105" t="n">
@@ -3481,24 +3489,20 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Edital CAPES/DAAD Probral nº 06/2021, formato, pdf, 254kb</t>
+          <t>Chamada Pública para Envio de Proposta de Curso Novo - Edital nº 20/2026</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/EDITAL6PROBRAL.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2844920.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>Alteração do Edital CAPES/DAAD Probral nº 06/2021, formato, pdf, 67kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400395_SEI_2398543_Edital_6_2021__1_.pdf/@@display-file/file ; Lista de inscritos do Edital CAPES/DAAD Probral nº 06/2021, formato, pdf, 47kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/18062021_Edital_6_2021_PROBRAL.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3508,22 +3512,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Edital CAPES/DAAD Probral nº 09/2023, formato - pdf, 472kb</t>
+          <t>Edital CAPES/DAAD Probral nº 06/2021, formato, pdf, 254kb</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/10042023_Edital_1950397_SEI_CAPES___1950165___Edital_9_2023.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/EDITAL6PROBRAL.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alteração do Edital CAPES/DAAD Probral nº 09/2023, formato - pdf, 60kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400189_SEI_2398591_Edital_21_2022.pdf/@@display-file/file ; Relação das inscrições do Edital CAPES/DAAD Probral nº 09/2023, formato, pdf, 412kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/19072023_Lista_Listagem_2018436_Probral_23.pdf/@@display-file/file ; Alteração do EditalCAPES/DAAD Probalnº9/2023, formato, pdf, 113kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/20062023_Edital_2001190_EDITAL_9_2023_SITE.pdf/@@display-file/file</t>
+          <t>Alteração do Edital CAPES/DAAD Probral nº 06/2021, formato, pdf, 67kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400395_SEI_2398543_Edital_6_2021__1_.pdf/@@display-file/file ; Lista de inscritos do Edital CAPES/DAAD Probral nº 06/2021, formato, pdf, 47kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/18062021_Edital_6_2021_PROBRAL.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3535,22 +3539,22 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Edital CAPES/DAAD Probral nº 09/2024, formato - pdf, 630kb</t>
+          <t>Edital CAPES/DAAD Probral nº 09/2023, formato - pdf, 472kb</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/04042024_EDITAL9CAPESDAADPROBRAL.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/10042023_Edital_1950397_SEI_CAPES___1950165___Edital_9_2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lista de inscritos do Edital CAPES/DAAD Probral nº 09/2024, formato - pdf, 334kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/21062024_Lista_Listagem_2398276_probral.pdf/@@display-file/file ; Alteração do Edital CAPES/DAAD Probral nº 09/2024, formato - pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/03062024_Edital_2388049_SEI_2386684_Edital_9_2024.pdf/@@display-file/file</t>
+          <t>Alteração do Edital CAPES/DAAD Probral nº 09/2023, formato - pdf, 60kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400189_SEI_2398591_Edital_21_2022.pdf/@@display-file/file ; Relação das inscrições do Edital CAPES/DAAD Probral nº 09/2023, formato, pdf, 412kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/19072023_Lista_Listagem_2018436_Probral_23.pdf/@@display-file/file ; Alteração do EditalCAPES/DAAD Probalnº9/2023, formato, pdf, 113kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/20062023_Edital_2001190_EDITAL_9_2023_SITE.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3562,14 +3566,14 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Edital CAPES/DAAD Probral nº 21/2022, formato, pdf, 376kb</t>
+          <t>Edital CAPES/DAAD Probral nº 09/2024, formato - pdf, 630kb</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/18042022_Edital_1681234_Edital_21.22.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/04042024_EDITAL9CAPESDAADPROBRAL.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -3577,7 +3581,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alteração do Edital CAPES/DAAD Probral nº 21/2022, formato, pdf, 101kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400189_SEI_2398591_Edital_21_2022.pdf/@@display-file/file ; Relação das inscrições do Edital CAPES/DAAD Probral nº21/2022, formato, pdf, 78kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/13072022_Lista_Listagem_1748985_Probral.pdf/@@display-file/file</t>
+          <t>Lista de inscritos do Edital CAPES/DAAD Probral nº 09/2024, formato - pdf, 334kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/21062024_Lista_Listagem_2398276_probral.pdf/@@display-file/file ; Alteração do Edital CAPES/DAAD Probral nº 09/2024, formato - pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/03062024_Edital_2388049_SEI_2386684_Edital_9_2024.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3589,22 +3593,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Edital Conjunto nº 5/2026 - Programa OBEDUC-EI - Observatório da Educação Especial Inclusiva</t>
+          <t>Edital CAPES/DAAD Probral nº 21/2022, formato, pdf, 376kb</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital-no-5.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/18042022_Edital_1681234_Edital_21.22.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Edital Conjunto nº 5/2026 - Programa OBEDUC-EI, formato, pdf, 9,67mb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital-no-5.pdf/@@display-file/file</t>
+          <t>Alteração do Edital CAPES/DAAD Probral nº 21/2022, formato, pdf, 101kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400189_SEI_2398591_Edital_21_2022.pdf/@@display-file/file ; Relação das inscrições do Edital CAPES/DAAD Probral nº21/2022, formato, pdf, 78kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/13072022_Lista_Listagem_1748985_Probral.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3616,20 +3620,24 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Edital Conjunto nº 6/2026 - CAPES/CNJ - Apoio a Pesquisas Judiciárias, formato, pdf, 257kb</t>
+          <t>Edital Conjunto nº 5/2026 - Programa OBEDUC-EI - Observatório da Educação Especial Inclusiva</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2873621_sei___23038-001405_2026_81.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital-no-5.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1</v>
-      </c>
-      <c r="G111" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Edital Conjunto nº 5/2026 - Programa OBEDUC-EI, formato, pdf, 9,67mb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital-no-5.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3639,24 +3647,20 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Edital nº 02/2024 - Projetos de Cooperação entre Instituições para Qualificação de Profissionais de Nível Superior (PCI) - formato, pdf, 87kb</t>
+          <t>Edital Conjunto nº 6/2026 - CAPES/CNJ - Apoio a Pesquisas Judiciárias, formato, pdf, 257kb</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/26022024_Edital_2328837_SEI_2326326_Edital_02_2024.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2873621_sei___23038-001405_2026_81.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>2</v>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>Alteração do Edital nº 02/2024 - Projetos de Cooperação entre Instituições para Qualificação de Profissionais de Nível Superior (PCI) - formato, pdf, 54kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/16052024_Edital_2379426_SEI_2379169_Edital_02_2024.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3666,20 +3670,24 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Edital nº 039/2013 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 400kb</t>
+          <t>Edital nº 02/2024 - Projetos de Cooperação entre Instituições para Qualificação de Profissionais de Nível Superior (PCI) - formato, pdf, 87kb</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_039_2013_PDPI.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/26022024_Edital_2328837_SEI_2326326_Edital_02_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1</v>
-      </c>
-      <c r="G113" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Alteração do Edital nº 02/2024 - Projetos de Cooperação entre Instituições para Qualificação de Profissionais de Nível Superior (PCI) - formato, pdf, 54kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/16052024_Edital_2379426_SEI_2379169_Edital_02_2024.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3689,24 +3697,20 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Edital nº 05/2023 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 473kb</t>
+          <t>Edital nº 039/2013 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 400kb</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15032023_Edital_1933938_Edital_5_2023.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_039_2013_PDPI.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>3</v>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>Alteração do Edital nº 05/2023 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 60kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400239_SEI_2399449_Edital_05_2023___ALTERACAO_II.pdf/@@display-file/file ; Relação das inscrições do Edital nº 05/2023 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 571kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/30052023_Lista_Listagem_1984677_Lista_de_inscritos_Math_Amsud_Edital_5.2023.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3716,22 +3720,22 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Edital nº 05/2024 - ProgramaCAPES/CLIMAT-AMSUD, formato - pdf, 239kb</t>
+          <t>Edital nº 05/2023 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 473kb</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20032024_Edital_2343766_SEI_2342530_Edital_05_2024.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15032023_Edital_1933938_Edital_5_2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Edital nº 05/2024 - ProgramaCAPES/STIC-AMSUD, formato - pdf, 239kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20032024_Edital_2343766_SEI_2342530_Edital_05_2024.pdf/@@display-file/file ; Alteração do Edital nº 05/2024 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 57kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07052024_Edital_2373417_SEI_2372656_Edital_05_2024.pdf/@@display-file/file ; Edital nº 05/2024 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 239kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20032024_Edital_2343766_SEI_2342530_Edital_05_2024.pdf/@@display-file/file</t>
+          <t>Alteração do Edital nº 05/2023 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 60kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400239_SEI_2399449_Edital_05_2023___ALTERACAO_II.pdf/@@display-file/file ; Relação das inscrições do Edital nº 05/2023 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 571kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/30052023_Lista_Listagem_1984677_Lista_de_inscritos_Math_Amsud_Edital_5.2023.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3743,22 +3747,22 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Edital nº 06/2023 - ProgramaCAPES/STIC-AMSUD, formato - pdf, 473kb</t>
+          <t>Edital nº 05/2024 - ProgramaCAPES/CLIMAT-AMSUD, formato - pdf, 239kb</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15032023_Edital_1933950_Edital_6_2023.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20032024_Edital_2343766_SEI_2342530_Edital_05_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alteração do Edital nº 06/2023 - Programa CAPES/STIC-AMSUD, formato - pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400119_SEI_2399429_Edital_6_2023___Alteracao_II.pdf/@@display-file/file ; Relação das inscrições do Edital nº 06/2023 - Programa CAPES/STIC-AMSUD, formato - pdf, 571kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/30052023_Lista_Listagem_1984493_Lista_de_inscritos_Stic_Amsud_Edital_6.2023.pdf/@@display-file/file</t>
+          <t>Edital nº 05/2024 - ProgramaCAPES/STIC-AMSUD, formato - pdf, 239kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20032024_Edital_2343766_SEI_2342530_Edital_05_2024.pdf/@@display-file/file ; Alteração do Edital nº 05/2024 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 57kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07052024_Edital_2373417_SEI_2372656_Edital_05_2024.pdf/@@display-file/file ; Edital nº 05/2024 - ProgramaCAPES/MATH-AMSUD, formato - pdf, 239kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20032024_Edital_2343766_SEI_2342530_Edital_05_2024.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3770,22 +3774,22 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Edital nº 06/2024 - PDSE - formato, pdf, 133kb</t>
+          <t>Edital nº 06/2023 - ProgramaCAPES/STIC-AMSUD, formato - pdf, 473kb</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/21032024_Edital_2344636_SEI_2343579_Edital_6_2024.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15032023_Edital_1933950_Edital_6_2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Prorrogação do Edital nº 06/2024 - PDSE - formato, pdf, 55kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/10052024_Edital_2376323_SEI_2375557_Edital_6_2024.pdf/@@display-file/file</t>
+          <t>Alteração do Edital nº 06/2023 - Programa CAPES/STIC-AMSUD, formato - pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400119_SEI_2399429_Edital_6_2023___Alteracao_II.pdf/@@display-file/file ; Relação das inscrições do Edital nº 06/2023 - Programa CAPES/STIC-AMSUD, formato - pdf, 571kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/30052023_Lista_Listagem_1984493_Lista_de_inscritos_Stic_Amsud_Edital_6.2023.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3797,22 +3801,22 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Edital nº 07/2023 - ProgramaCAPES/CLIMAT-AMSUD, formato - pdf, 466kb</t>
+          <t>Edital nº 06/2024 - PDSE - formato, pdf, 133kb</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15032023_Edital_1933965_Edital_7_2023_.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/21032024_Edital_2344636_SEI_2343579_Edital_6_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alteração doEdital nº 07/2023 - ProgramaCAPES/CLIMAT-AMSUD, formato - pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400133_SEI_2399445_Edital_07_2023___ALTERACAO_II.pdf/@@display-file/file ; Relação das inscrições do Edital nº 07/2023 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 570kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/30052023_Lista_Listagem_1984693_Lista_de_inscritos_Climat_Amsud_Edital_7.2023.pdf/@@display-file/file</t>
+          <t>Prorrogação do Edital nº 06/2024 - PDSE - formato, pdf, 55kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/10052024_Edital_2376323_SEI_2375557_Edital_6_2024.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3824,22 +3828,22 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Edital nº 08/2023 - CAPES/Cofecub, formato, pdf, 495kb</t>
+          <t>Edital nº 07/2023 - ProgramaCAPES/CLIMAT-AMSUD, formato - pdf, 466kb</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/03042023_Edital_1946708_Edital_8_2022.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15032023_Edital_1933965_Edital_7_2023_.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alteração doEdital nº 08/2023 - CAPES/Cofecub, formato, pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20062024_Edital_2401059_SEI_2399441_Edital_08_2023___ALTERACAO_II.pdf/@@display-file/file</t>
+          <t>Alteração doEdital nº 07/2023 - ProgramaCAPES/CLIMAT-AMSUD, formato - pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400133_SEI_2399445_Edital_07_2023___ALTERACAO_II.pdf/@@display-file/file ; Relação das inscrições do Edital nº 07/2023 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 570kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/30052023_Lista_Listagem_1984693_Lista_de_inscritos_Climat_Amsud_Edital_7.2023.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3851,22 +3855,22 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Edital nº 08/2024 - CAPES/Cofecub, formato, pdf, 213kb</t>
+          <t>Edital nº 08/2023 - CAPES/Cofecub, formato, pdf, 495kb</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/22032024_Edital_2345736_SEI_2343959_Edital_8.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/03042023_Edital_1946708_Edital_8_2022.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alteração do Edital nº 08/2024 - Programa CAPES/Cofecub, formato, pdf, 54kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23122024_Edital_2517712_SEI_2516934_Edital_8_2024.pdf/@@display-file/file ; Prorrogação do Edital nº 08/2024 - CAPES/Cofecub, formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/02072024_Edital_2409554_SEI_2409272_Edital_08_2024___Prorrogacao.pdf/@@display-file/file ; Alteração do Edital nº 08/2024 - CAPES/Cofecub, formato, pdf, 57kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07052024_Edital_2373782_SEI_2372654_Edital_08_2024.pdf/@@display-file/file</t>
+          <t>Alteração doEdital nº 08/2023 - CAPES/Cofecub, formato, pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20062024_Edital_2401059_SEI_2399441_Edital_08_2023___ALTERACAO_II.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -3878,20 +3882,24 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Edital nº 10/2022 - PDSE - formato, pdf, 337kb</t>
+          <t>Edital nº 08/2024 - CAPES/Cofecub, formato, pdf, 213kb</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/16022022_Edital10.22PDSE.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/22032024_Edital_2345736_SEI_2343959_Edital_8.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>1</v>
-      </c>
-      <c r="G121" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Alteração do Edital nº 08/2024 - Programa CAPES/Cofecub, formato, pdf, 54kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23122024_Edital_2517712_SEI_2516934_Edital_8_2024.pdf/@@display-file/file ; Prorrogação do Edital nº 08/2024 - CAPES/Cofecub, formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/02072024_Edital_2409554_SEI_2409272_Edital_08_2024___Prorrogacao.pdf/@@display-file/file ; Alteração do Edital nº 08/2024 - CAPES/Cofecub, formato, pdf, 57kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07052024_Edital_2373782_SEI_2372654_Edital_08_2024.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3901,14 +3909,14 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Edital nº 14/2025 - PCI - pdf, 83kb</t>
+          <t>Edital nº 10/2022 - PDSE - formato, pdf, 337kb</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/31072025_Edital_2646654_SEI_2644987_Edital_14_2025.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/16022022_Edital10.22PDSE.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F122" t="n">
@@ -3924,24 +3932,20 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Edital nº 16/2025 - formato, pdf, 360kb</t>
+          <t>Edital nº 14/2025 - PCI - pdf, 83kb</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11082025_Edital_2654124.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/31072025_Edital_2646654_SEI_2644987_Edital_14_2025.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>2</v>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>Lista de inscritos no edital nº 16/2025 - formato, pdf, 207kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/29102025_Lista_Listagem_2693783_SEI___23038.003238_2025_21_buffalo.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3951,20 +3955,24 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Edital nº 16/2026 - Programa AURORA — Continuidade da Trajetória de Mães Cientistas</t>
+          <t>Edital nº 16/2025 - formato, pdf, 360kb</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2818271_SEI_2817084_Edital_16_2026__1_.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11082025_Edital_2654124.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>1</v>
-      </c>
-      <c r="G124" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Lista de inscritos no edital nº 16/2025 - formato, pdf, 207kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/29102025_Lista_Listagem_2693783_SEI___23038.003238_2025_21_buffalo.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3974,14 +3982,14 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Edital nº 19/2017 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 315kb</t>
+          <t>Edital nº 16/2026 - Programa AURORA — Continuidade da Trajetória de Mães Cientistas</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/31052017Edital192017PDPI.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2818271_SEI_2817084_Edital_16_2026__1_.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -3997,14 +4005,14 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Edital nº 19/2026 - Programa Capes/Universidade em Buffalo (Capes/UB) - Professor Visitante - formato, pdf, 139kb</t>
+          <t>Edital nº 19/2017 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 315kb</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2843097_SEI_2842333_Edital_n__19_2026.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/31052017Edital192017PDPI.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F126" t="n">
@@ -4020,24 +4028,20 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Edital nº 20/2022 -Programa CAPES/STIC-AMSUD, formato, pdf - 286kb</t>
+          <t>Edital nº 19/2026 - Programa Capes/Universidade em Buffalo (Capes/UB) - Professor Visitante - formato, pdf, 139kb</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07042022_Edital_1673688_EDITAL_20_2022_STIC_AMSUD.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2843097_SEI_2842333_Edital_n__19_2026.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>3</v>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>Alteração do Edital nº 20/2022 -Programa CAPES/STIC-AMSUD, formato, pdf - 67kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400177_SEI_2399435_Edital_20_2022___ALTERACAO_I.pdf/@@display-file/file ; Relação das inscrições do Edital nº 20/2022 - Programa CAPES/STIC-AMSUD, formato - pdf, 358kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/06062022_Lista_Listagem_1727082_STIC.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4047,14 +4051,14 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Edital nº 21/2023 - Projetos de Cooperação entre Instituições para Qualificação de Profissionais de Nível Superior (PCI) - formato, pdf, 281kb</t>
+          <t>Edital nº 20/2022 -Programa CAPES/STIC-AMSUD, formato, pdf - 286kb</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/24082023_Edital_2043434_Edital_21_2023.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07042022_Edital_1673688_EDITAL_20_2022_STIC_AMSUD.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -4062,7 +4066,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Retificação do Edital nº 21/2023 - Projetos de Cooperação entre Instituições para Qualificação de Profissionais de Nível Superior (PCI) - formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/01112023_Edital_2262651_SEI_2262236_Edital_21_2023.pdf/@@display-file/file ; Alteração do Edital nº 21/2023 - Projetos de Cooperação entre Instituições para Qualificação de Profissionais de Nível Superior (PCI) - formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/31102023_Edital_2261925_SEI_2261451_Edital_22_2023.pdf/@@display-file/file</t>
+          <t>Alteração do Edital nº 20/2022 -Programa CAPES/STIC-AMSUD, formato, pdf - 67kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400177_SEI_2399435_Edital_20_2022___ALTERACAO_I.pdf/@@display-file/file ; Relação das inscrições do Edital nº 20/2022 - Programa CAPES/STIC-AMSUD, formato - pdf, 358kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/06062022_Lista_Listagem_1727082_STIC.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4074,20 +4078,24 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Edital nº 21/2026 - Programa de Desenvolvimento da Pós-Graduação (PDPG) – Parcerias Estratégicas nos Estados VI – Rede de Pesquisa e Desenvolvimento da Região Nordeste, formato, pdf, 177kb</t>
+          <t>Edital nº 21/2023 - Projetos de Cooperação entre Instituições para Qualificação de Profissionais de Nível Superior (PCI) - formato, pdf, 281kb</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2848691_sei_2847430_edital_n__21_2026.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/24082023_Edital_2043434_Edital_21_2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>1</v>
-      </c>
-      <c r="G129" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Retificação do Edital nº 21/2023 - Projetos de Cooperação entre Instituições para Qualificação de Profissionais de Nível Superior (PCI) - formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/01112023_Edital_2262651_SEI_2262236_Edital_21_2023.pdf/@@display-file/file ; Alteração do Edital nº 21/2023 - Projetos de Cooperação entre Instituições para Qualificação de Profissionais de Nível Superior (PCI) - formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/31102023_Edital_2261925_SEI_2261451_Edital_22_2023.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4097,24 +4105,20 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Edital nº 22/2026 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 150kb</t>
+          <t>Edital nº 21/2026 - Programa de Desenvolvimento da Pós-Graduação (PDPG) – Parcerias Estratégicas nos Estados VI – Rede de Pesquisa e Desenvolvimento da Região Nordeste, formato, pdf, 177kb</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/sei_2849220_edital_n__22_2026.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2848691_sei_2847430_edital_n__21_2026.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>2</v>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>Alteração Edital nº 22/2026 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 47,4kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2858430_sei_2857160_edital_22_2026___alteracao.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4124,22 +4128,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Edital nº 23/2026 - Programa de Desenvolvimento Acadêmico Indígena (PDAI), formato, pdf, 168kb</t>
+          <t>Edital nº 22/2026 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 150kb</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2851776_sei_2851450_edital_n__23_2026.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/sei_2849220_edital_n__22_2026.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alteração Edital nº 23/2026 - Programa de Desenvolvimento Acadêmico Indígena (PDAI), formato, pdf, 102kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2872644_edital_conjunto_23_2026___alteracao.pdf/@@display-file/file ; Relação dos Programas de Pós-Graduação (PPGs) - Edital nº 23/2026 - Programa de Desenvolvimento Acadêmico Indígena (PDAI), formato, pdf, 1.836kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/resultado_2881142_pdai_divulgacao_ppgs_bolsas_v-final_13-08-2026.pdf/@@display-file/file</t>
+          <t>Alteração Edital nº 22/2026 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 47,4kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2858430_sei_2857160_edital_22_2026___alteracao.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4151,22 +4155,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Edital nº 23/2026 - Programa Nacional de Formação de Professores da Educação Básica (PARFOR), formato, pdf, 168kb</t>
+          <t>Edital nº 23/2026 - Programa de Desenvolvimento Acadêmico Indígena (PDAI), formato, pdf, 168kb</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2855421_sei_2854365_edital_n__23_2026.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2851776_sei_2851450_edital_n__23_2026.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alteração Edital nº 23/2026 - Programa Nacional de Formação de Professores da Educação Básica (PARFOR), formato, pdf, 130kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2875930_edital_23_2026___alteracao.pdf/@@display-file/file</t>
+          <t>Alteração Edital nº 23/2026 - Programa de Desenvolvimento Acadêmico Indígena (PDAI), formato, pdf, 102kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2872644_edital_conjunto_23_2026___alteracao.pdf/@@display-file/file ; Relação dos Programas de Pós-Graduação (PPGs) - Edital nº 23/2026 - Programa de Desenvolvimento Acadêmico Indígena (PDAI), formato, pdf, 1.836kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/resultado_2881142_pdai_divulgacao_ppgs_bolsas_v-final_13-08-2026.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4178,20 +4182,24 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Edital nº 24/2026 - Cooperação entre Instituições para</t>
+          <t>Edital nº 23/2026 - Programa Nacional de Formação de Professores da Educação Básica (PARFOR), formato, pdf, 168kb</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2878169_edital_24_2026___pci.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2855421_sei_2854365_edital_n__23_2026.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>1</v>
-      </c>
-      <c r="G133" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Alteração Edital nº 23/2026 - Programa Nacional de Formação de Professores da Educação Básica (PARFOR), formato, pdf, 130kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2875930_edital_23_2026___alteracao.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4201,24 +4209,20 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Edital nº 25/2022 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 353kb</t>
+          <t>Edital nº 24/2026 - Cooperação entre Instituições para</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/04052022_Edital_1698011_SEI_CAPES___1696119___Edital_25.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2878169_edital_24_2026___pci.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>3</v>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>Alteração do edital nº 25/2022 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 67kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400217_SEI_2399433_Edital_25_2022___ALTERACAO_I.pdf/@@display-file/file ; Relação das inscrições do Edital nº 25/2022 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 353kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/06062022_Lista_Listagem_1727108_Climat.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4228,22 +4232,22 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Edital nº 25/2024 - Chamada Pública para envio de Proposta de Projeto de Cooperação entre Instituições para Qualificação de Profissionais de Nível Superior (PCI) - formato, pdf, 83kb</t>
+          <t>Edital nº 25/2022 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 353kb</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/17092024_Edital_2461148_SEI_2460992_Edital_25_2024.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/04052022_Edital_1698011_SEI_CAPES___1696119___Edital_25.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alteração do Edital nº 25/2024 - Chamada Pública para envio de Proposta de Projeto de Cooperação entre Instituições para Qualificação de Profissionais de Nível Superior (PCI) - formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/10122024_Edital_2510251_SEI_2508924_Edital_25_2024___Alteracao.pdf/@@display-file/file</t>
+          <t>Alteração do edital nº 25/2022 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 67kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400217_SEI_2399433_Edital_25_2022___ALTERACAO_I.pdf/@@display-file/file ; Relação das inscrições do Edital nº 25/2022 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 353kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/06062022_Lista_Listagem_1727108_Climat.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4255,20 +4259,24 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Edital nº 25/2026 - Edição 2027, formato, pdf, 145kb</t>
+          <t>Edital nº 25/2024 - Chamada Pública para envio de Proposta de Projeto de Cooperação entre Instituições para Qualificação de Profissionais de Nível Superior (PCI) - formato, pdf, 83kb</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2886643_sei_2886062_edital_n___25_2026.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/17092024_Edital_2461148_SEI_2460992_Edital_25_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>1</v>
-      </c>
-      <c r="G136" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Alteração do Edital nº 25/2024 - Chamada Pública para envio de Proposta de Projeto de Cooperação entre Instituições para Qualificação de Profissionais de Nível Superior (PCI) - formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/10122024_Edital_2510251_SEI_2508924_Edital_25_2024___Alteracao.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4278,24 +4286,20 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Edital nº 26/2024 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE) - Retificação - formato, pdf, 48kb</t>
+          <t>Edital nº 25/2026 - Edição 2027, formato, pdf, 145kb</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/14102024_Edital_2477735_SEI_2477608_Edital_N__26_2024.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/edital_2886643_sei_2886062_edital_n___25_2026.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>3</v>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>Alteração do Edital nº 26/2024 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE), formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/13032025_Edital_2560841_SEI_2559847_Edital_26_2024___ALTERACAO.pdf/@@display-file/file ; Edital nº 26/2024 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 135kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/08102024_Edital_2474014_SEI_2472849_Edital_26_2024.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4305,22 +4309,22 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Edital nº 27/2024 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 157kb</t>
+          <t>Edital nº 26/2024 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE) - Retificação - formato, pdf, 48kb</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/05112024_Edital_2490387_SEI_2489251_Edital_27_2024.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/14102024_Edital_2477735_SEI_2477608_Edital_N__26_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alteração do Edital 27/2024 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa no EUA - PDPI - formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/02122024_Edital_2505290_SEI_2504109_Edital_27_2024__.pdf/@@display-file/file</t>
+          <t>Alteração do Edital nº 26/2024 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE), formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/13032025_Edital_2560841_SEI_2559847_Edital_26_2024___ALTERACAO.pdf/@@display-file/file ; Edital nº 26/2024 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 135kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/08102024_Edital_2474014_SEI_2472849_Edital_26_2024.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4332,22 +4336,22 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Edital nº 30/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 110kb</t>
+          <t>Edital nº 27/2024 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 157kb</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/14022020_Edital_1145537_Edital_SITE.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/05112024_Edital_2490387_SEI_2489251_Edital_27_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Reabertura e alteração do Edital nº 30/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 222kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/28042022_Edital_1691552_SEI_CAPES___1685746___Edital_30_2019.pdf/@@display-file/file ; Suspensão do Edital nº 30/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 111kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_1326070_Edital_Suspensao_site.pdf/@@display-file/file</t>
+          <t>Alteração do Edital 27/2024 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa no EUA - PDPI - formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/02122024_Edital_2505290_SEI_2504109_Edital_27_2024__.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4359,14 +4363,14 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Edital nº 30/2023 - PDSE - formato, pdf, 125kb</t>
+          <t>Edital nº 30/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 110kb</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/06112023_Edital_2263037_SEI_2261948_Edital_30_2023.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/14022020_Edital_1145537_Edital_SITE.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F140" t="n">
@@ -4374,7 +4378,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Prorrogação do Edital nº 30/2023 - PDSE - formato, pdf, 136kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11012024_Edital_2306448_SEI_CAPES___2305414___Edital_30_2023___Prorrogacao.pdf/@@display-file/file ; Alteração do Edital nº 30/2023 - PDSE - formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/18122023_Edital_2293491_SEI_2293429_Edital_30_2023_Alteracao.pdf/@@display-file/file</t>
+          <t>Reabertura e alteração do Edital nº 30/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 222kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/28042022_Edital_1691552_SEI_CAPES___1685746___Edital_30_2019.pdf/@@display-file/file ; Suspensão do Edital nº 30/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 111kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_1326070_Edital_Suspensao_site.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4386,14 +4390,14 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Edital Nº 32/2022 - CAPES/Cofecub, formato, pdf, 225kb</t>
+          <t>Edital nº 30/2023 - PDSE - formato, pdf, 125kb</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29062022_EDITAL32_2022_COFECUB.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/06112023_Edital_2263037_SEI_2261948_Edital_30_2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F141" t="n">
@@ -4401,7 +4405,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alteração do Edital Nº 32/2022 - CAPES/Cofecub, formato, pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400143_SEI_2399437_Edital_32_2022___ALTERACAO_III.pdf/@@display-file/file ; Relação de inscritos do Edital Nº 32/2022 - CAPES/Cofecub, formato, pdf, 65kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/25082022_Lista_Listagem_1783309_EDITAL_32_2022___CAPES_COFECUB_Relacao_de_Inscricoes.pdf/@@display-file/file</t>
+          <t>Prorrogação do Edital nº 30/2023 - PDSE - formato, pdf, 136kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/11012024_Edital_2306448_SEI_CAPES___2305414___Edital_30_2023___Prorrogacao.pdf/@@display-file/file ; Alteração do Edital nº 30/2023 - PDSE - formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/18122023_Edital_2293491_SEI_2293429_Edital_30_2023_Alteracao.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4417,22 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Edital nº 32/2023 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 139kb</t>
+          <t>Edital Nº 32/2022 - CAPES/Cofecub, formato, pdf, 225kb</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/16112023_Edital_2271416_SEI_2268914_Edital_32_2023.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29062022_EDITAL32_2022_COFECUB.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alteração do Edital nº 32/2023 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 57kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09022024_SEI_2321458_Edital_N__32_2023___ALTERACAOPDPI.pdf/@@display-file/file</t>
+          <t>Alteração do Edital Nº 32/2022 - CAPES/Cofecub, formato, pdf, 68kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/19062024_Edital_2400143_SEI_2399437_Edital_32_2022___ALTERACAO_III.pdf/@@display-file/file ; Relação de inscritos do Edital Nº 32/2022 - CAPES/Cofecub, formato, pdf, 65kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/25082022_Lista_Listagem_1783309_EDITAL_32_2022___CAPES_COFECUB_Relacao_de_Inscricoes.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4440,20 +4444,24 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Edital nº 35/2011 - Certificação em Língua Inglesa - pdf, 615kb</t>
+          <t>Edital nº 32/2023 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 139kb</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_035_CertificacaoEUAprofLingIngl_Fulbright.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/16112023_Edital_2271416_SEI_2268914_Edital_32_2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>1</v>
-      </c>
-      <c r="G143" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Alteração do Edital nº 32/2023 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 57kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09022024_SEI_2321458_Edital_N__32_2023___ALTERACAOPDPI.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4463,14 +4471,14 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Edital nº 4/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 270kb</t>
+          <t>Edital nº 35/2011 - Certificação em Língua Inglesa - pdf, 615kb</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/08022019Edital4.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_035_CertificacaoEUAprofLingIngl_Fulbright.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F144" t="n">
@@ -4486,24 +4494,20 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Edital nº 44/2012 - Programa de Aperfeiçoamento para Professores de Língua Inglesa nos Eua, pdf, 272kb</t>
+          <t>Edital nº 4/2019 - Programa de Desenvolvimento Profissional para Professores de Língua Inglesa nos EUA - PDPI - pdf, 270kb</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_0442012_ProfLingIngl_EUA.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/08022019Edital4.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>3</v>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>Edital nº 44/2012 - Retificado - pdf, 528kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_0442012_ProfLIngRetif.pdf/@@display-file/file ; Retificação do Edital nº 44/2012 - pdf, 46kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/RetificacaoEdital442012_ProfLingInglEUA_01out12.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4513,22 +4517,22 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Edital nº 44/2022 - PDSE - formato, pdf, 337kb</t>
+          <t>Edital nº 44/2012 - Programa de Aperfeiçoamento para Professores de Língua Inglesa nos Eua, pdf, 272kb</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/22122022_Edital_1882688_Edital_44_2022.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_0442012_ProfLingIngl_EUA.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alteração do Edital nº 44/2022 - PDSE - formato, pdf, 146kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23052023_Edital_1981709_Edital_44_2023.pdf/@@display-file/file</t>
+          <t>Edital nº 44/2012 - Retificado - pdf, 528kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_0442012_ProfLIngRetif.pdf/@@display-file/file ; Retificação do Edital nº 44/2012 - pdf, 46kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/RetificacaoEdital442012_ProfLingInglEUA_01out12.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4540,20 +4544,24 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Edital nº 52/2010 - Certificação em Língua Inglesa, pdf, 60kbDF</t>
+          <t>Edital nº 44/2022 - PDSE - formato, pdf, 337kb</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_52_Certificacao_LinguaInglesa2010.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/22122022_Edital_1882688_Edital_44_2022.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1</v>
-      </c>
-      <c r="G147" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Alteração do Edital nº 44/2022 - PDSE - formato, pdf, 146kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23052023_Edital_1981709_Edital_44_2023.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4563,24 +4571,20 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Edital Nº09/2026 - Programa CAPES/BRAFITEC, formato, pdf, 209kb</t>
+          <t>Edital nº 52/2010 - Certificação em Língua Inglesa, pdf, 60kbDF</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2800035_SEI_2799041_Edital_9__de_2026.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Edital_52_Certificacao_LinguaInglesa2010.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>2</v>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>Edital n° 9/2026 - Lista de Inscritos, formato, pdf, 398kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/lista_listagem_2864548_sei_2863010_edital_minuta__.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4590,22 +4594,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Edital PAEP nº 06/2022 - formato, pdf, 331kb</t>
+          <t>Edital Nº09/2026 - Programa CAPES/BRAFITEC, formato, pdf, 209kb</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/02022022_Edital_1626836_SEI_CAPES___1626182___Edita_6.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2800035_SEI_2799041_Edital_9__de_2026.pdf</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alteração do Edital PAEP nº 06/2022 - formato, pdf, 80kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15062022_Edital_1733665_Edital_6_2022.pdf/@@display-file/file ; Reabertura do Edital PAEP nº 06/2022 - formato, pdf, 112kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/24032022_Edital_1661092_Edital_6.2022_reabertura.pdf/@@display-file/file</t>
+          <t>Edital n° 9/2026 - Lista de Inscritos, formato, pdf, 398kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/lista_listagem_2864548_sei_2863010_edital_minuta__.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4617,22 +4621,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Edital PAEP nº 11/2023 - formato, pdf, 264kb</t>
+          <t>Edital PAEP nº 06/2022 - formato, pdf, 331kb</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20042023_Edital_1959492_SEI_CAPES___1959158___Edital_11_2023.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/02022022_Edital_1626836_SEI_CAPES___1626182___Edita_6.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alteração doEdital PAEP nº 11/2023 - formato, pdf, 154kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/08092023_EDITAL112023ALTERAO.pdf/@@display-file/file</t>
+          <t>Alteração do Edital PAEP nº 06/2022 - formato, pdf, 80kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15062022_Edital_1733665_Edital_6_2022.pdf/@@display-file/file ; Reabertura do Edital PAEP nº 06/2022 - formato, pdf, 112kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/24032022_Edital_1661092_Edital_6.2022_reabertura.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4644,14 +4648,14 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Edital PAEP nº 19/2025 - formato, pdf, 136kb</t>
+          <t>Edital PAEP nº 11/2023 - formato, pdf, 264kb</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/12092025_Edital_2679718_SEI_2669828_Edital_19_2025.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20042023_Edital_1959492_SEI_CAPES___1959158___Edital_11_2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -4659,7 +4663,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alteração do edital PAEP nº 19/2025 - formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23102025_Edital_2706985_SEI_2706736_Edital_n__19_2025___ALTERACAO.pdf/@@display-file/file</t>
+          <t>Alteração doEdital PAEP nº 11/2023 - formato, pdf, 154kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/08092023_EDITAL112023ALTERAO.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4671,14 +4675,14 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Edital PAEP nº 22/2024 - Alteração - formato, pdf, 47kb</t>
+          <t>Edital PAEP nº 19/2025 - formato, pdf, 136kb</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2473082_SEI_2472594_Edital_22_2024___ALTERACAO.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/12092025_Edital_2679718_SEI_2669828_Edital_19_2025.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4686,7 +4690,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Edital PAEP nº 22/2024 - formato, pdf, 126kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/10092024_Edital_2457107_SEI_2457028_Edital_22_2024.pdf/@@display-file/file</t>
+          <t>Alteração do edital PAEP nº 19/2025 - formato, pdf, 51kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23102025_Edital_2706985_SEI_2706736_Edital_n__19_2025___ALTERACAO.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4698,20 +4702,24 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Edital PAEP nº 37/2023 - formato, pdf, 264kb</t>
+          <t>Edital PAEP nº 22/2024 - Alteração - formato, pdf, 47kb</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20122023_Edital_2295422_SEI_2295394_Edital_37_2023.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/Edital_2473082_SEI_2472594_Edital_22_2024___ALTERACAO.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1</v>
-      </c>
-      <c r="G153" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Edital PAEP nº 22/2024 - formato, pdf, 126kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/10092024_Edital_2457107_SEI_2457028_Edital_22_2024.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4721,24 +4729,20 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Edital PDSE nº 17/2025 – segunda chamada – relação de aprovadas na análise técnica após a análise dos recursos - formato, pdf, 1,438kb</t>
+          <t>Edital PAEP nº 37/2023 - formato, pdf, 264kb</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/lista_listagem_2878471_listagem_resultado_final_pdse_segunda_chamada.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20122023_Edital_2295422_SEI_2295394_Edital_37_2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>5</v>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>Lista de inscrições do Edital nº 17/2025 - Segunda chamada Programa Institucional de Doutorado Sanduíche no Exterior (PDSE) - formato, pdf, 1,4mb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/27042026_Lista_Listagem_2808119_Lista_de_inscricoes_homologadas_do_Edital_172025___PDSE___segunda_chamada___formato_pdf__2_.pdf/@@display-file/file ; Lista de inscrições do Edital nº 17/2025 - Primeira chamada Programa Institucional de Doutorado Sanduíche no Exterior (PDSE) - formato, pdf, 8,8mb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/29102025_Lista_Listagem_2708089_PDSE.pdf/@@display-file/file ; Alteração do Edital nº 17/2025 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE), formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/08102025_Edital_2696973_SEI_2695934_Edital_17_2025__.pdf/@@display-file/file ; Edital nº 17/2025 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 142kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/21082025_Edital_2662823_SEI_2661209_Edital_n__17_2025.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4748,22 +4752,22 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Lista de inscritos do Edital Conjunto nº 01/2024 - Programa Caminhos Amefricanos, formato, pdf, 407kb</t>
+          <t>Edital PDSE nº 17/2025 – segunda chamada – relação de aprovadas na análise técnica após a análise dos recursos - formato, pdf, 1,438kb</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15052024_Lista_Listagem_2374115_Inscritos_MIR.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/lista_listagem_2878471_listagem_resultado_final_pdse_segunda_chamada.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alteração do Edital Conjunto nº 01/2024 - Programa Caminhos Amefricanos, formato, pdf, 63kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29042024_Edital_2368101_SEI_2365347_Edital_Conjunto_n__1_CAPES_MIR.pdf/@@display-file/file</t>
+          <t>Lista de inscrições do Edital nº 17/2025 - Segunda chamada Programa Institucional de Doutorado Sanduíche no Exterior (PDSE) - formato, pdf, 1,4mb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/27042026_Lista_Listagem_2808119_Lista_de_inscricoes_homologadas_do_Edital_172025___PDSE___segunda_chamada___formato_pdf__2_.pdf/@@display-file/file ; Lista de inscrições do Edital nº 17/2025 - Primeira chamada Programa Institucional de Doutorado Sanduíche no Exterior (PDSE) - formato, pdf, 8,8mb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/29102025_Lista_Listagem_2708089_PDSE.pdf/@@display-file/file ; Alteração do Edital nº 17/2025 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE), formato, pdf, 52kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/08102025_Edital_2696973_SEI_2695934_Edital_17_2025__.pdf/@@display-file/file ; Edital nº 17/2025 - Programa Institucional de Doutorado Sanduíche no Exterior (PDSE)- formato, pdf, 142kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/21082025_Edital_2662823_SEI_2661209_Edital_n__17_2025.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4775,20 +4779,24 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Lista de inscritos do Edital nº 05/2024 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 46kb</t>
+          <t>Lista de inscritos do Edital Conjunto nº 01/2024 - Programa Caminhos Amefricanos, formato, pdf, 407kb</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/10062024_Lista_Listagem_2390159_Lista_de_Inscritos_3.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/15052024_Lista_Listagem_2374115_Inscritos_MIR.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>1</v>
-      </c>
-      <c r="G156" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Alteração do Edital Conjunto nº 01/2024 - Programa Caminhos Amefricanos, formato, pdf, 63kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29042024_Edital_2368101_SEI_2365347_Edital_Conjunto_n__1_CAPES_MIR.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4798,14 +4806,14 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Lista de inscritos doEdital nº 8/202 - CAPES/COFECUB, formato, pdf, 581kb</t>
+          <t>Lista de inscritos do Edital nº 05/2024 - Programa CAPES/CLIMAT-AMSUD, formato - pdf, 46kb</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/14062023_Lista_Listagem_1990268_Inscricoes_cofecub_2023.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/10062024_Lista_Listagem_2390159_Lista_de_Inscritos_3.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F157" t="n">
@@ -4821,24 +4829,20 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Lista de inscrições - Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 393kb</t>
+          <t>Lista de inscritos doEdital nº 8/202 - CAPES/COFECUB, formato, pdf, 581kb</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Lista_de_Inscricoes_Homologadas_PDSE___2020_REVISADA.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/14062023_Lista_Listagem_1990268_Inscricoes_cofecub_2023.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>4</v>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>Lista de candidaturas - Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 417kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/documentos/diretoria-de-relacoes-internacionais/pdse/Lista_Listagem_1439062_Lista_de_Inscricoes_Homologadas_PDSE___2020.pdf/@@display-file/file ; Retificação do Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 244kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/EDITAL192020_PDSERETIFICAO.pdf/@@display-file/file ; Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE)- formato, pdf, 236kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09102020_edital-19-pdse.pdf/@@display-file/file</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4848,14 +4852,14 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Lista de instituições e cursos pré-aprovados para a 3ª fase do Edital nº 08/2022 - Parfor - formato, pdf, 715kb</t>
+          <t>Lista de inscrições - Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 393kb</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/06052022_Relacao_1700579_LISTA_DE_IES_E_CURSOS_APROVADOS_PARA_A_3__ETAPA_DO_EDITAL_CAPES_N__08.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/Lista_de_Inscricoes_Homologadas_PDSE___2020_REVISADA.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F159" t="n">
@@ -4863,7 +4867,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alteraçãodo Edital nº 08/2022 - Parfor - formato, xls, 119kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20122022_Edital_1880841_Edital_8_2022___PARFOR.pdf/@@display-file/file ; Alteração do Edital nº 08/2022 - Parfor - formato, pdf, 128kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09062022_Edital_1729649_EDITAL___8_2022.pdf/@@display-file/file ; Edital nº 08/2022 - Parfor - formato, pdf, 203kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07022022_Edital_1629612_SEI_CAPES___1628279___Edital_8.pdf/@@display-file/file</t>
+          <t>Lista de candidaturas - Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 417kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/documentos/diretoria-de-relacoes-internacionais/pdse/Lista_Listagem_1439062_Lista_de_Inscricoes_Homologadas_PDSE___2020.pdf/@@display-file/file ; Retificação do Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE) - formato, pdf, 244kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/EDITAL192020_PDSERETIFICAO.pdf/@@display-file/file ; Edital nº 19/2020 - Programa Doutorado-sanduíche no Exterior (PDSE)- formato, pdf, 236kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09102020_edital-19-pdse.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4875,14 +4879,14 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Lista e inscritos do Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 520kb</t>
+          <t>Lista de instituições e cursos pré-aprovados para a 3ª fase do Edital nº 08/2022 - Parfor - formato, pdf, 715kb</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/20022024_Lista_Listagem_2324280_SEI_2323841_Inscritos_MIR.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/06052022_Relacao_1700579_LISTA_DE_IES_E_CURSOS_APROVADOS_PARA_A_3__ETAPA_DO_EDITAL_CAPES_N__08.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F160" t="n">
@@ -4890,7 +4894,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alteração do Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 54kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/12062024_Edital_2395239_SEI_2389783_Edital_34_2023.pdf/@@display-file/file ; Prorrogação do Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 54kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/28122023_Edital_2301024_SEI_2300438_Edital_Conjunto_n__34_2023_Prorrogacao.pdf/@@display-file/file ; Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 129kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/04122024_Edital_2282364_SEI_2279471_Edital_Conjunto_n__34_2023.pdf/@@display-file/file</t>
+          <t>Alteraçãodo Edital nº 08/2022 - Parfor - formato, xls, 119kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/20122022_Edital_1880841_Edital_8_2022___PARFOR.pdf/@@display-file/file ; Alteração do Edital nº 08/2022 - Parfor - formato, pdf, 128kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/09062022_Edital_1729649_EDITAL___8_2022.pdf/@@display-file/file ; Edital nº 08/2022 - Parfor - formato, pdf, 203kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/07022022_Edital_1629612_SEI_CAPES___1628279___Edital_8.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4902,22 +4906,22 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Lista final de inscritos no Edital n° 33/2022 - Brafitec, formato, pdf, 372kb</t>
+          <t>Lista e inscritos do Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 520kb</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/22092022_Lista_Listagem_1808291_Lista_inscritos_Brafitec_Edital_33_22.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/resultados-dos-editais/20022024_Lista_Listagem_2324280_SEI_2323841_Inscritos_MIR.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alteração do Edital n° 33/2022 - Brafitec, formato, pdf, 193kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23022023_Edital_1920292_Edital_33_22.pdf/@@display-file/file ; Edital n° 33/2022 - Brafitec, formato, pdf, 428kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29062022_EDITAL33_2022_BRAFITEC.pdf/@@display-file/file</t>
+          <t>Alteração do Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 54kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/12062024_Edital_2395239_SEI_2389783_Edital_34_2023.pdf/@@display-file/file ; Prorrogação do Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 54kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/28122023_Edital_2301024_SEI_2300438_Edital_Conjunto_n__34_2023_Prorrogacao.pdf/@@display-file/file ; Edital nº 34/2023 - Programa Caminhos Amefricanos, formato, pdf, 129kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/04122024_Edital_2282364_SEI_2279471_Edital_Conjunto_n__34_2023.pdf/@@display-file/file</t>
         </is>
       </c>
     </row>
@@ -4929,37 +4933,41 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Prorrogação do Edital nº 01/2024 - Programa Caminhos Amefricanos, formato, pdf, 69kb</t>
+          <t>Lista final de inscritos no Edital n° 33/2022 - Brafitec, formato, pdf, 372kb</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/30082024_Edital_2450719_SEI_2446271_Edital_Conjunto_1_2024.pdf/@@display-file/file</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/22092022_Lista_Listagem_1808291_Lista_inscritos_Brafitec_Edital_33_22.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>1</v>
-      </c>
-      <c r="G162" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Alteração do Edital n° 33/2022 - Brafitec, formato, pdf, 193kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/23022023_Edital_1920292_Edital_33_22.pdf/@@display-file/file ; Edital n° 33/2022 - Brafitec, formato, pdf, 428kb | https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/29062022_EDITAL33_2022_BRAFITEC.pdf/@@display-file/file</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>SETEC</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Chamada (documento Nº 6991254) para seleção de unidades da Rede Federal de Educação Profissional e Tecnológica e das redes públicas estaduais de Educação Profissional e Tecnológica, interessadas em receber apoio técnico para a implementação de programas de aprendizagem profissional articulados a cursos técnicos ou de qualificação profissional com componentes curriculares relacionados à sustentabilidade</t>
+          <t>Prorrogação do Edital nº 01/2024 - Programa Caminhos Amefricanos, formato, pdf, 69kb</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2026/SEI_6991254_chamada.pdf</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/editais/30082024_Edital_2450719_SEI_2446271_Edital_Conjunto_1_2024.pdf/@@display-file/file</t>
         </is>
       </c>
       <c r="F163" t="n">
@@ -4975,7 +4983,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Chamada (documento Nº 6991254) para seleção de unidades da Rede Federal de Educação Profissional e Tecnológica e das redes públicas estaduais de Educação Profissional e Tecnológica, interessadas em receber apoio técnico para a implementação de programas de aprendizagem profissional articulados a cursos técnicos ou de qualificação profissional com componentes curriculares relacionados à sustentabilidade.</t>
+          <t>Chamada (documento Nº 6991254) para seleção de unidades da Rede Federal de Educação Profissional e Tecnológica e das redes públicas estaduais de Educação Profissional e Tecnológica, interessadas em receber apoio técnico para a implementação de programas de aprendizagem profissional articulados a cursos técnicos ou de qualificação profissional com componentes curriculares relacionados à sustentabilidade</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -4998,14 +5006,14 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Chamada Pública com o objetivo de identificar, avaliar, cadastrar e disponibilizar metodologias, ferramentas e estudos sobre o mapeamento de demandas por Educação Profissional Técnica de Nível Médio, visando aprimorar a definição de ofertas de Educação Profissional Técnica de Nível Médio, no âmbito do Programa Juros por Educação.</t>
+          <t>Chamada (documento Nº 6991254) para seleção de unidades da Rede Federal de Educação Profissional e Tecnológica e das redes públicas estaduais de Educação Profissional e Tecnológica, interessadas em receber apoio técnico para a implementação de programas de aprendizagem profissional articulados a cursos técnicos ou de qualificação profissional com componentes curriculares relacionados à sustentabilidade.</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/SEI_6268868_Resultado_de_Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2026/SEI_6991254_chamada.pdf</t>
         </is>
       </c>
       <c r="F165" t="n">
@@ -5021,14 +5029,14 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Chamada Pública de Adesão das Instituições da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT), com objetivo de capacitação técnica para submissão de propostas em futuros editais de unidades Embrapii.</t>
+          <t>Chamada Pública com o objetivo de identificar, avaliar, cadastrar e disponibilizar metodologias, ferramentas e estudos sobre o mapeamento de demandas por Educação Profissional Técnica de Nível Médio, visando aprimorar a definição de ofertas de Educação Profissional Técnica de Nível Médio, no âmbito do Programa Juros por Educação.</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/edital-2025/SEI_MEC5650163ResultadodeEdital_.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/SEI_6268868_Resultado_de_Edital.pdf</t>
         </is>
       </c>
       <c r="F166" t="n">
@@ -5044,14 +5052,14 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Chamada Pública de Adesão à linha de fomento Qualifica Mais EnergIFE</t>
+          <t>Chamada Pública de Adesão das Instituições da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT), com objetivo de capacitação técnica para submissão de propostas em futuros editais de unidades Embrapii.</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/chamadapublica.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/edital-2025/SEI_MEC5650163ResultadodeEdital_.pdf</t>
         </is>
       </c>
       <c r="F167" t="n">
@@ -5067,14 +5075,14 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 01/2017 - Trata-se de chamada pública para seleção de servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) para capacitação em Gestão da Inovação.</t>
+          <t>Chamada Pública de Adesão à linha de fomento Qualifica Mais EnergIFE</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/extrato_chamada_dou_cp_01_2017.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/chamadapublica.pdf</t>
         </is>
       </c>
       <c r="F168" t="n">
@@ -5090,14 +5098,14 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 01/2018 - Trata-se da chamada pública para seleção de propostas e servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) em efetivo exercício, para participarem da capacitação em Gestão da Inovação (GI - CSIRO).</t>
+          <t>Chamada Pública nº 01/2017 - Trata-se de chamada pública para seleção de servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) para capacitação em Gestão da Inovação.</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/20181030Edital012018ChamadaPblicaGICSIRO.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/extrato_chamada_dou_cp_01_2017.pdf</t>
         </is>
       </c>
       <c r="F169" t="n">
@@ -5113,14 +5121,14 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 02/2017 - Trata-se de chamada pública para concurso sobre educação profissional da Secretaria de Educação Profissional e Tecnológica (Setec/MEC) em parceria com a Comunidade dos Países de Língua Portuguesa (CPLP).</t>
+          <t>Chamada Pública nº 01/2018 - Trata-se da chamada pública para seleção de propostas e servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) em efetivo exercício, para participarem da capacitação em Gestão da Inovação (GI - CSIRO).</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/edital_concurso_cplp_2017.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/20181030Edital012018ChamadaPblicaGICSIRO.pdf</t>
         </is>
       </c>
       <c r="F170" t="n">
@@ -5136,14 +5144,14 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 02/2018 - Trata-se da chamada pública para seleção de servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) para a capacitação Brasileiros Formando Formadores (BraFF).</t>
+          <t>Chamada Pública nº 02/2017 - Trata-se de chamada pública para concurso sobre educação profissional da Secretaria de Educação Profissional e Tecnológica (Setec/MEC) em parceria com a Comunidade dos Países de Língua Portuguesa (CPLP).</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/Edital_02_2018_BRAFF.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/edital_concurso_cplp_2017.pdf</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -5159,14 +5167,14 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 38/2018 - Trata do processo de seleção de propostas para credenciamento de instituições da Rede Federal, Faculdades de Tecnologia do Estado de São Paulo (Fatecs) e do Instituto Tecnológico de Aeronáutica (ITA) para atuação como Núcleo de Línguas (NucLi-IsF) no âmbito do Programa Idiomas sem Fronteiras (IsF).</t>
+          <t>Chamada Pública nº 02/2018 - Trata-se da chamada pública para seleção de servidores da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) para a capacitação Brasileiros Formando Formadores (BraFF).</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/Editaln382018ChamadaPblicaparacredenciamentodeinstituiesdaRFEPCTdasFatecsedoITA.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/Edital_02_2018_BRAFF.pdf</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -5182,14 +5190,14 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Chamada Pública nº 79/2016 - Trata-se de chamada pública para apresentação de propostas por instituição de educação profissional e tecnológica para a oferta de cursos de formação inicial e continuada ou de qualificação profissional e cursos técnicos de nível médio, presenciais ou à distância, sem transferência de recursos, no âmbito do PRONATEC, denominada “PROPOSTAS VOLUNTÁRIAS - PRONATEC”</t>
+          <t>Chamada Pública nº 38/2018 - Trata do processo de seleção de propostas para credenciamento de instituições da Rede Federal, Faculdades de Tecnologia do Estado de São Paulo (Fatecs) e do Instituto Tecnológico de Aeronáutica (ITA) para atuação como Núcleo de Línguas (NucLi-IsF) no âmbito do Programa Idiomas sem Fronteiras (IsF).</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/extrato_edital_79_2016_setec.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2018/Editaln382018ChamadaPblicaparacredenciamentodeinstituiesdaRFEPCTdasFatecsedoITA.pdf</t>
         </is>
       </c>
       <c r="F173" t="n">
@@ -5205,14 +5213,14 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Chamada Pública que estabelece os procedimentos para a autorização de oferta de cursos técnicos de nível médio por Instituições Privadas de Ensino Superior (IPES) para fins de habilitação ao Programa Juros por Educação, no âmbito do Programa de Pleno Pagamento de Dívidas dos Estados (Propag).</t>
+          <t>Chamada Pública nº 79/2016 - Trata-se de chamada pública para apresentação de propostas por instituição de educação profissional e tecnológica para a oferta de cursos de formação inicial e continuada ou de qualificação profissional e cursos técnicos de nível médio, presenciais ou à distância, sem transferência de recursos, no âmbito do PRONATEC, denominada “PROPOSTAS VOLUNTÁRIAS - PRONATEC”</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/FAQEdital6.2025.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/extrato_edital_79_2016_setec.pdf</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -5228,14 +5236,14 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Chamamento Público para credenciamento de profissionais no Banco de Especialistas para atuar no Projeto Assistec Inova, junto ao Ministério da Educação, no âmbito da Secretaria de Educação Profissional e Tecnológica.</t>
+          <t>Chamada Pública que estabelece os procedimentos para a autorização de oferta de cursos técnicos de nível médio por Instituições Privadas de Ensino Superior (IPES) para fins de habilitação ao Programa Juros por Educação, no âmbito do Programa de Pleno Pagamento de Dívidas dos Estados (Propag).</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/SEI_23000.035944_2024_89.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/FAQEdital6.2025.pdf</t>
         </is>
       </c>
       <c r="F175" t="n">
@@ -5251,14 +5259,14 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Edital 1/2026 - Chamada Pública de Adesão dos Institutos Federais de Educação, Ciência e Tecnologia, do Centro Federal de Educação Tecnológica Celso Suckow da Fonseca, do Centro Federal de Educação Tecnológica de Minas Gerais e do Colégio Pedro II, com objetivo de capacitação técnica para submissão de propostas em futuros editais de Unidades Embrapii.</t>
+          <t>Chamamento Público para credenciamento de profissionais no Banco de Especialistas para atuar no Projeto Assistec Inova, junto ao Ministério da Educação, no âmbito da Secretaria de Educação Profissional e Tecnológica.</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/edital12026.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/SEI_23000.035944_2024_89.pdf</t>
         </is>
       </c>
       <c r="F176" t="n">
@@ -5274,14 +5282,14 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Edital 84/2021 - Seleção de Projetos para desenvolvimento dos Ambientes de Promotores de Inovação na Rede Federal</t>
+          <t>Edital 1/2026 - Chamada Pública de Adesão dos Institutos Federais de Educação, Ciência e Tecnologia, do Centro Federal de Educação Tecnológica Celso Suckow da Fonseca, do Centro Federal de Educação Tecnológica de Minas Gerais e do Colégio Pedro II, com objetivo de capacitação técnica para submissão de propostas em futuros editais de Unidades Embrapii.</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/editais/2022/ResultadoetapaI.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/edital12026.pdf</t>
         </is>
       </c>
       <c r="F177" t="n">
@@ -5297,14 +5305,14 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Edital nº 01/2017 - APRESENTAÇÃO DE PROPOSTAS PARA A OFERTA DE VAGAS GRATUITAS EM CURSOS TÉCNICOS NA FORMA CONCOMITANTE, NO ÂMBITO DO PRONATEC/MEDIOTEC – 2º/2017 - A Secretária de Educação Profissional e Tecnológica do Ministério da Educação, no uso da atribuição que lhe confere o art. 13, Anexo I, do Decreto n° 7.690, de 02 de março de 2012, e considerando o disposto na Lei nº 12.513, de 26 de outubro de 2011, a Portaria nº 817, de 13 de agosto de 2015, a Portaria nº160, de 05 de março de 2013, alterada pela Portaria nº 701, de 13 de agosto de 2014, TORNA PÚBLICO os procedimentos e o cronograma para a apresentação de propostas visando a oferta de vagas gratuitas em cursos técnicos na forma concomitante e na modalidade presencial, no âmbito do Programa Nacional de Acesso ao Ensino Técnico e Emprego - PRONATEC, por meio da ação MEDIOTEC, para ingresso no segundo semestre de 2017.</t>
+          <t>Edital 84/2021 - Seleção de Projetos para desenvolvimento dos Ambientes de Promotores de Inovação na Rede Federal</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/edital_01_mediotec_2017.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/editais/2022/ResultadoetapaI.pdf</t>
         </is>
       </c>
       <c r="F178" t="n">
@@ -5320,14 +5328,14 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Edital nº 08/2024 - Chamamento Público visando à seleção de autores(as) para elaboração de capítulos de obra a ser publicada cuja temática central é a gestão de Núcleos de Inovação Tecnológica (NITs) e/ou de Agências de Inovação da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) Divulgação das Inscrições Homologadas</t>
+          <t>Edital nº 01/2017 - APRESENTAÇÃO DE PROPOSTAS PARA A OFERTA DE VAGAS GRATUITAS EM CURSOS TÉCNICOS NA FORMA CONCOMITANTE, NO ÂMBITO DO PRONATEC/MEDIOTEC – 2º/2017 - A Secretária de Educação Profissional e Tecnológica do Ministério da Educação, no uso da atribuição que lhe confere o art. 13, Anexo I, do Decreto n° 7.690, de 02 de março de 2012, e considerando o disposto na Lei nº 12.513, de 26 de outubro de 2011, a Portaria nº 817, de 13 de agosto de 2015, a Portaria nº160, de 05 de março de 2013, alterada pela Portaria nº 701, de 13 de agosto de 2014, TORNA PÚBLICO os procedimentos e o cronograma para a apresentação de propostas visando a oferta de vagas gratuitas em cursos técnicos na forma concomitante e na modalidade presencial, no âmbito do Programa Nacional de Acesso ao Ensino Técnico e Emprego - PRONATEC, por meio da ação MEDIOTEC, para ingresso no segundo semestre de 2017.</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/436.SEI_MEC5030251Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2017/edital_01_mediotec_2017.pdf</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -5343,14 +5351,14 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Edital nº 1/2023 - Seleção de proposta de selo comemorativo, em alusão aos 15 anos dos Institutos Federais.</t>
+          <t>Edital nº 08/2024 - Chamamento Público visando à seleção de autores(as) para elaboração de capítulos de obra a ser publicada cuja temática central é a gestão de Núcleos de Inovação Tecnológica (NITs) e/ou de Agências de Inovação da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT) Divulgação das Inscrições Homologadas</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC4094376Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/436.SEI_MEC5030251Edital.pdf</t>
         </is>
       </c>
       <c r="F180" t="n">
@@ -5366,14 +5374,14 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Edital nº 100/2022 - Chamamento Público para a seleção de propostas para o Desafio Soutec</t>
+          <t>Edital nº 1/2023 - Seleção de proposta de selo comemorativo, em alusão aos 15 anos dos Institutos Federais.</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/secretarias/secretaria-de-educacao-profissional/editais-2022/SEI_MEC3570188Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC4094376Edital.pdf</t>
         </is>
       </c>
       <c r="F181" t="n">
@@ -5389,14 +5397,14 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Edital nº 109/2022 - Chamamento Público - Seleção de projetos voltados à promoção do empreendedorismo inovador, com foco na Economia 4.0, associados ao ensino, à pesquisa e à extensão, destinado às instituições integrantes da Rede Federal de Educação Profissional, Científica e Tecnológica</t>
+          <t>Edital nº 100/2022 - Chamamento Público para a seleção de propostas para o Desafio Soutec</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital109.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/secretarias/secretaria-de-educacao-profissional/editais-2022/SEI_MEC3570188Edital.pdf</t>
         </is>
       </c>
       <c r="F182" t="n">
@@ -5412,14 +5420,14 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Edital nº 11/2024 - Chamamento Público para a seleção de projetos aptos a integrarem a 4ª Semana Nacional de Educação Profissional e Tecnológica Retificação do</t>
+          <t>Edital nº 109/2022 - Chamamento Público - Seleção de projetos voltados à promoção do empreendedorismo inovador, com foco na Economia 4.0, associados ao ensino, à pesquisa e à extensão, destinado às instituições integrantes da Rede Federal de Educação Profissional, Científica e Tecnológica</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-2024-1/Edital_11.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital109.pdf</t>
         </is>
       </c>
       <c r="F183" t="n">
@@ -5435,14 +5443,14 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Edital nº 15/2023 - Chamada Pública para o Workshop para elaboração de Itinerários Formativos em economia circular na Educação Profissional e Tecnológica</t>
+          <t>Edital nº 11/2024 - Chamamento Público para a seleção de projetos aptos a integrarem a 4ª Semana Nacional de Educação Profissional e Tecnológica Retificação do</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/SEI_MEC3884064Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-2024-1/Edital_11.pdf</t>
         </is>
       </c>
       <c r="F184" t="n">
@@ -5458,14 +5466,14 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Edital nº 2/2020 - IFES, de chamada pública para a seleção de projetos voltados à implementação das Oficinas 4.0, aberto às autarquias da Rede Federal.</t>
+          <t>Edital nº 15/2023 - Chamada Pública para o Workshop para elaboração de Itinerários Formativos em economia circular na Educação Profissional e Tecnológica</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>https://www.ifes.edu.br/chamadas-publicas/19329-chamada-publica-2-2020-apoio-a-implementacao-de-oficinas-4-0</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/SEI_MEC3884064Edital.pdf</t>
         </is>
       </c>
       <c r="F185" t="n">
@@ -5481,14 +5489,14 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Edital nº 20/2021 – Seleção de servidores para atuação em Projetos de Colaboração Técnica junto ao Ministério da Educação.</t>
+          <t>Edital nº 2/2020 - IFES, de chamada pública para a seleção de projetos voltados à implementação das Oficinas 4.0, aberto às autarquias da Rede Federal.</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/SEI_MEC2573324Edital.pdf</t>
+          <t>https://www.ifes.edu.br/chamadas-publicas/19329-chamada-publica-2-2020-apoio-a-implementacao-de-oficinas-4-0</t>
         </is>
       </c>
       <c r="F186" t="n">
@@ -5504,14 +5512,14 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Edital nº 25/2023 - Chamada Pública destinada a selecionar equipes da Rede Federal de Educação Profissional, Científica e Tecnológica (EPCT) para participação no projeto de formação em criatividade, inovação e prototipagem do mercosul (Hackathon Mercosul). Retificação do Edital</t>
+          <t>Edital nº 20/2021 – Seleção de servidores para atuação em Projetos de Colaboração Técnica junto ao Ministério da Educação.</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/SEI_MEC3913111Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/SEI_MEC2573324Edital.pdf</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -5527,14 +5535,14 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Edital nº 26 versão consolidada</t>
+          <t>Edital nº 25/2023 - Chamada Pública destinada a selecionar equipes da Rede Federal de Educação Profissional, Científica e Tecnológica (EPCT) para participação no projeto de formação em criatividade, inovação e prototipagem do mercosul (Hackathon Mercosul). Retificação do Edital</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC3980995Documento.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/SEI_MEC3913111Edital.pdf</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -5550,14 +5558,14 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Edital nº 3/2021 – Chamada Pública para seleção de projetos de iniciação tecnológica com foco na Economia 4.0. Acesse o edital .</t>
+          <t>Edital nº 26 versão consolidada</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr">
         <is>
-          <t>https://www.ifes.edu.br/chamadas-publicas/19351-chamada-publica-3-2020-projetos-iniciacao-tecnologica-economia-4-0</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC3980995Documento.pdf</t>
         </is>
       </c>
       <c r="F189" t="n">
@@ -5573,24 +5581,20 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Edital nº 35/2020 - Chamada Pública - que tem como objetivo selecionar projetos voltados à criação de Laboratórios IFMaker junto aos Institutos Federais de Educação, Ciência e Tecnologia; Centros Federais de Educação Tecnológica Celso Suckow da Fonseca – Cefet-RJ e de Minas Gerais – Cefet-MG e o Colégio Pedro II, conforme especificado no Despacho SEI nº 2064854</t>
+          <t>Edital nº 3/2021 – Chamada Pública para seleção de projetos de iniciação tecnológica com foco na Economia 4.0. Acesse o edital .</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2020/SEI_MEC_2064339_Edital_Chamada_Publica.pdf</t>
+          <t>https://www.ifes.edu.br/chamadas-publicas/19351-chamada-publica-3-2020-projetos-iniciacao-tecnologica-economia-4-0</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>2</v>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>Retificação Edital nº 35/2020 - Chamada Pública - Seleção de projetos voltados à criação de Laboratórios Maker junto à Rede Federal de Educação Profissional, Científica e Tecnológica Retificação de Cronograma ​do | https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/AlteraodecronogramaRedeMakeredital35.pdf</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -5600,20 +5604,24 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Edital nº 46, de 20 de julho de 2020, que torna público edital para adesão de estados e Distrito Federal à oferta de Curso de Especialização Lato Sensu em Docência para a Educação Profissional e Tecnológica (DocentEPT) aos professores da rede pública estadual e distrital que atuam na oferta de cursos de Educação Profissional e Tecnológica</t>
+          <t>Edital nº 35/2020 - Chamada Pública - que tem como objetivo selecionar projetos voltados à criação de Laboratórios IFMaker junto aos Institutos Federais de Educação, Ciência e Tecnologia; Centros Federais de Educação Tecnológica Celso Suckow da Fonseca – Cefet-RJ e de Minas Gerais – Cefet-MG e o Colégio Pedro II, conforme especificado no Despacho SEI nº 2064854</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2020/Editaldeadeso_DOU.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2020/SEI_MEC_2064339_Edital_Chamada_Publica.pdf</t>
         </is>
       </c>
       <c r="F191" t="n">
-        <v>1</v>
-      </c>
-      <c r="G191" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Retificação Edital nº 35/2020 - Chamada Pública - Seleção de projetos voltados à criação de Laboratórios Maker junto à Rede Federal de Educação Profissional, Científica e Tecnológica Retificação de Cronograma ​do | https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/AlteraodecronogramaRedeMakeredital35.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -5623,14 +5631,14 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Edital nº 47/2022 - Chamada Pública para oferta de cursos da Plataforma Aprenda Mais</t>
+          <t>Edital nº 46, de 20 de julho de 2020, que torna público edital para adesão de estados e Distrito Federal à oferta de Curso de Especialização Lato Sensu em Docência para a Educação Profissional e Tecnológica (DocentEPT) aos professores da rede pública estadual e distrital que atuam na oferta de cursos de Educação Profissional e Tecnológica</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/editais/2022/Editaln47.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2020/Editaldeadeso_DOU.pdf</t>
         </is>
       </c>
       <c r="F192" t="n">
@@ -5646,14 +5654,14 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Edital nº 48/2022 - Procedimentos para autorização da oferta de cursos técnicos de nível médio por Instituições Privadas de Ensino Superior – Anexos do</t>
+          <t>Edital nº 47/2022 - Chamada Pública para oferta de cursos da Plataforma Aprenda Mais</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/editais/2022/Editaln48.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/editais/2022/Editaln47.pdf</t>
         </is>
       </c>
       <c r="F193" t="n">
@@ -5669,14 +5677,14 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Edital nº 5 /2026 - Seleção de propostas de projetos de extensão voltados ao Acesso, à Permanência e ao Êxito no âmbito da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT).</t>
+          <t>Edital nº 48/2022 - Procedimentos para autorização da oferta de cursos técnicos de nível médio por Instituições Privadas de Ensino Superior – Anexos do</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2026/sei_7012727_edital_5.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/editais/2022/Editaln48.pdf</t>
         </is>
       </c>
       <c r="F194" t="n">
@@ -5692,14 +5700,14 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Edital nº 5/2020 – Chamada para seleção de projetos de apoio ao empreendedorismo inovador com foco na Economia 4.0. Acesse o edital .</t>
+          <t>Edital nº 5 /2026 - Seleção de propostas de projetos de extensão voltados ao Acesso, à Permanência e ao Êxito no âmbito da Rede Federal de Educação Profissional, Científica e Tecnológica (RFEPCT).</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
-          <t>https://www.ifes.edu.br/chamadas-publicas/19384-chamada-publica-05-2020-selecao-de-projetos-de-apoio-ao-empreendedorismo-inovador-com-foco-na-economia-4-0</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2026/sei_7012727_edital_5.pdf</t>
         </is>
       </c>
       <c r="F195" t="n">
@@ -5715,14 +5723,14 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Edital nº 5/2021 – IF Mais Empreendedor Nacional : Adesão ao Programa IF Mais Empreendedor Nacional</t>
+          <t>Edital nº 5/2020 – Chamada para seleção de projetos de apoio ao empreendedorismo inovador com foco na Economia 4.0. Acesse o edital .</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/editais/2021/Edital05.2021IFEMPREENDEDORNACIONAL.pdf</t>
+          <t>https://www.ifes.edu.br/chamadas-publicas/19384-chamada-publica-05-2020-selecao-de-projetos-de-apoio-ao-empreendedorismo-inovador-com-foco-na-economia-4-0</t>
         </is>
       </c>
       <c r="F196" t="n">
@@ -5738,14 +5746,14 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Edital nº 5/2024 - Seleção de propostas de novos Cursos Abertos, On-line e Massivos (MOOCs), desenvolvidos pela Rede Federa de Educação Profissional, Científica e Tecnológica, a serem disponibilizados na Plataforma APRENDA MAIS.</t>
+          <t>Edital nº 5/2021 – IF Mais Empreendedor Nacional : Adesão ao Programa IF Mais Empreendedor Nacional</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC4659481Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/editais/2021/Edital05.2021IFEMPREENDEDORNACIONAL.pdf</t>
         </is>
       </c>
       <c r="F197" t="n">
@@ -5761,14 +5769,14 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Edital nº 52/2016 – que torna público, para conhecimento dos interessados, que será realizado na modalidade concurso, o PROJETO DESAFIO DA EDUCAÇÃO PROFISSIONAL E TECNOLÓGICA, na forma do REGULAMENTO anexo a este edital, com o objetivo de promover uma campanha nacional para aprimorar a Educação Profissional e Tecnológica estimulando a sociedade a enviar propostas de ações inovadoras e compartilhar experiências exitosas de implementação de ações.</t>
+          <t>Edital nº 5/2024 - Seleção de propostas de novos Cursos Abertos, On-line e Massivos (MOOCs), desenvolvidos pela Rede Federa de Educação Profissional, Científica e Tecnológica, a serem disponibilizados na Plataforma APRENDA MAIS.</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/edital_n_52_2016.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/edital-2023/SEI_MEC4659481Edital.pdf</t>
         </is>
       </c>
       <c r="F198" t="n">
@@ -5784,14 +5792,14 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Edital nº 55/2016 , que torna público concurso PROJETO DESAFIO EDUCAÇÃO ZIKAZERO, na forma do REGULAMENTO anexo a este edital, com o objetivo de promover uma campanha nacional de mobilização para o enfrentamento ao Aedes aegyp e à microcefalia estimulando a sociedade a enviar propostas de ações inovadoras e compartilhar experiências exitosas de implementação de ações em prol do combate ao mosquito.</t>
+          <t>Edital nº 52/2016 – que torna público, para conhecimento dos interessados, que será realizado na modalidade concurso, o PROJETO DESAFIO DA EDUCAÇÃO PROFISSIONAL E TECNOLÓGICA, na forma do REGULAMENTO anexo a este edital, com o objetivo de promover uma campanha nacional para aprimorar a Educação Profissional e Tecnológica estimulando a sociedade a enviar propostas de ações inovadoras e compartilhar experiências exitosas de implementação de ações.</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/Edital_55_2016_SEI_MEC_0227936.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/edital_n_52_2016.pdf</t>
         </is>
       </c>
       <c r="F199" t="n">
@@ -5807,14 +5815,14 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Edital nº 6/2021 - Edital de Adesão das instituições ao Sistema Re-Saber</t>
+          <t>Edital nº 55/2016 , que torna público concurso PROJETO DESAFIO EDUCAÇÃO ZIKAZERO, na forma do REGULAMENTO anexo a este edital, com o objetivo de promover uma campanha nacional de mobilização para o enfrentamento ao Aedes aegyp e à microcefalia estimulando a sociedade a enviar propostas de ações inovadoras e compartilhar experiências exitosas de implementação de ações em prol do combate ao mosquito.</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/Edital_06_2021.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2016/Edital_55_2016_SEI_MEC_0227936.pdf</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -5830,14 +5838,14 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Edital nº 6/2024 - Edital visa selecionar a proposta de selo/logomarca que será utilizado em confecções comemorativas no contexto dos 115 anos da Rede Federal de Educação Profissional, Científica e Tecnológica, que poderá ser personalizado como selo postal, via Correios. *</t>
+          <t>Edital nº 6/2021 - Edital de Adesão das instituições ao Sistema Re-Saber</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-2024/325.SEI_MEC4985249Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/Edital_06_2021.pdf</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -5853,14 +5861,14 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Edital nº 61/2019 – Regulamento do Cadastro de Especialistas para compor o Banco de Avaliadores da Secretaria de Educação Profissional e Tecnológica.</t>
+          <t>Edital nº 6/2024 - Edital visa selecionar a proposta de selo/logomarca que será utilizado em confecções comemorativas no contexto dos 115 anos da Rede Federal de Educação Profissional, Científica e Tecnológica, que poderá ser personalizado como selo postal, via Correios. *</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2019/EDITALN612019.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-2024/325.SEI_MEC4985249Edital.pdf</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -5876,14 +5884,14 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Edital nº 63/2021- Seleção de Projetos de Promoção às Indicações Geográficas</t>
+          <t>Edital nº 61/2019 – Regulamento do Cadastro de Especialistas para compor o Banco de Avaliadores da Secretaria de Educação Profissional e Tecnológica.</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/editais/2021/Edital63.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2019/EDITALN612019.pdf</t>
         </is>
       </c>
       <c r="F203" t="n">
@@ -5899,14 +5907,14 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Edital nº 67/2021 - Chamada Pública de Projetos para apoio à implementação das Oficinas 4.0</t>
+          <t>Edital nº 63/2021- Seleção de Projetos de Promoção às Indicações Geográficas</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/SEI_MEC2898796Edital67.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/editais/2021/Edital63.pdf</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -5922,14 +5930,14 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Edital nº 68/2019 – Seleção de servidores para atuação em Projetos Educacionais de Colaboração Técnica junto ao Ministério da Educação.</t>
+          <t>Edital nº 67/2021 - Chamada Pública de Projetos para apoio à implementação das Oficinas 4.0</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2019/EDITALN682019.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/SEI_MEC2898796Edital67.pdf</t>
         </is>
       </c>
       <c r="F205" t="n">
@@ -5945,14 +5953,14 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Edital nº 83/2022 – Seleção de propostas de instituições da Rede Federal para a implementação de programa de capacitação de estudantes denominado Oficinas 4.0</t>
+          <t>Edital nº 68/2019 – Seleção de servidores para atuação em Projetos Educacionais de Colaboração Técnica junto ao Ministério da Educação.</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital83.2022.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2019/EDITALN682019.pdf</t>
         </is>
       </c>
       <c r="F206" t="n">
@@ -5968,14 +5976,14 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Edital nº 88/2022 – Seleção de projetos de iniciação tecnológica de instituições da RFEPCT para o desenvolvimento de ações de formação em programação e/ou robótica e/ou cultura maker para estudantes dos anos finais do ensino fundamental (6º ao 9º ano) das redes públicas de ensino. Retificação ​do</t>
+          <t>Edital nº 83/2022 – Seleção de propostas de instituições da Rede Federal para a implementação de programa de capacitação de estudantes denominado Oficinas 4.0</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital88.2022.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital83.2022.pdf</t>
         </is>
       </c>
       <c r="F207" t="n">
@@ -5991,14 +5999,14 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Edital nº 94/2022 – Chamada Pública para a capacitação de multiplicadores em bioeconomia para a Amazônia Legal. Chamada Pública para a Adesão de parceiros ofertantes da Rede Federal de Educação Profissional, Científica e Tecnológica – RFEPCT à linha de fomento Qualifica Mais EnergIFE, voltada à promoção da oferta de cursos na área das Energias Renováveis. Retificação do</t>
+          <t>Edital nº 88/2022 – Seleção de projetos de iniciação tecnológica de instituições da RFEPCT para o desenvolvimento de ações de formação em programação e/ou robótica e/ou cultura maker para estudantes dos anos finais do ensino fundamental (6º ao 9º ano) das redes públicas de ensino. Retificação ​do</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Editaln94.2022.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Edital88.2022.pdf</t>
         </is>
       </c>
       <c r="F208" t="n">
@@ -6014,14 +6022,14 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Edital nº 99/2022 - Chamamento Público para a seleção de projetos de inovação e trabalhos acadêmicos aptos a integrarem a Semana Nacional da Educação Profissional e Tecnológica Retificação do</t>
+          <t>Edital nº 94/2022 – Chamada Pública para a capacitação de multiplicadores em bioeconomia para a Amazônia Legal. Chamada Pública para a Adesão de parceiros ofertantes da Rede Federal de Educação Profissional, Científica e Tecnológica – RFEPCT à linha de fomento Qualifica Mais EnergIFE, voltada à promoção da oferta de cursos na área das Energias Renováveis. Retificação do</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/secretarias/secretaria-de-educacao-profissional/SEI_MEC3566713Edital.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Editaln94.2022.pdf</t>
         </is>
       </c>
       <c r="F209" t="n">
@@ -6037,14 +6045,14 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Programa Setec-Capes/NOVA de capacitação para Professores da Rede Federal de Educação Profissional, Científica e Tecnológica . A Secretaria de Educação Profissional e Tecnológica (Setec) do Ministério da Educação, com apoio da Coordenação de Aperfeiçoamento de Pessoal de Nível Superior (Capes), lançam chamada pública de capacitação para professores de inglês em efetivo exercício na Rede Federal de Educação Profissional - Institutos Federais, Cefets, Escolas Técnicas vinculas às Universidades Federais e Colégio Pedro II. (Retificação publicada no Diário Oficial da União em 02 de junho de 2016)</t>
+          <t>Edital nº 99/2022 - Chamamento Público para a seleção de projetos de inovação e trabalhos acadêmicos aptos a integrarem a Semana Nacional da Educação Profissional e Tecnológica Retificação do</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2015/chamada_setec_capes_nova_extrato_dou.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/secretarias/secretaria-de-educacao-profissional/SEI_MEC3566713Edital.pdf</t>
         </is>
       </c>
       <c r="F210" t="n">
@@ -6060,24 +6068,20 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Republicação do Edital nº 76/2022 - Chamamento Público para seleção de projetos voltados ao fortalecimento de Núcleos de Inovação Tecnológica e/ou Agências de Inovação.</t>
+          <t>Programa Setec-Capes/NOVA de capacitação para Professores da Rede Federal de Educação Profissional, Científica e Tecnológica . A Secretaria de Educação Profissional e Tecnológica (Setec) do Ministério da Educação, com apoio da Coordenação de Aperfeiçoamento de Pessoal de Nível Superior (Capes), lançam chamada pública de capacitação para professores de inglês em efetivo exercício na Rede Federal de Educação Profissional - Institutos Federais, Cefets, Escolas Técnicas vinculas às Universidades Federais e Colégio Pedro II. (Retificação publicada no Diário Oficial da União em 02 de junho de 2016)</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Republicaodoedital76.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/media/seb-1/pdf/editais/2015/chamada_setec_capes_nova_extrato_dou.pdf</t>
         </is>
       </c>
       <c r="F211" t="n">
-        <v>2</v>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>Retificação do Edital nº 76/2022 – novo cronograma | https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/SEI_23000.006585_2022_91.pdf</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -6087,20 +6091,24 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições da Rede Federal de Educação Profissional, Científica e Tecnológica).</t>
+          <t>Republicação do Edital nº 76/2022 - Chamamento Público para seleção de projetos voltados ao fortalecimento de Núcleos de Inovação Tecnológica e/ou Agências de Inovação.</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/ResultadoEdital10.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/Republicaodoedital76.pdf</t>
         </is>
       </c>
       <c r="F212" t="n">
-        <v>1</v>
-      </c>
-      <c r="G212" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Retificação do Edital nº 76/2022 – novo cronograma | https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais-1/editais-2022/SEI_23000.006585_2022_91.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -6110,14 +6118,14 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições Privadas de Ensino Superior que ofertam cursos técnicos e Escolas Técnicas Privadas).</t>
+          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições da Rede Federal de Educação Profissional, Científica e Tecnológica).</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr">
         <is>
-          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/ResultadoEdital09.pdf</t>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/ResultadoEdital10.pdf</t>
         </is>
       </c>
       <c r="F213" t="n">
@@ -6133,20 +6141,43 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições Públicas Estaduais e Distrital de Educação Profissional e Tecnológica).</t>
+          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições Privadas de Ensino Superior que ofertam cursos técnicos e Escolas Técnicas Privadas).</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr"/>
       <c r="E214" t="inlineStr">
         <is>
+          <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/ResultadoEdital09.pdf</t>
+        </is>
+      </c>
+      <c r="F214" t="n">
+        <v>1</v>
+      </c>
+      <c r="G214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>SETEC</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Seleção de projetos para Mostra Tecnológica da 5ª Semana Nacional da Educação Profissional e Tecnológica (Instituições Públicas Estaduais e Distrital de Educação Profissional e Tecnológica).</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr"/>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr">
+        <is>
           <t>https://www.gov.br/mec/pt-br/acesso-a-informacao/institucional/estrutura-organizacional/orgaos-especificos-singulares/secretaria-de-educacao-profissional/editais/2025/2147-resultado-preliminar.pdf</t>
         </is>
       </c>
-      <c r="F214" t="n">
-        <v>1</v>
-      </c>
-      <c r="G214" t="inlineStr"/>
+      <c r="F215" t="n">
+        <v>1</v>
+      </c>
+      <c r="G215" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/editais.xlsx
+++ b/editais.xlsx
@@ -1282,7 +1282,11 @@
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>https://www.fapesb.ba.gov.br/diretrizes-especificas-da-fapesb-chamada-mobility-confap-italy-2026/</t>
